--- a/docs/budget.xlsx
+++ b/docs/budget.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732CD243-55F3-4275-8CFA-D458AF68E204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Company definition" sheetId="2" r:id="rId1"/>
@@ -649,7 +649,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1044,7 +1044,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1055,15 +1055,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1072,27 +1065,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="5" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1263,14 +1238,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1570,33 +1557,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:316" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="118" t="s">
+      <c r="B1" s="109" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="E1" s="117" t="s">
+      <c r="E1" s="108" t="s">
         <v>120</v>
       </c>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="H1" s="116" t="s">
+      <c r="H1" s="107" t="s">
         <v>119</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="106" t="s">
         <v>131</v>
       </c>
-      <c r="J1" s="115" t="s">
+      <c r="J1" s="106" t="s">
         <v>118</v>
       </c>
-      <c r="K1" s="114" t="s">
+      <c r="K1" s="105" t="s">
         <v>132</v>
       </c>
       <c r="L1" s="4"/>
@@ -1905,32 +1892,32 @@
       <c r="LC1" s="4"/>
       <c r="LD1" s="4"/>
     </row>
-    <row r="2" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+    <row r="2" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="73">
+      <c r="B2" s="64">
         <v>1</v>
       </c>
-      <c r="C2" s="74">
+      <c r="C2" s="65">
         <v>76243</v>
       </c>
-      <c r="D2" s="74">
+      <c r="D2" s="65">
         <v>91781.35</v>
       </c>
-      <c r="E2" s="34">
-        <f>B2*D2</f>
+      <c r="E2" s="25">
+        <f t="shared" ref="E2:E10" si="0">B2*D2</f>
         <v>91781.35</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="111">
+      <c r="H2" s="102">
         <v>1</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="K2" s="110">
+      <c r="K2" s="101">
         <f>D24</f>
         <v>246372.66</v>
       </c>
@@ -2241,31 +2228,31 @@
       <c r="LD2" s="4"/>
     </row>
     <row r="3" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="76">
+      <c r="B3" s="67">
         <v>1</v>
       </c>
-      <c r="C3" s="77">
+      <c r="C3" s="68">
         <v>40550</v>
       </c>
-      <c r="D3" s="77">
+      <c r="D3" s="68">
         <v>53039.4</v>
       </c>
-      <c r="E3" s="87">
-        <f>B3*D3</f>
+      <c r="E3" s="78">
+        <f t="shared" si="0"/>
         <v>53039.4</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="109">
+      <c r="H3" s="100">
         <v>2</v>
       </c>
       <c r="I3" t="s">
         <v>134</v>
       </c>
-      <c r="K3" s="112">
+      <c r="K3" s="103">
         <f>B75</f>
         <v>335500.22000000003</v>
       </c>
@@ -2575,32 +2562,32 @@
       <c r="LC3" s="4"/>
       <c r="LD3" s="4"/>
     </row>
-    <row r="4" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
+    <row r="4" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="73">
+      <c r="B4" s="64">
         <v>1</v>
       </c>
-      <c r="C4" s="74">
+      <c r="C4" s="65">
         <v>25135</v>
       </c>
-      <c r="D4" s="74">
+      <c r="D4" s="65">
         <v>32876.58</v>
       </c>
-      <c r="E4" s="34">
-        <f>B4*D4</f>
+      <c r="E4" s="25">
+        <f t="shared" si="0"/>
         <v>32876.58</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="111">
+      <c r="H4" s="102">
         <v>3</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="K4" s="110">
+      <c r="K4" s="101">
         <f>K2+K3</f>
         <v>581872.88</v>
       </c>
@@ -2911,34 +2898,34 @@
       <c r="LD4" s="4"/>
     </row>
     <row r="5" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="76">
+      <c r="B5" s="67">
         <v>1</v>
       </c>
-      <c r="C5" s="77">
+      <c r="C5" s="68">
         <v>35574</v>
       </c>
-      <c r="D5" s="77">
+      <c r="D5" s="68">
         <v>46530.79</v>
       </c>
-      <c r="E5" s="87">
-        <f>B5*D5</f>
+      <c r="E5" s="78">
+        <f t="shared" si="0"/>
         <v>46530.79</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="109">
+      <c r="H5" s="100">
         <v>4</v>
       </c>
       <c r="I5" t="s">
         <v>136</v>
       </c>
-      <c r="J5" s="113">
+      <c r="J5" s="104">
         <v>0.25</v>
       </c>
-      <c r="K5" s="112">
+      <c r="K5" s="103">
         <f>K4*J5</f>
         <v>145468.22</v>
       </c>
@@ -3248,32 +3235,32 @@
       <c r="LC5" s="4"/>
       <c r="LD5" s="4"/>
     </row>
-    <row r="6" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="38" t="s">
+    <row r="6" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="B6" s="73">
+      <c r="B6" s="64">
         <v>1</v>
       </c>
-      <c r="C6" s="74">
+      <c r="C6" s="65">
         <v>41988</v>
       </c>
-      <c r="D6" s="74">
+      <c r="D6" s="65">
         <v>54920.3</v>
       </c>
-      <c r="E6" s="34">
-        <f>B6*D6</f>
+      <c r="E6" s="25">
+        <f t="shared" si="0"/>
         <v>54920.3</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="111">
+      <c r="H6" s="102">
         <v>5</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="K6" s="110">
+      <c r="K6" s="101">
         <f>K4+K5</f>
         <v>727341.1</v>
       </c>
@@ -3584,31 +3571,31 @@
       <c r="LD6" s="4"/>
     </row>
     <row r="7" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="76">
+      <c r="B7" s="67">
         <v>1</v>
       </c>
-      <c r="C7" s="77">
+      <c r="C7" s="68">
         <v>44369</v>
       </c>
-      <c r="D7" s="77">
+      <c r="D7" s="68">
         <v>58034.65</v>
       </c>
-      <c r="E7" s="87">
-        <f>B7*D7</f>
+      <c r="E7" s="78">
+        <f t="shared" si="0"/>
         <v>58034.65</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="109">
+      <c r="H7" s="100">
         <v>6</v>
       </c>
       <c r="I7" t="s">
         <v>138</v>
       </c>
-      <c r="K7" s="108">
+      <c r="K7" s="99">
         <f>E90</f>
         <v>781150.63500000001</v>
       </c>
@@ -3918,33 +3905,33 @@
       <c r="LC7" s="4"/>
       <c r="LD7" s="4"/>
     </row>
-    <row r="8" spans="1:316" s="24" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="38" t="s">
+    <row r="8" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="B8" s="73">
+      <c r="B8" s="64">
         <v>2</v>
       </c>
-      <c r="C8" s="74">
+      <c r="C8" s="65">
         <v>39879</v>
       </c>
-      <c r="D8" s="74">
+      <c r="D8" s="65">
         <v>52161.73</v>
       </c>
-      <c r="E8" s="34">
-        <f>B8*D8</f>
+      <c r="E8" s="25">
+        <f t="shared" si="0"/>
         <v>104323.46</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="107">
+      <c r="H8" s="98">
         <v>7</v>
       </c>
-      <c r="I8" s="106" t="s">
+      <c r="I8" s="97" t="s">
         <v>139</v>
       </c>
-      <c r="J8" s="106"/>
-      <c r="K8" s="105">
+      <c r="J8" s="97"/>
+      <c r="K8" s="96">
         <f>IFERROR((K7-K6)/K6,"sin valor")</f>
         <v>7.3981155471621277E-2</v>
       </c>
@@ -4255,20 +4242,20 @@
       <c r="LD8" s="4"/>
     </row>
     <row r="9" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="B9" s="76">
+      <c r="B9" s="67">
         <v>4</v>
       </c>
-      <c r="C9" s="77">
+      <c r="C9" s="68">
         <v>25872</v>
       </c>
-      <c r="D9" s="77">
+      <c r="D9" s="68">
         <v>33840.58</v>
       </c>
-      <c r="E9" s="87">
-        <f>B9*D9</f>
+      <c r="E9" s="78">
+        <f t="shared" si="0"/>
         <v>135362.32</v>
       </c>
       <c r="F9" s="4"/>
@@ -4579,21 +4566,21 @@
       <c r="LC9" s="4"/>
       <c r="LD9" s="4"/>
     </row>
-    <row r="10" spans="1:316" s="24" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="38" t="s">
+    <row r="10" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B10" s="73">
+      <c r="B10" s="64">
         <v>1</v>
       </c>
-      <c r="C10" s="74">
+      <c r="C10" s="65">
         <v>26849</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="65">
         <v>35118.49</v>
       </c>
-      <c r="E10" s="34">
-        <f>B10*D10</f>
+      <c r="E10" s="25">
+        <f t="shared" si="0"/>
         <v>35118.49</v>
       </c>
       <c r="F10" s="4"/>
@@ -4909,16 +4896,16 @@
       <c r="LD10" s="4"/>
     </row>
     <row r="11" spans="1:316" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="104" t="s">
+      <c r="A11" s="95" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="103">
+      <c r="B11" s="94">
         <f>SUM(B2:B10)</f>
         <v>13</v>
       </c>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="102">
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
+      <c r="E11" s="93">
         <f>SUM(E2:E10)</f>
         <v>611987.34000000008</v>
       </c>
@@ -5852,23 +5839,23 @@
       <c r="LC13" s="4"/>
       <c r="LD13" s="4"/>
     </row>
-    <row r="14" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="90" t="s">
+    <row r="14" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="101" t="s">
+      <c r="B14" s="92" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="83" t="s">
+      <c r="C14" s="74" t="s">
         <v>117</v>
       </c>
-      <c r="D14" s="101" t="s">
+      <c r="D14" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E14" s="74" t="s">
         <v>141</v>
       </c>
-      <c r="F14" s="100" t="s">
+      <c r="F14" s="91" t="s">
         <v>142</v>
       </c>
       <c r="G14"/>
@@ -6183,26 +6170,26 @@
       <c r="LD14" s="4"/>
     </row>
     <row r="15" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="40">
-        <f>D2</f>
+      <c r="B15" s="31">
+        <f t="shared" ref="B15:B23" si="1">D2</f>
         <v>91781.35</v>
       </c>
-      <c r="C15" s="99">
+      <c r="C15" s="90">
         <v>0</v>
       </c>
-      <c r="D15" s="40">
-        <f>ROUND(B15*C15,2)</f>
+      <c r="D15" s="31">
+        <f t="shared" ref="D15:D23" si="2">ROUND(B15*C15,2)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="98">
-        <f>1-C15</f>
+      <c r="E15" s="89">
+        <f t="shared" ref="E15:E23" si="3">1-C15</f>
         <v>1</v>
       </c>
-      <c r="F15" s="87">
-        <f>ROUND(B15*E15,2)</f>
+      <c r="F15" s="78">
+        <f t="shared" ref="F15:F23" si="4">ROUND(B15*E15,2)</f>
         <v>91781.35</v>
       </c>
       <c r="L15" s="4"/>
@@ -6511,27 +6498,27 @@
       <c r="LC15" s="4"/>
       <c r="LD15" s="4"/>
     </row>
-    <row r="16" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="38" t="s">
+    <row r="16" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="B16" s="37">
-        <f>D3</f>
+      <c r="B16" s="28">
+        <f t="shared" si="1"/>
         <v>53039.4</v>
       </c>
-      <c r="C16" s="97">
+      <c r="C16" s="88">
         <v>0.65</v>
       </c>
-      <c r="D16" s="37">
-        <f>ROUND(B16*C16,2)</f>
+      <c r="D16" s="28">
+        <f t="shared" si="2"/>
         <v>34475.61</v>
       </c>
-      <c r="E16" s="96">
-        <f>1-C16</f>
+      <c r="E16" s="87">
+        <f t="shared" si="3"/>
         <v>0.35</v>
       </c>
-      <c r="F16" s="34">
-        <f>ROUND(B16*E16,2)</f>
+      <c r="F16" s="25">
+        <f t="shared" si="4"/>
         <v>18563.79</v>
       </c>
       <c r="G16"/>
@@ -6846,26 +6833,26 @@
       <c r="LD16" s="4"/>
     </row>
     <row r="17" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="40">
-        <f>D4</f>
+      <c r="B17" s="31">
+        <f t="shared" si="1"/>
         <v>32876.58</v>
       </c>
-      <c r="C17" s="99">
+      <c r="C17" s="90">
         <v>0.5</v>
       </c>
-      <c r="D17" s="40">
-        <f>ROUND(B17*C17,2)</f>
+      <c r="D17" s="31">
+        <f t="shared" si="2"/>
         <v>16438.29</v>
       </c>
-      <c r="E17" s="98">
-        <f>1-C17</f>
+      <c r="E17" s="89">
+        <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="F17" s="87">
-        <f>ROUND(B17*E17,2)</f>
+      <c r="F17" s="78">
+        <f t="shared" si="4"/>
         <v>16438.29</v>
       </c>
       <c r="L17" s="4"/>
@@ -7174,27 +7161,27 @@
       <c r="LC17" s="4"/>
       <c r="LD17" s="4"/>
     </row>
-    <row r="18" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="38" t="s">
+    <row r="18" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="B18" s="37">
-        <f>D5</f>
+      <c r="B18" s="28">
+        <f t="shared" si="1"/>
         <v>46530.79</v>
       </c>
-      <c r="C18" s="97">
+      <c r="C18" s="88">
         <v>0.8</v>
       </c>
-      <c r="D18" s="37">
-        <f>ROUND(B18*C18,2)</f>
+      <c r="D18" s="28">
+        <f t="shared" si="2"/>
         <v>37224.629999999997</v>
       </c>
-      <c r="E18" s="96">
-        <f>1-C18</f>
+      <c r="E18" s="87">
+        <f t="shared" si="3"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="F18" s="34">
-        <f>ROUND(B18*E18,2)</f>
+      <c r="F18" s="25">
+        <f t="shared" si="4"/>
         <v>9306.16</v>
       </c>
       <c r="G18"/>
@@ -7509,26 +7496,26 @@
       <c r="LD18" s="4"/>
     </row>
     <row r="19" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A19" s="41" t="s">
+      <c r="A19" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="40">
-        <f>D6</f>
+      <c r="B19" s="31">
+        <f t="shared" si="1"/>
         <v>54920.3</v>
       </c>
-      <c r="C19" s="99">
+      <c r="C19" s="90">
         <v>0.85</v>
       </c>
-      <c r="D19" s="40">
-        <f>ROUND(B19*C19,2)</f>
+      <c r="D19" s="31">
+        <f t="shared" si="2"/>
         <v>46682.26</v>
       </c>
-      <c r="E19" s="98">
-        <f>1-C19</f>
+      <c r="E19" s="89">
+        <f t="shared" si="3"/>
         <v>0.15000000000000002</v>
       </c>
-      <c r="F19" s="87">
-        <f>ROUND(B19*E19,2)</f>
+      <c r="F19" s="78">
+        <f t="shared" si="4"/>
         <v>8238.0499999999993</v>
       </c>
       <c r="L19" s="4"/>
@@ -7837,27 +7824,27 @@
       <c r="LC19" s="4"/>
       <c r="LD19" s="4"/>
     </row>
-    <row r="20" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="38" t="s">
+    <row r="20" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="37">
-        <f>D7</f>
+      <c r="B20" s="28">
+        <f t="shared" si="1"/>
         <v>58034.65</v>
       </c>
-      <c r="C20" s="97">
+      <c r="C20" s="88">
         <v>0.75</v>
       </c>
-      <c r="D20" s="37">
-        <f>ROUND(B20*C20,2)</f>
+      <c r="D20" s="28">
+        <f t="shared" si="2"/>
         <v>43525.99</v>
       </c>
-      <c r="E20" s="96">
-        <f>1-C20</f>
+      <c r="E20" s="87">
+        <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="F20" s="34">
-        <f>ROUND(B20*E20,2)</f>
+      <c r="F20" s="25">
+        <f t="shared" si="4"/>
         <v>14508.66</v>
       </c>
       <c r="G20"/>
@@ -8172,26 +8159,26 @@
       <c r="LD20" s="4"/>
     </row>
     <row r="21" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="B21" s="40">
-        <f>D8</f>
+      <c r="B21" s="31">
+        <f t="shared" si="1"/>
         <v>52161.73</v>
       </c>
-      <c r="C21" s="99">
+      <c r="C21" s="90">
         <v>0.85</v>
       </c>
-      <c r="D21" s="40">
-        <f>ROUND(B21*C21,2)</f>
+      <c r="D21" s="31">
+        <f t="shared" si="2"/>
         <v>44337.47</v>
       </c>
-      <c r="E21" s="98">
-        <f>1-C21</f>
+      <c r="E21" s="89">
+        <f t="shared" si="3"/>
         <v>0.15000000000000002</v>
       </c>
-      <c r="F21" s="87">
-        <f>ROUND(B21*E21,2)</f>
+      <c r="F21" s="78">
+        <f t="shared" si="4"/>
         <v>7824.26</v>
       </c>
       <c r="L21" s="4"/>
@@ -8500,27 +8487,27 @@
       <c r="LC21" s="4"/>
       <c r="LD21" s="4"/>
     </row>
-    <row r="22" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="38" t="s">
+    <row r="22" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="B22" s="37">
-        <f>D9</f>
+      <c r="B22" s="28">
+        <f t="shared" si="1"/>
         <v>33840.58</v>
       </c>
-      <c r="C22" s="97">
+      <c r="C22" s="88">
         <v>0.7</v>
       </c>
-      <c r="D22" s="37">
-        <f>ROUND(B22*C22,2)</f>
+      <c r="D22" s="28">
+        <f t="shared" si="2"/>
         <v>23688.41</v>
       </c>
-      <c r="E22" s="96">
-        <f>1-C22</f>
+      <c r="E22" s="87">
+        <f t="shared" si="3"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="F22" s="34">
-        <f>ROUND(B22*E22,2)</f>
+      <c r="F22" s="25">
+        <f t="shared" si="4"/>
         <v>10152.17</v>
       </c>
       <c r="G22"/>
@@ -8835,26 +8822,26 @@
       <c r="LD22" s="4"/>
     </row>
     <row r="23" spans="1:316" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="33" t="s">
+      <c r="A23" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="B23" s="32">
-        <f>D10</f>
+      <c r="B23" s="23">
+        <f t="shared" si="1"/>
         <v>35118.49</v>
       </c>
-      <c r="C23" s="95">
+      <c r="C23" s="86">
         <v>0</v>
       </c>
-      <c r="D23" s="32">
-        <f>ROUND(B23*C23,2)</f>
+      <c r="D23" s="23">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E23" s="94">
-        <f>1-C23</f>
+      <c r="E23" s="85">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="F23" s="93">
-        <f>ROUND(B23*E23,2)</f>
+      <c r="F23" s="84">
+        <f t="shared" si="4"/>
         <v>35118.49</v>
       </c>
       <c r="L23" s="4"/>
@@ -9163,21 +9150,21 @@
       <c r="LC23" s="4"/>
       <c r="LD23" s="4"/>
     </row>
-    <row r="24" spans="1:316" s="24" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="28" t="s">
+    <row r="24" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B24" s="92">
+      <c r="B24" s="83">
         <f>SUM(B15:B23)</f>
         <v>458303.87000000005</v>
       </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="92">
+      <c r="C24" s="18"/>
+      <c r="D24" s="83">
         <f>SUM(D15:D23)</f>
         <v>246372.66</v>
       </c>
-      <c r="E24" s="27"/>
-      <c r="F24" s="91">
+      <c r="E24" s="18"/>
+      <c r="F24" s="82">
         <f>SUM(F15:F23)</f>
         <v>211931.22000000003</v>
       </c>
@@ -9802,14 +9789,14 @@
       <c r="LC25" s="4"/>
       <c r="LD25" s="4"/>
     </row>
-    <row r="26" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="90" t="s">
+    <row r="26" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="81" t="s">
         <v>143</v>
       </c>
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="C26" s="82" t="s">
+      <c r="C26" s="73" t="s">
         <v>145</v>
       </c>
       <c r="D26"/>
@@ -10127,14 +10114,14 @@
       <c r="LD26" s="4"/>
     </row>
     <row r="27" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="B27" s="77">
+      <c r="B27" s="68">
         <v>850</v>
       </c>
-      <c r="C27" s="87">
-        <f>B27*12</f>
+      <c r="C27" s="78">
+        <f t="shared" ref="C27:C49" si="5">B27*12</f>
         <v>10200</v>
       </c>
       <c r="L27" s="4"/>
@@ -10443,15 +10430,15 @@
       <c r="LC27" s="4"/>
       <c r="LD27" s="4"/>
     </row>
-    <row r="28" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="89" t="s">
+    <row r="28" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="80" t="s">
         <v>147</v>
       </c>
-      <c r="B28" s="74">
+      <c r="B28" s="65">
         <v>800</v>
       </c>
-      <c r="C28" s="34">
-        <f>B28*12</f>
+      <c r="C28" s="25">
+        <f t="shared" si="5"/>
         <v>9600</v>
       </c>
       <c r="D28"/>
@@ -10769,14 +10756,14 @@
       <c r="LD28" s="4"/>
     </row>
     <row r="29" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A29" s="88" t="s">
+      <c r="A29" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="B29" s="77">
+      <c r="B29" s="68">
         <v>550</v>
       </c>
-      <c r="C29" s="87">
-        <f>B29*12</f>
+      <c r="C29" s="78">
+        <f t="shared" si="5"/>
         <v>6600</v>
       </c>
       <c r="L29" s="4"/>
@@ -11085,15 +11072,15 @@
       <c r="LC29" s="4"/>
       <c r="LD29" s="4"/>
     </row>
-    <row r="30" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="89" t="s">
+    <row r="30" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="80" t="s">
         <v>149</v>
       </c>
-      <c r="B30" s="74">
+      <c r="B30" s="65">
         <v>400</v>
       </c>
-      <c r="C30" s="34">
-        <f>B30*12</f>
+      <c r="C30" s="25">
+        <f t="shared" si="5"/>
         <v>4800</v>
       </c>
       <c r="D30"/>
@@ -11411,14 +11398,14 @@
       <c r="LD30" s="4"/>
     </row>
     <row r="31" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A31" s="88" t="s">
+      <c r="A31" s="79" t="s">
         <v>150</v>
       </c>
-      <c r="B31" s="77">
+      <c r="B31" s="68">
         <v>120</v>
       </c>
-      <c r="C31" s="87">
-        <f>B31*12</f>
+      <c r="C31" s="78">
+        <f t="shared" si="5"/>
         <v>1440</v>
       </c>
       <c r="L31" s="4"/>
@@ -11727,15 +11714,15 @@
       <c r="LC31" s="4"/>
       <c r="LD31" s="4"/>
     </row>
-    <row r="32" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="89" t="s">
+    <row r="32" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="80" t="s">
         <v>151</v>
       </c>
-      <c r="B32" s="74">
+      <c r="B32" s="65">
         <v>1350</v>
       </c>
-      <c r="C32" s="34">
-        <f>B32*12</f>
+      <c r="C32" s="25">
+        <f t="shared" si="5"/>
         <v>16200</v>
       </c>
       <c r="D32"/>
@@ -12053,14 +12040,14 @@
       <c r="LD32" s="4"/>
     </row>
     <row r="33" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A33" s="88" t="s">
+      <c r="A33" s="79" t="s">
         <v>152</v>
       </c>
-      <c r="B33" s="77">
+      <c r="B33" s="68">
         <v>900</v>
       </c>
-      <c r="C33" s="87">
-        <f>B33*12</f>
+      <c r="C33" s="78">
+        <f t="shared" si="5"/>
         <v>10800</v>
       </c>
       <c r="L33" s="4"/>
@@ -12369,15 +12356,15 @@
       <c r="LC33" s="4"/>
       <c r="LD33" s="4"/>
     </row>
-    <row r="34" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="89" t="s">
+    <row r="34" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="80" t="s">
         <v>153</v>
       </c>
-      <c r="B34" s="74">
+      <c r="B34" s="65">
         <v>140</v>
       </c>
-      <c r="C34" s="34">
-        <f>B34*12</f>
+      <c r="C34" s="25">
+        <f t="shared" si="5"/>
         <v>1680</v>
       </c>
       <c r="D34"/>
@@ -12695,14 +12682,14 @@
       <c r="LD34" s="4"/>
     </row>
     <row r="35" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A35" s="88" t="s">
+      <c r="A35" s="79" t="s">
         <v>154</v>
       </c>
-      <c r="B35" s="77">
+      <c r="B35" s="68">
         <v>120</v>
       </c>
-      <c r="C35" s="87">
-        <f>B35*12</f>
+      <c r="C35" s="78">
+        <f t="shared" si="5"/>
         <v>1440</v>
       </c>
       <c r="L35" s="4"/>
@@ -13011,15 +12998,15 @@
       <c r="LC35" s="4"/>
       <c r="LD35" s="4"/>
     </row>
-    <row r="36" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="89" t="s">
+    <row r="36" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="80" t="s">
         <v>155</v>
       </c>
-      <c r="B36" s="74">
+      <c r="B36" s="65">
         <v>120</v>
       </c>
-      <c r="C36" s="34">
-        <f>B36*12</f>
+      <c r="C36" s="25">
+        <f t="shared" si="5"/>
         <v>1440</v>
       </c>
       <c r="D36"/>
@@ -13337,14 +13324,14 @@
       <c r="LD36" s="4"/>
     </row>
     <row r="37" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A37" s="88" t="s">
+      <c r="A37" s="79" t="s">
         <v>156</v>
       </c>
-      <c r="B37" s="77">
+      <c r="B37" s="68">
         <v>180</v>
       </c>
-      <c r="C37" s="87">
-        <f>B37*12</f>
+      <c r="C37" s="78">
+        <f t="shared" si="5"/>
         <v>2160</v>
       </c>
       <c r="L37" s="4"/>
@@ -13653,15 +13640,15 @@
       <c r="LC37" s="4"/>
       <c r="LD37" s="4"/>
     </row>
-    <row r="38" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="89" t="s">
+    <row r="38" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="B38" s="74">
+      <c r="B38" s="65">
         <v>55</v>
       </c>
-      <c r="C38" s="34">
-        <f>B38*12</f>
+      <c r="C38" s="25">
+        <f t="shared" si="5"/>
         <v>660</v>
       </c>
       <c r="D38"/>
@@ -13979,14 +13966,14 @@
       <c r="LD38" s="4"/>
     </row>
     <row r="39" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A39" s="88" t="s">
+      <c r="A39" s="79" t="s">
         <v>158</v>
       </c>
-      <c r="B39" s="77">
+      <c r="B39" s="68">
         <v>400</v>
       </c>
-      <c r="C39" s="87">
-        <f>B39*12</f>
+      <c r="C39" s="78">
+        <f t="shared" si="5"/>
         <v>4800</v>
       </c>
       <c r="L39" s="4"/>
@@ -14295,15 +14282,15 @@
       <c r="LC39" s="4"/>
       <c r="LD39" s="4"/>
     </row>
-    <row r="40" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="89" t="s">
+    <row r="40" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="80" t="s">
         <v>159</v>
       </c>
-      <c r="B40" s="74">
+      <c r="B40" s="65">
         <v>300</v>
       </c>
-      <c r="C40" s="34">
-        <f>B40*12</f>
+      <c r="C40" s="25">
+        <f t="shared" si="5"/>
         <v>3600</v>
       </c>
       <c r="D40"/>
@@ -14621,14 +14608,14 @@
       <c r="LD40" s="4"/>
     </row>
     <row r="41" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A41" s="88" t="s">
+      <c r="A41" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="B41" s="77">
+      <c r="B41" s="68">
         <v>150</v>
       </c>
-      <c r="C41" s="87">
-        <f>B41*12</f>
+      <c r="C41" s="78">
+        <f t="shared" si="5"/>
         <v>1800</v>
       </c>
       <c r="L41" s="4"/>
@@ -14937,15 +14924,15 @@
       <c r="LC41" s="4"/>
       <c r="LD41" s="4"/>
     </row>
-    <row r="42" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="89" t="s">
+    <row r="42" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="80" t="s">
         <v>161</v>
       </c>
-      <c r="B42" s="74">
+      <c r="B42" s="65">
         <v>500</v>
       </c>
-      <c r="C42" s="34">
-        <f>B42*12</f>
+      <c r="C42" s="25">
+        <f t="shared" si="5"/>
         <v>6000</v>
       </c>
       <c r="D42"/>
@@ -15263,14 +15250,14 @@
       <c r="LD42" s="4"/>
     </row>
     <row r="43" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A43" s="88" t="s">
+      <c r="A43" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="B43" s="77">
+      <c r="B43" s="68">
         <v>350</v>
       </c>
-      <c r="C43" s="87">
-        <f>B43*12</f>
+      <c r="C43" s="78">
+        <f t="shared" si="5"/>
         <v>4200</v>
       </c>
       <c r="L43" s="4"/>
@@ -15579,15 +15566,15 @@
       <c r="LC43" s="4"/>
       <c r="LD43" s="4"/>
     </row>
-    <row r="44" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="89" t="s">
+    <row r="44" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="80" t="s">
         <v>163</v>
       </c>
-      <c r="B44" s="74">
+      <c r="B44" s="65">
         <v>300</v>
       </c>
-      <c r="C44" s="34">
-        <f>B44*12</f>
+      <c r="C44" s="25">
+        <f t="shared" si="5"/>
         <v>3600</v>
       </c>
       <c r="D44"/>
@@ -15905,14 +15892,14 @@
       <c r="LD44" s="4"/>
     </row>
     <row r="45" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A45" s="88" t="s">
+      <c r="A45" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="B45" s="77">
+      <c r="B45" s="68">
         <v>200</v>
       </c>
-      <c r="C45" s="87">
-        <f>B45*12</f>
+      <c r="C45" s="78">
+        <f t="shared" si="5"/>
         <v>2400</v>
       </c>
       <c r="L45" s="4"/>
@@ -16221,15 +16208,15 @@
       <c r="LC45" s="4"/>
       <c r="LD45" s="4"/>
     </row>
-    <row r="46" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="89" t="s">
+    <row r="46" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="80" t="s">
         <v>165</v>
       </c>
-      <c r="B46" s="74">
+      <c r="B46" s="65">
         <v>50</v>
       </c>
-      <c r="C46" s="34">
-        <f>B46*12</f>
+      <c r="C46" s="25">
+        <f t="shared" si="5"/>
         <v>600</v>
       </c>
       <c r="D46"/>
@@ -16547,14 +16534,14 @@
       <c r="LD46" s="4"/>
     </row>
     <row r="47" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A47" s="88" t="s">
+      <c r="A47" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="B47" s="77">
+      <c r="B47" s="68">
         <v>150</v>
       </c>
-      <c r="C47" s="87">
-        <f>B47*12</f>
+      <c r="C47" s="78">
+        <f t="shared" si="5"/>
         <v>1800</v>
       </c>
       <c r="L47" s="4"/>
@@ -16863,15 +16850,15 @@
       <c r="LC47" s="4"/>
       <c r="LD47" s="4"/>
     </row>
-    <row r="48" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="89" t="s">
+    <row r="48" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="80" t="s">
         <v>167</v>
       </c>
-      <c r="B48" s="74">
+      <c r="B48" s="65">
         <v>250</v>
       </c>
-      <c r="C48" s="34">
-        <f>B48*12</f>
+      <c r="C48" s="25">
+        <f t="shared" si="5"/>
         <v>3000</v>
       </c>
       <c r="D48"/>
@@ -17189,14 +17176,14 @@
       <c r="LD48" s="4"/>
     </row>
     <row r="49" spans="1:316" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="88" t="s">
+      <c r="A49" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="B49" s="77">
+      <c r="B49" s="68">
         <v>685</v>
       </c>
-      <c r="C49" s="87">
-        <f>B49*12</f>
+      <c r="C49" s="78">
+        <f t="shared" si="5"/>
         <v>8220</v>
       </c>
       <c r="L49" s="4"/>
@@ -17505,12 +17492,12 @@
       <c r="LC49" s="4"/>
       <c r="LD49" s="4"/>
     </row>
-    <row r="50" spans="1:316" s="24" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="86" t="s">
+    <row r="50" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="85"/>
-      <c r="C50" s="84">
+      <c r="B50" s="76"/>
+      <c r="C50" s="75">
         <f>SUM(C27:C49)</f>
         <v>107040</v>
       </c>
@@ -18139,26 +18126,26 @@
       <c r="LC51" s="4"/>
       <c r="LD51" s="4"/>
     </row>
-    <row r="52" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="83" t="s">
+    <row r="52" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="74" t="s">
         <v>169</v>
       </c>
-      <c r="B52" s="83" t="s">
+      <c r="B52" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="C52" s="83" t="s">
+      <c r="C52" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="83" t="s">
+      <c r="D52" s="74" t="s">
         <v>170</v>
       </c>
-      <c r="E52" s="83" t="s">
+      <c r="E52" s="74" t="s">
         <v>145</v>
       </c>
-      <c r="F52" s="83" t="s">
+      <c r="F52" s="74" t="s">
         <v>171</v>
       </c>
-      <c r="G52" s="82" t="s">
+      <c r="G52" s="73" t="s">
         <v>172</v>
       </c>
       <c r="H52"/>
@@ -18472,27 +18459,27 @@
       <c r="LD52" s="4"/>
     </row>
     <row r="53" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A53" s="41" t="s">
+      <c r="A53" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="B53" s="76">
+      <c r="B53" s="67">
         <v>1</v>
       </c>
-      <c r="C53" s="77">
+      <c r="C53" s="68">
         <v>8000</v>
       </c>
-      <c r="D53" s="40">
-        <f>C53*B53</f>
+      <c r="D53" s="31">
+        <f t="shared" ref="D53:D60" si="6">C53*B53</f>
         <v>8000</v>
       </c>
-      <c r="E53" s="40">
+      <c r="E53" s="31">
         <f>D53</f>
         <v>8000</v>
       </c>
-      <c r="F53" s="76" t="s">
+      <c r="F53" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="G53" s="75"/>
+      <c r="G53" s="66"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
@@ -18799,28 +18786,28 @@
       <c r="LC53" s="4"/>
       <c r="LD53" s="4"/>
     </row>
-    <row r="54" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="38" t="s">
+    <row r="54" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="B54" s="73">
+      <c r="B54" s="64">
         <v>3</v>
       </c>
-      <c r="C54" s="74">
+      <c r="C54" s="65">
         <v>1000</v>
       </c>
-      <c r="D54" s="37">
-        <f>C54*B54</f>
+      <c r="D54" s="28">
+        <f t="shared" si="6"/>
         <v>3000</v>
       </c>
-      <c r="E54" s="37">
+      <c r="E54" s="28">
         <f>D54/G54</f>
         <v>750</v>
       </c>
-      <c r="F54" s="79" t="s">
+      <c r="F54" s="70" t="s">
         <v>174</v>
       </c>
-      <c r="G54" s="78">
+      <c r="G54" s="69">
         <v>4</v>
       </c>
       <c r="H54"/>
@@ -19134,27 +19121,27 @@
       <c r="LD54" s="4"/>
     </row>
     <row r="55" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A55" s="41" t="s">
+      <c r="A55" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="B55" s="76">
+      <c r="B55" s="67">
         <v>6</v>
       </c>
-      <c r="C55" s="77">
+      <c r="C55" s="68">
         <v>1400</v>
       </c>
-      <c r="D55" s="40">
-        <f>C55*B55</f>
+      <c r="D55" s="31">
+        <f t="shared" si="6"/>
         <v>8400</v>
       </c>
-      <c r="E55" s="40">
+      <c r="E55" s="31">
         <f>D55/G55</f>
         <v>2100</v>
       </c>
-      <c r="F55" s="81" t="s">
+      <c r="F55" s="72" t="s">
         <v>174</v>
       </c>
-      <c r="G55" s="80">
+      <c r="G55" s="71">
         <v>4</v>
       </c>
       <c r="L55" s="4"/>
@@ -19463,28 +19450,28 @@
       <c r="LC55" s="4"/>
       <c r="LD55" s="4"/>
     </row>
-    <row r="56" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="38" t="s">
+    <row r="56" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="B56" s="73">
+      <c r="B56" s="64">
         <v>5</v>
       </c>
-      <c r="C56" s="74">
+      <c r="C56" s="65">
         <v>1500</v>
       </c>
-      <c r="D56" s="37">
-        <f>C56*B56</f>
+      <c r="D56" s="28">
+        <f t="shared" si="6"/>
         <v>7500</v>
       </c>
-      <c r="E56" s="37">
+      <c r="E56" s="28">
         <f>D56/G56</f>
         <v>1875</v>
       </c>
-      <c r="F56" s="79" t="s">
+      <c r="F56" s="70" t="s">
         <v>174</v>
       </c>
-      <c r="G56" s="78">
+      <c r="G56" s="69">
         <v>4</v>
       </c>
       <c r="H56"/>
@@ -19798,27 +19785,27 @@
       <c r="LD56" s="4"/>
     </row>
     <row r="57" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A57" s="41" t="s">
+      <c r="A57" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B57" s="76">
+      <c r="B57" s="67">
         <v>10</v>
       </c>
-      <c r="C57" s="77">
+      <c r="C57" s="68">
         <v>200</v>
       </c>
-      <c r="D57" s="40">
-        <f>C57*B57</f>
+      <c r="D57" s="31">
+        <f t="shared" si="6"/>
         <v>2000</v>
       </c>
-      <c r="E57" s="40">
+      <c r="E57" s="31">
         <f>D57</f>
         <v>2000</v>
       </c>
-      <c r="F57" s="76" t="s">
+      <c r="F57" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="G57" s="75"/>
+      <c r="G57" s="66"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
@@ -20125,28 +20112,28 @@
       <c r="LC57" s="4"/>
       <c r="LD57" s="4"/>
     </row>
-    <row r="58" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="38" t="s">
+    <row r="58" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="B58" s="73">
+      <c r="B58" s="64">
         <v>1</v>
       </c>
-      <c r="C58" s="74">
+      <c r="C58" s="65">
         <v>99</v>
       </c>
-      <c r="D58" s="37">
-        <f>C58*B58</f>
+      <c r="D58" s="28">
+        <f t="shared" si="6"/>
         <v>99</v>
       </c>
-      <c r="E58" s="37">
+      <c r="E58" s="28">
         <f>D58</f>
         <v>99</v>
       </c>
-      <c r="F58" s="73" t="s">
+      <c r="F58" s="64" t="s">
         <v>173</v>
       </c>
-      <c r="G58" s="49"/>
+      <c r="G58" s="40"/>
       <c r="H58"/>
       <c r="I58"/>
       <c r="J58"/>
@@ -20458,27 +20445,27 @@
       <c r="LD58" s="4"/>
     </row>
     <row r="59" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A59" s="41" t="s">
+      <c r="A59" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="B59" s="76">
+      <c r="B59" s="67">
         <v>1</v>
       </c>
-      <c r="C59" s="77">
+      <c r="C59" s="68">
         <v>25</v>
       </c>
-      <c r="D59" s="40">
-        <f>C59*B59</f>
+      <c r="D59" s="31">
+        <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="E59" s="40">
+      <c r="E59" s="31">
         <f>D59</f>
         <v>25</v>
       </c>
-      <c r="F59" s="76" t="s">
+      <c r="F59" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="G59" s="75"/>
+      <c r="G59" s="66"/>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
@@ -20785,28 +20772,28 @@
       <c r="LC59" s="4"/>
       <c r="LD59" s="4"/>
     </row>
-    <row r="60" spans="1:316" s="24" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="38" t="s">
+    <row r="60" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="B60" s="73">
+      <c r="B60" s="64">
         <v>14</v>
       </c>
-      <c r="C60" s="74">
+      <c r="C60" s="65">
         <v>120</v>
       </c>
-      <c r="D60" s="37">
-        <f>C60*B60</f>
+      <c r="D60" s="28">
+        <f t="shared" si="6"/>
         <v>1680</v>
       </c>
-      <c r="E60" s="37">
+      <c r="E60" s="28">
         <f>D60</f>
         <v>1680</v>
       </c>
-      <c r="F60" s="73" t="s">
+      <c r="F60" s="64" t="s">
         <v>173</v>
       </c>
-      <c r="G60" s="49"/>
+      <c r="G60" s="40"/>
       <c r="H60"/>
       <c r="I60"/>
       <c r="J60"/>
@@ -21118,21 +21105,21 @@
       <c r="LD60" s="4"/>
     </row>
     <row r="61" spans="1:316" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="72" t="s">
+      <c r="A61" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B61" s="70"/>
-      <c r="C61" s="70"/>
-      <c r="D61" s="71">
+      <c r="B61" s="61"/>
+      <c r="C61" s="61"/>
+      <c r="D61" s="62">
         <f>SUM(D54:D60)</f>
         <v>22704</v>
       </c>
-      <c r="E61" s="71">
+      <c r="E61" s="62">
         <f>SUM(E53:E60)</f>
         <v>16529</v>
       </c>
-      <c r="F61" s="70"/>
-      <c r="G61" s="69"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="60"/>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4"/>
@@ -21754,19 +21741,19 @@
       <c r="LD62" s="4"/>
     </row>
     <row r="63" spans="1:316" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="68" t="s">
+      <c r="A63" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="B63" s="67" t="s">
+      <c r="B63" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="C63" s="67" t="s">
+      <c r="C63" s="58" t="s">
         <v>183</v>
       </c>
-      <c r="D63" s="67" t="s">
+      <c r="D63" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="E63" s="66" t="s">
+      <c r="E63" s="57" t="s">
         <v>185</v>
       </c>
       <c r="L63" s="4"/>
@@ -22075,18 +22062,18 @@
       <c r="LC63" s="4"/>
       <c r="LD63" s="4"/>
     </row>
-    <row r="64" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="38" t="s">
+    <row r="64" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="B64" s="65">
-        <f>C15</f>
+      <c r="B64" s="56">
+        <f t="shared" ref="B64:B72" si="7">C15</f>
         <v>0</v>
       </c>
-      <c r="C64" s="63"/>
-      <c r="D64" s="63"/>
-      <c r="E64" s="62">
-        <f>D64*B2</f>
+      <c r="C64" s="54"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="53">
+        <f t="shared" ref="E64:E72" si="8">D64*B2</f>
         <v>0</v>
       </c>
       <c r="F64"/>
@@ -22402,22 +22389,22 @@
       <c r="LD64" s="4"/>
     </row>
     <row r="65" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A65" s="41" t="s">
+      <c r="A65" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="B65" s="61">
-        <f>C16</f>
+      <c r="B65" s="52">
+        <f t="shared" si="7"/>
         <v>0.65</v>
       </c>
-      <c r="C65" s="60">
+      <c r="C65" s="51">
         <v>2008</v>
       </c>
       <c r="D65" s="3">
-        <f>C65*B65</f>
+        <f t="shared" ref="D65:D71" si="9">C65*B65</f>
         <v>1305.2</v>
       </c>
-      <c r="E65" s="59">
-        <f>D65*B3</f>
+      <c r="E65" s="50">
+        <f t="shared" si="8"/>
         <v>1305.2</v>
       </c>
       <c r="L65" s="4"/>
@@ -22726,23 +22713,23 @@
       <c r="LC65" s="4"/>
       <c r="LD65" s="4"/>
     </row>
-    <row r="66" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="38" t="s">
+    <row r="66" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="B66" s="65">
-        <f>C17</f>
+      <c r="B66" s="56">
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
-      <c r="C66" s="64">
+      <c r="C66" s="55">
         <v>2008</v>
       </c>
-      <c r="D66" s="63">
-        <f>C66*B66</f>
+      <c r="D66" s="54">
+        <f t="shared" si="9"/>
         <v>1004</v>
       </c>
-      <c r="E66" s="62">
-        <f>D66*B4</f>
+      <c r="E66" s="53">
+        <f t="shared" si="8"/>
         <v>1004</v>
       </c>
       <c r="F66"/>
@@ -23058,22 +23045,22 @@
       <c r="LD66" s="4"/>
     </row>
     <row r="67" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A67" s="41" t="s">
+      <c r="A67" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="B67" s="61">
-        <f>C18</f>
+      <c r="B67" s="52">
+        <f t="shared" si="7"/>
         <v>0.8</v>
       </c>
-      <c r="C67" s="60">
+      <c r="C67" s="51">
         <v>2008</v>
       </c>
       <c r="D67" s="3">
-        <f>C67*B67</f>
+        <f t="shared" si="9"/>
         <v>1606.4</v>
       </c>
-      <c r="E67" s="59">
-        <f>D67*B5</f>
+      <c r="E67" s="50">
+        <f t="shared" si="8"/>
         <v>1606.4</v>
       </c>
       <c r="L67" s="4"/>
@@ -23382,23 +23369,23 @@
       <c r="LC67" s="4"/>
       <c r="LD67" s="4"/>
     </row>
-    <row r="68" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="38" t="s">
+    <row r="68" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="B68" s="65">
-        <f>C19</f>
+      <c r="B68" s="56">
+        <f t="shared" si="7"/>
         <v>0.85</v>
       </c>
-      <c r="C68" s="64">
+      <c r="C68" s="55">
         <v>2008</v>
       </c>
-      <c r="D68" s="63">
-        <f>C68*B68</f>
+      <c r="D68" s="54">
+        <f t="shared" si="9"/>
         <v>1706.8</v>
       </c>
-      <c r="E68" s="62">
-        <f>D68*B6</f>
+      <c r="E68" s="53">
+        <f t="shared" si="8"/>
         <v>1706.8</v>
       </c>
       <c r="F68"/>
@@ -23714,22 +23701,22 @@
       <c r="LD68" s="4"/>
     </row>
     <row r="69" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A69" s="41" t="s">
+      <c r="A69" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="B69" s="61">
-        <f>C20</f>
+      <c r="B69" s="52">
+        <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
-      <c r="C69" s="60">
+      <c r="C69" s="51">
         <v>2008</v>
       </c>
       <c r="D69" s="3">
-        <f>C69*B69</f>
+        <f t="shared" si="9"/>
         <v>1506</v>
       </c>
-      <c r="E69" s="59">
-        <f>D69*B7</f>
+      <c r="E69" s="50">
+        <f t="shared" si="8"/>
         <v>1506</v>
       </c>
       <c r="L69" s="4"/>
@@ -24038,23 +24025,23 @@
       <c r="LC69" s="4"/>
       <c r="LD69" s="4"/>
     </row>
-    <row r="70" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="38" t="s">
+    <row r="70" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="B70" s="65">
-        <f>C21</f>
+      <c r="B70" s="56">
+        <f t="shared" si="7"/>
         <v>0.85</v>
       </c>
-      <c r="C70" s="64">
+      <c r="C70" s="55">
         <v>2008</v>
       </c>
-      <c r="D70" s="63">
-        <f>C70*B70</f>
+      <c r="D70" s="54">
+        <f t="shared" si="9"/>
         <v>1706.8</v>
       </c>
-      <c r="E70" s="62">
-        <f>D70*B8</f>
+      <c r="E70" s="53">
+        <f t="shared" si="8"/>
         <v>3413.6</v>
       </c>
       <c r="F70"/>
@@ -24370,22 +24357,22 @@
       <c r="LD70" s="4"/>
     </row>
     <row r="71" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A71" s="41" t="s">
+      <c r="A71" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="B71" s="61">
-        <f>C22</f>
+      <c r="B71" s="52">
+        <f t="shared" si="7"/>
         <v>0.7</v>
       </c>
-      <c r="C71" s="60">
+      <c r="C71" s="51">
         <v>2008</v>
       </c>
       <c r="D71" s="3">
-        <f>C71*B71</f>
+        <f t="shared" si="9"/>
         <v>1405.6</v>
       </c>
-      <c r="E71" s="59">
-        <f>D71*B9</f>
+      <c r="E71" s="50">
+        <f t="shared" si="8"/>
         <v>5622.4</v>
       </c>
       <c r="L71" s="4"/>
@@ -24694,18 +24681,18 @@
       <c r="LC71" s="4"/>
       <c r="LD71" s="4"/>
     </row>
-    <row r="72" spans="1:316" s="24" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="47" t="s">
+    <row r="72" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="B72" s="58">
-        <f>C23</f>
+      <c r="B72" s="49">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="C72" s="57"/>
-      <c r="D72" s="57"/>
-      <c r="E72" s="56">
-        <f>D72*B10</f>
+      <c r="C72" s="48"/>
+      <c r="D72" s="48"/>
+      <c r="E72" s="47">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F72"/>
@@ -25021,13 +25008,13 @@
       <c r="LD72" s="4"/>
     </row>
     <row r="73" spans="1:316" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="55" t="s">
+      <c r="A73" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="B73" s="54"/>
-      <c r="C73" s="54"/>
-      <c r="D73" s="53"/>
-      <c r="E73" s="52">
+      <c r="B73" s="45"/>
+      <c r="C73" s="45"/>
+      <c r="D73" s="44"/>
+      <c r="E73" s="43">
         <f>SUM(E64:E72)</f>
         <v>16164.4</v>
       </c>
@@ -25650,10 +25637,10 @@
       <c r="LD74" s="4"/>
     </row>
     <row r="75" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A75" s="51" t="s">
+      <c r="A75" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="B75" s="50">
+      <c r="B75" s="41">
         <f>E61+C50+F24</f>
         <v>335500.22000000003</v>
       </c>
@@ -25966,11 +25953,11 @@
       <c r="LC75" s="4"/>
       <c r="LD75" s="4"/>
     </row>
-    <row r="76" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="38" t="s">
+    <row r="76" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="B76" s="49">
+      <c r="B76" s="40">
         <f>SUMIFS(B2:B10,C15:C23,"&gt;0")</f>
         <v>11</v>
       </c>
@@ -26290,10 +26277,10 @@
       <c r="LD76" s="4"/>
     </row>
     <row r="77" spans="1:316" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="41" t="s">
+      <c r="A77" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="B77" s="48">
+      <c r="B77" s="39">
         <f>IFERROR(B75/B76,"sin valor")</f>
         <v>30500.020000000004</v>
       </c>
@@ -26603,11 +26590,11 @@
       <c r="LC77" s="4"/>
       <c r="LD77" s="4"/>
     </row>
-    <row r="78" spans="1:316" s="24" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="47" t="s">
+    <row r="78" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="B78" s="46">
+      <c r="B78" s="37">
         <f>B77*(1+J5)</f>
         <v>38125.025000000009</v>
       </c>
@@ -27239,23 +27226,23 @@
       <c r="LC79" s="4"/>
       <c r="LD79" s="4"/>
     </row>
-    <row r="80" spans="1:316" s="24" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="45" t="s">
+    <row r="80" spans="1:316" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A80" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="B80" s="43" t="s">
+      <c r="B80" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="C80" s="44" t="s">
+      <c r="C80" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="D80" s="44" t="s">
+      <c r="D80" s="35" t="s">
         <v>192</v>
       </c>
-      <c r="E80" s="43" t="s">
+      <c r="E80" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="F80" s="42" t="s">
+      <c r="F80" s="33" t="s">
         <v>194</v>
       </c>
       <c r="G80"/>
@@ -27570,26 +27557,26 @@
       <c r="LD80" s="4"/>
     </row>
     <row r="81" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A81" s="41" t="s">
+      <c r="A81" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="B81" s="40">
-        <f>IFERROR($D15/$D64,0)</f>
+      <c r="B81" s="31">
+        <f t="shared" ref="B81:B89" si="10">IFERROR($D15/$D64,0)</f>
         <v>0</v>
       </c>
-      <c r="C81" s="40">
-        <f>IFERROR(($D15+$B$78)/$D64,0)</f>
+      <c r="C81" s="31">
+        <f t="shared" ref="C81:C89" si="11">IFERROR(($D15+$B$78)/$D64,0)</f>
         <v>0</v>
       </c>
       <c r="D81" s="4">
-        <f>E64</f>
+        <f t="shared" ref="D81:D89" si="12">E64</f>
         <v>0</v>
       </c>
-      <c r="E81" s="39">
-        <f>D81*C81</f>
+      <c r="E81" s="30">
+        <f t="shared" ref="E81:E89" si="13">D81*C81</f>
         <v>0</v>
       </c>
-      <c r="F81" s="29">
+      <c r="F81" s="20">
         <f>IFERROR(($D15+$B$78)/$D64,0)</f>
         <v>0</v>
       </c>
@@ -27898,28 +27885,28 @@
       <c r="LC81" s="4"/>
       <c r="LD81" s="4"/>
     </row>
-    <row r="82" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="38" t="s">
+    <row r="82" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="B82" s="37">
-        <f>IFERROR($D16/$D65,0)</f>
+      <c r="B82" s="28">
+        <f t="shared" si="10"/>
         <v>26.414043824701196</v>
       </c>
-      <c r="C82" s="37">
-        <f>IFERROR(($D16+$B$78)/$D65,0)</f>
+      <c r="C82" s="28">
+        <f t="shared" si="11"/>
         <v>55.624145724793138</v>
       </c>
-      <c r="D82" s="36">
-        <f>E65</f>
+      <c r="D82" s="27">
+        <f t="shared" si="12"/>
         <v>1305.2</v>
       </c>
-      <c r="E82" s="35">
-        <f>D82*C82</f>
+      <c r="E82" s="26">
+        <f t="shared" si="13"/>
         <v>72600.635000000009</v>
       </c>
-      <c r="F82" s="34">
-        <f>IFERROR(($D16+$B$77)/$D65,0)</f>
+      <c r="F82" s="25">
+        <f t="shared" ref="F82:F89" si="14">IFERROR(($D16+$B$77)/$D65,0)</f>
         <v>49.782125344774748</v>
       </c>
       <c r="G82"/>
@@ -28234,27 +28221,27 @@
       <c r="LD82" s="4"/>
     </row>
     <row r="83" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A83" s="41" t="s">
+      <c r="A83" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="B83" s="40">
-        <f>IFERROR($D17/$D66,0)</f>
+      <c r="B83" s="31">
+        <f t="shared" si="10"/>
         <v>16.372798804780878</v>
       </c>
-      <c r="C83" s="40">
-        <f>IFERROR(($D17+$B$78)/$D66,0)</f>
+      <c r="C83" s="31">
+        <f t="shared" si="11"/>
         <v>54.345931274900408</v>
       </c>
       <c r="D83" s="4">
-        <f>E66</f>
+        <f t="shared" si="12"/>
         <v>1004</v>
       </c>
-      <c r="E83" s="39">
-        <f>D83*C83</f>
+      <c r="E83" s="30">
+        <f t="shared" si="13"/>
         <v>54563.31500000001</v>
       </c>
-      <c r="F83" s="29">
-        <f>IFERROR(($D17+$B$77)/$D66,0)</f>
+      <c r="F83" s="20">
+        <f t="shared" si="14"/>
         <v>46.751304780876502</v>
       </c>
       <c r="M83" s="4"/>
@@ -28562,28 +28549,28 @@
       <c r="LC83" s="4"/>
       <c r="LD83" s="4"/>
     </row>
-    <row r="84" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="38" t="s">
+    <row r="84" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="B84" s="37">
-        <f>IFERROR($D18/$D67,0)</f>
+      <c r="B84" s="28">
+        <f t="shared" si="10"/>
         <v>23.17270293824701</v>
       </c>
-      <c r="C84" s="37">
-        <f>IFERROR(($D18+$B$78)/$D67,0)</f>
+      <c r="C84" s="28">
+        <f t="shared" si="11"/>
         <v>46.90591073207171</v>
       </c>
-      <c r="D84" s="36">
-        <f>E67</f>
+      <c r="D84" s="27">
+        <f t="shared" si="12"/>
         <v>1606.4</v>
       </c>
-      <c r="E84" s="35">
-        <f>D84*C84</f>
+      <c r="E84" s="26">
+        <f t="shared" si="13"/>
         <v>75349.654999999999</v>
       </c>
-      <c r="F84" s="34">
-        <f>IFERROR(($D18+$B$77)/$D67,0)</f>
+      <c r="F84" s="25">
+        <f t="shared" si="14"/>
         <v>42.159269173306768</v>
       </c>
       <c r="G84"/>
@@ -28898,27 +28885,27 @@
       <c r="LD84" s="4"/>
     </row>
     <row r="85" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A85" s="41" t="s">
+      <c r="A85" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="B85" s="40">
-        <f>IFERROR($D19/$D68,0)</f>
+      <c r="B85" s="31">
+        <f t="shared" si="10"/>
         <v>27.350749941410829</v>
       </c>
-      <c r="C85" s="40">
-        <f>IFERROR(($D19+$B$78)/$D68,0)</f>
+      <c r="C85" s="31">
+        <f t="shared" si="11"/>
         <v>49.687886688539962</v>
       </c>
       <c r="D85" s="4">
-        <f>E68</f>
+        <f t="shared" si="12"/>
         <v>1706.8</v>
       </c>
-      <c r="E85" s="39">
-        <f>D85*C85</f>
+      <c r="E85" s="30">
+        <f t="shared" si="13"/>
         <v>84807.285000000003</v>
       </c>
-      <c r="F85" s="29">
-        <f>IFERROR(($D19+$B$77)/$D68,0)</f>
+      <c r="F85" s="20">
+        <f t="shared" si="14"/>
         <v>45.220459339114129</v>
       </c>
       <c r="M85" s="4"/>
@@ -29226,28 +29213,28 @@
       <c r="LC85" s="4"/>
       <c r="LD85" s="4"/>
     </row>
-    <row r="86" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="38" t="s">
+    <row r="86" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="B86" s="37">
-        <f>IFERROR($D20/$D69,0)</f>
+      <c r="B86" s="28">
+        <f t="shared" si="10"/>
         <v>28.901719787516598</v>
       </c>
-      <c r="C86" s="37">
-        <f>IFERROR(($D20+$B$78)/$D69,0)</f>
+      <c r="C86" s="28">
+        <f t="shared" si="11"/>
         <v>54.217141434262956</v>
       </c>
-      <c r="D86" s="36">
-        <f>E69</f>
+      <c r="D86" s="27">
+        <f t="shared" si="12"/>
         <v>1506</v>
       </c>
-      <c r="E86" s="35">
-        <f>D86*C86</f>
+      <c r="E86" s="26">
+        <f t="shared" si="13"/>
         <v>81651.015000000014</v>
       </c>
-      <c r="F86" s="34">
-        <f>IFERROR(($D20+$B$77)/$D69,0)</f>
+      <c r="F86" s="25">
+        <f t="shared" si="14"/>
         <v>49.154057104913683</v>
       </c>
       <c r="G86"/>
@@ -29562,27 +29549,27 @@
       <c r="LD86" s="4"/>
     </row>
     <row r="87" spans="1:316" x14ac:dyDescent="0.3">
-      <c r="A87" s="41" t="s">
+      <c r="A87" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="B87" s="40">
-        <f>IFERROR($D21/$D70,0)</f>
+      <c r="B87" s="31">
+        <f t="shared" si="10"/>
         <v>25.976956878368878</v>
       </c>
-      <c r="C87" s="40">
-        <f>IFERROR(($D21+$B$78)/$D70,0)</f>
+      <c r="C87" s="31">
+        <f t="shared" si="11"/>
         <v>48.314093625498018</v>
       </c>
       <c r="D87" s="4">
-        <f>E70</f>
+        <f t="shared" si="12"/>
         <v>3413.6</v>
       </c>
-      <c r="E87" s="39">
-        <f>D87*C87</f>
+      <c r="E87" s="30">
+        <f t="shared" si="13"/>
         <v>164924.99000000002</v>
       </c>
-      <c r="F87" s="29">
-        <f>IFERROR(($D21+$B$77)/$D70,0)</f>
+      <c r="F87" s="20">
+        <f t="shared" si="14"/>
         <v>43.846666276072185</v>
       </c>
       <c r="M87" s="4"/>
@@ -29890,28 +29877,28 @@
       <c r="LC87" s="4"/>
       <c r="LD87" s="4"/>
     </row>
-    <row r="88" spans="1:316" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="38" t="s">
+    <row r="88" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="B88" s="37">
-        <f>IFERROR($D22/$D71,0)</f>
+      <c r="B88" s="28">
+        <f t="shared" si="10"/>
         <v>16.852881331815595</v>
       </c>
-      <c r="C88" s="37">
-        <f>IFERROR(($D22+$B$78)/$D71,0)</f>
+      <c r="C88" s="28">
+        <f t="shared" si="11"/>
         <v>43.976547381900978</v>
       </c>
-      <c r="D88" s="36">
-        <f>E71</f>
+      <c r="D88" s="27">
+        <f t="shared" si="12"/>
         <v>5622.4</v>
       </c>
-      <c r="E88" s="35">
-        <f>D88*C88</f>
+      <c r="E88" s="26">
+        <f t="shared" si="13"/>
         <v>247253.74000000005</v>
       </c>
-      <c r="F88" s="34">
-        <f>IFERROR(($D22+$B$77)/$D71,0)</f>
+      <c r="F88" s="25">
+        <f t="shared" si="14"/>
         <v>38.551814171883898</v>
       </c>
       <c r="G88"/>
@@ -30226,27 +30213,27 @@
       <c r="LD88" s="4"/>
     </row>
     <row r="89" spans="1:316" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="33" t="s">
+      <c r="A89" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="B89" s="32">
-        <f>IFERROR($D23/$D72,0)</f>
+      <c r="B89" s="23">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="C89" s="32">
-        <f>IFERROR(($D23+$B$78)/$D72,0)</f>
+      <c r="C89" s="23">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D89" s="31">
-        <f>E72</f>
+      <c r="D89" s="22">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="E89" s="30">
-        <f>D89*C89</f>
+      <c r="E89" s="21">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F89" s="29">
-        <f>IFERROR(($D23+$B$77)/$D72,0)</f>
+      <c r="F89" s="20">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M89" s="4"/>
@@ -30554,21 +30541,21 @@
       <c r="LC89" s="4"/>
       <c r="LD89" s="4"/>
     </row>
-    <row r="90" spans="1:316" s="24" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="28" t="s">
+    <row r="90" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B90" s="27"/>
-      <c r="C90" s="27"/>
-      <c r="D90" s="27">
+      <c r="B90" s="18"/>
+      <c r="C90" s="18"/>
+      <c r="D90" s="18">
         <f>SUM(D81:D89)</f>
         <v>16164.4</v>
       </c>
-      <c r="E90" s="26">
+      <c r="E90" s="17">
         <f>SUM(E81:E89)</f>
         <v>781150.63500000001</v>
       </c>
-      <c r="F90" s="25"/>
+      <c r="F90" s="16"/>
       <c r="G90"/>
       <c r="H90"/>
       <c r="I90"/>
@@ -30906,52 +30893,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="118"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="14" t="s">
         <v>4</v>
       </c>
     </row>
@@ -30964,18 +30951,15 @@
       <c r="D3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="121" t="str">
+      <c r="H3" s="111" t="str">
         <f>_xlfn.XLOOKUP(E3,$D$77:$D$82,$E$77:$E$82,"")</f>
         <v/>
       </c>
-      <c r="I3" s="121" t="str">
+      <c r="I3" s="111" t="str">
         <f>IFERROR(H3*F3,"")</f>
         <v/>
       </c>
-      <c r="K3" s="125">
+      <c r="K3" s="115">
         <f>SUM(J4:J19)</f>
         <v>1493.463760343242</v>
       </c>
@@ -30986,31 +30970,31 @@
         <v>7</v>
       </c>
       <c r="C4" s="6"/>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>109</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4">
         <v>2</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="121">
+      <c r="H4" s="111">
         <f>_xlfn.XLOOKUP(E4,$D$77:$D$82,$E$77:$E$82,"")</f>
         <v>49.782125344774748</v>
       </c>
-      <c r="I4" s="121">
+      <c r="I4" s="111">
         <f t="shared" ref="I4:I67" si="0">IFERROR(H4*F4,"")</f>
         <v>99.564250689549496</v>
       </c>
-      <c r="J4" s="121">
+      <c r="J4" s="111">
         <f>I4</f>
         <v>99.564250689549496</v>
       </c>
-      <c r="K4" s="122"/>
+      <c r="K4" s="112"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
@@ -31018,31 +31002,31 @@
         <v>13</v>
       </c>
       <c r="C5" s="6"/>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" t="s">
         <v>109</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5">
         <v>2</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" t="s">
         <v>108</v>
       </c>
-      <c r="H5" s="121">
+      <c r="H5" s="111">
         <f t="shared" ref="H5:H68" si="1">_xlfn.XLOOKUP(E5,$D$77:$D$82,$E$77:$E$82,"")</f>
         <v>49.782125344774748</v>
       </c>
-      <c r="I5" s="121">
+      <c r="I5" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J5" s="121">
+      <c r="J5" s="111">
         <f>I5</f>
         <v>99.564250689549496</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="112"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
@@ -31050,25 +31034,22 @@
         <v>14</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="121" t="str">
+      <c r="H6" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I6" s="121" t="str">
+      <c r="I6" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J6" s="121">
+      <c r="J6" s="111">
         <f>SUM(I7:I19)</f>
         <v>1294.3352589641431</v>
       </c>
-      <c r="K6" s="122"/>
+      <c r="K6" s="112"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
@@ -31076,28 +31057,28 @@
       <c r="C7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" t="s">
         <v>109</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" t="s">
         <v>108</v>
       </c>
-      <c r="H7" s="121">
+      <c r="H7" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I7" s="121">
+      <c r="I7" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J7" s="121"/>
-      <c r="K7" s="122"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="112"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
@@ -31105,28 +31086,28 @@
       <c r="C8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" t="s">
         <v>109</v>
       </c>
-      <c r="F8" s="120">
+      <c r="F8">
         <v>2</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" t="s">
         <v>108</v>
       </c>
-      <c r="H8" s="121">
+      <c r="H8" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I8" s="121">
+      <c r="I8" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J8" s="121"/>
-      <c r="K8" s="122"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="112"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
@@ -31134,28 +31115,28 @@
       <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" t="s">
         <v>109</v>
       </c>
-      <c r="F9" s="120">
+      <c r="F9">
         <v>2</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" t="s">
         <v>108</v>
       </c>
-      <c r="H9" s="121">
+      <c r="H9" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I9" s="121">
+      <c r="I9" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J9" s="121"/>
-      <c r="K9" s="122"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="112"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
@@ -31163,28 +31144,28 @@
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" t="s">
         <v>109</v>
       </c>
-      <c r="F10" s="120">
+      <c r="F10">
         <v>2</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="121">
+      <c r="H10" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I10" s="121">
+      <c r="I10" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="112"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
@@ -31192,28 +31173,28 @@
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" t="s">
         <v>109</v>
       </c>
-      <c r="F11" s="120">
+      <c r="F11">
         <v>2</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" t="s">
         <v>108</v>
       </c>
-      <c r="H11" s="121">
+      <c r="H11" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I11" s="121">
+      <c r="I11" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J11" s="121"/>
-      <c r="K11" s="122"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="112"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
@@ -31221,28 +31202,28 @@
       <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" t="s">
         <v>109</v>
       </c>
-      <c r="F12" s="120">
+      <c r="F12">
         <v>2</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" t="s">
         <v>108</v>
       </c>
-      <c r="H12" s="121">
+      <c r="H12" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I12" s="121">
+      <c r="I12" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J12" s="121"/>
-      <c r="K12" s="122"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="112"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
@@ -31250,28 +31231,28 @@
       <c r="C13" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" t="s">
         <v>109</v>
       </c>
-      <c r="F13" s="120">
+      <c r="F13">
         <v>2</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="121">
+      <c r="H13" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I13" s="121">
+      <c r="I13" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J13" s="121"/>
-      <c r="K13" s="122"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="112"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
@@ -31279,28 +31260,28 @@
       <c r="C14" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" t="s">
         <v>109</v>
       </c>
-      <c r="F14" s="120">
+      <c r="F14">
         <v>2</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="121">
+      <c r="H14" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I14" s="121">
+      <c r="I14" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J14" s="121"/>
-      <c r="K14" s="122"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="112"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
@@ -31308,28 +31289,28 @@
       <c r="C15" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" t="s">
         <v>109</v>
       </c>
-      <c r="F15" s="120">
+      <c r="F15">
         <v>2</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" t="s">
         <v>108</v>
       </c>
-      <c r="H15" s="121">
+      <c r="H15" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I15" s="121">
+      <c r="I15" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J15" s="121"/>
-      <c r="K15" s="122"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="112"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
@@ -31337,28 +31318,28 @@
       <c r="C16" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" t="s">
         <v>109</v>
       </c>
-      <c r="F16" s="120">
+      <c r="F16">
         <v>2</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" t="s">
         <v>108</v>
       </c>
-      <c r="H16" s="121">
+      <c r="H16" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I16" s="121">
+      <c r="I16" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J16" s="121"/>
-      <c r="K16" s="122"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="112"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
@@ -31366,28 +31347,28 @@
       <c r="C17" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" t="s">
         <v>109</v>
       </c>
-      <c r="F17" s="120">
+      <c r="F17">
         <v>2</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" t="s">
         <v>108</v>
       </c>
-      <c r="H17" s="121">
+      <c r="H17" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I17" s="121">
+      <c r="I17" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J17" s="121"/>
-      <c r="K17" s="122"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="112"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
@@ -31395,28 +31376,28 @@
       <c r="C18" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" t="s">
         <v>109</v>
       </c>
-      <c r="F18" s="120">
+      <c r="F18">
         <v>2</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" t="s">
         <v>108</v>
       </c>
-      <c r="H18" s="121">
+      <c r="H18" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I18" s="121">
+      <c r="I18" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J18" s="121"/>
-      <c r="K18" s="122"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="112"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
@@ -31424,28 +31405,28 @@
       <c r="C19" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" t="s">
         <v>109</v>
       </c>
-      <c r="F19" s="120">
+      <c r="F19">
         <v>2</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" t="s">
         <v>108</v>
       </c>
-      <c r="H19" s="121">
+      <c r="H19" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I19" s="121">
+      <c r="I19" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J19" s="121"/>
-      <c r="K19" s="122"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="112"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -31456,19 +31437,16 @@
       <c r="D20" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="121" t="str">
+      <c r="H20" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I20" s="121" t="str">
+      <c r="I20" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J20" s="121"/>
-      <c r="K20" s="122">
+      <c r="J20" s="111"/>
+      <c r="K20" s="112">
         <f>SUM(J21:J30)</f>
         <v>2307.2124370166389</v>
       </c>
@@ -31479,31 +31457,31 @@
         <v>7</v>
       </c>
       <c r="C21" s="6"/>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" t="s">
         <v>111</v>
       </c>
-      <c r="F21" s="120">
+      <c r="F21">
         <v>1</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" t="s">
         <v>108</v>
       </c>
-      <c r="H21" s="121">
+      <c r="H21" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I21" s="121">
+      <c r="I21" s="111">
         <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="J21" s="121">
-        <f>I21</f>
+      <c r="J21" s="111">
+        <f t="shared" ref="J21:J30" si="2">I21</f>
         <v>42.159269173306768</v>
       </c>
-      <c r="K21" s="122"/>
+      <c r="K21" s="112"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
@@ -31511,31 +31489,31 @@
         <v>13</v>
       </c>
       <c r="C22" s="6"/>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" t="s">
         <v>112</v>
       </c>
-      <c r="F22" s="120">
+      <c r="F22">
         <v>4</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" t="s">
         <v>108</v>
       </c>
-      <c r="H22" s="121">
+      <c r="H22" s="111">
         <f t="shared" si="1"/>
         <v>45.220459339114129</v>
       </c>
-      <c r="I22" s="121">
+      <c r="I22" s="111">
         <f t="shared" si="0"/>
         <v>180.88183735645651</v>
       </c>
-      <c r="J22" s="121">
-        <f>I22</f>
+      <c r="J22" s="111">
+        <f t="shared" si="2"/>
         <v>180.88183735645651</v>
       </c>
-      <c r="K22" s="122"/>
+      <c r="K22" s="112"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
@@ -31543,31 +31521,31 @@
         <v>14</v>
       </c>
       <c r="C23" s="6"/>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="120">
+      <c r="F23">
         <v>2</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" t="s">
         <v>108</v>
       </c>
-      <c r="H23" s="121">
+      <c r="H23" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I23" s="121">
+      <c r="I23" s="111">
         <f t="shared" si="0"/>
         <v>84.318538346613536</v>
       </c>
-      <c r="J23" s="121">
-        <f>I23</f>
+      <c r="J23" s="111">
+        <f t="shared" si="2"/>
         <v>84.318538346613536</v>
       </c>
-      <c r="K23" s="122"/>
+      <c r="K23" s="112"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
@@ -31575,31 +31553,31 @@
         <v>99</v>
       </c>
       <c r="C24" s="6"/>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" t="s">
         <v>111</v>
       </c>
-      <c r="F24" s="120">
+      <c r="F24">
         <v>1</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" t="s">
         <v>108</v>
       </c>
-      <c r="H24" s="121">
+      <c r="H24" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I24" s="121">
+      <c r="I24" s="111">
         <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="J24" s="121">
-        <f>I24</f>
+      <c r="J24" s="111">
+        <f t="shared" si="2"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="K24" s="122"/>
+      <c r="K24" s="112"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
@@ -31607,31 +31585,31 @@
         <v>100</v>
       </c>
       <c r="C25" s="6"/>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" t="s">
         <v>111</v>
       </c>
-      <c r="F25" s="120">
+      <c r="F25">
         <v>2</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" t="s">
         <v>108</v>
       </c>
-      <c r="H25" s="121">
+      <c r="H25" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I25" s="121">
+      <c r="I25" s="111">
         <f t="shared" si="0"/>
         <v>84.318538346613536</v>
       </c>
-      <c r="J25" s="121">
-        <f>I25</f>
+      <c r="J25" s="111">
+        <f t="shared" si="2"/>
         <v>84.318538346613536</v>
       </c>
-      <c r="K25" s="122"/>
+      <c r="K25" s="112"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
@@ -31639,31 +31617,31 @@
         <v>101</v>
       </c>
       <c r="C26" s="6"/>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" t="s">
         <v>112</v>
       </c>
-      <c r="F26" s="120">
+      <c r="F26">
         <v>6</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" t="s">
         <v>108</v>
       </c>
-      <c r="H26" s="121">
+      <c r="H26" s="111">
         <f t="shared" si="1"/>
         <v>45.220459339114129</v>
       </c>
-      <c r="I26" s="121">
+      <c r="I26" s="111">
         <f t="shared" si="0"/>
         <v>271.32275603468474</v>
       </c>
-      <c r="J26" s="121">
-        <f>I26</f>
+      <c r="J26" s="111">
+        <f t="shared" si="2"/>
         <v>271.32275603468474</v>
       </c>
-      <c r="K26" s="122"/>
+      <c r="K26" s="112"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
@@ -31671,31 +31649,31 @@
         <v>102</v>
       </c>
       <c r="C27" s="6"/>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="120">
+      <c r="F27">
         <v>22</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" t="s">
         <v>108</v>
       </c>
-      <c r="H27" s="121">
+      <c r="H27" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I27" s="121">
+      <c r="I27" s="111">
         <f t="shared" si="0"/>
         <v>927.5039218127489</v>
       </c>
-      <c r="J27" s="121">
-        <f>I27</f>
+      <c r="J27" s="111">
+        <f t="shared" si="2"/>
         <v>927.5039218127489</v>
       </c>
-      <c r="K27" s="122"/>
+      <c r="K27" s="112"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
@@ -31703,31 +31681,31 @@
         <v>103</v>
       </c>
       <c r="C28" s="6"/>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" t="s">
         <v>111</v>
       </c>
-      <c r="F28" s="120">
+      <c r="F28">
         <v>6</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" t="s">
         <v>108</v>
       </c>
-      <c r="H28" s="121">
+      <c r="H28" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I28" s="121">
+      <c r="I28" s="111">
         <f t="shared" si="0"/>
         <v>252.95561503984061</v>
       </c>
-      <c r="J28" s="121">
-        <f>I28</f>
+      <c r="J28" s="111">
+        <f t="shared" si="2"/>
         <v>252.95561503984061</v>
       </c>
-      <c r="K28" s="122"/>
+      <c r="K28" s="112"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
@@ -31735,31 +31713,31 @@
         <v>104</v>
       </c>
       <c r="C29" s="6"/>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="120">
+      <c r="F29">
         <v>2</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" t="s">
         <v>108</v>
       </c>
-      <c r="H29" s="121">
+      <c r="H29" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I29" s="121">
+      <c r="I29" s="111">
         <f t="shared" si="0"/>
         <v>84.318538346613536</v>
       </c>
-      <c r="J29" s="121">
-        <f>I29</f>
+      <c r="J29" s="111">
+        <f t="shared" si="2"/>
         <v>84.318538346613536</v>
       </c>
-      <c r="K29" s="122"/>
+      <c r="K29" s="112"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
@@ -31767,31 +31745,31 @@
         <v>105</v>
       </c>
       <c r="C30" s="6"/>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" t="s">
         <v>111</v>
       </c>
-      <c r="F30" s="120">
+      <c r="F30">
         <v>8</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" t="s">
         <v>108</v>
       </c>
-      <c r="H30" s="121">
+      <c r="H30" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I30" s="121">
+      <c r="I30" s="111">
         <f t="shared" si="0"/>
         <v>337.27415338645415</v>
       </c>
-      <c r="J30" s="121">
-        <f>I30</f>
+      <c r="J30" s="111">
+        <f t="shared" si="2"/>
         <v>337.27415338645415</v>
       </c>
-      <c r="K30" s="122"/>
+      <c r="K30" s="112"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
@@ -31802,19 +31780,16 @@
       <c r="D31" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="121" t="str">
+      <c r="H31" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I31" s="121" t="str">
+      <c r="I31" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J31" s="121"/>
-      <c r="K31" s="122">
+      <c r="J31" s="111"/>
+      <c r="K31" s="112">
         <f>SUM(J32:J38)</f>
         <v>2273.3693320555312</v>
       </c>
@@ -31825,31 +31800,31 @@
         <v>7</v>
       </c>
       <c r="C32" s="6"/>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="120">
+      <c r="F32">
         <v>10</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" t="s">
         <v>108</v>
       </c>
-      <c r="H32" s="121">
+      <c r="H32" s="111">
         <f t="shared" si="1"/>
         <v>49.154057104913683</v>
       </c>
-      <c r="I32" s="121">
+      <c r="I32" s="111">
         <f t="shared" si="0"/>
         <v>491.54057104913682</v>
       </c>
-      <c r="J32" s="121">
-        <f>I32</f>
+      <c r="J32" s="111">
+        <f t="shared" ref="J32:J38" si="3">I32</f>
         <v>491.54057104913682</v>
       </c>
-      <c r="K32" s="122"/>
+      <c r="K32" s="112"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
@@ -31857,31 +31832,31 @@
         <v>13</v>
       </c>
       <c r="C33" s="6"/>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" t="s">
         <v>115</v>
       </c>
-      <c r="F33" s="120">
+      <c r="F33">
         <v>3</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" t="s">
         <v>108</v>
       </c>
-      <c r="H33" s="121">
+      <c r="H33" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I33" s="121">
+      <c r="I33" s="111">
         <f t="shared" si="0"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="J33" s="121">
-        <f>I33</f>
+      <c r="J33" s="111">
+        <f t="shared" si="3"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="K33" s="122"/>
+      <c r="K33" s="112"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
@@ -31889,31 +31864,31 @@
         <v>14</v>
       </c>
       <c r="C34" s="6"/>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" t="s">
         <v>114</v>
       </c>
-      <c r="F34" s="120">
+      <c r="F34">
         <v>8</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" t="s">
         <v>108</v>
       </c>
-      <c r="H34" s="121">
+      <c r="H34" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I34" s="121">
+      <c r="I34" s="111">
         <f t="shared" si="0"/>
         <v>350.77333020857748</v>
       </c>
-      <c r="J34" s="121">
-        <f>I34</f>
+      <c r="J34" s="111">
+        <f t="shared" si="3"/>
         <v>350.77333020857748</v>
       </c>
-      <c r="K34" s="122"/>
+      <c r="K34" s="112"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
@@ -31921,31 +31896,31 @@
         <v>99</v>
       </c>
       <c r="C35" s="6"/>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" t="s">
         <v>114</v>
       </c>
-      <c r="F35" s="120">
+      <c r="F35">
         <v>4</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" t="s">
         <v>108</v>
       </c>
-      <c r="H35" s="121">
+      <c r="H35" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I35" s="121">
+      <c r="I35" s="111">
         <f t="shared" si="0"/>
         <v>175.38666510428874</v>
       </c>
-      <c r="J35" s="121">
-        <f>I35</f>
+      <c r="J35" s="111">
+        <f t="shared" si="3"/>
         <v>175.38666510428874</v>
       </c>
-      <c r="K35" s="122"/>
+      <c r="K35" s="112"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
@@ -31953,31 +31928,31 @@
         <v>100</v>
       </c>
       <c r="C36" s="6"/>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" t="s">
         <v>114</v>
       </c>
-      <c r="F36" s="120">
+      <c r="F36">
         <v>6</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" t="s">
         <v>108</v>
       </c>
-      <c r="H36" s="121">
+      <c r="H36" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I36" s="121">
+      <c r="I36" s="111">
         <f t="shared" si="0"/>
         <v>263.07999765643308</v>
       </c>
-      <c r="J36" s="121">
-        <f>I36</f>
+      <c r="J36" s="111">
+        <f t="shared" si="3"/>
         <v>263.07999765643308</v>
       </c>
-      <c r="K36" s="122"/>
+      <c r="K36" s="112"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
@@ -31985,31 +31960,31 @@
         <v>101</v>
       </c>
       <c r="C37" s="6"/>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="120">
+      <c r="F37">
         <v>10</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" t="s">
         <v>108</v>
       </c>
-      <c r="H37" s="121">
+      <c r="H37" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I37" s="121">
+      <c r="I37" s="111">
         <f t="shared" si="0"/>
         <v>438.46666276072187</v>
       </c>
-      <c r="J37" s="121">
-        <f>I37</f>
+      <c r="J37" s="111">
+        <f t="shared" si="3"/>
         <v>438.46666276072187</v>
       </c>
-      <c r="K37" s="122"/>
+      <c r="K37" s="112"/>
     </row>
     <row r="38" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
@@ -32017,31 +31992,31 @@
         <v>102</v>
       </c>
       <c r="C38" s="6"/>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" t="s">
         <v>114</v>
       </c>
-      <c r="F38" s="120">
+      <c r="F38">
         <v>10</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" t="s">
         <v>108</v>
       </c>
-      <c r="H38" s="121">
+      <c r="H38" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I38" s="121">
+      <c r="I38" s="111">
         <f t="shared" si="0"/>
         <v>438.46666276072187</v>
       </c>
-      <c r="J38" s="121">
-        <f>I38</f>
+      <c r="J38" s="111">
+        <f t="shared" si="3"/>
         <v>438.46666276072187</v>
       </c>
-      <c r="K38" s="122"/>
+      <c r="K38" s="112"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
@@ -32052,28 +32027,28 @@
       <c r="D39" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="120">
+      <c r="F39">
         <v>3</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" t="s">
         <v>108</v>
       </c>
-      <c r="H39" s="121">
+      <c r="H39" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I39" s="121">
+      <c r="I39" s="111">
         <f t="shared" si="0"/>
         <v>131.53999882821654</v>
       </c>
-      <c r="J39" s="121">
+      <c r="J39" s="111">
         <f>SUM(I39)</f>
         <v>131.53999882821654</v>
       </c>
-      <c r="K39" s="121">
+      <c r="K39" s="111">
         <f>SUM(J39)</f>
         <v>131.53999882821654</v>
       </c>
@@ -32087,19 +32062,16 @@
       <c r="D40" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="121" t="str">
+      <c r="H40" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I40" s="121" t="str">
+      <c r="I40" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J40" s="121"/>
-      <c r="K40" s="122">
+      <c r="J40" s="111"/>
+      <c r="K40" s="112">
         <f>SUM(J41:J50)</f>
         <v>4386.8987937884322</v>
       </c>
@@ -32110,31 +32082,31 @@
         <v>7</v>
       </c>
       <c r="C41" s="6"/>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" t="s">
         <v>113</v>
       </c>
-      <c r="F41" s="120">
+      <c r="F41">
         <v>4</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="G41" t="s">
         <v>108</v>
       </c>
-      <c r="H41" s="121">
+      <c r="H41" s="111">
         <f t="shared" si="1"/>
         <v>49.154057104913683</v>
       </c>
-      <c r="I41" s="121">
+      <c r="I41" s="111">
         <f t="shared" si="0"/>
         <v>196.61622841965473</v>
       </c>
-      <c r="J41" s="121">
+      <c r="J41" s="111">
         <f>I41</f>
         <v>196.61622841965473</v>
       </c>
-      <c r="K41" s="122"/>
+      <c r="K41" s="112"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
@@ -32142,31 +32114,31 @@
         <v>13</v>
       </c>
       <c r="C42" s="6"/>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" t="s">
         <v>113</v>
       </c>
-      <c r="F42" s="120">
+      <c r="F42">
         <v>3</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" t="s">
         <v>108</v>
       </c>
-      <c r="H42" s="121">
+      <c r="H42" s="111">
         <f t="shared" si="1"/>
         <v>49.154057104913683</v>
       </c>
-      <c r="I42" s="121">
+      <c r="I42" s="111">
         <f t="shared" si="0"/>
         <v>147.46217131474106</v>
       </c>
-      <c r="J42" s="121">
+      <c r="J42" s="111">
         <f>I42</f>
         <v>147.46217131474106</v>
       </c>
-      <c r="K42" s="122"/>
+      <c r="K42" s="112"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
@@ -32174,25 +32146,22 @@
         <v>14</v>
       </c>
       <c r="C43" s="6"/>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="121" t="str">
+      <c r="H43" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I43" s="121" t="str">
+      <c r="I43" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J43" s="121">
+      <c r="J43" s="111">
         <f>SUM(I44:I50)</f>
         <v>4042.8203940540366</v>
       </c>
-      <c r="K43" s="122"/>
+      <c r="K43" s="112"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
@@ -32200,28 +32169,28 @@
       <c r="C44" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" t="s">
         <v>115</v>
       </c>
-      <c r="F44" s="120">
+      <c r="F44">
         <v>22</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="G44" t="s">
         <v>108</v>
       </c>
-      <c r="H44" s="121">
+      <c r="H44" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I44" s="121">
+      <c r="I44" s="111">
         <f t="shared" si="0"/>
         <v>848.13991178144579</v>
       </c>
-      <c r="J44" s="121"/>
-      <c r="K44" s="122"/>
+      <c r="J44" s="111"/>
+      <c r="K44" s="112"/>
     </row>
     <row r="45" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
@@ -32229,28 +32198,28 @@
       <c r="C45" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" t="s">
         <v>115</v>
       </c>
-      <c r="F45" s="120">
+      <c r="F45">
         <v>10</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="G45" t="s">
         <v>108</v>
       </c>
-      <c r="H45" s="121">
+      <c r="H45" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I45" s="121">
+      <c r="I45" s="111">
         <f t="shared" si="0"/>
         <v>385.51814171883899</v>
       </c>
-      <c r="J45" s="121"/>
-      <c r="K45" s="122"/>
+      <c r="J45" s="111"/>
+      <c r="K45" s="112"/>
     </row>
     <row r="46" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
@@ -32258,28 +32227,28 @@
       <c r="C46" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" t="s">
         <v>114</v>
       </c>
-      <c r="F46" s="120">
+      <c r="F46">
         <v>25</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G46" t="s">
         <v>108</v>
       </c>
-      <c r="H46" s="121">
+      <c r="H46" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I46" s="121">
+      <c r="I46" s="111">
         <f t="shared" si="0"/>
         <v>1096.1666569018046</v>
       </c>
-      <c r="J46" s="121"/>
-      <c r="K46" s="122"/>
+      <c r="J46" s="111"/>
+      <c r="K46" s="112"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
@@ -32287,28 +32256,28 @@
       <c r="C47" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" t="s">
         <v>115</v>
       </c>
-      <c r="F47" s="120">
+      <c r="F47">
         <v>6</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="G47" t="s">
         <v>108</v>
       </c>
-      <c r="H47" s="121">
+      <c r="H47" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I47" s="121">
+      <c r="I47" s="111">
         <f t="shared" si="0"/>
         <v>231.31088503130337</v>
       </c>
-      <c r="J47" s="121"/>
-      <c r="K47" s="122"/>
+      <c r="J47" s="111"/>
+      <c r="K47" s="112"/>
     </row>
     <row r="48" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
@@ -32316,28 +32285,28 @@
       <c r="C48" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" t="s">
         <v>114</v>
       </c>
-      <c r="F48" s="120">
+      <c r="F48">
         <v>15</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="G48" t="s">
         <v>108</v>
       </c>
-      <c r="H48" s="121">
+      <c r="H48" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I48" s="121">
+      <c r="I48" s="111">
         <f t="shared" si="0"/>
         <v>657.69999414108281</v>
       </c>
-      <c r="J48" s="121"/>
-      <c r="K48" s="122"/>
+      <c r="J48" s="111"/>
+      <c r="K48" s="112"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
@@ -32345,28 +32314,28 @@
       <c r="C49" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" t="s">
         <v>114</v>
       </c>
-      <c r="F49" s="120">
+      <c r="F49">
         <v>10</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="G49" t="s">
         <v>108</v>
       </c>
-      <c r="H49" s="121">
+      <c r="H49" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I49" s="121">
+      <c r="I49" s="111">
         <f t="shared" si="0"/>
         <v>438.46666276072187</v>
       </c>
-      <c r="J49" s="121"/>
-      <c r="K49" s="122"/>
+      <c r="J49" s="111"/>
+      <c r="K49" s="112"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
@@ -32374,28 +32343,28 @@
       <c r="C50" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" t="s">
         <v>115</v>
       </c>
-      <c r="F50" s="120">
+      <c r="F50">
         <v>10</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G50" t="s">
         <v>108</v>
       </c>
-      <c r="H50" s="121">
+      <c r="H50" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I50" s="121">
+      <c r="I50" s="111">
         <f t="shared" si="0"/>
         <v>385.51814171883899</v>
       </c>
-      <c r="J50" s="121"/>
-      <c r="K50" s="122"/>
+      <c r="J50" s="111"/>
+      <c r="K50" s="112"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
@@ -32406,19 +32375,16 @@
       <c r="D51" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="121" t="str">
+      <c r="H51" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I51" s="121" t="str">
+      <c r="I51" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J51" s="121"/>
-      <c r="K51" s="122">
+      <c r="J51" s="111"/>
+      <c r="K51" s="112">
         <f>SUM(J52:J60)</f>
         <v>1051.4886868492417</v>
       </c>
@@ -32429,31 +32395,31 @@
         <v>7</v>
       </c>
       <c r="C52" s="6"/>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" t="s">
         <v>115</v>
       </c>
-      <c r="F52" s="120">
+      <c r="F52">
         <v>4</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="G52" t="s">
         <v>108</v>
       </c>
-      <c r="H52" s="121">
+      <c r="H52" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I52" s="121">
+      <c r="I52" s="111">
         <f t="shared" si="0"/>
         <v>154.20725668753559</v>
       </c>
-      <c r="J52" s="121">
-        <f>I52</f>
+      <c r="J52" s="111">
+        <f t="shared" ref="J52:J60" si="4">I52</f>
         <v>154.20725668753559</v>
       </c>
-      <c r="K52" s="122"/>
+      <c r="K52" s="112"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
@@ -32461,31 +32427,31 @@
         <v>13</v>
       </c>
       <c r="C53" s="6"/>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" t="s">
         <v>115</v>
       </c>
-      <c r="F53" s="120">
+      <c r="F53">
         <v>3</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="G53" t="s">
         <v>108</v>
       </c>
-      <c r="H53" s="121">
+      <c r="H53" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I53" s="121">
+      <c r="I53" s="111">
         <f t="shared" si="0"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="J53" s="121">
-        <f>I53</f>
+      <c r="J53" s="111">
+        <f t="shared" si="4"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="K53" s="122"/>
+      <c r="K53" s="112"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
@@ -32493,31 +32459,31 @@
         <v>14</v>
       </c>
       <c r="C54" s="6"/>
-      <c r="D54" s="9" t="s">
+      <c r="D54" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" t="s">
         <v>115</v>
       </c>
-      <c r="F54" s="120">
+      <c r="F54">
         <v>5</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="G54" t="s">
         <v>108</v>
       </c>
-      <c r="H54" s="121">
+      <c r="H54" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I54" s="121">
+      <c r="I54" s="111">
         <f t="shared" si="0"/>
         <v>192.7590708594195</v>
       </c>
-      <c r="J54" s="121">
-        <f>I54</f>
+      <c r="J54" s="111">
+        <f t="shared" si="4"/>
         <v>192.7590708594195</v>
       </c>
-      <c r="K54" s="122"/>
+      <c r="K54" s="112"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
@@ -32525,31 +32491,31 @@
         <v>99</v>
       </c>
       <c r="C55" s="6"/>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" t="s">
         <v>115</v>
       </c>
-      <c r="F55" s="120">
+      <c r="F55">
         <v>3</v>
       </c>
-      <c r="G55" s="8" t="s">
+      <c r="G55" t="s">
         <v>108</v>
       </c>
-      <c r="H55" s="121">
+      <c r="H55" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I55" s="121">
+      <c r="I55" s="111">
         <f t="shared" si="0"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="J55" s="121">
-        <f>I55</f>
+      <c r="J55" s="111">
+        <f t="shared" si="4"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="K55" s="122"/>
+      <c r="K55" s="112"/>
     </row>
     <row r="56" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
@@ -32557,31 +32523,31 @@
         <v>100</v>
       </c>
       <c r="C56" s="6"/>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" t="s">
         <v>115</v>
       </c>
-      <c r="F56" s="120">
+      <c r="F56">
         <v>3</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="G56" t="s">
         <v>108</v>
       </c>
-      <c r="H56" s="121">
+      <c r="H56" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I56" s="121">
+      <c r="I56" s="111">
         <f t="shared" si="0"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="J56" s="121">
-        <f>I56</f>
+      <c r="J56" s="111">
+        <f t="shared" si="4"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="K56" s="122"/>
+      <c r="K56" s="112"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
@@ -32589,31 +32555,31 @@
         <v>101</v>
       </c>
       <c r="C57" s="6"/>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" t="s">
         <v>115</v>
       </c>
-      <c r="F57" s="120">
+      <c r="F57">
         <v>2</v>
       </c>
-      <c r="G57" s="8" t="s">
+      <c r="G57" t="s">
         <v>108</v>
       </c>
-      <c r="H57" s="121">
+      <c r="H57" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I57" s="121">
+      <c r="I57" s="111">
         <f t="shared" si="0"/>
         <v>77.103628343767795</v>
       </c>
-      <c r="J57" s="121">
-        <f>I57</f>
+      <c r="J57" s="111">
+        <f t="shared" si="4"/>
         <v>77.103628343767795</v>
       </c>
-      <c r="K57" s="122"/>
+      <c r="K57" s="112"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
@@ -32621,31 +32587,31 @@
         <v>102</v>
       </c>
       <c r="C58" s="6"/>
-      <c r="D58" s="9" t="s">
+      <c r="D58" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" t="s">
         <v>115</v>
       </c>
-      <c r="F58" s="120">
+      <c r="F58">
         <v>3</v>
       </c>
-      <c r="G58" s="8" t="s">
+      <c r="G58" t="s">
         <v>108</v>
       </c>
-      <c r="H58" s="121">
+      <c r="H58" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I58" s="121">
+      <c r="I58" s="111">
         <f t="shared" si="0"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="J58" s="121">
-        <f>I58</f>
+      <c r="J58" s="111">
+        <f t="shared" si="4"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="K58" s="122"/>
+      <c r="K58" s="112"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
@@ -32653,31 +32619,31 @@
         <v>103</v>
       </c>
       <c r="C59" s="6"/>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" t="s">
         <v>115</v>
       </c>
-      <c r="F59" s="120">
+      <c r="F59">
         <v>2</v>
       </c>
-      <c r="G59" s="8" t="s">
+      <c r="G59" t="s">
         <v>108</v>
       </c>
-      <c r="H59" s="121">
+      <c r="H59" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I59" s="121">
+      <c r="I59" s="111">
         <f t="shared" si="0"/>
         <v>77.103628343767795</v>
       </c>
-      <c r="J59" s="121">
-        <f>I59</f>
+      <c r="J59" s="111">
+        <f t="shared" si="4"/>
         <v>77.103628343767795</v>
       </c>
-      <c r="K59" s="122"/>
+      <c r="K59" s="112"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
@@ -32685,31 +32651,31 @@
         <v>104</v>
       </c>
       <c r="C60" s="6"/>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" t="s">
         <v>114</v>
       </c>
-      <c r="F60" s="120">
+      <c r="F60">
         <v>2</v>
       </c>
-      <c r="G60" s="8" t="s">
+      <c r="G60" t="s">
         <v>108</v>
       </c>
-      <c r="H60" s="121">
+      <c r="H60" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I60" s="121">
+      <c r="I60" s="111">
         <f t="shared" si="0"/>
         <v>87.693332552144369</v>
       </c>
-      <c r="J60" s="121">
-        <f>I60</f>
+      <c r="J60" s="111">
+        <f t="shared" si="4"/>
         <v>87.693332552144369</v>
       </c>
-      <c r="K60" s="122"/>
+      <c r="K60" s="112"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
@@ -32720,19 +32686,16 @@
       <c r="D61" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="121" t="str">
+      <c r="H61" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I61" s="121" t="str">
+      <c r="I61" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J61" s="121"/>
-      <c r="K61" s="122">
+      <c r="J61" s="111"/>
+      <c r="K61" s="112">
         <f>SUM(J62:J73)</f>
         <v>1382.5443437881208</v>
       </c>
@@ -32743,31 +32706,31 @@
         <v>7</v>
       </c>
       <c r="C62" s="6"/>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" t="s">
         <v>109</v>
       </c>
-      <c r="F62" s="120">
+      <c r="F62">
         <v>1</v>
       </c>
-      <c r="G62" s="8" t="s">
+      <c r="G62" t="s">
         <v>108</v>
       </c>
-      <c r="H62" s="121">
+      <c r="H62" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I62" s="121">
+      <c r="I62" s="111">
         <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J62" s="121">
-        <f>I62</f>
+      <c r="J62" s="111">
+        <f t="shared" ref="J62:J73" si="5">I62</f>
         <v>49.782125344774748</v>
       </c>
-      <c r="K62" s="122"/>
+      <c r="K62" s="112"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
@@ -32775,31 +32738,31 @@
         <v>13</v>
       </c>
       <c r="C63" s="6"/>
-      <c r="D63" s="9" t="s">
+      <c r="D63" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" t="s">
         <v>109</v>
       </c>
-      <c r="F63" s="120">
+      <c r="F63">
         <v>1</v>
       </c>
-      <c r="G63" s="8" t="s">
+      <c r="G63" t="s">
         <v>108</v>
       </c>
-      <c r="H63" s="121">
+      <c r="H63" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I63" s="121">
+      <c r="I63" s="111">
         <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J63" s="121">
-        <f>I63</f>
+      <c r="J63" s="111">
+        <f t="shared" si="5"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="K63" s="122"/>
+      <c r="K63" s="112"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
@@ -32807,31 +32770,31 @@
         <v>14</v>
       </c>
       <c r="C64" s="6"/>
-      <c r="D64" s="9" t="s">
+      <c r="D64" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" t="s">
         <v>112</v>
       </c>
-      <c r="F64" s="120">
+      <c r="F64">
         <v>1</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="G64" t="s">
         <v>108</v>
       </c>
-      <c r="H64" s="121">
+      <c r="H64" s="111">
         <f t="shared" si="1"/>
         <v>45.220459339114129</v>
       </c>
-      <c r="I64" s="121">
+      <c r="I64" s="111">
         <f t="shared" si="0"/>
         <v>45.220459339114129</v>
       </c>
-      <c r="J64" s="121">
-        <f>I64</f>
+      <c r="J64" s="111">
+        <f t="shared" si="5"/>
         <v>45.220459339114129</v>
       </c>
-      <c r="K64" s="122"/>
+      <c r="K64" s="112"/>
     </row>
     <row r="65" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
@@ -32839,31 +32802,31 @@
         <v>99</v>
       </c>
       <c r="C65" s="6"/>
-      <c r="D65" s="9" t="s">
+      <c r="D65" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" t="s">
         <v>112</v>
       </c>
-      <c r="F65" s="120">
+      <c r="F65">
         <v>2</v>
       </c>
-      <c r="G65" s="8" t="s">
+      <c r="G65" t="s">
         <v>108</v>
       </c>
-      <c r="H65" s="121">
+      <c r="H65" s="111">
         <f t="shared" si="1"/>
         <v>45.220459339114129</v>
       </c>
-      <c r="I65" s="121">
+      <c r="I65" s="111">
         <f t="shared" si="0"/>
         <v>90.440918678228257</v>
       </c>
-      <c r="J65" s="121">
-        <f>I65</f>
+      <c r="J65" s="111">
+        <f t="shared" si="5"/>
         <v>90.440918678228257</v>
       </c>
-      <c r="K65" s="122"/>
+      <c r="K65" s="112"/>
     </row>
     <row r="66" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
@@ -32871,31 +32834,31 @@
         <v>100</v>
       </c>
       <c r="C66" s="6"/>
-      <c r="D66" s="9" t="s">
+      <c r="D66" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" t="s">
         <v>109</v>
       </c>
-      <c r="F66" s="120">
+      <c r="F66">
         <v>2</v>
       </c>
-      <c r="G66" s="8" t="s">
+      <c r="G66" t="s">
         <v>108</v>
       </c>
-      <c r="H66" s="121">
+      <c r="H66" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I66" s="121">
+      <c r="I66" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J66" s="121">
-        <f>I66</f>
+      <c r="J66" s="111">
+        <f t="shared" si="5"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="K66" s="122"/>
+      <c r="K66" s="112"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
@@ -32903,31 +32866,31 @@
         <v>101</v>
       </c>
       <c r="C67" s="6"/>
-      <c r="D67" s="9" t="s">
+      <c r="D67" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" t="s">
         <v>111</v>
       </c>
-      <c r="F67" s="120">
+      <c r="F67">
         <v>3</v>
       </c>
-      <c r="G67" s="8" t="s">
+      <c r="G67" t="s">
         <v>108</v>
       </c>
-      <c r="H67" s="121">
+      <c r="H67" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I67" s="121">
+      <c r="I67" s="111">
         <f t="shared" si="0"/>
         <v>126.4778075199203</v>
       </c>
-      <c r="J67" s="121">
-        <f>I67</f>
+      <c r="J67" s="111">
+        <f t="shared" si="5"/>
         <v>126.4778075199203</v>
       </c>
-      <c r="K67" s="122"/>
+      <c r="K67" s="112"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
@@ -32935,31 +32898,31 @@
         <v>102</v>
       </c>
       <c r="C68" s="6"/>
-      <c r="D68" s="9" t="s">
+      <c r="D68" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" t="s">
         <v>113</v>
       </c>
-      <c r="F68" s="120">
+      <c r="F68">
         <v>5</v>
       </c>
-      <c r="G68" s="8" t="s">
+      <c r="G68" t="s">
         <v>108</v>
       </c>
-      <c r="H68" s="121">
+      <c r="H68" s="111">
         <f t="shared" si="1"/>
         <v>49.154057104913683</v>
       </c>
-      <c r="I68" s="121">
-        <f t="shared" ref="I68:I73" si="2">IFERROR(H68*F68,"")</f>
+      <c r="I68" s="111">
+        <f t="shared" ref="I68:I73" si="6">IFERROR(H68*F68,"")</f>
         <v>245.77028552456841</v>
       </c>
-      <c r="J68" s="121">
-        <f>I68</f>
+      <c r="J68" s="111">
+        <f t="shared" si="5"/>
         <v>245.77028552456841</v>
       </c>
-      <c r="K68" s="122"/>
+      <c r="K68" s="112"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
@@ -32967,31 +32930,31 @@
         <v>103</v>
       </c>
       <c r="C69" s="6"/>
-      <c r="D69" s="9" t="s">
+      <c r="D69" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" t="s">
         <v>114</v>
       </c>
-      <c r="F69" s="120">
+      <c r="F69">
         <v>5</v>
       </c>
-      <c r="G69" s="8" t="s">
+      <c r="G69" t="s">
         <v>108</v>
       </c>
-      <c r="H69" s="121">
-        <f t="shared" ref="H69:H73" si="3">_xlfn.XLOOKUP(E69,$D$77:$D$82,$E$77:$E$82,"")</f>
+      <c r="H69" s="111">
+        <f t="shared" ref="H69:H73" si="7">_xlfn.XLOOKUP(E69,$D$77:$D$82,$E$77:$E$82,"")</f>
         <v>43.846666276072185</v>
       </c>
-      <c r="I69" s="121">
-        <f t="shared" si="2"/>
+      <c r="I69" s="111">
+        <f t="shared" si="6"/>
         <v>219.23333138036094</v>
       </c>
-      <c r="J69" s="121">
-        <f>I69</f>
+      <c r="J69" s="111">
+        <f t="shared" si="5"/>
         <v>219.23333138036094</v>
       </c>
-      <c r="K69" s="122"/>
+      <c r="K69" s="112"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
@@ -32999,31 +32962,31 @@
         <v>104</v>
       </c>
       <c r="C70" s="6"/>
-      <c r="D70" s="9" t="s">
+      <c r="D70" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" t="s">
         <v>114</v>
       </c>
-      <c r="F70" s="120">
+      <c r="F70">
         <v>2</v>
       </c>
-      <c r="G70" s="8" t="s">
+      <c r="G70" t="s">
         <v>108</v>
       </c>
-      <c r="H70" s="121">
-        <f t="shared" si="3"/>
+      <c r="H70" s="111">
+        <f t="shared" si="7"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I70" s="121">
-        <f t="shared" si="2"/>
+      <c r="I70" s="111">
+        <f t="shared" si="6"/>
         <v>87.693332552144369</v>
       </c>
-      <c r="J70" s="121">
-        <f>I70</f>
+      <c r="J70" s="111">
+        <f t="shared" si="5"/>
         <v>87.693332552144369</v>
       </c>
-      <c r="K70" s="122"/>
+      <c r="K70" s="112"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
@@ -33031,31 +32994,31 @@
         <v>105</v>
       </c>
       <c r="C71" s="6"/>
-      <c r="D71" s="9" t="s">
+      <c r="D71" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" t="s">
         <v>114</v>
       </c>
-      <c r="F71" s="120">
+      <c r="F71">
         <v>5</v>
       </c>
-      <c r="G71" s="8" t="s">
+      <c r="G71" t="s">
         <v>108</v>
       </c>
-      <c r="H71" s="121">
-        <f t="shared" si="3"/>
+      <c r="H71" s="111">
+        <f t="shared" si="7"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I71" s="121">
-        <f t="shared" si="2"/>
+      <c r="I71" s="111">
+        <f t="shared" si="6"/>
         <v>219.23333138036094</v>
       </c>
-      <c r="J71" s="121">
-        <f>I71</f>
+      <c r="J71" s="111">
+        <f t="shared" si="5"/>
         <v>219.23333138036094</v>
       </c>
-      <c r="K71" s="122"/>
+      <c r="K71" s="112"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
@@ -33063,78 +33026,78 @@
         <v>106</v>
       </c>
       <c r="C72" s="6"/>
-      <c r="D72" s="9" t="s">
+      <c r="D72" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" t="s">
         <v>109</v>
       </c>
-      <c r="F72" s="120">
+      <c r="F72">
         <v>2</v>
       </c>
-      <c r="G72" s="8" t="s">
+      <c r="G72" t="s">
         <v>108</v>
       </c>
-      <c r="H72" s="121">
-        <f t="shared" si="3"/>
+      <c r="H72" s="111">
+        <f t="shared" si="7"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I72" s="121">
-        <f t="shared" si="2"/>
+      <c r="I72" s="111">
+        <f t="shared" si="6"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J72" s="121">
-        <f>I72</f>
+      <c r="J72" s="111">
+        <f t="shared" si="5"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="K72" s="122"/>
+      <c r="K72" s="112"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12" t="s">
+      <c r="A73" s="8"/>
+      <c r="B73" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C73" s="12"/>
-      <c r="D73" s="13" t="s">
+      <c r="C73" s="9"/>
+      <c r="D73" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="14" t="s">
+      <c r="E73" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="F73" s="14">
+      <c r="F73" s="11">
         <v>1</v>
       </c>
-      <c r="G73" s="14" t="s">
+      <c r="G73" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="H73" s="121">
-        <f t="shared" si="3"/>
+      <c r="H73" s="111">
+        <f t="shared" si="7"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I73" s="121">
-        <f t="shared" si="2"/>
+      <c r="I73" s="111">
+        <f t="shared" si="6"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J73" s="121">
-        <f>I73</f>
+      <c r="J73" s="111">
+        <f t="shared" si="5"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="K73" s="123"/>
+      <c r="K73" s="113"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" s="21" t="s">
+      <c r="A74" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="B74" s="22"/>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="22"/>
-      <c r="J74" s="22"/>
-      <c r="K74" s="124">
+      <c r="B74" s="120"/>
+      <c r="C74" s="120"/>
+      <c r="D74" s="120"/>
+      <c r="E74" s="120"/>
+      <c r="F74" s="120"/>
+      <c r="G74" s="120"/>
+      <c r="H74" s="120"/>
+      <c r="I74" s="120"/>
+      <c r="J74" s="120"/>
+      <c r="K74" s="114">
         <f>SUM(K3:K73)</f>
         <v>13026.517352669423</v>
       </c>
@@ -33148,7 +33111,7 @@
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D76" s="23" t="s">
+      <c r="D76" s="7" t="s">
         <v>110</v>
       </c>
       <c r="E76" t="s">
@@ -33157,7 +33120,7 @@
       <c r="J76" t="s">
         <v>197</v>
       </c>
-      <c r="K76" s="126">
+      <c r="K76" s="111">
         <f>K74*(1+K75)</f>
         <v>16283.14669083678</v>
       </c>
@@ -33166,7 +33129,7 @@
       <c r="D77" t="s">
         <v>109</v>
       </c>
-      <c r="E77" s="119">
+      <c r="E77" s="110">
         <f>'Company definition'!F82</f>
         <v>49.782125344774748</v>
       </c>
@@ -33175,7 +33138,7 @@
       <c r="D78" t="s">
         <v>112</v>
       </c>
-      <c r="E78" s="119">
+      <c r="E78" s="110">
         <f>'Company definition'!F85</f>
         <v>45.220459339114129</v>
       </c>
@@ -33184,7 +33147,7 @@
       <c r="D79" t="s">
         <v>111</v>
       </c>
-      <c r="E79" s="119">
+      <c r="E79" s="110">
         <f>'Company definition'!F84</f>
         <v>42.159269173306768</v>
       </c>
@@ -33193,7 +33156,7 @@
       <c r="D80" t="s">
         <v>113</v>
       </c>
-      <c r="E80" s="119">
+      <c r="E80" s="110">
         <f>'Company definition'!F86</f>
         <v>49.154057104913683</v>
       </c>
@@ -33202,7 +33165,7 @@
       <c r="D81" t="s">
         <v>114</v>
       </c>
-      <c r="E81" s="119">
+      <c r="E81" s="110">
         <f>'Company definition'!F87</f>
         <v>43.846666276072185</v>
       </c>
@@ -33211,7 +33174,7 @@
       <c r="D82" t="s">
         <v>115</v>
       </c>
-      <c r="E82" s="119">
+      <c r="E82" s="110">
         <f>'Company definition'!F88</f>
         <v>38.551814171883898</v>
       </c>
@@ -33250,55 +33213,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="118"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="127" t="s">
+      <c r="M2" t="s">
         <v>198</v>
       </c>
       <c r="N2">
@@ -33315,25 +33278,22 @@
       <c r="D3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="121" t="str">
+      <c r="H3" s="111" t="str">
         <f>_xlfn.XLOOKUP(E3,$D$77:$D$82,$E$77:$E$82,"")</f>
         <v/>
       </c>
-      <c r="I3" s="121" t="str">
+      <c r="I3" s="111" t="str">
         <f>IFERROR(H3*F3,"")</f>
         <v/>
       </c>
-      <c r="K3" s="125">
+      <c r="K3" s="115">
         <f>SUM(J4:J19)</f>
         <v>1194.7710082745937</v>
       </c>
       <c r="M3" t="s">
         <v>199</v>
       </c>
-      <c r="N3" s="126">
+      <c r="N3" s="111">
         <f>K76</f>
         <v>16729.515715661983</v>
       </c>
@@ -33344,35 +33304,35 @@
         <v>7</v>
       </c>
       <c r="C4" s="6"/>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" t="s">
         <v>109</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4">
         <v>2</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="121">
+      <c r="H4" s="111">
         <f>_xlfn.XLOOKUP(E4,$D$77:$D$82,$E$77:$E$82,"")</f>
         <v>49.782125344774748</v>
       </c>
-      <c r="I4" s="121">
+      <c r="I4" s="111">
         <f t="shared" ref="I4:I67" si="0">IFERROR(H4*F4,"")</f>
         <v>99.564250689549496</v>
       </c>
-      <c r="J4" s="121">
+      <c r="J4" s="111">
         <f>I4</f>
         <v>99.564250689549496</v>
       </c>
-      <c r="K4" s="122"/>
+      <c r="K4" s="112"/>
       <c r="M4" t="s">
         <v>200</v>
       </c>
-      <c r="N4" s="126">
+      <c r="N4" s="111">
         <f>N3-N2</f>
         <v>446.36902482520236</v>
       </c>
@@ -33383,31 +33343,31 @@
         <v>13</v>
       </c>
       <c r="C5" s="6"/>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" t="s">
         <v>109</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5">
         <v>2</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" t="s">
         <v>108</v>
       </c>
-      <c r="H5" s="121">
+      <c r="H5" s="111">
         <f t="shared" ref="H5:H68" si="1">_xlfn.XLOOKUP(E5,$D$77:$D$82,$E$77:$E$82,"")</f>
         <v>49.782125344774748</v>
       </c>
-      <c r="I5" s="121">
+      <c r="I5" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J5" s="121">
+      <c r="J5" s="111">
         <f>I5</f>
         <v>99.564250689549496</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="112"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
@@ -33415,25 +33375,22 @@
         <v>14</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="121" t="str">
+      <c r="H6" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I6" s="121" t="str">
+      <c r="I6" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J6" s="121">
+      <c r="J6" s="111">
         <f>SUM(I7:I19)</f>
         <v>995.64250689549476</v>
       </c>
-      <c r="K6" s="122"/>
+      <c r="K6" s="112"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
@@ -33441,28 +33398,28 @@
       <c r="C7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" t="s">
         <v>109</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" t="s">
         <v>108</v>
       </c>
-      <c r="H7" s="121">
+      <c r="H7" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I7" s="121">
+      <c r="I7" s="111">
         <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J7" s="121"/>
-      <c r="K7" s="122"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="112"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
@@ -33470,28 +33427,28 @@
       <c r="C8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" t="s">
         <v>109</v>
       </c>
-      <c r="F8" s="120">
+      <c r="F8">
         <v>2</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" t="s">
         <v>108</v>
       </c>
-      <c r="H8" s="121">
+      <c r="H8" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I8" s="121">
+      <c r="I8" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J8" s="121"/>
-      <c r="K8" s="122"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="112"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
@@ -33499,28 +33456,28 @@
       <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" t="s">
         <v>109</v>
       </c>
-      <c r="F9" s="120">
+      <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" t="s">
         <v>108</v>
       </c>
-      <c r="H9" s="121">
+      <c r="H9" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I9" s="121">
+      <c r="I9" s="111">
         <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J9" s="121"/>
-      <c r="K9" s="122"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="112"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
@@ -33528,28 +33485,28 @@
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" t="s">
         <v>109</v>
       </c>
-      <c r="F10" s="120">
+      <c r="F10">
         <v>2</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="121">
+      <c r="H10" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I10" s="121">
+      <c r="I10" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="112"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
@@ -33557,28 +33514,28 @@
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" t="s">
         <v>109</v>
       </c>
-      <c r="F11" s="120">
+      <c r="F11">
         <v>1</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" t="s">
         <v>108</v>
       </c>
-      <c r="H11" s="121">
+      <c r="H11" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I11" s="121">
+      <c r="I11" s="111">
         <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J11" s="121"/>
-      <c r="K11" s="122"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="112"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
@@ -33586,28 +33543,28 @@
       <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" t="s">
         <v>109</v>
       </c>
-      <c r="F12" s="120">
+      <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" t="s">
         <v>108</v>
       </c>
-      <c r="H12" s="121">
+      <c r="H12" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I12" s="121">
+      <c r="I12" s="111">
         <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J12" s="121"/>
-      <c r="K12" s="122"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="112"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
@@ -33615,28 +33572,28 @@
       <c r="C13" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" t="s">
         <v>109</v>
       </c>
-      <c r="F13" s="120">
+      <c r="F13">
         <v>2</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="121">
+      <c r="H13" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I13" s="121">
+      <c r="I13" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J13" s="121"/>
-      <c r="K13" s="122"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="112"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
@@ -33644,28 +33601,28 @@
       <c r="C14" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" t="s">
         <v>109</v>
       </c>
-      <c r="F14" s="120">
+      <c r="F14">
         <v>2</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="121">
+      <c r="H14" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I14" s="121">
+      <c r="I14" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J14" s="121"/>
-      <c r="K14" s="122"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="112"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
@@ -33673,28 +33630,28 @@
       <c r="C15" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" t="s">
         <v>109</v>
       </c>
-      <c r="F15" s="120">
+      <c r="F15">
         <v>2</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" t="s">
         <v>108</v>
       </c>
-      <c r="H15" s="121">
+      <c r="H15" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I15" s="121">
+      <c r="I15" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J15" s="121"/>
-      <c r="K15" s="122"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="112"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
@@ -33702,28 +33659,28 @@
       <c r="C16" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" t="s">
         <v>109</v>
       </c>
-      <c r="F16" s="120">
+      <c r="F16">
         <v>2</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" t="s">
         <v>108</v>
       </c>
-      <c r="H16" s="121">
+      <c r="H16" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I16" s="121">
+      <c r="I16" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J16" s="121"/>
-      <c r="K16" s="122"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="112"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
@@ -33731,28 +33688,28 @@
       <c r="C17" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" t="s">
         <v>109</v>
       </c>
-      <c r="F17" s="120">
+      <c r="F17">
         <v>1</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" t="s">
         <v>108</v>
       </c>
-      <c r="H17" s="121">
+      <c r="H17" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I17" s="121">
+      <c r="I17" s="111">
         <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J17" s="121"/>
-      <c r="K17" s="122"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="112"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
@@ -33760,28 +33717,28 @@
       <c r="C18" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" t="s">
         <v>109</v>
       </c>
-      <c r="F18" s="120">
+      <c r="F18">
         <v>2</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" t="s">
         <v>108</v>
       </c>
-      <c r="H18" s="121">
+      <c r="H18" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I18" s="121">
+      <c r="I18" s="111">
         <f t="shared" si="0"/>
         <v>99.564250689549496</v>
       </c>
-      <c r="J18" s="121"/>
-      <c r="K18" s="122"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="112"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
@@ -33789,28 +33746,28 @@
       <c r="C19" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" t="s">
         <v>109</v>
       </c>
-      <c r="F19" s="120">
+      <c r="F19">
         <v>1</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" t="s">
         <v>108</v>
       </c>
-      <c r="H19" s="121">
+      <c r="H19" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I19" s="121">
+      <c r="I19" s="111">
         <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J19" s="121"/>
-      <c r="K19" s="122"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="112"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -33821,19 +33778,16 @@
       <c r="D20" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="121" t="str">
+      <c r="H20" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I20" s="121" t="str">
+      <c r="I20" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J20" s="121"/>
-      <c r="K20" s="122">
+      <c r="J20" s="111"/>
+      <c r="K20" s="112">
         <f>SUM(J21:J30)</f>
         <v>2433.690244536559</v>
       </c>
@@ -33844,31 +33798,31 @@
         <v>7</v>
       </c>
       <c r="C21" s="6"/>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" t="s">
         <v>111</v>
       </c>
-      <c r="F21" s="120">
+      <c r="F21">
         <v>1</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" t="s">
         <v>108</v>
       </c>
-      <c r="H21" s="121">
+      <c r="H21" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I21" s="121">
+      <c r="I21" s="111">
         <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="J21" s="121">
-        <f>I21</f>
+      <c r="J21" s="111">
+        <f t="shared" ref="J21:J30" si="2">I21</f>
         <v>42.159269173306768</v>
       </c>
-      <c r="K21" s="122"/>
+      <c r="K21" s="112"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
@@ -33876,31 +33830,31 @@
         <v>13</v>
       </c>
       <c r="C22" s="6"/>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" t="s">
         <v>112</v>
       </c>
-      <c r="F22" s="120">
+      <c r="F22">
         <v>4</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" t="s">
         <v>108</v>
       </c>
-      <c r="H22" s="121">
+      <c r="H22" s="111">
         <f t="shared" si="1"/>
         <v>45.220459339114129</v>
       </c>
-      <c r="I22" s="121">
+      <c r="I22" s="111">
         <f t="shared" si="0"/>
         <v>180.88183735645651</v>
       </c>
-      <c r="J22" s="121">
-        <f>I22</f>
+      <c r="J22" s="111">
+        <f t="shared" si="2"/>
         <v>180.88183735645651</v>
       </c>
-      <c r="K22" s="122"/>
+      <c r="K22" s="112"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
@@ -33908,31 +33862,31 @@
         <v>14</v>
       </c>
       <c r="C23" s="6"/>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="120">
+      <c r="F23">
         <v>1</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" t="s">
         <v>108</v>
       </c>
-      <c r="H23" s="121">
+      <c r="H23" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I23" s="121">
+      <c r="I23" s="111">
         <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="J23" s="121">
-        <f>I23</f>
+      <c r="J23" s="111">
+        <f t="shared" si="2"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="K23" s="122"/>
+      <c r="K23" s="112"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
@@ -33940,31 +33894,31 @@
         <v>99</v>
       </c>
       <c r="C24" s="6"/>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" t="s">
         <v>111</v>
       </c>
-      <c r="F24" s="120">
+      <c r="F24">
         <v>1</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" t="s">
         <v>108</v>
       </c>
-      <c r="H24" s="121">
+      <c r="H24" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I24" s="121">
+      <c r="I24" s="111">
         <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="J24" s="121">
-        <f>I24</f>
+      <c r="J24" s="111">
+        <f t="shared" si="2"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="K24" s="122"/>
+      <c r="K24" s="112"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
@@ -33972,31 +33926,31 @@
         <v>100</v>
       </c>
       <c r="C25" s="6"/>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" t="s">
         <v>111</v>
       </c>
-      <c r="F25" s="120">
+      <c r="F25">
         <v>2</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" t="s">
         <v>108</v>
       </c>
-      <c r="H25" s="121">
+      <c r="H25" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I25" s="121">
+      <c r="I25" s="111">
         <f t="shared" si="0"/>
         <v>84.318538346613536</v>
       </c>
-      <c r="J25" s="121">
-        <f>I25</f>
+      <c r="J25" s="111">
+        <f t="shared" si="2"/>
         <v>84.318538346613536</v>
       </c>
-      <c r="K25" s="122"/>
+      <c r="K25" s="112"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
@@ -34004,31 +33958,31 @@
         <v>101</v>
       </c>
       <c r="C26" s="6"/>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" t="s">
         <v>112</v>
       </c>
-      <c r="F26" s="120">
+      <c r="F26">
         <v>6</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" t="s">
         <v>108</v>
       </c>
-      <c r="H26" s="121">
+      <c r="H26" s="111">
         <f t="shared" si="1"/>
         <v>45.220459339114129</v>
       </c>
-      <c r="I26" s="121">
+      <c r="I26" s="111">
         <f t="shared" si="0"/>
         <v>271.32275603468474</v>
       </c>
-      <c r="J26" s="121">
-        <f>I26</f>
+      <c r="J26" s="111">
+        <f t="shared" si="2"/>
         <v>271.32275603468474</v>
       </c>
-      <c r="K26" s="122"/>
+      <c r="K26" s="112"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
@@ -34036,31 +33990,31 @@
         <v>102</v>
       </c>
       <c r="C27" s="6"/>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="120">
+      <c r="F27">
         <v>22</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" t="s">
         <v>108</v>
       </c>
-      <c r="H27" s="121">
+      <c r="H27" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I27" s="121">
+      <c r="I27" s="111">
         <f t="shared" si="0"/>
         <v>927.5039218127489</v>
       </c>
-      <c r="J27" s="121">
-        <f>I27</f>
+      <c r="J27" s="111">
+        <f t="shared" si="2"/>
         <v>927.5039218127489</v>
       </c>
-      <c r="K27" s="122"/>
+      <c r="K27" s="112"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
@@ -34068,31 +34022,31 @@
         <v>103</v>
       </c>
       <c r="C28" s="6"/>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" t="s">
         <v>111</v>
       </c>
-      <c r="F28" s="120">
+      <c r="F28">
         <v>8</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" t="s">
         <v>108</v>
       </c>
-      <c r="H28" s="121">
+      <c r="H28" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I28" s="121">
+      <c r="I28" s="111">
         <f t="shared" si="0"/>
         <v>337.27415338645415</v>
       </c>
-      <c r="J28" s="121">
-        <f>I28</f>
+      <c r="J28" s="111">
+        <f t="shared" si="2"/>
         <v>337.27415338645415</v>
       </c>
-      <c r="K28" s="122"/>
+      <c r="K28" s="112"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
@@ -34100,31 +34054,31 @@
         <v>104</v>
       </c>
       <c r="C29" s="6"/>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="120">
+      <c r="F29">
         <v>4</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" t="s">
         <v>108</v>
       </c>
-      <c r="H29" s="121">
+      <c r="H29" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I29" s="121">
+      <c r="I29" s="111">
         <f t="shared" si="0"/>
         <v>168.63707669322707</v>
       </c>
-      <c r="J29" s="121">
-        <f>I29</f>
+      <c r="J29" s="111">
+        <f t="shared" si="2"/>
         <v>168.63707669322707</v>
       </c>
-      <c r="K29" s="122"/>
+      <c r="K29" s="112"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
@@ -34132,31 +34086,31 @@
         <v>105</v>
       </c>
       <c r="C30" s="6"/>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" t="s">
         <v>111</v>
       </c>
-      <c r="F30" s="120">
+      <c r="F30">
         <v>8</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" t="s">
         <v>108</v>
       </c>
-      <c r="H30" s="121">
+      <c r="H30" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I30" s="121">
+      <c r="I30" s="111">
         <f t="shared" si="0"/>
         <v>337.27415338645415</v>
       </c>
-      <c r="J30" s="121">
-        <f>I30</f>
+      <c r="J30" s="111">
+        <f t="shared" si="2"/>
         <v>337.27415338645415</v>
       </c>
-      <c r="K30" s="122"/>
+      <c r="K30" s="112"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
@@ -34167,19 +34121,16 @@
       <c r="D31" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="121" t="str">
+      <c r="H31" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I31" s="121" t="str">
+      <c r="I31" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J31" s="121"/>
-      <c r="K31" s="122">
+      <c r="J31" s="111"/>
+      <c r="K31" s="112">
         <f>SUM(J32:J38)</f>
         <v>2361.0626646076757</v>
       </c>
@@ -34190,31 +34141,31 @@
         <v>7</v>
       </c>
       <c r="C32" s="6"/>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="120">
+      <c r="F32">
         <v>10</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" t="s">
         <v>108</v>
       </c>
-      <c r="H32" s="121">
+      <c r="H32" s="111">
         <f t="shared" si="1"/>
         <v>49.154057104913683</v>
       </c>
-      <c r="I32" s="121">
+      <c r="I32" s="111">
         <f t="shared" si="0"/>
         <v>491.54057104913682</v>
       </c>
-      <c r="J32" s="121">
-        <f>I32</f>
+      <c r="J32" s="111">
+        <f t="shared" ref="J32:J38" si="3">I32</f>
         <v>491.54057104913682</v>
       </c>
-      <c r="K32" s="122"/>
+      <c r="K32" s="112"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
@@ -34222,31 +34173,31 @@
         <v>13</v>
       </c>
       <c r="C33" s="6"/>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" t="s">
         <v>115</v>
       </c>
-      <c r="F33" s="120">
+      <c r="F33">
         <v>3</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" t="s">
         <v>108</v>
       </c>
-      <c r="H33" s="121">
+      <c r="H33" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I33" s="121">
+      <c r="I33" s="111">
         <f t="shared" si="0"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="J33" s="121">
-        <f>I33</f>
+      <c r="J33" s="111">
+        <f t="shared" si="3"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="K33" s="122"/>
+      <c r="K33" s="112"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
@@ -34254,31 +34205,31 @@
         <v>14</v>
       </c>
       <c r="C34" s="6"/>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" t="s">
         <v>114</v>
       </c>
-      <c r="F34" s="120">
+      <c r="F34">
         <v>8</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" t="s">
         <v>108</v>
       </c>
-      <c r="H34" s="121">
+      <c r="H34" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I34" s="121">
+      <c r="I34" s="111">
         <f t="shared" si="0"/>
         <v>350.77333020857748</v>
       </c>
-      <c r="J34" s="121">
-        <f>I34</f>
+      <c r="J34" s="111">
+        <f t="shared" si="3"/>
         <v>350.77333020857748</v>
       </c>
-      <c r="K34" s="122"/>
+      <c r="K34" s="112"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
@@ -34286,31 +34237,31 @@
         <v>99</v>
       </c>
       <c r="C35" s="6"/>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" t="s">
         <v>114</v>
       </c>
-      <c r="F35" s="120">
+      <c r="F35">
         <v>4</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" t="s">
         <v>108</v>
       </c>
-      <c r="H35" s="121">
+      <c r="H35" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I35" s="121">
+      <c r="I35" s="111">
         <f t="shared" si="0"/>
         <v>175.38666510428874</v>
       </c>
-      <c r="J35" s="121">
-        <f>I35</f>
+      <c r="J35" s="111">
+        <f t="shared" si="3"/>
         <v>175.38666510428874</v>
       </c>
-      <c r="K35" s="122"/>
+      <c r="K35" s="112"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
@@ -34318,31 +34269,31 @@
         <v>100</v>
       </c>
       <c r="C36" s="6"/>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" t="s">
         <v>114</v>
       </c>
-      <c r="F36" s="120">
+      <c r="F36">
         <v>6</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" t="s">
         <v>108</v>
       </c>
-      <c r="H36" s="121">
+      <c r="H36" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I36" s="121">
+      <c r="I36" s="111">
         <f t="shared" si="0"/>
         <v>263.07999765643308</v>
       </c>
-      <c r="J36" s="121">
-        <f>I36</f>
+      <c r="J36" s="111">
+        <f t="shared" si="3"/>
         <v>263.07999765643308</v>
       </c>
-      <c r="K36" s="122"/>
+      <c r="K36" s="112"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
@@ -34350,31 +34301,31 @@
         <v>101</v>
       </c>
       <c r="C37" s="6"/>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="120">
+      <c r="F37">
         <v>12</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" t="s">
         <v>108</v>
       </c>
-      <c r="H37" s="121">
+      <c r="H37" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I37" s="121">
+      <c r="I37" s="111">
         <f t="shared" si="0"/>
         <v>526.15999531286616</v>
       </c>
-      <c r="J37" s="121">
-        <f>I37</f>
+      <c r="J37" s="111">
+        <f t="shared" si="3"/>
         <v>526.15999531286616</v>
       </c>
-      <c r="K37" s="122"/>
+      <c r="K37" s="112"/>
     </row>
     <row r="38" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
@@ -34382,31 +34333,31 @@
         <v>102</v>
       </c>
       <c r="C38" s="6"/>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" t="s">
         <v>114</v>
       </c>
-      <c r="F38" s="120">
+      <c r="F38">
         <v>10</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" t="s">
         <v>108</v>
       </c>
-      <c r="H38" s="121">
+      <c r="H38" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I38" s="121">
+      <c r="I38" s="111">
         <f t="shared" si="0"/>
         <v>438.46666276072187</v>
       </c>
-      <c r="J38" s="121">
-        <f>I38</f>
+      <c r="J38" s="111">
+        <f t="shared" si="3"/>
         <v>438.46666276072187</v>
       </c>
-      <c r="K38" s="122"/>
+      <c r="K38" s="112"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
@@ -34417,28 +34368,28 @@
       <c r="D39" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="120">
+      <c r="F39">
         <v>6</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" t="s">
         <v>108</v>
       </c>
-      <c r="H39" s="121">
+      <c r="H39" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I39" s="121">
+      <c r="I39" s="111">
         <f t="shared" si="0"/>
         <v>263.07999765643308</v>
       </c>
-      <c r="J39" s="121">
+      <c r="J39" s="111">
         <f>SUM(I39)</f>
         <v>263.07999765643308</v>
       </c>
-      <c r="K39" s="121">
+      <c r="K39" s="111">
         <f>SUM(J39)</f>
         <v>263.07999765643308</v>
       </c>
@@ -34452,19 +34403,16 @@
       <c r="D40" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="121" t="str">
+      <c r="H40" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I40" s="121" t="str">
+      <c r="I40" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J40" s="121"/>
-      <c r="K40" s="122">
+      <c r="J40" s="111"/>
+      <c r="K40" s="112">
         <f>SUM(J41:J50)</f>
         <v>4485.1818305489533</v>
       </c>
@@ -34475,31 +34423,31 @@
         <v>7</v>
       </c>
       <c r="C41" s="6"/>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" t="s">
         <v>113</v>
       </c>
-      <c r="F41" s="120">
+      <c r="F41">
         <v>6</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="G41" t="s">
         <v>108</v>
       </c>
-      <c r="H41" s="121">
+      <c r="H41" s="111">
         <f t="shared" si="1"/>
         <v>49.154057104913683</v>
       </c>
-      <c r="I41" s="121">
+      <c r="I41" s="111">
         <f t="shared" si="0"/>
         <v>294.92434262948211</v>
       </c>
-      <c r="J41" s="121">
+      <c r="J41" s="111">
         <f>I41</f>
         <v>294.92434262948211</v>
       </c>
-      <c r="K41" s="122"/>
+      <c r="K41" s="112"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
@@ -34507,31 +34455,31 @@
         <v>13</v>
       </c>
       <c r="C42" s="6"/>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" t="s">
         <v>113</v>
       </c>
-      <c r="F42" s="120">
+      <c r="F42">
         <v>1</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" t="s">
         <v>108</v>
       </c>
-      <c r="H42" s="121">
+      <c r="H42" s="111">
         <f t="shared" si="1"/>
         <v>49.154057104913683</v>
       </c>
-      <c r="I42" s="121">
+      <c r="I42" s="111">
         <f t="shared" si="0"/>
         <v>49.154057104913683</v>
       </c>
-      <c r="J42" s="121">
+      <c r="J42" s="111">
         <f>I42</f>
         <v>49.154057104913683</v>
       </c>
-      <c r="K42" s="122"/>
+      <c r="K42" s="112"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
@@ -34539,25 +34487,22 @@
         <v>14</v>
       </c>
       <c r="C43" s="6"/>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="121" t="str">
+      <c r="H43" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I43" s="121" t="str">
+      <c r="I43" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J43" s="121">
+      <c r="J43" s="111">
         <f>SUM(I44:I50)</f>
         <v>4141.1034308145572</v>
       </c>
-      <c r="K43" s="122"/>
+      <c r="K43" s="112"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
@@ -34565,28 +34510,28 @@
       <c r="C44" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" t="s">
         <v>115</v>
       </c>
-      <c r="F44" s="120">
+      <c r="F44">
         <v>22</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="G44" t="s">
         <v>108</v>
       </c>
-      <c r="H44" s="121">
+      <c r="H44" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I44" s="121">
+      <c r="I44" s="111">
         <f t="shared" si="0"/>
         <v>848.13991178144579</v>
       </c>
-      <c r="J44" s="121"/>
-      <c r="K44" s="122"/>
+      <c r="J44" s="111"/>
+      <c r="K44" s="112"/>
     </row>
     <row r="45" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
@@ -34594,28 +34539,28 @@
       <c r="C45" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" t="s">
         <v>115</v>
       </c>
-      <c r="F45" s="120">
+      <c r="F45">
         <v>6</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="G45" t="s">
         <v>108</v>
       </c>
-      <c r="H45" s="121">
+      <c r="H45" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I45" s="121">
+      <c r="I45" s="111">
         <f t="shared" si="0"/>
         <v>231.31088503130337</v>
       </c>
-      <c r="J45" s="121"/>
-      <c r="K45" s="122"/>
+      <c r="J45" s="111"/>
+      <c r="K45" s="112"/>
     </row>
     <row r="46" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
@@ -34623,28 +34568,28 @@
       <c r="C46" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" t="s">
         <v>114</v>
       </c>
-      <c r="F46" s="120">
+      <c r="F46">
         <v>24</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G46" t="s">
         <v>108</v>
       </c>
-      <c r="H46" s="121">
+      <c r="H46" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I46" s="121">
+      <c r="I46" s="111">
         <f t="shared" si="0"/>
         <v>1052.3199906257323</v>
       </c>
-      <c r="J46" s="121"/>
-      <c r="K46" s="122"/>
+      <c r="J46" s="111"/>
+      <c r="K46" s="112"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
@@ -34652,28 +34597,28 @@
       <c r="C47" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" t="s">
         <v>115</v>
       </c>
-      <c r="F47" s="120">
+      <c r="F47">
         <v>12</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="G47" t="s">
         <v>108</v>
       </c>
-      <c r="H47" s="121">
+      <c r="H47" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I47" s="121">
+      <c r="I47" s="111">
         <f t="shared" si="0"/>
         <v>462.62177006260674</v>
       </c>
-      <c r="J47" s="121"/>
-      <c r="K47" s="122"/>
+      <c r="J47" s="111"/>
+      <c r="K47" s="112"/>
     </row>
     <row r="48" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
@@ -34681,28 +34626,28 @@
       <c r="C48" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" t="s">
         <v>114</v>
       </c>
-      <c r="F48" s="120">
+      <c r="F48">
         <v>20</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="G48" t="s">
         <v>108</v>
       </c>
-      <c r="H48" s="121">
+      <c r="H48" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I48" s="121">
+      <c r="I48" s="111">
         <f t="shared" si="0"/>
         <v>876.93332552144375</v>
       </c>
-      <c r="J48" s="121"/>
-      <c r="K48" s="122"/>
+      <c r="J48" s="111"/>
+      <c r="K48" s="112"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
@@ -34710,28 +34655,28 @@
       <c r="C49" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" t="s">
         <v>114</v>
       </c>
-      <c r="F49" s="120">
+      <c r="F49">
         <v>10</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="G49" t="s">
         <v>108</v>
       </c>
-      <c r="H49" s="121">
+      <c r="H49" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I49" s="121">
+      <c r="I49" s="111">
         <f t="shared" si="0"/>
         <v>438.46666276072187</v>
       </c>
-      <c r="J49" s="121"/>
-      <c r="K49" s="122"/>
+      <c r="J49" s="111"/>
+      <c r="K49" s="112"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
@@ -34739,28 +34684,28 @@
       <c r="C50" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" t="s">
         <v>115</v>
       </c>
-      <c r="F50" s="120">
+      <c r="F50">
         <v>6</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G50" t="s">
         <v>108</v>
       </c>
-      <c r="H50" s="121">
+      <c r="H50" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I50" s="121">
+      <c r="I50" s="111">
         <f t="shared" si="0"/>
         <v>231.31088503130337</v>
       </c>
-      <c r="J50" s="121"/>
-      <c r="K50" s="122"/>
+      <c r="J50" s="111"/>
+      <c r="K50" s="112"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
@@ -34771,19 +34716,16 @@
       <c r="D51" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="121" t="str">
+      <c r="H51" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I51" s="121" t="str">
+      <c r="I51" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J51" s="121"/>
-      <c r="K51" s="122">
+      <c r="J51" s="111"/>
+      <c r="K51" s="112">
         <f>SUM(J52:J60)</f>
         <v>1359.9032002243127</v>
       </c>
@@ -34794,31 +34736,31 @@
         <v>7</v>
       </c>
       <c r="C52" s="6"/>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" t="s">
         <v>115</v>
       </c>
-      <c r="F52" s="120">
+      <c r="F52">
         <v>6</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="G52" t="s">
         <v>108</v>
       </c>
-      <c r="H52" s="121">
+      <c r="H52" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I52" s="121">
+      <c r="I52" s="111">
         <f t="shared" si="0"/>
         <v>231.31088503130337</v>
       </c>
-      <c r="J52" s="121">
-        <f>I52</f>
+      <c r="J52" s="111">
+        <f t="shared" ref="J52:J60" si="4">I52</f>
         <v>231.31088503130337</v>
       </c>
-      <c r="K52" s="122"/>
+      <c r="K52" s="112"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
@@ -34826,31 +34768,31 @@
         <v>13</v>
       </c>
       <c r="C53" s="6"/>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" t="s">
         <v>115</v>
       </c>
-      <c r="F53" s="120">
+      <c r="F53">
         <v>4</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="G53" t="s">
         <v>108</v>
       </c>
-      <c r="H53" s="121">
+      <c r="H53" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I53" s="121">
+      <c r="I53" s="111">
         <f t="shared" si="0"/>
         <v>154.20725668753559</v>
       </c>
-      <c r="J53" s="121">
-        <f>I53</f>
+      <c r="J53" s="111">
+        <f t="shared" si="4"/>
         <v>154.20725668753559</v>
       </c>
-      <c r="K53" s="122"/>
+      <c r="K53" s="112"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
@@ -34858,31 +34800,31 @@
         <v>14</v>
       </c>
       <c r="C54" s="6"/>
-      <c r="D54" s="9" t="s">
+      <c r="D54" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" t="s">
         <v>115</v>
       </c>
-      <c r="F54" s="120">
+      <c r="F54">
         <v>5</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="G54" t="s">
         <v>108</v>
       </c>
-      <c r="H54" s="121">
+      <c r="H54" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I54" s="121">
+      <c r="I54" s="111">
         <f t="shared" si="0"/>
         <v>192.7590708594195</v>
       </c>
-      <c r="J54" s="121">
-        <f>I54</f>
+      <c r="J54" s="111">
+        <f t="shared" si="4"/>
         <v>192.7590708594195</v>
       </c>
-      <c r="K54" s="122"/>
+      <c r="K54" s="112"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
@@ -34890,31 +34832,31 @@
         <v>99</v>
       </c>
       <c r="C55" s="6"/>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" t="s">
         <v>115</v>
       </c>
-      <c r="F55" s="120">
+      <c r="F55">
         <v>3</v>
       </c>
-      <c r="G55" s="8" t="s">
+      <c r="G55" t="s">
         <v>108</v>
       </c>
-      <c r="H55" s="121">
+      <c r="H55" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I55" s="121">
+      <c r="I55" s="111">
         <f t="shared" si="0"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="J55" s="121">
-        <f>I55</f>
+      <c r="J55" s="111">
+        <f t="shared" si="4"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="K55" s="122"/>
+      <c r="K55" s="112"/>
     </row>
     <row r="56" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
@@ -34922,31 +34864,31 @@
         <v>100</v>
       </c>
       <c r="C56" s="6"/>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" t="s">
         <v>115</v>
       </c>
-      <c r="F56" s="120">
+      <c r="F56">
         <v>4</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="G56" t="s">
         <v>108</v>
       </c>
-      <c r="H56" s="121">
+      <c r="H56" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I56" s="121">
+      <c r="I56" s="111">
         <f t="shared" si="0"/>
         <v>154.20725668753559</v>
       </c>
-      <c r="J56" s="121">
-        <f>I56</f>
+      <c r="J56" s="111">
+        <f t="shared" si="4"/>
         <v>154.20725668753559</v>
       </c>
-      <c r="K56" s="122"/>
+      <c r="K56" s="112"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
@@ -34954,31 +34896,31 @@
         <v>101</v>
       </c>
       <c r="C57" s="6"/>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" t="s">
         <v>115</v>
       </c>
-      <c r="F57" s="120">
+      <c r="F57">
         <v>5</v>
       </c>
-      <c r="G57" s="8" t="s">
+      <c r="G57" t="s">
         <v>108</v>
       </c>
-      <c r="H57" s="121">
+      <c r="H57" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I57" s="121">
+      <c r="I57" s="111">
         <f t="shared" si="0"/>
         <v>192.7590708594195</v>
       </c>
-      <c r="J57" s="121">
-        <f>I57</f>
+      <c r="J57" s="111">
+        <f t="shared" si="4"/>
         <v>192.7590708594195</v>
       </c>
-      <c r="K57" s="122"/>
+      <c r="K57" s="112"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
@@ -34986,31 +34928,31 @@
         <v>102</v>
       </c>
       <c r="C58" s="6"/>
-      <c r="D58" s="9" t="s">
+      <c r="D58" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" t="s">
         <v>115</v>
       </c>
-      <c r="F58" s="120">
+      <c r="F58">
         <v>3</v>
       </c>
-      <c r="G58" s="8" t="s">
+      <c r="G58" t="s">
         <v>108</v>
       </c>
-      <c r="H58" s="121">
+      <c r="H58" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I58" s="121">
+      <c r="I58" s="111">
         <f t="shared" si="0"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="J58" s="121">
-        <f>I58</f>
+      <c r="J58" s="111">
+        <f t="shared" si="4"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="K58" s="122"/>
+      <c r="K58" s="112"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
@@ -35018,31 +34960,31 @@
         <v>103</v>
       </c>
       <c r="C59" s="6"/>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" t="s">
         <v>115</v>
       </c>
-      <c r="F59" s="120">
+      <c r="F59">
         <v>3</v>
       </c>
-      <c r="G59" s="8" t="s">
+      <c r="G59" t="s">
         <v>108</v>
       </c>
-      <c r="H59" s="121">
+      <c r="H59" s="111">
         <f t="shared" si="1"/>
         <v>38.551814171883898</v>
       </c>
-      <c r="I59" s="121">
+      <c r="I59" s="111">
         <f t="shared" si="0"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="J59" s="121">
-        <f>I59</f>
+      <c r="J59" s="111">
+        <f t="shared" si="4"/>
         <v>115.65544251565169</v>
       </c>
-      <c r="K59" s="122"/>
+      <c r="K59" s="112"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
@@ -35050,31 +34992,31 @@
         <v>104</v>
       </c>
       <c r="C60" s="6"/>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" t="s">
         <v>114</v>
       </c>
-      <c r="F60" s="120">
+      <c r="F60">
         <v>2</v>
       </c>
-      <c r="G60" s="8" t="s">
+      <c r="G60" t="s">
         <v>108</v>
       </c>
-      <c r="H60" s="121">
+      <c r="H60" s="111">
         <f t="shared" si="1"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I60" s="121">
+      <c r="I60" s="111">
         <f t="shared" si="0"/>
         <v>87.693332552144369</v>
       </c>
-      <c r="J60" s="121">
-        <f>I60</f>
+      <c r="J60" s="111">
+        <f t="shared" si="4"/>
         <v>87.693332552144369</v>
       </c>
-      <c r="K60" s="122"/>
+      <c r="K60" s="112"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
@@ -35085,19 +35027,16 @@
       <c r="D61" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="121" t="str">
+      <c r="H61" s="111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I61" s="121" t="str">
+      <c r="I61" s="111" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J61" s="121"/>
-      <c r="K61" s="122">
+      <c r="J61" s="111"/>
+      <c r="K61" s="112">
         <f>SUM(J62:J73)</f>
         <v>1285.9236266810587</v>
       </c>
@@ -35108,31 +35047,31 @@
         <v>7</v>
       </c>
       <c r="C62" s="6"/>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" t="s">
         <v>109</v>
       </c>
-      <c r="F62" s="120">
+      <c r="F62">
         <v>1</v>
       </c>
-      <c r="G62" s="8" t="s">
+      <c r="G62" t="s">
         <v>108</v>
       </c>
-      <c r="H62" s="121">
+      <c r="H62" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I62" s="121">
+      <c r="I62" s="111">
         <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J62" s="121">
-        <f>I62</f>
+      <c r="J62" s="111">
+        <f t="shared" ref="J62:J73" si="5">I62</f>
         <v>49.782125344774748</v>
       </c>
-      <c r="K62" s="122"/>
+      <c r="K62" s="112"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
@@ -35140,31 +35079,31 @@
         <v>13</v>
       </c>
       <c r="C63" s="6"/>
-      <c r="D63" s="9" t="s">
+      <c r="D63" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" t="s">
         <v>109</v>
       </c>
-      <c r="F63" s="120">
+      <c r="F63">
         <v>1</v>
       </c>
-      <c r="G63" s="8" t="s">
+      <c r="G63" t="s">
         <v>108</v>
       </c>
-      <c r="H63" s="121">
+      <c r="H63" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I63" s="121">
+      <c r="I63" s="111">
         <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J63" s="121">
-        <f>I63</f>
+      <c r="J63" s="111">
+        <f t="shared" si="5"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="K63" s="122"/>
+      <c r="K63" s="112"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
@@ -35172,31 +35111,31 @@
         <v>14</v>
       </c>
       <c r="C64" s="6"/>
-      <c r="D64" s="9" t="s">
+      <c r="D64" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" t="s">
         <v>112</v>
       </c>
-      <c r="F64" s="120">
+      <c r="F64">
         <v>1</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="G64" t="s">
         <v>108</v>
       </c>
-      <c r="H64" s="121">
+      <c r="H64" s="111">
         <f t="shared" si="1"/>
         <v>45.220459339114129</v>
       </c>
-      <c r="I64" s="121">
+      <c r="I64" s="111">
         <f t="shared" si="0"/>
         <v>45.220459339114129</v>
       </c>
-      <c r="J64" s="121">
-        <f>I64</f>
+      <c r="J64" s="111">
+        <f t="shared" si="5"/>
         <v>45.220459339114129</v>
       </c>
-      <c r="K64" s="122"/>
+      <c r="K64" s="112"/>
     </row>
     <row r="65" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
@@ -35204,31 +35143,31 @@
         <v>99</v>
       </c>
       <c r="C65" s="6"/>
-      <c r="D65" s="9" t="s">
+      <c r="D65" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" t="s">
         <v>112</v>
       </c>
-      <c r="F65" s="120">
+      <c r="F65">
         <v>2</v>
       </c>
-      <c r="G65" s="8" t="s">
+      <c r="G65" t="s">
         <v>108</v>
       </c>
-      <c r="H65" s="121">
+      <c r="H65" s="111">
         <f t="shared" si="1"/>
         <v>45.220459339114129</v>
       </c>
-      <c r="I65" s="121">
+      <c r="I65" s="111">
         <f t="shared" si="0"/>
         <v>90.440918678228257</v>
       </c>
-      <c r="J65" s="121">
-        <f>I65</f>
+      <c r="J65" s="111">
+        <f t="shared" si="5"/>
         <v>90.440918678228257</v>
       </c>
-      <c r="K65" s="122"/>
+      <c r="K65" s="112"/>
     </row>
     <row r="66" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
@@ -35236,31 +35175,31 @@
         <v>100</v>
       </c>
       <c r="C66" s="6"/>
-      <c r="D66" s="9" t="s">
+      <c r="D66" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" t="s">
         <v>109</v>
       </c>
-      <c r="F66" s="120">
+      <c r="F66">
         <v>3</v>
       </c>
-      <c r="G66" s="8" t="s">
+      <c r="G66" t="s">
         <v>108</v>
       </c>
-      <c r="H66" s="121">
+      <c r="H66" s="111">
         <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I66" s="121">
+      <c r="I66" s="111">
         <f t="shared" si="0"/>
         <v>149.34637603432424</v>
       </c>
-      <c r="J66" s="121">
-        <f>I66</f>
+      <c r="J66" s="111">
+        <f t="shared" si="5"/>
         <v>149.34637603432424</v>
       </c>
-      <c r="K66" s="122"/>
+      <c r="K66" s="112"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
@@ -35268,31 +35207,31 @@
         <v>101</v>
       </c>
       <c r="C67" s="6"/>
-      <c r="D67" s="9" t="s">
+      <c r="D67" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" t="s">
         <v>111</v>
       </c>
-      <c r="F67" s="120">
+      <c r="F67">
         <v>2</v>
       </c>
-      <c r="G67" s="8" t="s">
+      <c r="G67" t="s">
         <v>108</v>
       </c>
-      <c r="H67" s="121">
+      <c r="H67" s="111">
         <f t="shared" si="1"/>
         <v>42.159269173306768</v>
       </c>
-      <c r="I67" s="121">
+      <c r="I67" s="111">
         <f t="shared" si="0"/>
         <v>84.318538346613536</v>
       </c>
-      <c r="J67" s="121">
-        <f>I67</f>
+      <c r="J67" s="111">
+        <f t="shared" si="5"/>
         <v>84.318538346613536</v>
       </c>
-      <c r="K67" s="122"/>
+      <c r="K67" s="112"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
@@ -35300,31 +35239,31 @@
         <v>102</v>
       </c>
       <c r="C68" s="6"/>
-      <c r="D68" s="9" t="s">
+      <c r="D68" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" t="s">
         <v>113</v>
       </c>
-      <c r="F68" s="120">
+      <c r="F68">
         <v>3</v>
       </c>
-      <c r="G68" s="8" t="s">
+      <c r="G68" t="s">
         <v>108</v>
       </c>
-      <c r="H68" s="121">
+      <c r="H68" s="111">
         <f t="shared" si="1"/>
         <v>49.154057104913683</v>
       </c>
-      <c r="I68" s="121">
-        <f t="shared" ref="I68:I73" si="2">IFERROR(H68*F68,"")</f>
+      <c r="I68" s="111">
+        <f t="shared" ref="I68:I73" si="6">IFERROR(H68*F68,"")</f>
         <v>147.46217131474106</v>
       </c>
-      <c r="J68" s="121">
-        <f>I68</f>
+      <c r="J68" s="111">
+        <f t="shared" si="5"/>
         <v>147.46217131474106</v>
       </c>
-      <c r="K68" s="122"/>
+      <c r="K68" s="112"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
@@ -35332,31 +35271,31 @@
         <v>103</v>
       </c>
       <c r="C69" s="6"/>
-      <c r="D69" s="9" t="s">
+      <c r="D69" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" t="s">
         <v>114</v>
       </c>
-      <c r="F69" s="120">
+      <c r="F69">
         <v>6</v>
       </c>
-      <c r="G69" s="8" t="s">
+      <c r="G69" t="s">
         <v>108</v>
       </c>
-      <c r="H69" s="121">
-        <f t="shared" ref="H69:H73" si="3">_xlfn.XLOOKUP(E69,$D$77:$D$82,$E$77:$E$82,"")</f>
+      <c r="H69" s="111">
+        <f t="shared" ref="H69:H73" si="7">_xlfn.XLOOKUP(E69,$D$77:$D$82,$E$77:$E$82,"")</f>
         <v>43.846666276072185</v>
       </c>
-      <c r="I69" s="121">
-        <f t="shared" si="2"/>
+      <c r="I69" s="111">
+        <f t="shared" si="6"/>
         <v>263.07999765643308</v>
       </c>
-      <c r="J69" s="121">
-        <f>I69</f>
+      <c r="J69" s="111">
+        <f t="shared" si="5"/>
         <v>263.07999765643308</v>
       </c>
-      <c r="K69" s="122"/>
+      <c r="K69" s="112"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
@@ -35364,31 +35303,31 @@
         <v>104</v>
       </c>
       <c r="C70" s="6"/>
-      <c r="D70" s="9" t="s">
+      <c r="D70" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" t="s">
         <v>114</v>
       </c>
-      <c r="F70" s="120">
+      <c r="F70">
         <v>2</v>
       </c>
-      <c r="G70" s="8" t="s">
+      <c r="G70" t="s">
         <v>108</v>
       </c>
-      <c r="H70" s="121">
-        <f t="shared" si="3"/>
+      <c r="H70" s="111">
+        <f t="shared" si="7"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I70" s="121">
-        <f t="shared" si="2"/>
+      <c r="I70" s="111">
+        <f t="shared" si="6"/>
         <v>87.693332552144369</v>
       </c>
-      <c r="J70" s="121">
-        <f>I70</f>
+      <c r="J70" s="111">
+        <f t="shared" si="5"/>
         <v>87.693332552144369</v>
       </c>
-      <c r="K70" s="122"/>
+      <c r="K70" s="112"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
@@ -35396,31 +35335,31 @@
         <v>105</v>
       </c>
       <c r="C71" s="6"/>
-      <c r="D71" s="9" t="s">
+      <c r="D71" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" t="s">
         <v>114</v>
       </c>
-      <c r="F71" s="120">
+      <c r="F71">
         <v>5</v>
       </c>
-      <c r="G71" s="8" t="s">
+      <c r="G71" t="s">
         <v>108</v>
       </c>
-      <c r="H71" s="121">
-        <f t="shared" si="3"/>
+      <c r="H71" s="111">
+        <f t="shared" si="7"/>
         <v>43.846666276072185</v>
       </c>
-      <c r="I71" s="121">
-        <f t="shared" si="2"/>
+      <c r="I71" s="111">
+        <f t="shared" si="6"/>
         <v>219.23333138036094</v>
       </c>
-      <c r="J71" s="121">
-        <f>I71</f>
+      <c r="J71" s="111">
+        <f t="shared" si="5"/>
         <v>219.23333138036094</v>
       </c>
-      <c r="K71" s="122"/>
+      <c r="K71" s="112"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
@@ -35428,78 +35367,78 @@
         <v>106</v>
       </c>
       <c r="C72" s="6"/>
-      <c r="D72" s="9" t="s">
+      <c r="D72" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" t="s">
         <v>109</v>
       </c>
-      <c r="F72" s="120">
+      <c r="F72">
         <v>1</v>
       </c>
-      <c r="G72" s="8" t="s">
+      <c r="G72" t="s">
         <v>108</v>
       </c>
-      <c r="H72" s="121">
-        <f t="shared" si="3"/>
+      <c r="H72" s="111">
+        <f t="shared" si="7"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I72" s="121">
-        <f t="shared" si="2"/>
+      <c r="I72" s="111">
+        <f t="shared" si="6"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J72" s="121">
-        <f>I72</f>
+      <c r="J72" s="111">
+        <f t="shared" si="5"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="K72" s="122"/>
+      <c r="K72" s="112"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12" t="s">
+      <c r="A73" s="8"/>
+      <c r="B73" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C73" s="12"/>
-      <c r="D73" s="13" t="s">
+      <c r="C73" s="9"/>
+      <c r="D73" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="14" t="s">
+      <c r="E73" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="F73" s="14">
+      <c r="F73" s="11">
         <v>1</v>
       </c>
-      <c r="G73" s="14" t="s">
+      <c r="G73" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="H73" s="121">
-        <f t="shared" si="3"/>
+      <c r="H73" s="111">
+        <f t="shared" si="7"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I73" s="121">
-        <f t="shared" si="2"/>
+      <c r="I73" s="111">
+        <f t="shared" si="6"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J73" s="121">
-        <f>I73</f>
+      <c r="J73" s="111">
+        <f t="shared" si="5"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="K73" s="123"/>
+      <c r="K73" s="113"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" s="21" t="s">
+      <c r="A74" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="B74" s="22"/>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="22"/>
-      <c r="J74" s="22"/>
-      <c r="K74" s="124">
+      <c r="B74" s="120"/>
+      <c r="C74" s="120"/>
+      <c r="D74" s="120"/>
+      <c r="E74" s="120"/>
+      <c r="F74" s="120"/>
+      <c r="G74" s="120"/>
+      <c r="H74" s="120"/>
+      <c r="I74" s="120"/>
+      <c r="J74" s="120"/>
+      <c r="K74" s="114">
         <f>SUM(K3:K73)</f>
         <v>13383.612572529586</v>
       </c>
@@ -35514,7 +35453,7 @@
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D76" s="23" t="s">
+      <c r="D76" s="7" t="s">
         <v>110</v>
       </c>
       <c r="E76" t="s">
@@ -35523,7 +35462,7 @@
       <c r="J76" t="s">
         <v>197</v>
       </c>
-      <c r="K76" s="126">
+      <c r="K76" s="111">
         <f>K74*(1+K75)</f>
         <v>16729.515715661983</v>
       </c>
@@ -35532,7 +35471,7 @@
       <c r="D77" t="s">
         <v>109</v>
       </c>
-      <c r="E77" s="119">
+      <c r="E77" s="110">
         <f>'Company definition'!F82</f>
         <v>49.782125344774748</v>
       </c>
@@ -35541,7 +35480,7 @@
       <c r="D78" t="s">
         <v>112</v>
       </c>
-      <c r="E78" s="119">
+      <c r="E78" s="110">
         <f>'Company definition'!F85</f>
         <v>45.220459339114129</v>
       </c>
@@ -35550,7 +35489,7 @@
       <c r="D79" t="s">
         <v>111</v>
       </c>
-      <c r="E79" s="119">
+      <c r="E79" s="110">
         <f>'Company definition'!F84</f>
         <v>42.159269173306768</v>
       </c>
@@ -35559,7 +35498,7 @@
       <c r="D80" t="s">
         <v>113</v>
       </c>
-      <c r="E80" s="119">
+      <c r="E80" s="110">
         <f>'Company definition'!F86</f>
         <v>49.154057104913683</v>
       </c>
@@ -35568,7 +35507,7 @@
       <c r="D81" t="s">
         <v>114</v>
       </c>
-      <c r="E81" s="119">
+      <c r="E81" s="110">
         <f>'Company definition'!F87</f>
         <v>43.846666276072185</v>
       </c>
@@ -35577,7 +35516,7 @@
       <c r="D82" t="s">
         <v>115</v>
       </c>
-      <c r="E82" s="119">
+      <c r="E82" s="110">
         <f>'Company definition'!F88</f>
         <v>38.551814171883898</v>
       </c>

--- a/docs/budget.xlsx
+++ b/docs/budget.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Desktop\proyectos\IRBoard\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732CD243-55F3-4275-8CFA-D458AF68E204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FFC3930-7616-4036-A087-C25AF39D5A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Company definition" sheetId="2" r:id="rId1"/>
-    <sheet name="Costs" sheetId="1" r:id="rId2"/>
-    <sheet name="Final costs" sheetId="3" r:id="rId3"/>
+    <sheet name="Costs_init" sheetId="1" r:id="rId2"/>
+    <sheet name="Client_init" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="216">
   <si>
     <t>I1</t>
   </si>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>Resource</t>
-  </si>
-  <si>
-    <t>IrBoard costs breakdown</t>
   </si>
   <si>
     <t>Project management</t>
@@ -208,9 +205,6 @@
     <t xml:space="preserve">   Design user management</t>
   </si>
   <si>
-    <t xml:space="preserve">   Design document management and diagram modelling</t>
-  </si>
-  <si>
     <t>Set up SonarQube for Quality Assurance</t>
   </si>
   <si>
@@ -238,9 +232,6 @@
     <t xml:space="preserve">      Develop user management module</t>
   </si>
   <si>
-    <t xml:space="preserve">      Develop document management and Draw.io integration</t>
-  </si>
-  <si>
     <t xml:space="preserve">      Develop modifying concurrency system</t>
   </si>
   <si>
@@ -262,16 +253,10 @@
     <t xml:space="preserve">   Test user management module</t>
   </si>
   <si>
-    <t xml:space="preserve">   Test document management and Draw.io integration</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Test modifying concurrency system</t>
   </si>
   <si>
     <t xml:space="preserve">   Test search and filtering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Accesibility testing</t>
   </si>
   <si>
     <t xml:space="preserve">   Load testing</t>
@@ -628,19 +613,79 @@
     <t>Hourly  rate (without profit)</t>
   </si>
   <si>
-    <t>profits cut</t>
+    <t>Category 1: IrBoard development costs breakdown</t>
   </si>
   <si>
-    <t>customer's price</t>
+    <t>Category 2: Other</t>
   </si>
   <si>
-    <t>Original customer's price</t>
+    <t xml:space="preserve">   Usability and accesibility testing</t>
   </si>
   <si>
-    <t>Actual cost with profit</t>
+    <t xml:space="preserve">   Design document management </t>
   </si>
   <si>
-    <t>revenue lost</t>
+    <t xml:space="preserve">      Develop document management </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Test document management  </t>
+  </si>
+  <si>
+    <t>Travel and transportation expenses</t>
+  </si>
+  <si>
+    <t>Travel to client facilities (deployment/support)</t>
+  </si>
+  <si>
+    <t>Meals/daily allowance</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>meals</t>
+  </si>
+  <si>
+    <t>IrBoard costs</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Cat. Num</t>
+  </si>
+  <si>
+    <t>IrBoard development costs breakdown</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Profit (25%)</t>
+  </si>
+  <si>
+    <t>Simplified client budget</t>
+  </si>
+  <si>
+    <t>Detailed client budget</t>
+  </si>
+  <si>
+    <t>amount to be increased on the first category</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>with proportional increase</t>
+  </si>
+  <si>
+    <t>total hours</t>
+  </si>
+  <si>
+    <t>increase per hour</t>
   </si>
 </sst>
 </file>
@@ -736,7 +781,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1038,13 +1083,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1257,6 +1335,38 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1558,33 +1668,33 @@
   <sheetData>
     <row r="1" spans="1:316" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="59" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B1" s="109" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E1" s="108" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="107" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I1" s="106" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J1" s="106" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K1" s="105" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -1894,7 +2004,7 @@
     </row>
     <row r="2" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B2" s="64">
         <v>1</v>
@@ -1915,7 +2025,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K2" s="101">
         <f>D24</f>
@@ -2229,7 +2339,7 @@
     </row>
     <row r="3" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A3" s="32" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B3" s="67">
         <v>1</v>
@@ -2250,7 +2360,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K3" s="103">
         <f>B75</f>
@@ -2564,7 +2674,7 @@
     </row>
     <row r="4" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B4" s="64">
         <v>1</v>
@@ -2585,7 +2695,7 @@
         <v>3</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K4" s="101">
         <f>K2+K3</f>
@@ -2899,7 +3009,7 @@
     </row>
     <row r="5" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A5" s="32" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B5" s="67">
         <v>1</v>
@@ -2920,7 +3030,7 @@
         <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="J5" s="104">
         <v>0.25</v>
@@ -3237,7 +3347,7 @@
     </row>
     <row r="6" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="29" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B6" s="64">
         <v>1</v>
@@ -3258,7 +3368,7 @@
         <v>5</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K6" s="101">
         <f>K4+K5</f>
@@ -3572,7 +3682,7 @@
     </row>
     <row r="7" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B7" s="67">
         <v>1</v>
@@ -3593,7 +3703,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="K7" s="99">
         <f>E90</f>
@@ -3907,7 +4017,7 @@
     </row>
     <row r="8" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="29" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B8" s="64">
         <v>2</v>
@@ -3928,7 +4038,7 @@
         <v>7</v>
       </c>
       <c r="I8" s="97" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="J8" s="97"/>
       <c r="K8" s="96">
@@ -4243,7 +4353,7 @@
     </row>
     <row r="9" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B9" s="67">
         <v>4</v>
@@ -4568,7 +4678,7 @@
     </row>
     <row r="10" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="29" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B10" s="64">
         <v>1</v>
@@ -4897,7 +5007,7 @@
     </row>
     <row r="11" spans="1:316" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="95" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B11" s="94">
         <f>SUM(B2:B10)</f>
@@ -5841,22 +5951,22 @@
     </row>
     <row r="14" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="81" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B14" s="92" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C14" s="74" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D14" s="92" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E14" s="74" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F14" s="91" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G14"/>
       <c r="H14"/>
@@ -6171,7 +6281,7 @@
     </row>
     <row r="15" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A15" s="32" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B15" s="31">
         <f t="shared" ref="B15:B23" si="1">D2</f>
@@ -6500,7 +6610,7 @@
     </row>
     <row r="16" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="29" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B16" s="28">
         <f t="shared" si="1"/>
@@ -6834,7 +6944,7 @@
     </row>
     <row r="17" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A17" s="32" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B17" s="31">
         <f t="shared" si="1"/>
@@ -7163,7 +7273,7 @@
     </row>
     <row r="18" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="29" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B18" s="28">
         <f t="shared" si="1"/>
@@ -7497,7 +7607,7 @@
     </row>
     <row r="19" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A19" s="32" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B19" s="31">
         <f t="shared" si="1"/>
@@ -7826,7 +7936,7 @@
     </row>
     <row r="20" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="29" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B20" s="28">
         <f t="shared" si="1"/>
@@ -8160,7 +8270,7 @@
     </row>
     <row r="21" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B21" s="31">
         <f t="shared" si="1"/>
@@ -8489,7 +8599,7 @@
     </row>
     <row r="22" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="29" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B22" s="28">
         <f t="shared" si="1"/>
@@ -8823,7 +8933,7 @@
     </row>
     <row r="23" spans="1:316" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="24" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B23" s="23">
         <f t="shared" si="1"/>
@@ -9152,7 +9262,7 @@
     </row>
     <row r="24" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="19" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B24" s="83">
         <f>SUM(B15:B23)</f>
@@ -9791,13 +9901,13 @@
     </row>
     <row r="26" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="81" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B26" s="74" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C26" s="73" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -10115,7 +10225,7 @@
     </row>
     <row r="27" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A27" s="79" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B27" s="68">
         <v>850</v>
@@ -10432,7 +10542,7 @@
     </row>
     <row r="28" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="80" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B28" s="65">
         <v>800</v>
@@ -10757,7 +10867,7 @@
     </row>
     <row r="29" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A29" s="79" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B29" s="68">
         <v>550</v>
@@ -11074,7 +11184,7 @@
     </row>
     <row r="30" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="80" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B30" s="65">
         <v>400</v>
@@ -11399,7 +11509,7 @@
     </row>
     <row r="31" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A31" s="79" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B31" s="68">
         <v>120</v>
@@ -11716,7 +11826,7 @@
     </row>
     <row r="32" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="80" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B32" s="65">
         <v>1350</v>
@@ -12041,7 +12151,7 @@
     </row>
     <row r="33" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A33" s="79" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B33" s="68">
         <v>900</v>
@@ -12358,7 +12468,7 @@
     </row>
     <row r="34" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="80" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B34" s="65">
         <v>140</v>
@@ -12683,7 +12793,7 @@
     </row>
     <row r="35" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A35" s="79" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B35" s="68">
         <v>120</v>
@@ -13000,7 +13110,7 @@
     </row>
     <row r="36" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="80" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B36" s="65">
         <v>120</v>
@@ -13325,7 +13435,7 @@
     </row>
     <row r="37" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A37" s="79" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B37" s="68">
         <v>180</v>
@@ -13642,7 +13752,7 @@
     </row>
     <row r="38" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="80" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B38" s="65">
         <v>55</v>
@@ -13967,7 +14077,7 @@
     </row>
     <row r="39" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A39" s="79" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B39" s="68">
         <v>400</v>
@@ -14284,7 +14394,7 @@
     </row>
     <row r="40" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="80" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B40" s="65">
         <v>300</v>
@@ -14609,7 +14719,7 @@
     </row>
     <row r="41" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A41" s="79" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B41" s="68">
         <v>150</v>
@@ -14926,7 +15036,7 @@
     </row>
     <row r="42" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="80" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B42" s="65">
         <v>500</v>
@@ -15251,7 +15361,7 @@
     </row>
     <row r="43" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A43" s="79" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B43" s="68">
         <v>350</v>
@@ -15568,7 +15678,7 @@
     </row>
     <row r="44" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="80" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B44" s="65">
         <v>300</v>
@@ -15893,7 +16003,7 @@
     </row>
     <row r="45" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A45" s="79" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B45" s="68">
         <v>200</v>
@@ -16210,7 +16320,7 @@
     </row>
     <row r="46" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="80" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B46" s="65">
         <v>50</v>
@@ -16535,7 +16645,7 @@
     </row>
     <row r="47" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A47" s="79" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B47" s="68">
         <v>150</v>
@@ -16852,7 +16962,7 @@
     </row>
     <row r="48" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="80" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B48" s="65">
         <v>250</v>
@@ -17177,7 +17287,7 @@
     </row>
     <row r="49" spans="1:316" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="79" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B49" s="68">
         <v>685</v>
@@ -18128,7 +18238,7 @@
     </row>
     <row r="52" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="74" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B52" s="74" t="s">
         <v>17</v>
@@ -18137,16 +18247,16 @@
         <v>18</v>
       </c>
       <c r="D52" s="74" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E52" s="74" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F52" s="74" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G52" s="73" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="H52"/>
       <c r="I52"/>
@@ -18460,7 +18570,7 @@
     </row>
     <row r="53" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A53" s="32" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B53" s="67">
         <v>1</v>
@@ -18477,7 +18587,7 @@
         <v>8000</v>
       </c>
       <c r="F53" s="67" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G53" s="66"/>
       <c r="L53" s="4"/>
@@ -18788,7 +18898,7 @@
     </row>
     <row r="54" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="29" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B54" s="64">
         <v>3</v>
@@ -18805,7 +18915,7 @@
         <v>750</v>
       </c>
       <c r="F54" s="70" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G54" s="69">
         <v>4</v>
@@ -19122,7 +19232,7 @@
     </row>
     <row r="55" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A55" s="32" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B55" s="67">
         <v>6</v>
@@ -19139,7 +19249,7 @@
         <v>2100</v>
       </c>
       <c r="F55" s="72" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G55" s="71">
         <v>4</v>
@@ -19452,7 +19562,7 @@
     </row>
     <row r="56" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="29" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B56" s="64">
         <v>5</v>
@@ -19469,7 +19579,7 @@
         <v>1875</v>
       </c>
       <c r="F56" s="70" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G56" s="69">
         <v>4</v>
@@ -19786,7 +19896,7 @@
     </row>
     <row r="57" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A57" s="32" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B57" s="67">
         <v>10</v>
@@ -19803,7 +19913,7 @@
         <v>2000</v>
       </c>
       <c r="F57" s="67" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G57" s="66"/>
       <c r="L57" s="4"/>
@@ -20114,7 +20224,7 @@
     </row>
     <row r="58" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="29" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B58" s="64">
         <v>1</v>
@@ -20131,7 +20241,7 @@
         <v>99</v>
       </c>
       <c r="F58" s="64" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G58" s="40"/>
       <c r="H58"/>
@@ -20446,7 +20556,7 @@
     </row>
     <row r="59" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A59" s="32" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B59" s="67">
         <v>1</v>
@@ -20463,7 +20573,7 @@
         <v>25</v>
       </c>
       <c r="F59" s="67" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G59" s="66"/>
       <c r="L59" s="4"/>
@@ -20774,7 +20884,7 @@
     </row>
     <row r="60" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="29" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B60" s="64">
         <v>14</v>
@@ -20791,7 +20901,7 @@
         <v>1680</v>
       </c>
       <c r="F60" s="64" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G60" s="40"/>
       <c r="H60"/>
@@ -21742,19 +21852,19 @@
     </row>
     <row r="63" spans="1:316" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A63" s="59" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B63" s="58" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C63" s="58" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D63" s="58" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E63" s="57" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
@@ -22064,7 +22174,7 @@
     </row>
     <row r="64" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="29" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B64" s="56">
         <f t="shared" ref="B64:B72" si="7">C15</f>
@@ -22390,7 +22500,7 @@
     </row>
     <row r="65" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A65" s="32" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B65" s="52">
         <f t="shared" si="7"/>
@@ -22715,7 +22825,7 @@
     </row>
     <row r="66" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="29" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B66" s="56">
         <f t="shared" si="7"/>
@@ -23046,7 +23156,7 @@
     </row>
     <row r="67" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A67" s="32" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B67" s="52">
         <f t="shared" si="7"/>
@@ -23371,7 +23481,7 @@
     </row>
     <row r="68" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="29" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B68" s="56">
         <f t="shared" si="7"/>
@@ -23702,7 +23812,7 @@
     </row>
     <row r="69" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A69" s="32" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B69" s="52">
         <f t="shared" si="7"/>
@@ -24027,7 +24137,7 @@
     </row>
     <row r="70" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="29" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B70" s="56">
         <f t="shared" si="7"/>
@@ -24358,7 +24468,7 @@
     </row>
     <row r="71" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A71" s="32" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B71" s="52">
         <f t="shared" si="7"/>
@@ -24683,7 +24793,7 @@
     </row>
     <row r="72" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="38" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B72" s="49">
         <f t="shared" si="7"/>
@@ -25009,7 +25119,7 @@
     </row>
     <row r="73" spans="1:316" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="46" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B73" s="45"/>
       <c r="C73" s="45"/>
@@ -25638,7 +25748,7 @@
     </row>
     <row r="75" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A75" s="42" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B75" s="41">
         <f>E61+C50+F24</f>
@@ -25955,7 +26065,7 @@
     </row>
     <row r="76" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="29" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B76" s="40">
         <f>SUMIFS(B2:B10,C15:C23,"&gt;0")</f>
@@ -26278,7 +26388,7 @@
     </row>
     <row r="77" spans="1:316" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="32" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B77" s="39">
         <f>IFERROR(B75/B76,"sin valor")</f>
@@ -26592,7 +26702,7 @@
     </row>
     <row r="78" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="38" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B78" s="37">
         <f>B77*(1+J5)</f>
@@ -27228,22 +27338,22 @@
     </row>
     <row r="80" spans="1:316" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A80" s="36" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B80" s="34" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D80" s="35" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E80" s="34" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F80" s="33" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G80"/>
       <c r="H80"/>
@@ -27558,7 +27668,7 @@
     </row>
     <row r="81" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A81" s="32" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B81" s="31">
         <f t="shared" ref="B81:B89" si="10">IFERROR($D15/$D64,0)</f>
@@ -27887,7 +27997,7 @@
     </row>
     <row r="82" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="29" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B82" s="28">
         <f t="shared" si="10"/>
@@ -28222,7 +28332,7 @@
     </row>
     <row r="83" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A83" s="32" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B83" s="31">
         <f t="shared" si="10"/>
@@ -28551,7 +28661,7 @@
     </row>
     <row r="84" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="29" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B84" s="28">
         <f t="shared" si="10"/>
@@ -28886,7 +28996,7 @@
     </row>
     <row r="85" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A85" s="32" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B85" s="31">
         <f t="shared" si="10"/>
@@ -29215,7 +29325,7 @@
     </row>
     <row r="86" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="29" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B86" s="28">
         <f t="shared" si="10"/>
@@ -29550,7 +29660,7 @@
     </row>
     <row r="87" spans="1:316" x14ac:dyDescent="0.3">
       <c r="A87" s="32" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B87" s="31">
         <f t="shared" si="10"/>
@@ -29879,7 +29989,7 @@
     </row>
     <row r="88" spans="1:316" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="29" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B88" s="28">
         <f t="shared" si="10"/>
@@ -30214,7 +30324,7 @@
     </row>
     <row r="89" spans="1:316" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="24" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B89" s="23">
         <f t="shared" si="10"/>
@@ -30543,7 +30653,7 @@
     </row>
     <row r="90" spans="1:316" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="19" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B90" s="18"/>
       <c r="C90" s="18"/>
@@ -30879,7 +30989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:R82"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -30890,11 +31000,17 @@
     <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="116" t="s">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="B1" s="117"/>
       <c r="C1" s="117"/>
@@ -30906,8 +31022,16 @@
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
       <c r="K1" s="118"/>
+      <c r="L1" s="140" t="s">
+        <v>213</v>
+      </c>
+      <c r="N1" s="119" t="s">
+        <v>203</v>
+      </c>
+      <c r="O1" s="120"/>
+      <c r="P1" s="132"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -30941,18 +31065,28 @@
       <c r="K2" s="14" t="s">
         <v>4</v>
       </c>
+      <c r="L2" s="137"/>
+      <c r="N2" s="130" t="s">
+        <v>205</v>
+      </c>
+      <c r="O2" s="129" t="s">
+        <v>204</v>
+      </c>
+      <c r="P2" s="131" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3" s="111" t="str">
-        <f>_xlfn.XLOOKUP(E3,$D$77:$D$82,$E$77:$E$82,"")</f>
+        <f>_xlfn.XLOOKUP(E3,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v/>
       </c>
       <c r="I3" s="111" t="str">
@@ -30963,27 +31097,41 @@
         <f>SUM(J4:J19)</f>
         <v>1493.463760343242</v>
       </c>
+      <c r="L3" s="139" t="str">
+        <f>IFERROR(I3+($P$10*F3),"")</f>
+        <v/>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" s="125" t="s">
+        <v>206</v>
+      </c>
+      <c r="P3" s="133">
+        <f>K74</f>
+        <v>13026.517352669423</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H4" s="111">
-        <f>_xlfn.XLOOKUP(E4,$D$77:$D$82,$E$77:$E$82,"")</f>
+        <f>_xlfn.XLOOKUP(E4,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I4" s="111">
@@ -30995,27 +31143,41 @@
         <v>99.564250689549496</v>
       </c>
       <c r="K4" s="112"/>
+      <c r="L4" s="139">
+        <f t="shared" ref="L4:L67" si="1">IFERROR(I4+($P$10*F4),"")</f>
+        <v>122.72425068954949</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="125" t="s">
+        <v>207</v>
+      </c>
+      <c r="P4" s="133">
+        <f>K81</f>
+        <v>172.5</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H5" s="111">
-        <f t="shared" ref="H5:H68" si="1">_xlfn.XLOOKUP(E5,$D$77:$D$82,$E$77:$E$82,"")</f>
+        <f>_xlfn.XLOOKUP(E5,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I5" s="111">
@@ -31027,18 +31189,32 @@
         <v>99.564250689549496</v>
       </c>
       <c r="K5" s="112"/>
+      <c r="L5" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="125" t="s">
+        <v>208</v>
+      </c>
+      <c r="P5" s="112">
+        <f>0.25*(P3+P4)</f>
+        <v>3299.7543381673559</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H6" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E6,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v/>
       </c>
       <c r="I6" s="111" t="str">
@@ -31050,27 +31226,36 @@
         <v>1294.3352589641431</v>
       </c>
       <c r="K6" s="112"/>
+      <c r="L6" s="139"/>
+      <c r="N6" s="119" t="s">
+        <v>115</v>
+      </c>
+      <c r="O6" s="120"/>
+      <c r="P6" s="134">
+        <f>SUM(P3:P5)</f>
+        <v>16498.77169083678</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H7" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E7,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I7" s="111">
@@ -31079,27 +31264,31 @@
       </c>
       <c r="J7" s="111"/>
       <c r="K7" s="112"/>
+      <c r="L7" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H8" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E8,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I8" s="111">
@@ -31108,27 +31297,38 @@
       </c>
       <c r="J8" s="111"/>
       <c r="K8" s="112"/>
+      <c r="L8" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
+      <c r="O8" t="s">
+        <v>211</v>
+      </c>
+      <c r="P8" s="111">
+        <f>P6-P3</f>
+        <v>3472.2543381673568</v>
+      </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H9" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E9,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I9" s="111">
@@ -31137,27 +31337,38 @@
       </c>
       <c r="J9" s="111"/>
       <c r="K9" s="112"/>
+      <c r="L9" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
+      <c r="O9" t="s">
+        <v>214</v>
+      </c>
+      <c r="P9" s="136">
+        <f>SUM(F4:F73)</f>
+        <v>300</v>
+      </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H10" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E10,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I10" s="111">
@@ -31166,27 +31377,38 @@
       </c>
       <c r="J10" s="111"/>
       <c r="K10" s="112"/>
+      <c r="L10" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
+      <c r="O10" t="s">
+        <v>215</v>
+      </c>
+      <c r="P10" s="136">
+        <f>ROUNDUP(P8/P9,2)</f>
+        <v>11.58</v>
+      </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H11" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E11,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I11" s="111">
@@ -31195,27 +31417,31 @@
       </c>
       <c r="J11" s="111"/>
       <c r="K11" s="112"/>
+      <c r="L11" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H12" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E12,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I12" s="111">
@@ -31224,27 +31450,31 @@
       </c>
       <c r="J12" s="111"/>
       <c r="K12" s="112"/>
+      <c r="L12" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H13" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E13,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I13" s="111">
@@ -31253,27 +31483,31 @@
       </c>
       <c r="J13" s="111"/>
       <c r="K13" s="112"/>
+      <c r="L13" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H14" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E14,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I14" s="111">
@@ -31282,27 +31516,31 @@
       </c>
       <c r="J14" s="111"/>
       <c r="K14" s="112"/>
+      <c r="L14" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H15" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E15,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I15" s="111">
@@ -31311,27 +31549,31 @@
       </c>
       <c r="J15" s="111"/>
       <c r="K15" s="112"/>
+      <c r="L15" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H16" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E16,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I16" s="111">
@@ -31340,27 +31582,31 @@
       </c>
       <c r="J16" s="111"/>
       <c r="K16" s="112"/>
+      <c r="L16" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H17" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E17,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I17" s="111">
@@ -31369,27 +31615,31 @@
       </c>
       <c r="J17" s="111"/>
       <c r="K17" s="112"/>
+      <c r="L17" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F18">
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H18" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E18,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I18" s="111">
@@ -31398,27 +31648,31 @@
       </c>
       <c r="J18" s="111"/>
       <c r="K18" s="112"/>
+      <c r="L18" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F19">
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H19" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E19,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I19" s="111">
@@ -31427,18 +31681,28 @@
       </c>
       <c r="J19" s="111"/>
       <c r="K19" s="112"/>
+      <c r="L19" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="R19" t="s">
+        <v>190</v>
+      </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H20" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E20,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v/>
       </c>
       <c r="I20" s="111" t="str">
@@ -31450,27 +31714,38 @@
         <f>SUM(J21:J30)</f>
         <v>2307.2124370166389</v>
       </c>
+      <c r="L20" s="139" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R20" s="110">
+        <f>'Company definition'!F82</f>
+        <v>49.782125344774748</v>
+      </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H21" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E21,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>42.159269173306768</v>
       </c>
       <c r="I21" s="111">
@@ -31482,27 +31757,38 @@
         <v>42.159269173306768</v>
       </c>
       <c r="K21" s="112"/>
+      <c r="L21" s="139">
+        <f t="shared" si="1"/>
+        <v>53.739269173306766</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>107</v>
+      </c>
+      <c r="R21" s="110">
+        <f>'Company definition'!F85</f>
+        <v>45.220459339114129</v>
+      </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F22">
         <v>4</v>
       </c>
       <c r="G22" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H22" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E22,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>45.220459339114129</v>
       </c>
       <c r="I22" s="111">
@@ -31514,27 +31800,38 @@
         <v>180.88183735645651</v>
       </c>
       <c r="K22" s="112"/>
+      <c r="L22" s="139">
+        <f t="shared" si="1"/>
+        <v>227.20183735645651</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>106</v>
+      </c>
+      <c r="R22" s="110">
+        <f>'Company definition'!F84</f>
+        <v>42.159269173306768</v>
+      </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F23">
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H23" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E23,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>42.159269173306768</v>
       </c>
       <c r="I23" s="111">
@@ -31546,27 +31843,38 @@
         <v>84.318538346613536</v>
       </c>
       <c r="K23" s="112"/>
+      <c r="L23" s="139">
+        <f t="shared" si="1"/>
+        <v>107.47853834661353</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>108</v>
+      </c>
+      <c r="R23" s="110">
+        <f>'Company definition'!F86</f>
+        <v>49.154057104913683</v>
+      </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H24" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E24,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>42.159269173306768</v>
       </c>
       <c r="I24" s="111">
@@ -31578,27 +31886,38 @@
         <v>42.159269173306768</v>
       </c>
       <c r="K24" s="112"/>
+      <c r="L24" s="139">
+        <f t="shared" si="1"/>
+        <v>53.739269173306766</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>109</v>
+      </c>
+      <c r="R24" s="110">
+        <f>'Company definition'!F87</f>
+        <v>43.846666276072185</v>
+      </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F25">
         <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H25" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E25,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>42.159269173306768</v>
       </c>
       <c r="I25" s="111">
@@ -31610,27 +31929,38 @@
         <v>84.318538346613536</v>
       </c>
       <c r="K25" s="112"/>
+      <c r="L25" s="139">
+        <f t="shared" si="1"/>
+        <v>107.47853834661353</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>110</v>
+      </c>
+      <c r="R25" s="110">
+        <f>'Company definition'!F88</f>
+        <v>38.551814171883898</v>
+      </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F26">
         <v>6</v>
       </c>
       <c r="G26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H26" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E26,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>45.220459339114129</v>
       </c>
       <c r="I26" s="111">
@@ -31642,27 +31972,31 @@
         <v>271.32275603468474</v>
       </c>
       <c r="K26" s="112"/>
+      <c r="L26" s="139">
+        <f t="shared" si="1"/>
+        <v>340.80275603468476</v>
+      </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F27">
         <v>22</v>
       </c>
       <c r="G27" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H27" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E27,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>42.159269173306768</v>
       </c>
       <c r="I27" s="111">
@@ -31674,27 +32008,31 @@
         <v>927.5039218127489</v>
       </c>
       <c r="K27" s="112"/>
+      <c r="L27" s="139">
+        <f t="shared" si="1"/>
+        <v>1182.2639218127488</v>
+      </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F28">
         <v>6</v>
       </c>
       <c r="G28" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H28" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E28,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>42.159269173306768</v>
       </c>
       <c r="I28" s="111">
@@ -31706,27 +32044,31 @@
         <v>252.95561503984061</v>
       </c>
       <c r="K28" s="112"/>
+      <c r="L28" s="139">
+        <f t="shared" si="1"/>
+        <v>322.43561503984063</v>
+      </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F29">
         <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H29" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E29,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>42.159269173306768</v>
       </c>
       <c r="I29" s="111">
@@ -31738,27 +32080,31 @@
         <v>84.318538346613536</v>
       </c>
       <c r="K29" s="112"/>
+      <c r="L29" s="139">
+        <f t="shared" si="1"/>
+        <v>107.47853834661353</v>
+      </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F30">
         <v>8</v>
       </c>
       <c r="G30" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H30" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E30,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>42.159269173306768</v>
       </c>
       <c r="I30" s="111">
@@ -31770,18 +32116,22 @@
         <v>337.27415338645415</v>
       </c>
       <c r="K30" s="112"/>
+      <c r="L30" s="139">
+        <f t="shared" si="1"/>
+        <v>429.91415338645413</v>
+      </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H31" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E31,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v/>
       </c>
       <c r="I31" s="111" t="str">
@@ -31793,27 +32143,31 @@
         <f>SUM(J32:J38)</f>
         <v>2273.3693320555312</v>
       </c>
+      <c r="L31" s="139" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F32">
         <v>10</v>
       </c>
       <c r="G32" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H32" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E32,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.154057104913683</v>
       </c>
       <c r="I32" s="111">
@@ -31825,27 +32179,31 @@
         <v>491.54057104913682</v>
       </c>
       <c r="K32" s="112"/>
+      <c r="L32" s="139">
+        <f t="shared" si="1"/>
+        <v>607.34057104913677</v>
+      </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E33" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F33">
         <v>3</v>
       </c>
       <c r="G33" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H33" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E33,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I33" s="111">
@@ -31857,27 +32215,31 @@
         <v>115.65544251565169</v>
       </c>
       <c r="K33" s="112"/>
+      <c r="L33" s="139">
+        <f t="shared" si="1"/>
+        <v>150.39544251565169</v>
+      </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E34" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F34">
         <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H34" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E34,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I34" s="111">
@@ -31889,27 +32251,31 @@
         <v>350.77333020857748</v>
       </c>
       <c r="K34" s="112"/>
+      <c r="L34" s="139">
+        <f t="shared" si="1"/>
+        <v>443.41333020857746</v>
+      </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E35" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F35">
         <v>4</v>
       </c>
       <c r="G35" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H35" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E35,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I35" s="111">
@@ -31921,27 +32287,31 @@
         <v>175.38666510428874</v>
       </c>
       <c r="K35" s="112"/>
+      <c r="L35" s="139">
+        <f t="shared" si="1"/>
+        <v>221.70666510428873</v>
+      </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F36">
         <v>6</v>
       </c>
       <c r="G36" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H36" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E36,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I36" s="111">
@@ -31953,27 +32323,31 @@
         <v>263.07999765643308</v>
       </c>
       <c r="K36" s="112"/>
+      <c r="L36" s="139">
+        <f t="shared" si="1"/>
+        <v>332.5599976564331</v>
+      </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E37" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F37">
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H37" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E37,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I37" s="111">
@@ -31985,27 +32359,31 @@
         <v>438.46666276072187</v>
       </c>
       <c r="K37" s="112"/>
+      <c r="L37" s="139">
+        <f t="shared" si="1"/>
+        <v>554.26666276072183</v>
+      </c>
     </row>
-    <row r="38" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="1" t="s">
-        <v>56</v>
+        <v>194</v>
       </c>
       <c r="E38" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F38">
         <v>10</v>
       </c>
       <c r="G38" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H38" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E38,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I38" s="111">
@@ -32017,27 +32395,31 @@
         <v>438.46666276072187</v>
       </c>
       <c r="K38" s="112"/>
+      <c r="L38" s="139">
+        <f t="shared" si="1"/>
+        <v>554.26666276072183</v>
+      </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E39" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F39">
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H39" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E39,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I39" s="111">
@@ -32052,18 +32434,22 @@
         <f>SUM(J39)</f>
         <v>131.53999882821654</v>
       </c>
+      <c r="L39" s="139">
+        <f t="shared" si="1"/>
+        <v>166.27999882821655</v>
+      </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H40" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E40,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v/>
       </c>
       <c r="I40" s="111" t="str">
@@ -32075,27 +32461,31 @@
         <f>SUM(J41:J50)</f>
         <v>4386.8987937884322</v>
       </c>
+      <c r="L40" s="139" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E41" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F41">
         <v>4</v>
       </c>
       <c r="G41" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H41" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E41,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.154057104913683</v>
       </c>
       <c r="I41" s="111">
@@ -32107,27 +32497,31 @@
         <v>196.61622841965473</v>
       </c>
       <c r="K41" s="112"/>
+      <c r="L41" s="139">
+        <f t="shared" si="1"/>
+        <v>242.93622841965473</v>
+      </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E42" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F42">
         <v>3</v>
       </c>
       <c r="G42" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H42" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E42,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.154057104913683</v>
       </c>
       <c r="I42" s="111">
@@ -32139,18 +32533,22 @@
         <v>147.46217131474106</v>
       </c>
       <c r="K42" s="112"/>
+      <c r="L42" s="139">
+        <f t="shared" si="1"/>
+        <v>182.20217131474107</v>
+      </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H43" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E43,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v/>
       </c>
       <c r="I43" s="111" t="str">
@@ -32162,27 +32560,31 @@
         <v>4042.8203940540366</v>
       </c>
       <c r="K43" s="112"/>
+      <c r="L43" s="139" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E44" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F44">
         <v>22</v>
       </c>
       <c r="G44" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H44" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E44,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I44" s="111">
@@ -32191,27 +32593,31 @@
       </c>
       <c r="J44" s="111"/>
       <c r="K44" s="112"/>
+      <c r="L44" s="139">
+        <f t="shared" si="1"/>
+        <v>1102.8999117814458</v>
+      </c>
     </row>
-    <row r="45" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E45" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F45">
         <v>10</v>
       </c>
       <c r="G45" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H45" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E45,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I45" s="111">
@@ -32220,27 +32626,31 @@
       </c>
       <c r="J45" s="111"/>
       <c r="K45" s="112"/>
+      <c r="L45" s="139">
+        <f t="shared" si="1"/>
+        <v>501.318141718839</v>
+      </c>
     </row>
-    <row r="46" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E46" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F46">
         <v>25</v>
       </c>
       <c r="G46" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H46" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E46,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I46" s="111">
@@ -32249,27 +32659,31 @@
       </c>
       <c r="J46" s="111"/>
       <c r="K46" s="112"/>
+      <c r="L46" s="139">
+        <f t="shared" si="1"/>
+        <v>1385.6666569018046</v>
+      </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E47" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F47">
         <v>6</v>
       </c>
       <c r="G47" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H47" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E47,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I47" s="111">
@@ -32278,27 +32692,31 @@
       </c>
       <c r="J47" s="111"/>
       <c r="K47" s="112"/>
+      <c r="L47" s="139">
+        <f t="shared" si="1"/>
+        <v>300.79088503130339</v>
+      </c>
     </row>
-    <row r="48" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="E48" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F48">
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H48" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E48,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I48" s="111">
@@ -32307,27 +32725,31 @@
       </c>
       <c r="J48" s="111"/>
       <c r="K48" s="112"/>
+      <c r="L48" s="139">
+        <f t="shared" si="1"/>
+        <v>831.39999414108274</v>
+      </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E49" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F49">
         <v>10</v>
       </c>
       <c r="G49" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H49" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E49,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I49" s="111">
@@ -32336,27 +32758,31 @@
       </c>
       <c r="J49" s="111"/>
       <c r="K49" s="112"/>
+      <c r="L49" s="139">
+        <f t="shared" si="1"/>
+        <v>554.26666276072183</v>
+      </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E50" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F50">
         <v>10</v>
       </c>
       <c r="G50" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H50" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E50,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I50" s="111">
@@ -32365,18 +32791,22 @@
       </c>
       <c r="J50" s="111"/>
       <c r="K50" s="112"/>
+      <c r="L50" s="139">
+        <f t="shared" si="1"/>
+        <v>501.318141718839</v>
+      </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H51" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E51,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v/>
       </c>
       <c r="I51" s="111" t="str">
@@ -32388,27 +32818,31 @@
         <f>SUM(J52:J60)</f>
         <v>1051.4886868492417</v>
       </c>
+      <c r="L51" s="139" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E52" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F52">
         <v>4</v>
       </c>
       <c r="G52" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H52" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E52,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I52" s="111">
@@ -32420,27 +32854,31 @@
         <v>154.20725668753559</v>
       </c>
       <c r="K52" s="112"/>
+      <c r="L52" s="139">
+        <f t="shared" si="1"/>
+        <v>200.52725668753558</v>
+      </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E53" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F53">
         <v>3</v>
       </c>
       <c r="G53" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H53" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E53,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I53" s="111">
@@ -32452,27 +32890,31 @@
         <v>115.65544251565169</v>
       </c>
       <c r="K53" s="112"/>
+      <c r="L53" s="139">
+        <f t="shared" si="1"/>
+        <v>150.39544251565169</v>
+      </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E54" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F54">
         <v>5</v>
       </c>
       <c r="G54" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H54" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E54,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I54" s="111">
@@ -32484,27 +32926,31 @@
         <v>192.7590708594195</v>
       </c>
       <c r="K54" s="112"/>
+      <c r="L54" s="139">
+        <f t="shared" si="1"/>
+        <v>250.6590708594195</v>
+      </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C55" s="6"/>
       <c r="D55" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E55" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F55">
         <v>3</v>
       </c>
       <c r="G55" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H55" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E55,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I55" s="111">
@@ -32516,27 +32962,31 @@
         <v>115.65544251565169</v>
       </c>
       <c r="K55" s="112"/>
+      <c r="L55" s="139">
+        <f t="shared" si="1"/>
+        <v>150.39544251565169</v>
+      </c>
     </row>
-    <row r="56" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="1" t="s">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="E56" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F56">
         <v>3</v>
       </c>
       <c r="G56" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H56" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E56,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I56" s="111">
@@ -32548,27 +32998,31 @@
         <v>115.65544251565169</v>
       </c>
       <c r="K56" s="112"/>
+      <c r="L56" s="139">
+        <f t="shared" si="1"/>
+        <v>150.39544251565169</v>
+      </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E57" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F57">
         <v>2</v>
       </c>
       <c r="G57" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H57" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E57,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I57" s="111">
@@ -32580,27 +33034,31 @@
         <v>77.103628343767795</v>
       </c>
       <c r="K57" s="112"/>
+      <c r="L57" s="139">
+        <f t="shared" si="1"/>
+        <v>100.26362834376779</v>
+      </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E58" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F58">
         <v>3</v>
       </c>
       <c r="G58" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H58" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E58,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I58" s="111">
@@ -32612,27 +33070,31 @@
         <v>115.65544251565169</v>
       </c>
       <c r="K58" s="112"/>
+      <c r="L58" s="139">
+        <f t="shared" si="1"/>
+        <v>150.39544251565169</v>
+      </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C59" s="6"/>
       <c r="D59" s="1" t="s">
-        <v>77</v>
+        <v>193</v>
       </c>
       <c r="E59" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F59">
         <v>2</v>
       </c>
       <c r="G59" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H59" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E59,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>38.551814171883898</v>
       </c>
       <c r="I59" s="111">
@@ -32644,27 +33106,31 @@
         <v>77.103628343767795</v>
       </c>
       <c r="K59" s="112"/>
+      <c r="L59" s="139">
+        <f t="shared" si="1"/>
+        <v>100.26362834376779</v>
+      </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E60" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F60">
         <v>2</v>
       </c>
       <c r="G60" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H60" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E60,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I60" s="111">
@@ -32676,18 +33142,22 @@
         <v>87.693332552144369</v>
       </c>
       <c r="K60" s="112"/>
+      <c r="L60" s="139">
+        <f t="shared" si="1"/>
+        <v>110.85333255214437</v>
+      </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H61" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E61,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v/>
       </c>
       <c r="I61" s="111" t="str">
@@ -32699,27 +33169,31 @@
         <f>SUM(J62:J73)</f>
         <v>1382.5443437881208</v>
       </c>
+      <c r="L61" s="139" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
-    <row r="62" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E62" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H62" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E62,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I62" s="111">
@@ -32731,27 +33205,31 @@
         <v>49.782125344774748</v>
       </c>
       <c r="K62" s="112"/>
+      <c r="L62" s="139">
+        <f t="shared" si="1"/>
+        <v>61.362125344774746</v>
+      </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E63" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H63" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E63,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I63" s="111">
@@ -32763,27 +33241,31 @@
         <v>49.782125344774748</v>
       </c>
       <c r="K63" s="112"/>
+      <c r="L63" s="139">
+        <f t="shared" si="1"/>
+        <v>61.362125344774746</v>
+      </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E64" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H64" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E64,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>45.220459339114129</v>
       </c>
       <c r="I64" s="111">
@@ -32795,27 +33277,31 @@
         <v>45.220459339114129</v>
       </c>
       <c r="K64" s="112"/>
+      <c r="L64" s="139">
+        <f t="shared" si="1"/>
+        <v>56.800459339114127</v>
+      </c>
     </row>
-    <row r="65" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C65" s="6"/>
       <c r="D65" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E65" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F65">
         <v>2</v>
       </c>
       <c r="G65" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H65" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E65,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>45.220459339114129</v>
       </c>
       <c r="I65" s="111">
@@ -32827,27 +33313,31 @@
         <v>90.440918678228257</v>
       </c>
       <c r="K65" s="112"/>
+      <c r="L65" s="139">
+        <f t="shared" si="1"/>
+        <v>113.60091867822825</v>
+      </c>
     </row>
-    <row r="66" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E66" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F66">
         <v>2</v>
       </c>
       <c r="G66" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H66" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E66,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I66" s="111">
@@ -32859,27 +33349,31 @@
         <v>99.564250689549496</v>
       </c>
       <c r="K66" s="112"/>
+      <c r="L66" s="139">
+        <f t="shared" si="1"/>
+        <v>122.72425068954949</v>
+      </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C67" s="6"/>
       <c r="D67" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E67" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F67">
         <v>3</v>
       </c>
       <c r="G67" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H67" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E67,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>42.159269173306768</v>
       </c>
       <c r="I67" s="111">
@@ -32891,27 +33385,31 @@
         <v>126.4778075199203</v>
       </c>
       <c r="K67" s="112"/>
+      <c r="L67" s="139">
+        <f t="shared" si="1"/>
+        <v>161.21780751992031</v>
+      </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E68" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F68">
         <v>5</v>
       </c>
       <c r="G68" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H68" s="111">
-        <f t="shared" si="1"/>
+        <f>_xlfn.XLOOKUP(E68,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.154057104913683</v>
       </c>
       <c r="I68" s="111">
@@ -32923,27 +33421,31 @@
         <v>245.77028552456841</v>
       </c>
       <c r="K68" s="112"/>
+      <c r="L68" s="139">
+        <f t="shared" ref="L68:L73" si="7">IFERROR(I68+($P$10*F68),"")</f>
+        <v>303.67028552456838</v>
+      </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C69" s="6"/>
       <c r="D69" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E69" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F69">
         <v>5</v>
       </c>
       <c r="G69" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H69" s="111">
-        <f t="shared" ref="H69:H73" si="7">_xlfn.XLOOKUP(E69,$D$77:$D$82,$E$77:$E$82,"")</f>
+        <f>_xlfn.XLOOKUP(E69,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I69" s="111">
@@ -32955,27 +33457,31 @@
         <v>219.23333138036094</v>
       </c>
       <c r="K69" s="112"/>
+      <c r="L69" s="139">
+        <f t="shared" si="7"/>
+        <v>277.13333138036091</v>
+      </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E70" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F70">
         <v>2</v>
       </c>
       <c r="G70" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H70" s="111">
-        <f t="shared" si="7"/>
+        <f>_xlfn.XLOOKUP(E70,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I70" s="111">
@@ -32987,27 +33493,31 @@
         <v>87.693332552144369</v>
       </c>
       <c r="K70" s="112"/>
+      <c r="L70" s="139">
+        <f t="shared" si="7"/>
+        <v>110.85333255214437</v>
+      </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C71" s="6"/>
       <c r="D71" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E71" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F71">
         <v>5</v>
       </c>
       <c r="G71" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H71" s="111">
-        <f t="shared" si="7"/>
+        <f>_xlfn.XLOOKUP(E71,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I71" s="111">
@@ -33019,27 +33529,31 @@
         <v>219.23333138036094</v>
       </c>
       <c r="K71" s="112"/>
+      <c r="L71" s="139">
+        <f t="shared" si="7"/>
+        <v>277.13333138036091</v>
+      </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E72" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F72">
         <v>2</v>
       </c>
       <c r="G72" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H72" s="111">
-        <f t="shared" si="7"/>
+        <f>_xlfn.XLOOKUP(E72,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I72" s="111">
@@ -33051,27 +33565,31 @@
         <v>99.564250689549496</v>
       </c>
       <c r="K72" s="112"/>
+      <c r="L72" s="139">
+        <f t="shared" si="7"/>
+        <v>122.72425068954949</v>
+      </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
       <c r="B73" s="9" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F73" s="11">
         <v>1</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H73" s="111">
-        <f t="shared" si="7"/>
+        <f>_xlfn.XLOOKUP(E73,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>49.782125344774748</v>
       </c>
       <c r="I73" s="111">
@@ -33083,8 +33601,12 @@
         <v>49.782125344774748</v>
       </c>
       <c r="K73" s="113"/>
+      <c r="L73" s="139">
+        <f t="shared" si="7"/>
+        <v>61.362125344774746</v>
+      </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="119" t="s">
         <v>4</v>
       </c>
@@ -33101,93 +33623,186 @@
         <f>SUM(K3:K73)</f>
         <v>13026.517352669423</v>
       </c>
+      <c r="L74" s="135">
+        <f>SUM(L3:L73)</f>
+        <v>16500.51735266942</v>
+      </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="J75" t="s">
-        <v>196</v>
-      </c>
-      <c r="K75" s="2">
-        <v>0.25</v>
-      </c>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D76" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E76" t="s">
-        <v>195</v>
-      </c>
-      <c r="J76" t="s">
+    <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="121" t="s">
+        <v>192</v>
+      </c>
+      <c r="B76" s="122"/>
+      <c r="C76" s="122"/>
+      <c r="D76" s="122"/>
+      <c r="E76" s="122"/>
+      <c r="F76" s="122"/>
+      <c r="G76" s="122"/>
+      <c r="H76" s="122"/>
+      <c r="I76" s="122"/>
+      <c r="J76" s="122"/>
+      <c r="K76" s="123"/>
+      <c r="L76" s="138"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J77" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="K77" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="L77" s="137"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78" s="124"/>
+      <c r="C78" s="124"/>
+      <c r="D78" s="125" t="s">
         <v>197</v>
       </c>
-      <c r="K76" s="111">
-        <f>K74*(1+K75)</f>
-        <v>16283.14669083678</v>
-      </c>
+      <c r="E78" s="125"/>
+      <c r="F78" s="125"/>
+      <c r="G78" s="125"/>
+      <c r="H78" s="127"/>
+      <c r="I78" s="127"/>
+      <c r="J78" s="127">
+        <f>SUM(I79:I80)</f>
+        <v>172.5</v>
+      </c>
+      <c r="K78" s="128">
+        <f>J78</f>
+        <v>172.5</v>
+      </c>
+      <c r="L78" s="127"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D77" t="s">
-        <v>109</v>
-      </c>
-      <c r="E77" s="110">
-        <f>'Company definition'!F82</f>
-        <v>49.782125344774748</v>
-      </c>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="5"/>
+      <c r="B79" s="124" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="124"/>
+      <c r="D79" s="125" t="s">
+        <v>198</v>
+      </c>
+      <c r="E79" s="125" t="s">
+        <v>200</v>
+      </c>
+      <c r="F79" s="125">
+        <v>150</v>
+      </c>
+      <c r="G79" s="126" t="s">
+        <v>201</v>
+      </c>
+      <c r="H79" s="127">
+        <v>0.35</v>
+      </c>
+      <c r="I79" s="127">
+        <f>H79*F79</f>
+        <v>52.5</v>
+      </c>
+      <c r="J79" s="127"/>
+      <c r="K79" s="128"/>
+      <c r="L79" s="127"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D78" t="s">
-        <v>112</v>
-      </c>
-      <c r="E78" s="110">
-        <f>'Company definition'!F85</f>
-        <v>45.220459339114129</v>
-      </c>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="5"/>
+      <c r="B80" s="124" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" s="124"/>
+      <c r="D80" s="125" t="s">
+        <v>199</v>
+      </c>
+      <c r="E80" s="125" t="s">
+        <v>200</v>
+      </c>
+      <c r="F80" s="125">
+        <v>6</v>
+      </c>
+      <c r="G80" s="126" t="s">
+        <v>202</v>
+      </c>
+      <c r="H80" s="127">
+        <v>20</v>
+      </c>
+      <c r="I80" s="127">
+        <f>H80*F80</f>
+        <v>120</v>
+      </c>
+      <c r="J80" s="127"/>
+      <c r="K80" s="128"/>
+      <c r="L80" s="127"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D79" t="s">
-        <v>111</v>
-      </c>
-      <c r="E79" s="110">
-        <f>'Company definition'!F84</f>
-        <v>42.159269173306768</v>
-      </c>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="119" t="s">
+        <v>4</v>
+      </c>
+      <c r="B81" s="120"/>
+      <c r="C81" s="120"/>
+      <c r="D81" s="120"/>
+      <c r="E81" s="120"/>
+      <c r="F81" s="120"/>
+      <c r="G81" s="120"/>
+      <c r="H81" s="120"/>
+      <c r="I81" s="120"/>
+      <c r="J81" s="120"/>
+      <c r="K81" s="114">
+        <f>SUM(K78:K80)</f>
+        <v>172.5</v>
+      </c>
+      <c r="L81" s="135"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D80" t="s">
-        <v>113</v>
-      </c>
-      <c r="E80" s="110">
-        <f>'Company definition'!F86</f>
-        <v>49.154057104913683</v>
-      </c>
-    </row>
-    <row r="81" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D81" t="s">
-        <v>114</v>
-      </c>
-      <c r="E81" s="110">
-        <f>'Company definition'!F87</f>
-        <v>43.846666276072185</v>
-      </c>
-    </row>
-    <row r="82" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D82" t="s">
-        <v>115</v>
-      </c>
-      <c r="E82" s="110">
-        <f>'Company definition'!F88</f>
-        <v>38.551814171883898</v>
-      </c>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A76:K76"/>
+    <mergeCell ref="A81:J81"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="N6:O6"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E73" xr:uid="{2FF9A132-8776-4FE0-B050-ADA1CD0962E0}">
-      <formula1>$D$77:$D$82</formula1>
+      <formula1>$Q$20:$Q$25</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -33196,38 +33811,37 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1BC6334-ABDB-402C-9F6E-AACD57B8B147}">
-  <dimension ref="A1:N82"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A99F06-5152-4136-849C-8D726824663D}">
+  <dimension ref="A1:K56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.5546875" customWidth="1"/>
-    <col min="5" max="5" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="116" t="s">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="B1" s="117"/>
       <c r="C1" s="117"/>
       <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="G1" s="119" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="120"/>
+      <c r="I1" s="132"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -33235,2302 +33849,803 @@
         <v>1</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="M2" t="s">
-        <v>198</v>
-      </c>
-      <c r="N2">
-        <f>Costs!K76</f>
-        <v>16283.14669083678</v>
+      <c r="G2" s="130" t="s">
+        <v>205</v>
+      </c>
+      <c r="H2" s="129" t="s">
+        <v>204</v>
+      </c>
+      <c r="I2" s="131" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="111" t="str">
-        <f>_xlfn.XLOOKUP(E3,$D$77:$D$82,$E$77:$E$82,"")</f>
-        <v/>
-      </c>
-      <c r="I3" s="111" t="str">
-        <f>IFERROR(H3*F3,"")</f>
-        <v/>
-      </c>
-      <c r="K3" s="115">
-        <f>SUM(J4:J19)</f>
-        <v>1194.7710082745937</v>
-      </c>
-      <c r="M3" t="s">
-        <v>199</v>
-      </c>
-      <c r="N3" s="111">
-        <f>K76</f>
-        <v>16729.515715661983</v>
+      <c r="C3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="136"/>
+      <c r="E3" s="115">
+        <f>SUM(D4:D6)</f>
+        <v>1840.8637603432428</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="125" t="s">
+        <v>206</v>
+      </c>
+      <c r="I3" s="133">
+        <f>E54</f>
+        <v>16500.517352669427</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4" t="s">
-        <v>108</v>
-      </c>
-      <c r="H4" s="111">
-        <f>_xlfn.XLOOKUP(E4,$D$77:$D$82,$E$77:$E$82,"")</f>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I4" s="111">
-        <f t="shared" ref="I4:I67" si="0">IFERROR(H4*F4,"")</f>
-        <v>99.564250689549496</v>
-      </c>
-      <c r="J4" s="111">
-        <f>I4</f>
-        <v>99.564250689549496</v>
-      </c>
-      <c r="K4" s="112"/>
-      <c r="M4" t="s">
-        <v>200</v>
-      </c>
-      <c r="N4" s="111">
-        <f>N3-N2</f>
-        <v>446.36902482520236</v>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="136">
+        <f>Costs_init!L4</f>
+        <v>122.72425068954949</v>
+      </c>
+      <c r="E4" s="112"/>
+      <c r="G4" s="119" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="120"/>
+      <c r="I4" s="134">
+        <f>SUM(I3)</f>
+        <v>16500.517352669427</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H5" s="111">
-        <f t="shared" ref="H5:H68" si="1">_xlfn.XLOOKUP(E5,$D$77:$D$82,$E$77:$E$82,"")</f>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I5" s="111">
-        <f t="shared" si="0"/>
-        <v>99.564250689549496</v>
-      </c>
-      <c r="J5" s="111">
-        <f>I5</f>
-        <v>99.564250689549496</v>
-      </c>
-      <c r="K5" s="112"/>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="136">
+        <f>Costs_init!L5</f>
+        <v>122.72425068954949</v>
+      </c>
+      <c r="E5" s="112"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="135"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="111" t="str">
-        <f t="shared" si="1"/>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="136">
+        <f>SUM(Costs_init!L7:L19)</f>
+        <v>1595.4152589641437</v>
+      </c>
+      <c r="E6" s="112"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="136"/>
+      <c r="E7" s="112">
+        <f>SUM(D8:D17)</f>
+        <v>2932.5324370166391</v>
+      </c>
+      <c r="K7" s="110"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="136">
+        <f>Costs_init!L21</f>
+        <v>53.739269173306766</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="K8" s="110"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="136">
+        <f>Costs_init!L22</f>
+        <v>227.20183735645651</v>
+      </c>
+      <c r="E9" s="112"/>
+      <c r="K9" s="110"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="136">
+        <f>Costs_init!L23</f>
+        <v>107.47853834661353</v>
+      </c>
+      <c r="E10" s="112"/>
+      <c r="K10" s="110"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="136">
+        <f>Costs_init!L24</f>
+        <v>53.739269173306766</v>
+      </c>
+      <c r="E11" s="112"/>
+      <c r="K11" s="110"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="136">
+        <f>Costs_init!L25</f>
+        <v>107.47853834661353</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="K12" s="110"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="136">
+        <f>Costs_init!L26</f>
+        <v>340.80275603468476</v>
+      </c>
+      <c r="E13" s="112"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="136">
+        <f>Costs_init!L27</f>
+        <v>1182.2639218127488</v>
+      </c>
+      <c r="E14" s="112"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="136">
+        <f>Costs_init!L28</f>
+        <v>322.43561503984063</v>
+      </c>
+      <c r="E15" s="112"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="136">
+        <f>Costs_init!L29</f>
+        <v>107.47853834661353</v>
+      </c>
+      <c r="E16" s="112"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="136">
+        <f>Costs_init!L30</f>
+        <v>429.91415338645413</v>
+      </c>
+      <c r="E17" s="112"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="136" t="str">
+        <f>Costs_init!L31</f>
         <v/>
       </c>
-      <c r="I6" s="111" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J6" s="111">
-        <f>SUM(I7:I19)</f>
-        <v>995.64250689549476</v>
-      </c>
-      <c r="K6" s="112"/>
+      <c r="E18" s="112">
+        <f>SUM(D19:D25)</f>
+        <v>2863.9493320555316</v>
+      </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>109</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>108</v>
-      </c>
-      <c r="H7" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I7" s="111">
-        <f t="shared" si="0"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="J7" s="111"/>
-      <c r="K7" s="112"/>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="136">
+        <f>Costs_init!L32</f>
+        <v>607.34057104913677</v>
+      </c>
+      <c r="E19" s="112"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H8" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I8" s="111">
-        <f t="shared" si="0"/>
-        <v>99.564250689549496</v>
-      </c>
-      <c r="J8" s="111"/>
-      <c r="K8" s="112"/>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="136">
+        <f>Costs_init!L33</f>
+        <v>150.39544251565169</v>
+      </c>
+      <c r="E20" s="112"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H9" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I9" s="111">
-        <f t="shared" si="0"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="J9" s="111"/>
-      <c r="K9" s="112"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10" t="s">
-        <v>108</v>
-      </c>
-      <c r="H10" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I10" s="111">
-        <f t="shared" si="0"/>
-        <v>99.564250689549496</v>
-      </c>
-      <c r="J10" s="111"/>
-      <c r="K10" s="112"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>109</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>108</v>
-      </c>
-      <c r="H11" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I11" s="111">
-        <f t="shared" si="0"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="J11" s="111"/>
-      <c r="K11" s="112"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" t="s">
-        <v>109</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>108</v>
-      </c>
-      <c r="H12" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I12" s="111">
-        <f t="shared" si="0"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="J12" s="111"/>
-      <c r="K12" s="112"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" t="s">
-        <v>109</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13" t="s">
-        <v>108</v>
-      </c>
-      <c r="H13" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I13" s="111">
-        <f t="shared" si="0"/>
-        <v>99.564250689549496</v>
-      </c>
-      <c r="J13" s="111"/>
-      <c r="K13" s="112"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" t="s">
-        <v>109</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14" t="s">
-        <v>108</v>
-      </c>
-      <c r="H14" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I14" s="111">
-        <f t="shared" si="0"/>
-        <v>99.564250689549496</v>
-      </c>
-      <c r="J14" s="111"/>
-      <c r="K14" s="112"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" t="s">
-        <v>109</v>
-      </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
-      <c r="G15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H15" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I15" s="111">
-        <f t="shared" si="0"/>
-        <v>99.564250689549496</v>
-      </c>
-      <c r="J15" s="111"/>
-      <c r="K15" s="112"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" t="s">
-        <v>109</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H16" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I16" s="111">
-        <f t="shared" si="0"/>
-        <v>99.564250689549496</v>
-      </c>
-      <c r="J16" s="111"/>
-      <c r="K16" s="112"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I17" s="111">
-        <f t="shared" si="0"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="J17" s="111"/>
-      <c r="K17" s="112"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="G18" t="s">
-        <v>108</v>
-      </c>
-      <c r="H18" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I18" s="111">
-        <f t="shared" si="0"/>
-        <v>99.564250689549496</v>
-      </c>
-      <c r="J18" s="111"/>
-      <c r="K18" s="112"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" t="s">
-        <v>109</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>108</v>
-      </c>
-      <c r="H19" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I19" s="111">
-        <f t="shared" si="0"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="J19" s="111"/>
-      <c r="K19" s="112"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H20" s="111" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I20" s="111" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="111"/>
-      <c r="K20" s="112">
-        <f>SUM(J21:J30)</f>
-        <v>2433.690244536559</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" t="s">
-        <v>111</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>108</v>
-      </c>
-      <c r="H21" s="111">
-        <f t="shared" si="1"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="I21" s="111">
-        <f t="shared" si="0"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="J21" s="111">
-        <f t="shared" ref="J21:J30" si="2">I21</f>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="K21" s="112"/>
+        <v>14</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="136">
+        <f>Costs_init!L34</f>
+        <v>443.41333020857746</v>
+      </c>
+      <c r="E21" s="112"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" t="s">
-        <v>112</v>
-      </c>
-      <c r="F22">
-        <v>4</v>
-      </c>
-      <c r="G22" t="s">
-        <v>108</v>
-      </c>
-      <c r="H22" s="111">
-        <f t="shared" si="1"/>
-        <v>45.220459339114129</v>
-      </c>
-      <c r="I22" s="111">
-        <f t="shared" si="0"/>
-        <v>180.88183735645651</v>
-      </c>
-      <c r="J22" s="111">
-        <f t="shared" si="2"/>
-        <v>180.88183735645651</v>
-      </c>
-      <c r="K22" s="112"/>
+        <v>94</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="136">
+        <f>Costs_init!L35</f>
+        <v>221.70666510428873</v>
+      </c>
+      <c r="E22" s="112"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" t="s">
-        <v>108</v>
-      </c>
-      <c r="H23" s="111">
-        <f t="shared" si="1"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="I23" s="111">
-        <f t="shared" si="0"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="J23" s="111">
-        <f t="shared" si="2"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="K23" s="112"/>
+        <v>95</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="136">
+        <f>Costs_init!L36</f>
+        <v>332.5599976564331</v>
+      </c>
+      <c r="E23" s="112"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" t="s">
-        <v>111</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24" t="s">
-        <v>108</v>
-      </c>
-      <c r="H24" s="111">
-        <f t="shared" si="1"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="I24" s="111">
-        <f t="shared" si="0"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="J24" s="111">
-        <f t="shared" si="2"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="K24" s="112"/>
+        <v>96</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="136">
+        <f>Costs_init!L37</f>
+        <v>554.26666276072183</v>
+      </c>
+      <c r="E24" s="112"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25">
-        <v>2</v>
-      </c>
-      <c r="G25" t="s">
-        <v>108</v>
-      </c>
-      <c r="H25" s="111">
-        <f t="shared" si="1"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="I25" s="111">
-        <f t="shared" si="0"/>
-        <v>84.318538346613536</v>
-      </c>
-      <c r="J25" s="111">
-        <f t="shared" si="2"/>
-        <v>84.318538346613536</v>
-      </c>
-      <c r="K25" s="112"/>
+        <v>97</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" s="136">
+        <f>Costs_init!L38</f>
+        <v>554.26666276072183</v>
+      </c>
+      <c r="E25" s="112"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26">
-        <v>6</v>
-      </c>
-      <c r="G26" t="s">
-        <v>108</v>
-      </c>
-      <c r="H26" s="111">
-        <f t="shared" si="1"/>
-        <v>45.220459339114129</v>
-      </c>
-      <c r="I26" s="111">
-        <f t="shared" si="0"/>
-        <v>271.32275603468474</v>
-      </c>
-      <c r="J26" s="111">
-        <f t="shared" si="2"/>
-        <v>271.32275603468474</v>
-      </c>
-      <c r="K26" s="112"/>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="136">
+        <f>Costs_init!L39</f>
+        <v>166.27999882821655</v>
+      </c>
+      <c r="E26" s="111">
+        <f>D26</f>
+        <v>166.27999882821655</v>
+      </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" t="s">
-        <v>111</v>
-      </c>
-      <c r="F27">
-        <v>22</v>
-      </c>
-      <c r="G27" t="s">
-        <v>108</v>
-      </c>
-      <c r="H27" s="111">
-        <f t="shared" si="1"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="I27" s="111">
-        <f t="shared" si="0"/>
-        <v>927.5039218127489</v>
-      </c>
-      <c r="J27" s="111">
-        <f t="shared" si="2"/>
-        <v>927.5039218127489</v>
-      </c>
-      <c r="K27" s="112"/>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="136" t="str">
+        <f>Costs_init!L40</f>
+        <v/>
+      </c>
+      <c r="E27" s="112">
+        <f>SUM(D28:D30)</f>
+        <v>5602.7987937884327</v>
+      </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28">
-        <v>8</v>
-      </c>
-      <c r="G28" t="s">
-        <v>108</v>
-      </c>
-      <c r="H28" s="111">
-        <f t="shared" si="1"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="I28" s="111">
-        <f t="shared" si="0"/>
-        <v>337.27415338645415</v>
-      </c>
-      <c r="J28" s="111">
-        <f t="shared" si="2"/>
-        <v>337.27415338645415</v>
-      </c>
-      <c r="K28" s="112"/>
+        <v>7</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="136">
+        <f>Costs_init!L41</f>
+        <v>242.93622841965473</v>
+      </c>
+      <c r="E28" s="112"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" t="s">
-        <v>111</v>
-      </c>
-      <c r="F29">
-        <v>4</v>
-      </c>
-      <c r="G29" t="s">
-        <v>108</v>
-      </c>
-      <c r="H29" s="111">
-        <f t="shared" si="1"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="I29" s="111">
-        <f t="shared" si="0"/>
-        <v>168.63707669322707</v>
-      </c>
-      <c r="J29" s="111">
-        <f t="shared" si="2"/>
-        <v>168.63707669322707</v>
-      </c>
-      <c r="K29" s="112"/>
+        <v>13</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="136">
+        <f>Costs_init!L42</f>
+        <v>182.20217131474107</v>
+      </c>
+      <c r="E29" s="112"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" t="s">
-        <v>111</v>
-      </c>
-      <c r="F30">
-        <v>8</v>
-      </c>
-      <c r="G30" t="s">
-        <v>108</v>
-      </c>
-      <c r="H30" s="111">
-        <f t="shared" si="1"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="I30" s="111">
-        <f t="shared" si="0"/>
-        <v>337.27415338645415</v>
-      </c>
-      <c r="J30" s="111">
-        <f t="shared" si="2"/>
-        <v>337.27415338645415</v>
-      </c>
-      <c r="K30" s="112"/>
+        <v>14</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="136">
+        <f>SUM(Costs_init!L44:L50)</f>
+        <v>5177.6603940540372</v>
+      </c>
+      <c r="E30" s="112"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H31" s="111" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I31" s="111" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="111"/>
-      <c r="K31" s="112">
-        <f>SUM(J32:J38)</f>
-        <v>2361.0626646076757</v>
+      <c r="C31" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="136"/>
+      <c r="E31" s="112">
+        <f>SUM(D32:D40)</f>
+        <v>1364.1486868492418</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32" t="s">
-        <v>113</v>
-      </c>
-      <c r="F32">
-        <v>10</v>
-      </c>
-      <c r="G32" t="s">
-        <v>108</v>
-      </c>
-      <c r="H32" s="111">
-        <f t="shared" si="1"/>
-        <v>49.154057104913683</v>
-      </c>
-      <c r="I32" s="111">
-        <f t="shared" si="0"/>
-        <v>491.54057104913682</v>
-      </c>
-      <c r="J32" s="111">
-        <f t="shared" ref="J32:J38" si="3">I32</f>
-        <v>491.54057104913682</v>
-      </c>
-      <c r="K32" s="112"/>
+      <c r="C32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="136">
+        <f>Costs_init!L52</f>
+        <v>200.52725668753558</v>
+      </c>
+      <c r="E32" s="112"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" t="s">
-        <v>115</v>
-      </c>
-      <c r="F33">
-        <v>3</v>
-      </c>
-      <c r="G33" t="s">
-        <v>108</v>
-      </c>
-      <c r="H33" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I33" s="111">
-        <f t="shared" si="0"/>
-        <v>115.65544251565169</v>
-      </c>
-      <c r="J33" s="111">
-        <f t="shared" si="3"/>
-        <v>115.65544251565169</v>
-      </c>
-      <c r="K33" s="112"/>
+      <c r="C33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="136">
+        <f>Costs_init!L53</f>
+        <v>150.39544251565169</v>
+      </c>
+      <c r="E33" s="112"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" t="s">
-        <v>114</v>
-      </c>
-      <c r="F34">
-        <v>8</v>
-      </c>
-      <c r="G34" t="s">
-        <v>108</v>
-      </c>
-      <c r="H34" s="111">
-        <f t="shared" si="1"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I34" s="111">
-        <f t="shared" si="0"/>
-        <v>350.77333020857748</v>
-      </c>
-      <c r="J34" s="111">
-        <f t="shared" si="3"/>
-        <v>350.77333020857748</v>
-      </c>
-      <c r="K34" s="112"/>
+      <c r="C34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="136">
+        <f>Costs_init!L54</f>
+        <v>250.6590708594195</v>
+      </c>
+      <c r="E34" s="112"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E35" t="s">
-        <v>114</v>
-      </c>
-      <c r="F35">
-        <v>4</v>
-      </c>
-      <c r="G35" t="s">
-        <v>108</v>
-      </c>
-      <c r="H35" s="111">
-        <f t="shared" si="1"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I35" s="111">
-        <f t="shared" si="0"/>
-        <v>175.38666510428874</v>
-      </c>
-      <c r="J35" s="111">
-        <f t="shared" si="3"/>
-        <v>175.38666510428874</v>
-      </c>
-      <c r="K35" s="112"/>
+        <v>94</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="136">
+        <f>Costs_init!L55</f>
+        <v>150.39544251565169</v>
+      </c>
+      <c r="E35" s="112"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" t="s">
-        <v>114</v>
-      </c>
-      <c r="F36">
-        <v>6</v>
-      </c>
-      <c r="G36" t="s">
-        <v>108</v>
-      </c>
-      <c r="H36" s="111">
-        <f t="shared" si="1"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I36" s="111">
-        <f t="shared" si="0"/>
-        <v>263.07999765643308</v>
-      </c>
-      <c r="J36" s="111">
-        <f t="shared" si="3"/>
-        <v>263.07999765643308</v>
-      </c>
-      <c r="K36" s="112"/>
+        <v>95</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" s="136">
+        <f>Costs_init!L56</f>
+        <v>150.39544251565169</v>
+      </c>
+      <c r="E36" s="112"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E37" t="s">
-        <v>114</v>
-      </c>
-      <c r="F37">
-        <v>12</v>
-      </c>
-      <c r="G37" t="s">
-        <v>108</v>
-      </c>
-      <c r="H37" s="111">
-        <f t="shared" si="1"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I37" s="111">
-        <f t="shared" si="0"/>
-        <v>526.15999531286616</v>
-      </c>
-      <c r="J37" s="111">
-        <f t="shared" si="3"/>
-        <v>526.15999531286616</v>
-      </c>
-      <c r="K37" s="112"/>
+        <v>96</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="136">
+        <f>Costs_init!L57</f>
+        <v>100.26362834376779</v>
+      </c>
+      <c r="E37" s="112"/>
     </row>
-    <row r="38" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" t="s">
-        <v>114</v>
-      </c>
-      <c r="F38">
-        <v>10</v>
-      </c>
-      <c r="G38" t="s">
-        <v>108</v>
-      </c>
-      <c r="H38" s="111">
-        <f t="shared" si="1"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I38" s="111">
-        <f t="shared" si="0"/>
-        <v>438.46666276072187</v>
-      </c>
-      <c r="J38" s="111">
-        <f t="shared" si="3"/>
-        <v>438.46666276072187</v>
-      </c>
-      <c r="K38" s="112"/>
+        <v>97</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" s="136">
+        <f>Costs_init!L58</f>
+        <v>150.39544251565169</v>
+      </c>
+      <c r="E38" s="112"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E39" t="s">
-        <v>114</v>
-      </c>
-      <c r="F39">
-        <v>6</v>
-      </c>
-      <c r="G39" t="s">
-        <v>108</v>
-      </c>
-      <c r="H39" s="111">
-        <f t="shared" si="1"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I39" s="111">
-        <f t="shared" si="0"/>
-        <v>263.07999765643308</v>
-      </c>
-      <c r="J39" s="111">
-        <f>SUM(I39)</f>
-        <v>263.07999765643308</v>
-      </c>
-      <c r="K39" s="111">
-        <f>SUM(J39)</f>
-        <v>263.07999765643308</v>
-      </c>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" s="136">
+        <f>Costs_init!L59</f>
+        <v>100.26362834376779</v>
+      </c>
+      <c r="E39" s="112"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H40" s="111" t="str">
-        <f t="shared" si="1"/>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" s="136">
+        <f>Costs_init!L60</f>
+        <v>110.85333255214437</v>
+      </c>
+      <c r="E40" s="112"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="136" t="str">
+        <f>Costs_init!L61</f>
         <v/>
       </c>
-      <c r="I40" s="111" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="111"/>
-      <c r="K40" s="112">
-        <f>SUM(J41:J50)</f>
-        <v>4485.1818305489533</v>
+      <c r="E41" s="112">
+        <f>SUM(D42:D53)</f>
+        <v>1729.9443437881205</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" t="s">
-        <v>113</v>
-      </c>
-      <c r="F41">
-        <v>6</v>
-      </c>
-      <c r="G41" t="s">
-        <v>108</v>
-      </c>
-      <c r="H41" s="111">
-        <f t="shared" si="1"/>
-        <v>49.154057104913683</v>
-      </c>
-      <c r="I41" s="111">
-        <f t="shared" si="0"/>
-        <v>294.92434262948211</v>
-      </c>
-      <c r="J41" s="111">
-        <f>I41</f>
-        <v>294.92434262948211</v>
-      </c>
-      <c r="K41" s="112"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" t="s">
-        <v>113</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>108</v>
-      </c>
-      <c r="H42" s="111">
-        <f t="shared" si="1"/>
-        <v>49.154057104913683</v>
-      </c>
-      <c r="I42" s="111">
-        <f t="shared" si="0"/>
-        <v>49.154057104913683</v>
-      </c>
-      <c r="J42" s="111">
-        <f>I42</f>
-        <v>49.154057104913683</v>
-      </c>
-      <c r="K42" s="112"/>
+        <v>7</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" s="136">
+        <f>Costs_init!L62</f>
+        <v>61.362125344774746</v>
+      </c>
+      <c r="E42" s="112"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" s="136">
+        <f>Costs_init!L63</f>
+        <v>61.362125344774746</v>
+      </c>
+      <c r="E43" s="112"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="5"/>
+      <c r="B44" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H43" s="111" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I43" s="111" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="111">
-        <f>SUM(I44:I50)</f>
-        <v>4141.1034308145572</v>
-      </c>
-      <c r="K43" s="112"/>
+      <c r="C44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" s="136">
+        <f>Costs_init!L64</f>
+        <v>56.800459339114127</v>
+      </c>
+      <c r="E44" s="112"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="5"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" t="s">
-        <v>115</v>
-      </c>
-      <c r="F44">
-        <v>22</v>
-      </c>
-      <c r="G44" t="s">
-        <v>108</v>
-      </c>
-      <c r="H44" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I44" s="111">
-        <f t="shared" si="0"/>
-        <v>848.13991178144579</v>
-      </c>
-      <c r="J44" s="111"/>
-      <c r="K44" s="112"/>
+    <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="5"/>
+      <c r="B45" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="136">
+        <f>Costs_init!L65</f>
+        <v>113.60091867822825</v>
+      </c>
+      <c r="E45" s="112"/>
     </row>
-    <row r="45" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E45" t="s">
-        <v>115</v>
-      </c>
-      <c r="F45">
-        <v>6</v>
-      </c>
-      <c r="G45" t="s">
-        <v>108</v>
-      </c>
-      <c r="H45" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I45" s="111">
-        <f t="shared" si="0"/>
-        <v>231.31088503130337</v>
-      </c>
-      <c r="J45" s="111"/>
-      <c r="K45" s="112"/>
+    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="5"/>
+      <c r="B46" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="136">
+        <f>Costs_init!L66</f>
+        <v>122.72425068954949</v>
+      </c>
+      <c r="E46" s="112"/>
     </row>
-    <row r="46" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="5"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" t="s">
-        <v>114</v>
-      </c>
-      <c r="F46">
-        <v>24</v>
-      </c>
-      <c r="G46" t="s">
-        <v>108</v>
-      </c>
-      <c r="H46" s="111">
-        <f t="shared" si="1"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I46" s="111">
-        <f t="shared" si="0"/>
-        <v>1052.3199906257323</v>
-      </c>
-      <c r="J46" s="111"/>
-      <c r="K46" s="112"/>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="5"/>
+      <c r="B47" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="136">
+        <f>Costs_init!L67</f>
+        <v>161.21780751992031</v>
+      </c>
+      <c r="E47" s="112"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A47" s="5"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E47" t="s">
-        <v>115</v>
-      </c>
-      <c r="F47">
-        <v>12</v>
-      </c>
-      <c r="G47" t="s">
-        <v>108</v>
-      </c>
-      <c r="H47" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I47" s="111">
-        <f t="shared" si="0"/>
-        <v>462.62177006260674</v>
-      </c>
-      <c r="J47" s="111"/>
-      <c r="K47" s="112"/>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="5"/>
+      <c r="B48" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="136">
+        <f>Costs_init!L68</f>
+        <v>303.67028552456838</v>
+      </c>
+      <c r="E48" s="112"/>
     </row>
-    <row r="48" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="5"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E48" t="s">
-        <v>114</v>
-      </c>
-      <c r="F48">
-        <v>20</v>
-      </c>
-      <c r="G48" t="s">
-        <v>108</v>
-      </c>
-      <c r="H48" s="111">
-        <f t="shared" si="1"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I48" s="111">
-        <f t="shared" si="0"/>
-        <v>876.93332552144375</v>
-      </c>
-      <c r="J48" s="111"/>
-      <c r="K48" s="112"/>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
+      <c r="B49" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" s="136">
+        <f>Costs_init!L69</f>
+        <v>277.13333138036091</v>
+      </c>
+      <c r="E49" s="112"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="5"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E49" t="s">
-        <v>114</v>
-      </c>
-      <c r="F49">
-        <v>10</v>
-      </c>
-      <c r="G49" t="s">
-        <v>108</v>
-      </c>
-      <c r="H49" s="111">
-        <f t="shared" si="1"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I49" s="111">
-        <f t="shared" si="0"/>
-        <v>438.46666276072187</v>
-      </c>
-      <c r="J49" s="111"/>
-      <c r="K49" s="112"/>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="5"/>
+      <c r="B50" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="136">
+        <f>Costs_init!L70</f>
+        <v>110.85333255214437</v>
+      </c>
+      <c r="E50" s="112"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="5"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E50" t="s">
-        <v>115</v>
-      </c>
-      <c r="F50">
-        <v>6</v>
-      </c>
-      <c r="G50" t="s">
-        <v>108</v>
-      </c>
-      <c r="H50" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I50" s="111">
-        <f t="shared" si="0"/>
-        <v>231.31088503130337</v>
-      </c>
-      <c r="J50" s="111"/>
-      <c r="K50" s="112"/>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="5"/>
+      <c r="B51" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D51" s="136">
+        <f>Costs_init!L71</f>
+        <v>277.13333138036091</v>
+      </c>
+      <c r="E51" s="112"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H51" s="111" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I51" s="111" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="111"/>
-      <c r="K51" s="112">
-        <f>SUM(J52:J60)</f>
-        <v>1359.9032002243127</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E52" t="s">
-        <v>115</v>
-      </c>
-      <c r="F52">
-        <v>6</v>
-      </c>
-      <c r="G52" t="s">
-        <v>108</v>
-      </c>
-      <c r="H52" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I52" s="111">
-        <f t="shared" si="0"/>
-        <v>231.31088503130337</v>
-      </c>
-      <c r="J52" s="111">
-        <f t="shared" ref="J52:J60" si="4">I52</f>
-        <v>231.31088503130337</v>
-      </c>
-      <c r="K52" s="112"/>
+        <v>101</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="136">
+        <f>Costs_init!L72</f>
+        <v>122.72425068954949</v>
+      </c>
+      <c r="E52" s="112"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="5"/>
-      <c r="B53" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E53" t="s">
-        <v>115</v>
-      </c>
-      <c r="F53">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="8"/>
+      <c r="B53" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" s="136">
+        <f>Costs_init!L73</f>
+        <v>61.362125344774746</v>
+      </c>
+      <c r="E53" s="113"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="G53" t="s">
-        <v>108</v>
-      </c>
-      <c r="H53" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I53" s="111">
-        <f t="shared" si="0"/>
-        <v>154.20725668753559</v>
-      </c>
-      <c r="J53" s="111">
-        <f t="shared" si="4"/>
-        <v>154.20725668753559</v>
-      </c>
-      <c r="K53" s="112"/>
+      <c r="B54" s="120"/>
+      <c r="C54" s="120"/>
+      <c r="D54" s="120"/>
+      <c r="E54" s="114">
+        <f>SUM(E3:E53)</f>
+        <v>16500.517352669427</v>
+      </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="5"/>
-      <c r="B54" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E54" t="s">
-        <v>115</v>
-      </c>
-      <c r="F54">
-        <v>5</v>
-      </c>
-      <c r="G54" t="s">
-        <v>108</v>
-      </c>
-      <c r="H54" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I54" s="111">
-        <f t="shared" si="0"/>
-        <v>192.7590708594195</v>
-      </c>
-      <c r="J54" s="111">
-        <f t="shared" si="4"/>
-        <v>192.7590708594195</v>
-      </c>
-      <c r="K54" s="112"/>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E55" s="2"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="5"/>
-      <c r="B55" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E55" t="s">
-        <v>115</v>
-      </c>
-      <c r="F55">
-        <v>3</v>
-      </c>
-      <c r="G55" t="s">
-        <v>108</v>
-      </c>
-      <c r="H55" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I55" s="111">
-        <f t="shared" si="0"/>
-        <v>115.65544251565169</v>
-      </c>
-      <c r="J55" s="111">
-        <f t="shared" si="4"/>
-        <v>115.65544251565169</v>
-      </c>
-      <c r="K55" s="112"/>
-    </row>
-    <row r="56" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="5"/>
-      <c r="B56" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C56" s="6"/>
-      <c r="D56" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E56" t="s">
-        <v>115</v>
-      </c>
-      <c r="F56">
-        <v>4</v>
-      </c>
-      <c r="G56" t="s">
-        <v>108</v>
-      </c>
-      <c r="H56" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I56" s="111">
-        <f t="shared" si="0"/>
-        <v>154.20725668753559</v>
-      </c>
-      <c r="J56" s="111">
-        <f t="shared" si="4"/>
-        <v>154.20725668753559</v>
-      </c>
-      <c r="K56" s="112"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="5"/>
-      <c r="B57" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E57" t="s">
-        <v>115</v>
-      </c>
-      <c r="F57">
-        <v>5</v>
-      </c>
-      <c r="G57" t="s">
-        <v>108</v>
-      </c>
-      <c r="H57" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I57" s="111">
-        <f t="shared" si="0"/>
-        <v>192.7590708594195</v>
-      </c>
-      <c r="J57" s="111">
-        <f t="shared" si="4"/>
-        <v>192.7590708594195</v>
-      </c>
-      <c r="K57" s="112"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="5"/>
-      <c r="B58" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E58" t="s">
-        <v>115</v>
-      </c>
-      <c r="F58">
-        <v>3</v>
-      </c>
-      <c r="G58" t="s">
-        <v>108</v>
-      </c>
-      <c r="H58" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I58" s="111">
-        <f t="shared" si="0"/>
-        <v>115.65544251565169</v>
-      </c>
-      <c r="J58" s="111">
-        <f t="shared" si="4"/>
-        <v>115.65544251565169</v>
-      </c>
-      <c r="K58" s="112"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="5"/>
-      <c r="B59" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E59" t="s">
-        <v>115</v>
-      </c>
-      <c r="F59">
-        <v>3</v>
-      </c>
-      <c r="G59" t="s">
-        <v>108</v>
-      </c>
-      <c r="H59" s="111">
-        <f t="shared" si="1"/>
-        <v>38.551814171883898</v>
-      </c>
-      <c r="I59" s="111">
-        <f t="shared" si="0"/>
-        <v>115.65544251565169</v>
-      </c>
-      <c r="J59" s="111">
-        <f t="shared" si="4"/>
-        <v>115.65544251565169</v>
-      </c>
-      <c r="K59" s="112"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60" s="5"/>
-      <c r="B60" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E60" t="s">
-        <v>114</v>
-      </c>
-      <c r="F60">
-        <v>2</v>
-      </c>
-      <c r="G60" t="s">
-        <v>108</v>
-      </c>
-      <c r="H60" s="111">
-        <f t="shared" si="1"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I60" s="111">
-        <f t="shared" si="0"/>
-        <v>87.693332552144369</v>
-      </c>
-      <c r="J60" s="111">
-        <f t="shared" si="4"/>
-        <v>87.693332552144369</v>
-      </c>
-      <c r="K60" s="112"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H61" s="111" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I61" s="111" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="111"/>
-      <c r="K61" s="112">
-        <f>SUM(J62:J73)</f>
-        <v>1285.9236266810587</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="5"/>
-      <c r="B62" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="6"/>
-      <c r="D62" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E62" t="s">
-        <v>109</v>
-      </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
-      <c r="G62" t="s">
-        <v>108</v>
-      </c>
-      <c r="H62" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I62" s="111">
-        <f t="shared" si="0"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="J62" s="111">
-        <f t="shared" ref="J62:J73" si="5">I62</f>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="K62" s="112"/>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="5"/>
-      <c r="B63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E63" t="s">
-        <v>109</v>
-      </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-      <c r="G63" t="s">
-        <v>108</v>
-      </c>
-      <c r="H63" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I63" s="111">
-        <f t="shared" si="0"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="J63" s="111">
-        <f t="shared" si="5"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="K63" s="112"/>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="5"/>
-      <c r="B64" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C64" s="6"/>
-      <c r="D64" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E64" t="s">
-        <v>112</v>
-      </c>
-      <c r="F64">
-        <v>1</v>
-      </c>
-      <c r="G64" t="s">
-        <v>108</v>
-      </c>
-      <c r="H64" s="111">
-        <f t="shared" si="1"/>
-        <v>45.220459339114129</v>
-      </c>
-      <c r="I64" s="111">
-        <f t="shared" si="0"/>
-        <v>45.220459339114129</v>
-      </c>
-      <c r="J64" s="111">
-        <f t="shared" si="5"/>
-        <v>45.220459339114129</v>
-      </c>
-      <c r="K64" s="112"/>
-    </row>
-    <row r="65" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="5"/>
-      <c r="B65" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C65" s="6"/>
-      <c r="D65" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E65" t="s">
-        <v>112</v>
-      </c>
-      <c r="F65">
-        <v>2</v>
-      </c>
-      <c r="G65" t="s">
-        <v>108</v>
-      </c>
-      <c r="H65" s="111">
-        <f t="shared" si="1"/>
-        <v>45.220459339114129</v>
-      </c>
-      <c r="I65" s="111">
-        <f t="shared" si="0"/>
-        <v>90.440918678228257</v>
-      </c>
-      <c r="J65" s="111">
-        <f t="shared" si="5"/>
-        <v>90.440918678228257</v>
-      </c>
-      <c r="K65" s="112"/>
-    </row>
-    <row r="66" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="5"/>
-      <c r="B66" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C66" s="6"/>
-      <c r="D66" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E66" t="s">
-        <v>109</v>
-      </c>
-      <c r="F66">
-        <v>3</v>
-      </c>
-      <c r="G66" t="s">
-        <v>108</v>
-      </c>
-      <c r="H66" s="111">
-        <f t="shared" si="1"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I66" s="111">
-        <f t="shared" si="0"/>
-        <v>149.34637603432424</v>
-      </c>
-      <c r="J66" s="111">
-        <f t="shared" si="5"/>
-        <v>149.34637603432424</v>
-      </c>
-      <c r="K66" s="112"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67" s="5"/>
-      <c r="B67" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C67" s="6"/>
-      <c r="D67" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E67" t="s">
-        <v>111</v>
-      </c>
-      <c r="F67">
-        <v>2</v>
-      </c>
-      <c r="G67" t="s">
-        <v>108</v>
-      </c>
-      <c r="H67" s="111">
-        <f t="shared" si="1"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="I67" s="111">
-        <f t="shared" si="0"/>
-        <v>84.318538346613536</v>
-      </c>
-      <c r="J67" s="111">
-        <f t="shared" si="5"/>
-        <v>84.318538346613536</v>
-      </c>
-      <c r="K67" s="112"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" s="5"/>
-      <c r="B68" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C68" s="6"/>
-      <c r="D68" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E68" t="s">
-        <v>113</v>
-      </c>
-      <c r="F68">
-        <v>3</v>
-      </c>
-      <c r="G68" t="s">
-        <v>108</v>
-      </c>
-      <c r="H68" s="111">
-        <f t="shared" si="1"/>
-        <v>49.154057104913683</v>
-      </c>
-      <c r="I68" s="111">
-        <f t="shared" ref="I68:I73" si="6">IFERROR(H68*F68,"")</f>
-        <v>147.46217131474106</v>
-      </c>
-      <c r="J68" s="111">
-        <f t="shared" si="5"/>
-        <v>147.46217131474106</v>
-      </c>
-      <c r="K68" s="112"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="5"/>
-      <c r="B69" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C69" s="6"/>
-      <c r="D69" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E69" t="s">
-        <v>114</v>
-      </c>
-      <c r="F69">
-        <v>6</v>
-      </c>
-      <c r="G69" t="s">
-        <v>108</v>
-      </c>
-      <c r="H69" s="111">
-        <f t="shared" ref="H69:H73" si="7">_xlfn.XLOOKUP(E69,$D$77:$D$82,$E$77:$E$82,"")</f>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I69" s="111">
-        <f t="shared" si="6"/>
-        <v>263.07999765643308</v>
-      </c>
-      <c r="J69" s="111">
-        <f t="shared" si="5"/>
-        <v>263.07999765643308</v>
-      </c>
-      <c r="K69" s="112"/>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" s="5"/>
-      <c r="B70" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C70" s="6"/>
-      <c r="D70" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E70" t="s">
-        <v>114</v>
-      </c>
-      <c r="F70">
-        <v>2</v>
-      </c>
-      <c r="G70" t="s">
-        <v>108</v>
-      </c>
-      <c r="H70" s="111">
-        <f t="shared" si="7"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I70" s="111">
-        <f t="shared" si="6"/>
-        <v>87.693332552144369</v>
-      </c>
-      <c r="J70" s="111">
-        <f t="shared" si="5"/>
-        <v>87.693332552144369</v>
-      </c>
-      <c r="K70" s="112"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="5"/>
-      <c r="B71" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C71" s="6"/>
-      <c r="D71" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E71" t="s">
-        <v>114</v>
-      </c>
-      <c r="F71">
-        <v>5</v>
-      </c>
-      <c r="G71" t="s">
-        <v>108</v>
-      </c>
-      <c r="H71" s="111">
-        <f t="shared" si="7"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I71" s="111">
-        <f t="shared" si="6"/>
-        <v>219.23333138036094</v>
-      </c>
-      <c r="J71" s="111">
-        <f t="shared" si="5"/>
-        <v>219.23333138036094</v>
-      </c>
-      <c r="K71" s="112"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="5"/>
-      <c r="B72" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C72" s="6"/>
-      <c r="D72" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E72" t="s">
-        <v>109</v>
-      </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
-      <c r="G72" t="s">
-        <v>108</v>
-      </c>
-      <c r="H72" s="111">
-        <f t="shared" si="7"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I72" s="111">
-        <f t="shared" si="6"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="J72" s="111">
-        <f t="shared" si="5"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="K72" s="112"/>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C73" s="9"/>
-      <c r="D73" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="F73" s="11">
-        <v>1</v>
-      </c>
-      <c r="G73" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="H73" s="111">
-        <f t="shared" si="7"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I73" s="111">
-        <f t="shared" si="6"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="J73" s="111">
-        <f t="shared" si="5"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="K73" s="113"/>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" s="119" t="s">
-        <v>4</v>
-      </c>
-      <c r="B74" s="120"/>
-      <c r="C74" s="120"/>
-      <c r="D74" s="120"/>
-      <c r="E74" s="120"/>
-      <c r="F74" s="120"/>
-      <c r="G74" s="120"/>
-      <c r="H74" s="120"/>
-      <c r="I74" s="120"/>
-      <c r="J74" s="120"/>
-      <c r="K74" s="114">
-        <f>SUM(K3:K73)</f>
-        <v>13383.612572529586</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="J75" t="s">
-        <v>196</v>
-      </c>
-      <c r="K75" s="2">
-        <f>Costs!K75</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D76" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E76" t="s">
-        <v>195</v>
-      </c>
-      <c r="J76" t="s">
-        <v>197</v>
-      </c>
-      <c r="K76" s="111">
-        <f>K74*(1+K75)</f>
-        <v>16729.515715661983</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D77" t="s">
-        <v>109</v>
-      </c>
-      <c r="E77" s="110">
-        <f>'Company definition'!F82</f>
-        <v>49.782125344774748</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D78" t="s">
-        <v>112</v>
-      </c>
-      <c r="E78" s="110">
-        <f>'Company definition'!F85</f>
-        <v>45.220459339114129</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D79" t="s">
-        <v>111</v>
-      </c>
-      <c r="E79" s="110">
-        <f>'Company definition'!F84</f>
-        <v>42.159269173306768</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D80" t="s">
-        <v>113</v>
-      </c>
-      <c r="E80" s="110">
-        <f>'Company definition'!F86</f>
-        <v>49.154057104913683</v>
-      </c>
-    </row>
-    <row r="81" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D81" t="s">
-        <v>114</v>
-      </c>
-      <c r="E81" s="110">
-        <f>'Company definition'!F87</f>
-        <v>43.846666276072185</v>
-      </c>
-    </row>
-    <row r="82" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D82" t="s">
-        <v>115</v>
-      </c>
-      <c r="E82" s="110">
-        <f>'Company definition'!F88</f>
-        <v>38.551814171883898</v>
-      </c>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A74:J74"/>
+  <mergeCells count="4">
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E73" xr:uid="{4CD2D6A9-C0F5-474D-9512-378F9EDC2D26}">
-      <formula1>$D$77:$D$82</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/docs/budget.xlsx
+++ b/docs/budget.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Desktop\proyectos\IRBoard\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FFC3930-7616-4036-A087-C25AF39D5A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965A530D-4CE8-438C-B313-7FE2C2223067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Company definition" sheetId="2" r:id="rId1"/>
@@ -685,7 +685,7 @@
     <t>total hours</t>
   </si>
   <si>
-    <t>increase per hour</t>
+    <t>Dilution increase per billable hour</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1122,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1321,6 +1321,29 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1328,12 +1351,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1345,29 +1362,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -31009,27 +31004,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="129" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="140" t="s">
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="125" t="s">
         <v>213</v>
       </c>
-      <c r="N1" s="119" t="s">
+      <c r="N1" s="126" t="s">
         <v>203</v>
       </c>
-      <c r="O1" s="120"/>
-      <c r="P1" s="132"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="128"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -31065,14 +31060,14 @@
       <c r="K2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="137"/>
-      <c r="N2" s="130" t="s">
+      <c r="L2" s="118"/>
+      <c r="N2" s="119" t="s">
         <v>205</v>
       </c>
-      <c r="O2" s="129" t="s">
+      <c r="O2" s="118" t="s">
         <v>204</v>
       </c>
-      <c r="P2" s="131" t="s">
+      <c r="P2" s="120" t="s">
         <v>4</v>
       </c>
     </row>
@@ -31086,7 +31081,7 @@
         <v>20</v>
       </c>
       <c r="H3" s="111" t="str">
-        <f>_xlfn.XLOOKUP(E3,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" ref="H3:H34" si="0">_xlfn.XLOOKUP(E3,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v/>
       </c>
       <c r="I3" s="111" t="str">
@@ -31097,17 +31092,17 @@
         <f>SUM(J4:J19)</f>
         <v>1493.463760343242</v>
       </c>
-      <c r="L3" s="139" t="str">
+      <c r="L3" s="110" t="str">
         <f>IFERROR(I3+($P$10*F3),"")</f>
         <v/>
       </c>
       <c r="N3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="125" t="s">
+      <c r="O3" t="s">
         <v>206</v>
       </c>
-      <c r="P3" s="133">
+      <c r="P3" s="121">
         <f>K74</f>
         <v>13026.517352669423</v>
       </c>
@@ -31131,11 +31126,11 @@
         <v>103</v>
       </c>
       <c r="H4" s="111">
-        <f>_xlfn.XLOOKUP(E4,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I4" s="111">
-        <f t="shared" ref="I4:I67" si="0">IFERROR(H4*F4,"")</f>
+        <f t="shared" ref="I4:I67" si="1">IFERROR(H4*F4,"")</f>
         <v>99.564250689549496</v>
       </c>
       <c r="J4" s="111">
@@ -31143,17 +31138,17 @@
         <v>99.564250689549496</v>
       </c>
       <c r="K4" s="112"/>
-      <c r="L4" s="139">
-        <f t="shared" ref="L4:L67" si="1">IFERROR(I4+($P$10*F4),"")</f>
+      <c r="L4" s="110">
+        <f t="shared" ref="L4:L67" si="2">IFERROR(I4+($P$10*F4),"")</f>
         <v>122.72425068954949</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="125" t="s">
+      <c r="O4" t="s">
         <v>207</v>
       </c>
-      <c r="P4" s="133">
+      <c r="P4" s="121">
         <f>K81</f>
         <v>172.5</v>
       </c>
@@ -31177,11 +31172,11 @@
         <v>103</v>
       </c>
       <c r="H5" s="111">
-        <f>_xlfn.XLOOKUP(E5,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I5" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J5" s="111">
@@ -31189,14 +31184,14 @@
         <v>99.564250689549496</v>
       </c>
       <c r="K5" s="112"/>
-      <c r="L5" s="139">
-        <f t="shared" si="1"/>
+      <c r="L5" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="125" t="s">
+      <c r="O5" t="s">
         <v>208</v>
       </c>
       <c r="P5" s="112">
@@ -31214,11 +31209,11 @@
         <v>23</v>
       </c>
       <c r="H6" s="111" t="str">
-        <f>_xlfn.XLOOKUP(E6,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I6" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J6" s="111">
@@ -31226,12 +31221,12 @@
         <v>1294.3352589641431</v>
       </c>
       <c r="K6" s="112"/>
-      <c r="L6" s="139"/>
-      <c r="N6" s="119" t="s">
+      <c r="L6" s="110"/>
+      <c r="N6" s="126" t="s">
         <v>115</v>
       </c>
-      <c r="O6" s="120"/>
-      <c r="P6" s="134">
+      <c r="O6" s="127"/>
+      <c r="P6" s="122">
         <f>SUM(P3:P5)</f>
         <v>16498.77169083678</v>
       </c>
@@ -31255,17 +31250,17 @@
         <v>103</v>
       </c>
       <c r="H7" s="111">
-        <f>_xlfn.XLOOKUP(E7,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I7" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J7" s="111"/>
       <c r="K7" s="112"/>
-      <c r="L7" s="139">
-        <f t="shared" si="1"/>
+      <c r="L7" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
     </row>
@@ -31288,17 +31283,17 @@
         <v>103</v>
       </c>
       <c r="H8" s="111">
-        <f>_xlfn.XLOOKUP(E8,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I8" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J8" s="111"/>
       <c r="K8" s="112"/>
-      <c r="L8" s="139">
-        <f t="shared" si="1"/>
+      <c r="L8" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
       <c r="O8" t="s">
@@ -31328,23 +31323,23 @@
         <v>103</v>
       </c>
       <c r="H9" s="111">
-        <f>_xlfn.XLOOKUP(E9,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I9" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J9" s="111"/>
       <c r="K9" s="112"/>
-      <c r="L9" s="139">
-        <f t="shared" si="1"/>
+      <c r="L9" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
       <c r="O9" t="s">
         <v>214</v>
       </c>
-      <c r="P9" s="136">
+      <c r="P9" s="135">
         <f>SUM(F4:F73)</f>
         <v>300</v>
       </c>
@@ -31368,23 +31363,23 @@
         <v>103</v>
       </c>
       <c r="H10" s="111">
-        <f>_xlfn.XLOOKUP(E10,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I10" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J10" s="111"/>
       <c r="K10" s="112"/>
-      <c r="L10" s="139">
-        <f t="shared" si="1"/>
+      <c r="L10" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
       <c r="O10" t="s">
         <v>215</v>
       </c>
-      <c r="P10" s="136">
+      <c r="P10" s="123">
         <f>ROUNDUP(P8/P9,2)</f>
         <v>11.58</v>
       </c>
@@ -31408,17 +31403,17 @@
         <v>103</v>
       </c>
       <c r="H11" s="111">
-        <f>_xlfn.XLOOKUP(E11,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I11" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J11" s="111"/>
       <c r="K11" s="112"/>
-      <c r="L11" s="139">
-        <f t="shared" si="1"/>
+      <c r="L11" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
     </row>
@@ -31441,17 +31436,17 @@
         <v>103</v>
       </c>
       <c r="H12" s="111">
-        <f>_xlfn.XLOOKUP(E12,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I12" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J12" s="111"/>
       <c r="K12" s="112"/>
-      <c r="L12" s="139">
-        <f t="shared" si="1"/>
+      <c r="L12" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
     </row>
@@ -31474,17 +31469,17 @@
         <v>103</v>
       </c>
       <c r="H13" s="111">
-        <f>_xlfn.XLOOKUP(E13,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I13" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J13" s="111"/>
       <c r="K13" s="112"/>
-      <c r="L13" s="139">
-        <f t="shared" si="1"/>
+      <c r="L13" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
     </row>
@@ -31507,17 +31502,17 @@
         <v>103</v>
       </c>
       <c r="H14" s="111">
-        <f>_xlfn.XLOOKUP(E14,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I14" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J14" s="111"/>
       <c r="K14" s="112"/>
-      <c r="L14" s="139">
-        <f t="shared" si="1"/>
+      <c r="L14" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
     </row>
@@ -31540,17 +31535,17 @@
         <v>103</v>
       </c>
       <c r="H15" s="111">
-        <f>_xlfn.XLOOKUP(E15,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I15" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J15" s="111"/>
       <c r="K15" s="112"/>
-      <c r="L15" s="139">
-        <f t="shared" si="1"/>
+      <c r="L15" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
     </row>
@@ -31573,17 +31568,17 @@
         <v>103</v>
       </c>
       <c r="H16" s="111">
-        <f>_xlfn.XLOOKUP(E16,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I16" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J16" s="111"/>
       <c r="K16" s="112"/>
-      <c r="L16" s="139">
-        <f t="shared" si="1"/>
+      <c r="L16" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
     </row>
@@ -31606,17 +31601,17 @@
         <v>103</v>
       </c>
       <c r="H17" s="111">
-        <f>_xlfn.XLOOKUP(E17,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I17" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J17" s="111"/>
       <c r="K17" s="112"/>
-      <c r="L17" s="139">
-        <f t="shared" si="1"/>
+      <c r="L17" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
     </row>
@@ -31639,17 +31634,17 @@
         <v>103</v>
       </c>
       <c r="H18" s="111">
-        <f>_xlfn.XLOOKUP(E18,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I18" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J18" s="111"/>
       <c r="K18" s="112"/>
-      <c r="L18" s="139">
-        <f t="shared" si="1"/>
+      <c r="L18" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
     </row>
@@ -31672,17 +31667,17 @@
         <v>103</v>
       </c>
       <c r="H19" s="111">
-        <f>_xlfn.XLOOKUP(E19,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I19" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J19" s="111"/>
       <c r="K19" s="112"/>
-      <c r="L19" s="139">
-        <f t="shared" si="1"/>
+      <c r="L19" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
       <c r="Q19" s="7" t="s">
@@ -31702,11 +31697,11 @@
         <v>37</v>
       </c>
       <c r="H20" s="111" t="str">
-        <f>_xlfn.XLOOKUP(E20,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I20" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J20" s="111"/>
@@ -31714,8 +31709,8 @@
         <f>SUM(J21:J30)</f>
         <v>2307.2124370166389</v>
       </c>
-      <c r="L20" s="139" t="str">
-        <f t="shared" si="1"/>
+      <c r="L20" s="110" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q20" t="s">
@@ -31745,20 +31740,20 @@
         <v>103</v>
       </c>
       <c r="H21" s="111">
-        <f>_xlfn.XLOOKUP(E21,$Q$20:$Q$25,$R$20:$R$25,"")</f>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="I21" s="111">
         <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
+      <c r="I21" s="111">
+        <f t="shared" si="1"/>
+        <v>42.159269173306768</v>
+      </c>
       <c r="J21" s="111">
-        <f t="shared" ref="J21:J30" si="2">I21</f>
+        <f t="shared" ref="J21:J30" si="3">I21</f>
         <v>42.159269173306768</v>
       </c>
       <c r="K21" s="112"/>
-      <c r="L21" s="139">
-        <f t="shared" si="1"/>
+      <c r="L21" s="110">
+        <f t="shared" si="2"/>
         <v>53.739269173306766</v>
       </c>
       <c r="Q21" t="s">
@@ -31788,20 +31783,20 @@
         <v>103</v>
       </c>
       <c r="H22" s="111">
-        <f>_xlfn.XLOOKUP(E22,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>45.220459339114129</v>
       </c>
       <c r="I22" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>180.88183735645651</v>
       </c>
       <c r="J22" s="111">
+        <f t="shared" si="3"/>
+        <v>180.88183735645651</v>
+      </c>
+      <c r="K22" s="112"/>
+      <c r="L22" s="110">
         <f t="shared" si="2"/>
-        <v>180.88183735645651</v>
-      </c>
-      <c r="K22" s="112"/>
-      <c r="L22" s="139">
-        <f t="shared" si="1"/>
         <v>227.20183735645651</v>
       </c>
       <c r="Q22" t="s">
@@ -31831,20 +31826,20 @@
         <v>103</v>
       </c>
       <c r="H23" s="111">
-        <f>_xlfn.XLOOKUP(E23,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
       <c r="I23" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>84.318538346613536</v>
       </c>
       <c r="J23" s="111">
+        <f t="shared" si="3"/>
+        <v>84.318538346613536</v>
+      </c>
+      <c r="K23" s="112"/>
+      <c r="L23" s="110">
         <f t="shared" si="2"/>
-        <v>84.318538346613536</v>
-      </c>
-      <c r="K23" s="112"/>
-      <c r="L23" s="139">
-        <f t="shared" si="1"/>
         <v>107.47853834661353</v>
       </c>
       <c r="Q23" t="s">
@@ -31874,20 +31869,20 @@
         <v>103</v>
       </c>
       <c r="H24" s="111">
-        <f>_xlfn.XLOOKUP(E24,$Q$20:$Q$25,$R$20:$R$25,"")</f>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="I24" s="111">
         <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
+      <c r="I24" s="111">
+        <f t="shared" si="1"/>
+        <v>42.159269173306768</v>
+      </c>
       <c r="J24" s="111">
+        <f t="shared" si="3"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="K24" s="112"/>
+      <c r="L24" s="110">
         <f t="shared" si="2"/>
-        <v>42.159269173306768</v>
-      </c>
-      <c r="K24" s="112"/>
-      <c r="L24" s="139">
-        <f t="shared" si="1"/>
         <v>53.739269173306766</v>
       </c>
       <c r="Q24" t="s">
@@ -31917,20 +31912,20 @@
         <v>103</v>
       </c>
       <c r="H25" s="111">
-        <f>_xlfn.XLOOKUP(E25,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
       <c r="I25" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>84.318538346613536</v>
       </c>
       <c r="J25" s="111">
+        <f t="shared" si="3"/>
+        <v>84.318538346613536</v>
+      </c>
+      <c r="K25" s="112"/>
+      <c r="L25" s="110">
         <f t="shared" si="2"/>
-        <v>84.318538346613536</v>
-      </c>
-      <c r="K25" s="112"/>
-      <c r="L25" s="139">
-        <f t="shared" si="1"/>
         <v>107.47853834661353</v>
       </c>
       <c r="Q25" t="s">
@@ -31960,20 +31955,20 @@
         <v>103</v>
       </c>
       <c r="H26" s="111">
-        <f>_xlfn.XLOOKUP(E26,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>45.220459339114129</v>
       </c>
       <c r="I26" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>271.32275603468474</v>
       </c>
       <c r="J26" s="111">
+        <f t="shared" si="3"/>
+        <v>271.32275603468474</v>
+      </c>
+      <c r="K26" s="112"/>
+      <c r="L26" s="110">
         <f t="shared" si="2"/>
-        <v>271.32275603468474</v>
-      </c>
-      <c r="K26" s="112"/>
-      <c r="L26" s="139">
-        <f t="shared" si="1"/>
         <v>340.80275603468476</v>
       </c>
     </row>
@@ -31996,20 +31991,20 @@
         <v>103</v>
       </c>
       <c r="H27" s="111">
-        <f>_xlfn.XLOOKUP(E27,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
       <c r="I27" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>927.5039218127489</v>
       </c>
       <c r="J27" s="111">
+        <f t="shared" si="3"/>
+        <v>927.5039218127489</v>
+      </c>
+      <c r="K27" s="112"/>
+      <c r="L27" s="110">
         <f t="shared" si="2"/>
-        <v>927.5039218127489</v>
-      </c>
-      <c r="K27" s="112"/>
-      <c r="L27" s="139">
-        <f t="shared" si="1"/>
         <v>1182.2639218127488</v>
       </c>
     </row>
@@ -32032,20 +32027,20 @@
         <v>103</v>
       </c>
       <c r="H28" s="111">
-        <f>_xlfn.XLOOKUP(E28,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
       <c r="I28" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>252.95561503984061</v>
       </c>
       <c r="J28" s="111">
+        <f t="shared" si="3"/>
+        <v>252.95561503984061</v>
+      </c>
+      <c r="K28" s="112"/>
+      <c r="L28" s="110">
         <f t="shared" si="2"/>
-        <v>252.95561503984061</v>
-      </c>
-      <c r="K28" s="112"/>
-      <c r="L28" s="139">
-        <f t="shared" si="1"/>
         <v>322.43561503984063</v>
       </c>
     </row>
@@ -32068,20 +32063,20 @@
         <v>103</v>
       </c>
       <c r="H29" s="111">
-        <f>_xlfn.XLOOKUP(E29,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
       <c r="I29" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>84.318538346613536</v>
       </c>
       <c r="J29" s="111">
+        <f t="shared" si="3"/>
+        <v>84.318538346613536</v>
+      </c>
+      <c r="K29" s="112"/>
+      <c r="L29" s="110">
         <f t="shared" si="2"/>
-        <v>84.318538346613536</v>
-      </c>
-      <c r="K29" s="112"/>
-      <c r="L29" s="139">
-        <f t="shared" si="1"/>
         <v>107.47853834661353</v>
       </c>
     </row>
@@ -32104,20 +32099,20 @@
         <v>103</v>
       </c>
       <c r="H30" s="111">
-        <f>_xlfn.XLOOKUP(E30,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>42.159269173306768</v>
       </c>
       <c r="I30" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>337.27415338645415</v>
       </c>
       <c r="J30" s="111">
+        <f t="shared" si="3"/>
+        <v>337.27415338645415</v>
+      </c>
+      <c r="K30" s="112"/>
+      <c r="L30" s="110">
         <f t="shared" si="2"/>
-        <v>337.27415338645415</v>
-      </c>
-      <c r="K30" s="112"/>
-      <c r="L30" s="139">
-        <f t="shared" si="1"/>
         <v>429.91415338645413</v>
       </c>
     </row>
@@ -32131,11 +32126,11 @@
         <v>48</v>
       </c>
       <c r="H31" s="111" t="str">
-        <f>_xlfn.XLOOKUP(E31,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I31" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J31" s="111"/>
@@ -32143,8 +32138,8 @@
         <f>SUM(J32:J38)</f>
         <v>2273.3693320555312</v>
       </c>
-      <c r="L31" s="139" t="str">
-        <f t="shared" si="1"/>
+      <c r="L31" s="110" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -32167,20 +32162,20 @@
         <v>103</v>
       </c>
       <c r="H32" s="111">
-        <f>_xlfn.XLOOKUP(E32,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>49.154057104913683</v>
       </c>
       <c r="I32" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>491.54057104913682</v>
       </c>
       <c r="J32" s="111">
-        <f t="shared" ref="J32:J38" si="3">I32</f>
+        <f t="shared" ref="J32:J38" si="4">I32</f>
         <v>491.54057104913682</v>
       </c>
       <c r="K32" s="112"/>
-      <c r="L32" s="139">
-        <f t="shared" si="1"/>
+      <c r="L32" s="110">
+        <f t="shared" si="2"/>
         <v>607.34057104913677</v>
       </c>
     </row>
@@ -32203,20 +32198,20 @@
         <v>103</v>
       </c>
       <c r="H33" s="111">
-        <f>_xlfn.XLOOKUP(E33,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I33" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115.65544251565169</v>
       </c>
       <c r="J33" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>115.65544251565169</v>
       </c>
       <c r="K33" s="112"/>
-      <c r="L33" s="139">
-        <f t="shared" si="1"/>
+      <c r="L33" s="110">
+        <f t="shared" si="2"/>
         <v>150.39544251565169</v>
       </c>
     </row>
@@ -32239,20 +32234,20 @@
         <v>103</v>
       </c>
       <c r="H34" s="111">
-        <f>_xlfn.XLOOKUP(E34,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="0"/>
         <v>43.846666276072185</v>
       </c>
       <c r="I34" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>350.77333020857748</v>
       </c>
       <c r="J34" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>350.77333020857748</v>
       </c>
       <c r="K34" s="112"/>
-      <c r="L34" s="139">
-        <f t="shared" si="1"/>
+      <c r="L34" s="110">
+        <f t="shared" si="2"/>
         <v>443.41333020857746</v>
       </c>
     </row>
@@ -32275,20 +32270,20 @@
         <v>103</v>
       </c>
       <c r="H35" s="111">
-        <f>_xlfn.XLOOKUP(E35,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" ref="H35:H66" si="5">_xlfn.XLOOKUP(E35,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>43.846666276072185</v>
       </c>
       <c r="I35" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>175.38666510428874</v>
       </c>
       <c r="J35" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>175.38666510428874</v>
       </c>
       <c r="K35" s="112"/>
-      <c r="L35" s="139">
-        <f t="shared" si="1"/>
+      <c r="L35" s="110">
+        <f t="shared" si="2"/>
         <v>221.70666510428873</v>
       </c>
     </row>
@@ -32311,20 +32306,20 @@
         <v>103</v>
       </c>
       <c r="H36" s="111">
-        <f>_xlfn.XLOOKUP(E36,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>43.846666276072185</v>
       </c>
       <c r="I36" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>263.07999765643308</v>
       </c>
       <c r="J36" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>263.07999765643308</v>
       </c>
       <c r="K36" s="112"/>
-      <c r="L36" s="139">
-        <f t="shared" si="1"/>
+      <c r="L36" s="110">
+        <f t="shared" si="2"/>
         <v>332.5599976564331</v>
       </c>
     </row>
@@ -32347,20 +32342,20 @@
         <v>103</v>
       </c>
       <c r="H37" s="111">
-        <f>_xlfn.XLOOKUP(E37,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>43.846666276072185</v>
       </c>
       <c r="I37" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>438.46666276072187</v>
       </c>
       <c r="J37" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>438.46666276072187</v>
       </c>
       <c r="K37" s="112"/>
-      <c r="L37" s="139">
-        <f t="shared" si="1"/>
+      <c r="L37" s="110">
+        <f t="shared" si="2"/>
         <v>554.26666276072183</v>
       </c>
     </row>
@@ -32383,20 +32378,20 @@
         <v>103</v>
       </c>
       <c r="H38" s="111">
-        <f>_xlfn.XLOOKUP(E38,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>43.846666276072185</v>
       </c>
       <c r="I38" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>438.46666276072187</v>
       </c>
       <c r="J38" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>438.46666276072187</v>
       </c>
       <c r="K38" s="112"/>
-      <c r="L38" s="139">
-        <f t="shared" si="1"/>
+      <c r="L38" s="110">
+        <f t="shared" si="2"/>
         <v>554.26666276072183</v>
       </c>
     </row>
@@ -32419,11 +32414,11 @@
         <v>103</v>
       </c>
       <c r="H39" s="111">
-        <f>_xlfn.XLOOKUP(E39,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>43.846666276072185</v>
       </c>
       <c r="I39" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>131.53999882821654</v>
       </c>
       <c r="J39" s="111">
@@ -32434,8 +32429,8 @@
         <f>SUM(J39)</f>
         <v>131.53999882821654</v>
       </c>
-      <c r="L39" s="139">
-        <f t="shared" si="1"/>
+      <c r="L39" s="110">
+        <f t="shared" si="2"/>
         <v>166.27999882821655</v>
       </c>
     </row>
@@ -32449,11 +32444,11 @@
         <v>56</v>
       </c>
       <c r="H40" s="111" t="str">
-        <f>_xlfn.XLOOKUP(E40,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="I40" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J40" s="111"/>
@@ -32461,8 +32456,8 @@
         <f>SUM(J41:J50)</f>
         <v>4386.8987937884322</v>
       </c>
-      <c r="L40" s="139" t="str">
-        <f t="shared" si="1"/>
+      <c r="L40" s="110" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -32485,11 +32480,11 @@
         <v>103</v>
       </c>
       <c r="H41" s="111">
-        <f>_xlfn.XLOOKUP(E41,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>49.154057104913683</v>
       </c>
       <c r="I41" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>196.61622841965473</v>
       </c>
       <c r="J41" s="111">
@@ -32497,8 +32492,8 @@
         <v>196.61622841965473</v>
       </c>
       <c r="K41" s="112"/>
-      <c r="L41" s="139">
-        <f t="shared" si="1"/>
+      <c r="L41" s="110">
+        <f t="shared" si="2"/>
         <v>242.93622841965473</v>
       </c>
     </row>
@@ -32521,11 +32516,11 @@
         <v>103</v>
       </c>
       <c r="H42" s="111">
-        <f>_xlfn.XLOOKUP(E42,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>49.154057104913683</v>
       </c>
       <c r="I42" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>147.46217131474106</v>
       </c>
       <c r="J42" s="111">
@@ -32533,8 +32528,8 @@
         <v>147.46217131474106</v>
       </c>
       <c r="K42" s="112"/>
-      <c r="L42" s="139">
-        <f t="shared" si="1"/>
+      <c r="L42" s="110">
+        <f t="shared" si="2"/>
         <v>182.20217131474107</v>
       </c>
     </row>
@@ -32548,11 +32543,11 @@
         <v>59</v>
       </c>
       <c r="H43" s="111" t="str">
-        <f>_xlfn.XLOOKUP(E43,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="I43" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J43" s="111">
@@ -32560,8 +32555,8 @@
         <v>4042.8203940540366</v>
       </c>
       <c r="K43" s="112"/>
-      <c r="L43" s="139" t="str">
-        <f t="shared" si="1"/>
+      <c r="L43" s="110" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -32584,17 +32579,17 @@
         <v>103</v>
       </c>
       <c r="H44" s="111">
-        <f>_xlfn.XLOOKUP(E44,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I44" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>848.13991178144579</v>
       </c>
       <c r="J44" s="111"/>
       <c r="K44" s="112"/>
-      <c r="L44" s="139">
-        <f t="shared" si="1"/>
+      <c r="L44" s="110">
+        <f t="shared" si="2"/>
         <v>1102.8999117814458</v>
       </c>
     </row>
@@ -32617,17 +32612,17 @@
         <v>103</v>
       </c>
       <c r="H45" s="111">
-        <f>_xlfn.XLOOKUP(E45,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I45" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>385.51814171883899</v>
       </c>
       <c r="J45" s="111"/>
       <c r="K45" s="112"/>
-      <c r="L45" s="139">
-        <f t="shared" si="1"/>
+      <c r="L45" s="110">
+        <f t="shared" si="2"/>
         <v>501.318141718839</v>
       </c>
     </row>
@@ -32650,17 +32645,17 @@
         <v>103</v>
       </c>
       <c r="H46" s="111">
-        <f>_xlfn.XLOOKUP(E46,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>43.846666276072185</v>
       </c>
       <c r="I46" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1096.1666569018046</v>
       </c>
       <c r="J46" s="111"/>
       <c r="K46" s="112"/>
-      <c r="L46" s="139">
-        <f t="shared" si="1"/>
+      <c r="L46" s="110">
+        <f t="shared" si="2"/>
         <v>1385.6666569018046</v>
       </c>
     </row>
@@ -32683,17 +32678,17 @@
         <v>103</v>
       </c>
       <c r="H47" s="111">
-        <f>_xlfn.XLOOKUP(E47,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I47" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>231.31088503130337</v>
       </c>
       <c r="J47" s="111"/>
       <c r="K47" s="112"/>
-      <c r="L47" s="139">
-        <f t="shared" si="1"/>
+      <c r="L47" s="110">
+        <f t="shared" si="2"/>
         <v>300.79088503130339</v>
       </c>
     </row>
@@ -32716,17 +32711,17 @@
         <v>103</v>
       </c>
       <c r="H48" s="111">
-        <f>_xlfn.XLOOKUP(E48,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>43.846666276072185</v>
       </c>
       <c r="I48" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>657.69999414108281</v>
       </c>
       <c r="J48" s="111"/>
       <c r="K48" s="112"/>
-      <c r="L48" s="139">
-        <f t="shared" si="1"/>
+      <c r="L48" s="110">
+        <f t="shared" si="2"/>
         <v>831.39999414108274</v>
       </c>
     </row>
@@ -32749,17 +32744,17 @@
         <v>103</v>
       </c>
       <c r="H49" s="111">
-        <f>_xlfn.XLOOKUP(E49,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>43.846666276072185</v>
       </c>
       <c r="I49" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>438.46666276072187</v>
       </c>
       <c r="J49" s="111"/>
       <c r="K49" s="112"/>
-      <c r="L49" s="139">
-        <f t="shared" si="1"/>
+      <c r="L49" s="110">
+        <f t="shared" si="2"/>
         <v>554.26666276072183</v>
       </c>
     </row>
@@ -32782,17 +32777,17 @@
         <v>103</v>
       </c>
       <c r="H50" s="111">
-        <f>_xlfn.XLOOKUP(E50,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I50" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>385.51814171883899</v>
       </c>
       <c r="J50" s="111"/>
       <c r="K50" s="112"/>
-      <c r="L50" s="139">
-        <f t="shared" si="1"/>
+      <c r="L50" s="110">
+        <f t="shared" si="2"/>
         <v>501.318141718839</v>
       </c>
     </row>
@@ -32806,11 +32801,11 @@
         <v>66</v>
       </c>
       <c r="H51" s="111" t="str">
-        <f>_xlfn.XLOOKUP(E51,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="I51" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J51" s="111"/>
@@ -32818,8 +32813,8 @@
         <f>SUM(J52:J60)</f>
         <v>1051.4886868492417</v>
       </c>
-      <c r="L51" s="139" t="str">
-        <f t="shared" si="1"/>
+      <c r="L51" s="110" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -32842,20 +32837,20 @@
         <v>103</v>
       </c>
       <c r="H52" s="111">
-        <f>_xlfn.XLOOKUP(E52,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I52" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>154.20725668753559</v>
       </c>
       <c r="J52" s="111">
-        <f t="shared" ref="J52:J60" si="4">I52</f>
+        <f t="shared" ref="J52:J60" si="6">I52</f>
         <v>154.20725668753559</v>
       </c>
       <c r="K52" s="112"/>
-      <c r="L52" s="139">
-        <f t="shared" si="1"/>
+      <c r="L52" s="110">
+        <f t="shared" si="2"/>
         <v>200.52725668753558</v>
       </c>
     </row>
@@ -32878,20 +32873,20 @@
         <v>103</v>
       </c>
       <c r="H53" s="111">
-        <f>_xlfn.XLOOKUP(E53,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I53" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115.65544251565169</v>
       </c>
       <c r="J53" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>115.65544251565169</v>
       </c>
       <c r="K53" s="112"/>
-      <c r="L53" s="139">
-        <f t="shared" si="1"/>
+      <c r="L53" s="110">
+        <f t="shared" si="2"/>
         <v>150.39544251565169</v>
       </c>
     </row>
@@ -32914,20 +32909,20 @@
         <v>103</v>
       </c>
       <c r="H54" s="111">
-        <f>_xlfn.XLOOKUP(E54,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I54" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>192.7590708594195</v>
       </c>
       <c r="J54" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>192.7590708594195</v>
       </c>
       <c r="K54" s="112"/>
-      <c r="L54" s="139">
-        <f t="shared" si="1"/>
+      <c r="L54" s="110">
+        <f t="shared" si="2"/>
         <v>250.6590708594195</v>
       </c>
     </row>
@@ -32950,20 +32945,20 @@
         <v>103</v>
       </c>
       <c r="H55" s="111">
-        <f>_xlfn.XLOOKUP(E55,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I55" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115.65544251565169</v>
       </c>
       <c r="J55" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>115.65544251565169</v>
       </c>
       <c r="K55" s="112"/>
-      <c r="L55" s="139">
-        <f t="shared" si="1"/>
+      <c r="L55" s="110">
+        <f t="shared" si="2"/>
         <v>150.39544251565169</v>
       </c>
     </row>
@@ -32986,20 +32981,20 @@
         <v>103</v>
       </c>
       <c r="H56" s="111">
-        <f>_xlfn.XLOOKUP(E56,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I56" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115.65544251565169</v>
       </c>
       <c r="J56" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>115.65544251565169</v>
       </c>
       <c r="K56" s="112"/>
-      <c r="L56" s="139">
-        <f t="shared" si="1"/>
+      <c r="L56" s="110">
+        <f t="shared" si="2"/>
         <v>150.39544251565169</v>
       </c>
     </row>
@@ -33022,20 +33017,20 @@
         <v>103</v>
       </c>
       <c r="H57" s="111">
-        <f>_xlfn.XLOOKUP(E57,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I57" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>77.103628343767795</v>
       </c>
       <c r="J57" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>77.103628343767795</v>
       </c>
       <c r="K57" s="112"/>
-      <c r="L57" s="139">
-        <f t="shared" si="1"/>
+      <c r="L57" s="110">
+        <f t="shared" si="2"/>
         <v>100.26362834376779</v>
       </c>
     </row>
@@ -33058,20 +33053,20 @@
         <v>103</v>
       </c>
       <c r="H58" s="111">
-        <f>_xlfn.XLOOKUP(E58,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I58" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115.65544251565169</v>
       </c>
       <c r="J58" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>115.65544251565169</v>
       </c>
       <c r="K58" s="112"/>
-      <c r="L58" s="139">
-        <f t="shared" si="1"/>
+      <c r="L58" s="110">
+        <f t="shared" si="2"/>
         <v>150.39544251565169</v>
       </c>
     </row>
@@ -33094,20 +33089,20 @@
         <v>103</v>
       </c>
       <c r="H59" s="111">
-        <f>_xlfn.XLOOKUP(E59,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>38.551814171883898</v>
       </c>
       <c r="I59" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>77.103628343767795</v>
       </c>
       <c r="J59" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>77.103628343767795</v>
       </c>
       <c r="K59" s="112"/>
-      <c r="L59" s="139">
-        <f t="shared" si="1"/>
+      <c r="L59" s="110">
+        <f t="shared" si="2"/>
         <v>100.26362834376779</v>
       </c>
     </row>
@@ -33130,20 +33125,20 @@
         <v>103</v>
       </c>
       <c r="H60" s="111">
-        <f>_xlfn.XLOOKUP(E60,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>43.846666276072185</v>
       </c>
       <c r="I60" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>87.693332552144369</v>
       </c>
       <c r="J60" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>87.693332552144369</v>
       </c>
       <c r="K60" s="112"/>
-      <c r="L60" s="139">
-        <f t="shared" si="1"/>
+      <c r="L60" s="110">
+        <f t="shared" si="2"/>
         <v>110.85333255214437</v>
       </c>
     </row>
@@ -33157,11 +33152,11 @@
         <v>74</v>
       </c>
       <c r="H61" s="111" t="str">
-        <f>_xlfn.XLOOKUP(E61,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="I61" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J61" s="111"/>
@@ -33169,8 +33164,8 @@
         <f>SUM(J62:J73)</f>
         <v>1382.5443437881208</v>
       </c>
-      <c r="L61" s="139" t="str">
-        <f t="shared" si="1"/>
+      <c r="L61" s="110" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -33193,20 +33188,20 @@
         <v>103</v>
       </c>
       <c r="H62" s="111">
-        <f>_xlfn.XLOOKUP(E62,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I62" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>49.782125344774748</v>
       </c>
       <c r="J62" s="111">
-        <f t="shared" ref="J62:J73" si="5">I62</f>
+        <f t="shared" ref="J62:J73" si="7">I62</f>
         <v>49.782125344774748</v>
       </c>
       <c r="K62" s="112"/>
-      <c r="L62" s="139">
-        <f t="shared" si="1"/>
+      <c r="L62" s="110">
+        <f t="shared" si="2"/>
         <v>61.362125344774746</v>
       </c>
     </row>
@@ -33229,20 +33224,20 @@
         <v>103</v>
       </c>
       <c r="H63" s="111">
-        <f>_xlfn.XLOOKUP(E63,$Q$20:$Q$25,$R$20:$R$25,"")</f>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="I63" s="111">
-        <f t="shared" si="0"/>
-        <v>49.782125344774748</v>
-      </c>
-      <c r="J63" s="111">
         <f t="shared" si="5"/>
         <v>49.782125344774748</v>
       </c>
+      <c r="I63" s="111">
+        <f t="shared" si="1"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="J63" s="111">
+        <f t="shared" si="7"/>
+        <v>49.782125344774748</v>
+      </c>
       <c r="K63" s="112"/>
-      <c r="L63" s="139">
-        <f t="shared" si="1"/>
+      <c r="L63" s="110">
+        <f t="shared" si="2"/>
         <v>61.362125344774746</v>
       </c>
     </row>
@@ -33265,20 +33260,20 @@
         <v>103</v>
       </c>
       <c r="H64" s="111">
-        <f>_xlfn.XLOOKUP(E64,$Q$20:$Q$25,$R$20:$R$25,"")</f>
-        <v>45.220459339114129</v>
-      </c>
-      <c r="I64" s="111">
-        <f t="shared" si="0"/>
-        <v>45.220459339114129</v>
-      </c>
-      <c r="J64" s="111">
         <f t="shared" si="5"/>
         <v>45.220459339114129</v>
       </c>
+      <c r="I64" s="111">
+        <f t="shared" si="1"/>
+        <v>45.220459339114129</v>
+      </c>
+      <c r="J64" s="111">
+        <f t="shared" si="7"/>
+        <v>45.220459339114129</v>
+      </c>
       <c r="K64" s="112"/>
-      <c r="L64" s="139">
-        <f t="shared" si="1"/>
+      <c r="L64" s="110">
+        <f t="shared" si="2"/>
         <v>56.800459339114127</v>
       </c>
     </row>
@@ -33301,20 +33296,20 @@
         <v>103</v>
       </c>
       <c r="H65" s="111">
-        <f>_xlfn.XLOOKUP(E65,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>45.220459339114129</v>
       </c>
       <c r="I65" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>90.440918678228257</v>
       </c>
       <c r="J65" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>90.440918678228257</v>
       </c>
       <c r="K65" s="112"/>
-      <c r="L65" s="139">
-        <f t="shared" si="1"/>
+      <c r="L65" s="110">
+        <f t="shared" si="2"/>
         <v>113.60091867822825</v>
       </c>
     </row>
@@ -33337,20 +33332,20 @@
         <v>103</v>
       </c>
       <c r="H66" s="111">
-        <f>_xlfn.XLOOKUP(E66,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="5"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I66" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J66" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>99.564250689549496</v>
       </c>
       <c r="K66" s="112"/>
-      <c r="L66" s="139">
-        <f t="shared" si="1"/>
+      <c r="L66" s="110">
+        <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
     </row>
@@ -33373,20 +33368,20 @@
         <v>103</v>
       </c>
       <c r="H67" s="111">
-        <f>_xlfn.XLOOKUP(E67,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" ref="H67:H73" si="8">_xlfn.XLOOKUP(E67,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>42.159269173306768</v>
       </c>
       <c r="I67" s="111">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>126.4778075199203</v>
       </c>
       <c r="J67" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>126.4778075199203</v>
       </c>
       <c r="K67" s="112"/>
-      <c r="L67" s="139">
-        <f t="shared" si="1"/>
+      <c r="L67" s="110">
+        <f t="shared" si="2"/>
         <v>161.21780751992031</v>
       </c>
     </row>
@@ -33409,20 +33404,20 @@
         <v>103</v>
       </c>
       <c r="H68" s="111">
-        <f>_xlfn.XLOOKUP(E68,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="8"/>
         <v>49.154057104913683</v>
       </c>
       <c r="I68" s="111">
-        <f t="shared" ref="I68:I73" si="6">IFERROR(H68*F68,"")</f>
+        <f t="shared" ref="I68:I73" si="9">IFERROR(H68*F68,"")</f>
         <v>245.77028552456841</v>
       </c>
       <c r="J68" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>245.77028552456841</v>
       </c>
       <c r="K68" s="112"/>
-      <c r="L68" s="139">
-        <f t="shared" ref="L68:L73" si="7">IFERROR(I68+($P$10*F68),"")</f>
+      <c r="L68" s="110">
+        <f t="shared" ref="L68:L73" si="10">IFERROR(I68+($P$10*F68),"")</f>
         <v>303.67028552456838</v>
       </c>
     </row>
@@ -33445,20 +33440,20 @@
         <v>103</v>
       </c>
       <c r="H69" s="111">
-        <f>_xlfn.XLOOKUP(E69,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="8"/>
         <v>43.846666276072185</v>
       </c>
       <c r="I69" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>219.23333138036094</v>
       </c>
       <c r="J69" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>219.23333138036094</v>
       </c>
       <c r="K69" s="112"/>
-      <c r="L69" s="139">
-        <f t="shared" si="7"/>
+      <c r="L69" s="110">
+        <f t="shared" si="10"/>
         <v>277.13333138036091</v>
       </c>
     </row>
@@ -33481,20 +33476,20 @@
         <v>103</v>
       </c>
       <c r="H70" s="111">
-        <f>_xlfn.XLOOKUP(E70,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="8"/>
         <v>43.846666276072185</v>
       </c>
       <c r="I70" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>87.693332552144369</v>
       </c>
       <c r="J70" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>87.693332552144369</v>
       </c>
       <c r="K70" s="112"/>
-      <c r="L70" s="139">
-        <f t="shared" si="7"/>
+      <c r="L70" s="110">
+        <f t="shared" si="10"/>
         <v>110.85333255214437</v>
       </c>
     </row>
@@ -33517,20 +33512,20 @@
         <v>103</v>
       </c>
       <c r="H71" s="111">
-        <f>_xlfn.XLOOKUP(E71,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="8"/>
         <v>43.846666276072185</v>
       </c>
       <c r="I71" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>219.23333138036094</v>
       </c>
       <c r="J71" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>219.23333138036094</v>
       </c>
       <c r="K71" s="112"/>
-      <c r="L71" s="139">
-        <f t="shared" si="7"/>
+      <c r="L71" s="110">
+        <f t="shared" si="10"/>
         <v>277.13333138036091</v>
       </c>
     </row>
@@ -33553,20 +33548,20 @@
         <v>103</v>
       </c>
       <c r="H72" s="111">
-        <f>_xlfn.XLOOKUP(E72,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="8"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I72" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>99.564250689549496</v>
       </c>
       <c r="J72" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>99.564250689549496</v>
       </c>
       <c r="K72" s="112"/>
-      <c r="L72" s="139">
-        <f t="shared" si="7"/>
+      <c r="L72" s="110">
+        <f t="shared" si="10"/>
         <v>122.72425068954949</v>
       </c>
     </row>
@@ -33589,41 +33584,41 @@
         <v>103</v>
       </c>
       <c r="H73" s="111">
-        <f>_xlfn.XLOOKUP(E73,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" si="8"/>
         <v>49.782125344774748</v>
       </c>
       <c r="I73" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>49.782125344774748</v>
       </c>
       <c r="J73" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>49.782125344774748</v>
       </c>
       <c r="K73" s="113"/>
-      <c r="L73" s="139">
-        <f t="shared" si="7"/>
+      <c r="L73" s="110">
+        <f t="shared" si="10"/>
         <v>61.362125344774746</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="119" t="s">
+      <c r="A74" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="B74" s="120"/>
-      <c r="C74" s="120"/>
-      <c r="D74" s="120"/>
-      <c r="E74" s="120"/>
-      <c r="F74" s="120"/>
-      <c r="G74" s="120"/>
-      <c r="H74" s="120"/>
-      <c r="I74" s="120"/>
-      <c r="J74" s="120"/>
+      <c r="B74" s="127"/>
+      <c r="C74" s="127"/>
+      <c r="D74" s="127"/>
+      <c r="E74" s="127"/>
+      <c r="F74" s="127"/>
+      <c r="G74" s="127"/>
+      <c r="H74" s="127"/>
+      <c r="I74" s="127"/>
+      <c r="J74" s="127"/>
       <c r="K74" s="114">
         <f>SUM(K3:K73)</f>
         <v>13026.517352669423</v>
       </c>
-      <c r="L74" s="135">
+      <c r="L74" s="111">
         <f>SUM(L3:L73)</f>
         <v>16500.51735266942</v>
       </c>
@@ -33633,20 +33628,20 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="121" t="s">
+      <c r="A76" s="132" t="s">
         <v>192</v>
       </c>
-      <c r="B76" s="122"/>
-      <c r="C76" s="122"/>
-      <c r="D76" s="122"/>
-      <c r="E76" s="122"/>
-      <c r="F76" s="122"/>
-      <c r="G76" s="122"/>
-      <c r="H76" s="122"/>
-      <c r="I76" s="122"/>
-      <c r="J76" s="122"/>
-      <c r="K76" s="123"/>
-      <c r="L76" s="138"/>
+      <c r="B76" s="133"/>
+      <c r="C76" s="133"/>
+      <c r="D76" s="133"/>
+      <c r="E76" s="133"/>
+      <c r="F76" s="133"/>
+      <c r="G76" s="133"/>
+      <c r="H76" s="133"/>
+      <c r="I76" s="133"/>
+      <c r="J76" s="133"/>
+      <c r="K76" s="134"/>
+      <c r="L76" s="124"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
@@ -33682,108 +33677,105 @@
       <c r="K77" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="L77" s="137"/>
+      <c r="L77" s="118"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B78" s="124"/>
-      <c r="C78" s="124"/>
-      <c r="D78" s="125" t="s">
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" t="s">
         <v>197</v>
       </c>
-      <c r="E78" s="125"/>
-      <c r="F78" s="125"/>
-      <c r="G78" s="125"/>
-      <c r="H78" s="127"/>
-      <c r="I78" s="127"/>
-      <c r="J78" s="127">
+      <c r="H78" s="116"/>
+      <c r="I78" s="116"/>
+      <c r="J78" s="116">
         <f>SUM(I79:I80)</f>
         <v>172.5</v>
       </c>
-      <c r="K78" s="128">
+      <c r="K78" s="117">
         <f>J78</f>
         <v>172.5</v>
       </c>
-      <c r="L78" s="127"/>
+      <c r="L78" s="116"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
-      <c r="B79" s="124" t="s">
+      <c r="B79" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C79" s="124"/>
-      <c r="D79" s="125" t="s">
+      <c r="C79" s="6"/>
+      <c r="D79" t="s">
         <v>198</v>
       </c>
-      <c r="E79" s="125" t="s">
+      <c r="E79" t="s">
         <v>200</v>
       </c>
-      <c r="F79" s="125">
+      <c r="F79">
         <v>150</v>
       </c>
-      <c r="G79" s="126" t="s">
+      <c r="G79" t="s">
         <v>201</v>
       </c>
-      <c r="H79" s="127">
+      <c r="H79" s="116">
         <v>0.35</v>
       </c>
-      <c r="I79" s="127">
+      <c r="I79" s="116">
         <f>H79*F79</f>
         <v>52.5</v>
       </c>
-      <c r="J79" s="127"/>
-      <c r="K79" s="128"/>
-      <c r="L79" s="127"/>
+      <c r="J79" s="116"/>
+      <c r="K79" s="117"/>
+      <c r="L79" s="116"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
-      <c r="B80" s="124" t="s">
+      <c r="B80" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C80" s="124"/>
-      <c r="D80" s="125" t="s">
+      <c r="C80" s="6"/>
+      <c r="D80" t="s">
         <v>199</v>
       </c>
-      <c r="E80" s="125" t="s">
+      <c r="E80" t="s">
         <v>200</v>
       </c>
-      <c r="F80" s="125">
+      <c r="F80">
         <v>6</v>
       </c>
-      <c r="G80" s="126" t="s">
+      <c r="G80" t="s">
         <v>202</v>
       </c>
-      <c r="H80" s="127">
+      <c r="H80" s="116">
         <v>20</v>
       </c>
-      <c r="I80" s="127">
+      <c r="I80" s="116">
         <f>H80*F80</f>
         <v>120</v>
       </c>
-      <c r="J80" s="127"/>
-      <c r="K80" s="128"/>
-      <c r="L80" s="127"/>
+      <c r="J80" s="116"/>
+      <c r="K80" s="117"/>
+      <c r="L80" s="116"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="119" t="s">
+      <c r="A81" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="B81" s="120"/>
-      <c r="C81" s="120"/>
-      <c r="D81" s="120"/>
-      <c r="E81" s="120"/>
-      <c r="F81" s="120"/>
-      <c r="G81" s="120"/>
-      <c r="H81" s="120"/>
-      <c r="I81" s="120"/>
-      <c r="J81" s="120"/>
+      <c r="B81" s="127"/>
+      <c r="C81" s="127"/>
+      <c r="D81" s="127"/>
+      <c r="E81" s="127"/>
+      <c r="F81" s="127"/>
+      <c r="G81" s="127"/>
+      <c r="H81" s="127"/>
+      <c r="I81" s="127"/>
+      <c r="J81" s="127"/>
       <c r="K81" s="114">
         <f>SUM(K78:K80)</f>
         <v>172.5</v>
       </c>
-      <c r="L81" s="135"/>
+      <c r="L81" s="111"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
@@ -33828,18 +33820,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="129" t="s">
         <v>210</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="118"/>
-      <c r="G1" s="119" t="s">
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="131"/>
+      <c r="G1" s="126" t="s">
         <v>209</v>
       </c>
-      <c r="H1" s="120"/>
-      <c r="I1" s="132"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="128"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -33857,13 +33849,13 @@
       <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="130" t="s">
+      <c r="G2" s="119" t="s">
         <v>205</v>
       </c>
-      <c r="H2" s="129" t="s">
+      <c r="H2" s="118" t="s">
         <v>204</v>
       </c>
-      <c r="I2" s="131" t="s">
+      <c r="I2" s="120" t="s">
         <v>4</v>
       </c>
     </row>
@@ -33875,7 +33867,7 @@
       <c r="C3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="136"/>
+      <c r="D3" s="123"/>
       <c r="E3" s="115">
         <f>SUM(D4:D6)</f>
         <v>1840.8637603432428</v>
@@ -33883,10 +33875,10 @@
       <c r="G3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="125" t="s">
+      <c r="H3" t="s">
         <v>206</v>
       </c>
-      <c r="I3" s="133">
+      <c r="I3" s="121">
         <f>E54</f>
         <v>16500.517352669427</v>
       </c>
@@ -33899,16 +33891,16 @@
       <c r="C4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="136">
+      <c r="D4" s="123">
         <f>Costs_init!L4</f>
         <v>122.72425068954949</v>
       </c>
       <c r="E4" s="112"/>
-      <c r="G4" s="119" t="s">
+      <c r="G4" s="126" t="s">
         <v>115</v>
       </c>
-      <c r="H4" s="120"/>
-      <c r="I4" s="134">
+      <c r="H4" s="127"/>
+      <c r="I4" s="122">
         <f>SUM(I3)</f>
         <v>16500.517352669427</v>
       </c>
@@ -33921,14 +33913,13 @@
       <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="136">
+      <c r="D5" s="123">
         <f>Costs_init!L5</f>
         <v>122.72425068954949</v>
       </c>
       <c r="E5" s="112"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="135"/>
+      <c r="G5" s="6"/>
+      <c r="I5" s="111"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
@@ -33938,7 +33929,7 @@
       <c r="C6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="136">
+      <c r="D6" s="123">
         <f>SUM(Costs_init!L7:L19)</f>
         <v>1595.4152589641437</v>
       </c>
@@ -33952,7 +33943,7 @@
       <c r="C7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="136"/>
+      <c r="D7" s="123"/>
       <c r="E7" s="112">
         <f>SUM(D8:D17)</f>
         <v>2932.5324370166391</v>
@@ -33967,7 +33958,7 @@
       <c r="C8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="136">
+      <c r="D8" s="123">
         <f>Costs_init!L21</f>
         <v>53.739269173306766</v>
       </c>
@@ -33982,7 +33973,7 @@
       <c r="C9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="136">
+      <c r="D9" s="123">
         <f>Costs_init!L22</f>
         <v>227.20183735645651</v>
       </c>
@@ -33997,7 +33988,7 @@
       <c r="C10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="136">
+      <c r="D10" s="123">
         <f>Costs_init!L23</f>
         <v>107.47853834661353</v>
       </c>
@@ -34012,7 +34003,7 @@
       <c r="C11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="136">
+      <c r="D11" s="123">
         <f>Costs_init!L24</f>
         <v>53.739269173306766</v>
       </c>
@@ -34027,7 +34018,7 @@
       <c r="C12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="136">
+      <c r="D12" s="123">
         <f>Costs_init!L25</f>
         <v>107.47853834661353</v>
       </c>
@@ -34042,7 +34033,7 @@
       <c r="C13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="136">
+      <c r="D13" s="123">
         <f>Costs_init!L26</f>
         <v>340.80275603468476</v>
       </c>
@@ -34056,7 +34047,7 @@
       <c r="C14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="136">
+      <c r="D14" s="123">
         <f>Costs_init!L27</f>
         <v>1182.2639218127488</v>
       </c>
@@ -34070,7 +34061,7 @@
       <c r="C15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="136">
+      <c r="D15" s="123">
         <f>Costs_init!L28</f>
         <v>322.43561503984063</v>
       </c>
@@ -34084,7 +34075,7 @@
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="136">
+      <c r="D16" s="123">
         <f>Costs_init!L29</f>
         <v>107.47853834661353</v>
       </c>
@@ -34098,7 +34089,7 @@
       <c r="C17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="136">
+      <c r="D17" s="123">
         <f>Costs_init!L30</f>
         <v>429.91415338645413</v>
       </c>
@@ -34112,7 +34103,7 @@
       <c r="C18" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="136" t="str">
+      <c r="D18" s="123" t="str">
         <f>Costs_init!L31</f>
         <v/>
       </c>
@@ -34129,7 +34120,7 @@
       <c r="C19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="136">
+      <c r="D19" s="123">
         <f>Costs_init!L32</f>
         <v>607.34057104913677</v>
       </c>
@@ -34143,7 +34134,7 @@
       <c r="C20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="136">
+      <c r="D20" s="123">
         <f>Costs_init!L33</f>
         <v>150.39544251565169</v>
       </c>
@@ -34157,7 +34148,7 @@
       <c r="C21" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="136">
+      <c r="D21" s="123">
         <f>Costs_init!L34</f>
         <v>443.41333020857746</v>
       </c>
@@ -34171,7 +34162,7 @@
       <c r="C22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="136">
+      <c r="D22" s="123">
         <f>Costs_init!L35</f>
         <v>221.70666510428873</v>
       </c>
@@ -34185,7 +34176,7 @@
       <c r="C23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="136">
+      <c r="D23" s="123">
         <f>Costs_init!L36</f>
         <v>332.5599976564331</v>
       </c>
@@ -34199,7 +34190,7 @@
       <c r="C24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="136">
+      <c r="D24" s="123">
         <f>Costs_init!L37</f>
         <v>554.26666276072183</v>
       </c>
@@ -34213,7 +34204,7 @@
       <c r="C25" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D25" s="136">
+      <c r="D25" s="123">
         <f>Costs_init!L38</f>
         <v>554.26666276072183</v>
       </c>
@@ -34227,7 +34218,7 @@
       <c r="C26" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="136">
+      <c r="D26" s="123">
         <f>Costs_init!L39</f>
         <v>166.27999882821655</v>
       </c>
@@ -34244,7 +34235,7 @@
       <c r="C27" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="136" t="str">
+      <c r="D27" s="123" t="str">
         <f>Costs_init!L40</f>
         <v/>
       </c>
@@ -34261,7 +34252,7 @@
       <c r="C28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="136">
+      <c r="D28" s="123">
         <f>Costs_init!L41</f>
         <v>242.93622841965473</v>
       </c>
@@ -34275,7 +34266,7 @@
       <c r="C29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="136">
+      <c r="D29" s="123">
         <f>Costs_init!L42</f>
         <v>182.20217131474107</v>
       </c>
@@ -34289,7 +34280,7 @@
       <c r="C30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="136">
+      <c r="D30" s="123">
         <f>SUM(Costs_init!L44:L50)</f>
         <v>5177.6603940540372</v>
       </c>
@@ -34303,7 +34294,7 @@
       <c r="C31" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="136"/>
+      <c r="D31" s="123"/>
       <c r="E31" s="112">
         <f>SUM(D32:D40)</f>
         <v>1364.1486868492418</v>
@@ -34317,7 +34308,7 @@
       <c r="C32" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="136">
+      <c r="D32" s="123">
         <f>Costs_init!L52</f>
         <v>200.52725668753558</v>
       </c>
@@ -34331,7 +34322,7 @@
       <c r="C33" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="136">
+      <c r="D33" s="123">
         <f>Costs_init!L53</f>
         <v>150.39544251565169</v>
       </c>
@@ -34345,7 +34336,7 @@
       <c r="C34" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D34" s="136">
+      <c r="D34" s="123">
         <f>Costs_init!L54</f>
         <v>250.6590708594195</v>
       </c>
@@ -34359,7 +34350,7 @@
       <c r="C35" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D35" s="136">
+      <c r="D35" s="123">
         <f>Costs_init!L55</f>
         <v>150.39544251565169</v>
       </c>
@@ -34373,7 +34364,7 @@
       <c r="C36" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D36" s="136">
+      <c r="D36" s="123">
         <f>Costs_init!L56</f>
         <v>150.39544251565169</v>
       </c>
@@ -34387,7 +34378,7 @@
       <c r="C37" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D37" s="136">
+      <c r="D37" s="123">
         <f>Costs_init!L57</f>
         <v>100.26362834376779</v>
       </c>
@@ -34401,7 +34392,7 @@
       <c r="C38" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D38" s="136">
+      <c r="D38" s="123">
         <f>Costs_init!L58</f>
         <v>150.39544251565169</v>
       </c>
@@ -34415,7 +34406,7 @@
       <c r="C39" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D39" s="136">
+      <c r="D39" s="123">
         <f>Costs_init!L59</f>
         <v>100.26362834376779</v>
       </c>
@@ -34429,7 +34420,7 @@
       <c r="C40" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D40" s="136">
+      <c r="D40" s="123">
         <f>Costs_init!L60</f>
         <v>110.85333255214437</v>
       </c>
@@ -34443,7 +34434,7 @@
       <c r="C41" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D41" s="136" t="str">
+      <c r="D41" s="123" t="str">
         <f>Costs_init!L61</f>
         <v/>
       </c>
@@ -34460,7 +34451,7 @@
       <c r="C42" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D42" s="136">
+      <c r="D42" s="123">
         <f>Costs_init!L62</f>
         <v>61.362125344774746</v>
       </c>
@@ -34474,7 +34465,7 @@
       <c r="C43" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D43" s="136">
+      <c r="D43" s="123">
         <f>Costs_init!L63</f>
         <v>61.362125344774746</v>
       </c>
@@ -34488,7 +34479,7 @@
       <c r="C44" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D44" s="136">
+      <c r="D44" s="123">
         <f>Costs_init!L64</f>
         <v>56.800459339114127</v>
       </c>
@@ -34502,7 +34493,7 @@
       <c r="C45" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="136">
+      <c r="D45" s="123">
         <f>Costs_init!L65</f>
         <v>113.60091867822825</v>
       </c>
@@ -34516,7 +34507,7 @@
       <c r="C46" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D46" s="136">
+      <c r="D46" s="123">
         <f>Costs_init!L66</f>
         <v>122.72425068954949</v>
       </c>
@@ -34530,7 +34521,7 @@
       <c r="C47" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="136">
+      <c r="D47" s="123">
         <f>Costs_init!L67</f>
         <v>161.21780751992031</v>
       </c>
@@ -34544,7 +34535,7 @@
       <c r="C48" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D48" s="136">
+      <c r="D48" s="123">
         <f>Costs_init!L68</f>
         <v>303.67028552456838</v>
       </c>
@@ -34558,7 +34549,7 @@
       <c r="C49" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D49" s="136">
+      <c r="D49" s="123">
         <f>Costs_init!L69</f>
         <v>277.13333138036091</v>
       </c>
@@ -34572,7 +34563,7 @@
       <c r="C50" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D50" s="136">
+      <c r="D50" s="123">
         <f>Costs_init!L70</f>
         <v>110.85333255214437</v>
       </c>
@@ -34586,7 +34577,7 @@
       <c r="C51" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D51" s="136">
+      <c r="D51" s="123">
         <f>Costs_init!L71</f>
         <v>277.13333138036091</v>
       </c>
@@ -34600,7 +34591,7 @@
       <c r="C52" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D52" s="136">
+      <c r="D52" s="123">
         <f>Costs_init!L72</f>
         <v>122.72425068954949</v>
       </c>
@@ -34614,19 +34605,19 @@
       <c r="C53" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D53" s="136">
+      <c r="D53" s="123">
         <f>Costs_init!L73</f>
         <v>61.362125344774746</v>
       </c>
       <c r="E53" s="113"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="119" t="s">
+      <c r="A54" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="120"/>
-      <c r="C54" s="120"/>
-      <c r="D54" s="120"/>
+      <c r="B54" s="127"/>
+      <c r="C54" s="127"/>
+      <c r="D54" s="127"/>
       <c r="E54" s="114">
         <f>SUM(E3:E53)</f>
         <v>16500.517352669427</v>

--- a/docs/budget.xlsx
+++ b/docs/budget.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Desktop\proyectos\IRBoard\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965A530D-4CE8-438C-B313-7FE2C2223067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE692509-35D9-4BFA-B51B-C27FC9234824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Company definition" sheetId="2" r:id="rId1"/>
     <sheet name="Costs_init" sheetId="1" r:id="rId2"/>
     <sheet name="Client_init" sheetId="5" r:id="rId3"/>
+    <sheet name="Costs_final" sheetId="6" r:id="rId4"/>
+    <sheet name="Client_final" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="216">
   <si>
     <t>I1</t>
   </si>
@@ -1335,6 +1337,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1362,7 +1365,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -31004,27 +31006,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="130" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="130"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="131"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="132"/>
       <c r="L1" s="125" t="s">
         <v>213</v>
       </c>
-      <c r="N1" s="126" t="s">
+      <c r="N1" s="127" t="s">
         <v>203</v>
       </c>
-      <c r="O1" s="127"/>
-      <c r="P1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="129"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -31222,10 +31224,10 @@
       </c>
       <c r="K6" s="112"/>
       <c r="L6" s="110"/>
-      <c r="N6" s="126" t="s">
+      <c r="N6" s="127" t="s">
         <v>115</v>
       </c>
-      <c r="O6" s="127"/>
+      <c r="O6" s="128"/>
       <c r="P6" s="122">
         <f>SUM(P3:P5)</f>
         <v>16498.77169083678</v>
@@ -31339,7 +31341,7 @@
       <c r="O9" t="s">
         <v>214</v>
       </c>
-      <c r="P9" s="135">
+      <c r="P9" s="126">
         <f>SUM(F4:F73)</f>
         <v>300</v>
       </c>
@@ -33602,18 +33604,18 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="126" t="s">
+      <c r="A74" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="B74" s="127"/>
-      <c r="C74" s="127"/>
-      <c r="D74" s="127"/>
-      <c r="E74" s="127"/>
-      <c r="F74" s="127"/>
-      <c r="G74" s="127"/>
-      <c r="H74" s="127"/>
-      <c r="I74" s="127"/>
-      <c r="J74" s="127"/>
+      <c r="B74" s="128"/>
+      <c r="C74" s="128"/>
+      <c r="D74" s="128"/>
+      <c r="E74" s="128"/>
+      <c r="F74" s="128"/>
+      <c r="G74" s="128"/>
+      <c r="H74" s="128"/>
+      <c r="I74" s="128"/>
+      <c r="J74" s="128"/>
       <c r="K74" s="114">
         <f>SUM(K3:K73)</f>
         <v>13026.517352669423</v>
@@ -33628,19 +33630,19 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="132" t="s">
+      <c r="A76" s="133" t="s">
         <v>192</v>
       </c>
-      <c r="B76" s="133"/>
-      <c r="C76" s="133"/>
-      <c r="D76" s="133"/>
-      <c r="E76" s="133"/>
-      <c r="F76" s="133"/>
-      <c r="G76" s="133"/>
-      <c r="H76" s="133"/>
-      <c r="I76" s="133"/>
-      <c r="J76" s="133"/>
-      <c r="K76" s="134"/>
+      <c r="B76" s="134"/>
+      <c r="C76" s="134"/>
+      <c r="D76" s="134"/>
+      <c r="E76" s="134"/>
+      <c r="F76" s="134"/>
+      <c r="G76" s="134"/>
+      <c r="H76" s="134"/>
+      <c r="I76" s="134"/>
+      <c r="J76" s="134"/>
+      <c r="K76" s="135"/>
       <c r="L76" s="124"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
@@ -33759,18 +33761,18 @@
       <c r="L80" s="116"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="126" t="s">
+      <c r="A81" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="B81" s="127"/>
-      <c r="C81" s="127"/>
-      <c r="D81" s="127"/>
-      <c r="E81" s="127"/>
-      <c r="F81" s="127"/>
-      <c r="G81" s="127"/>
-      <c r="H81" s="127"/>
-      <c r="I81" s="127"/>
-      <c r="J81" s="127"/>
+      <c r="B81" s="128"/>
+      <c r="C81" s="128"/>
+      <c r="D81" s="128"/>
+      <c r="E81" s="128"/>
+      <c r="F81" s="128"/>
+      <c r="G81" s="128"/>
+      <c r="H81" s="128"/>
+      <c r="I81" s="128"/>
+      <c r="J81" s="128"/>
       <c r="K81" s="114">
         <f>SUM(K78:K80)</f>
         <v>172.5</v>
@@ -33820,18 +33822,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="130" t="s">
         <v>210</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="131"/>
-      <c r="G1" s="126" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="132"/>
+      <c r="G1" s="127" t="s">
         <v>209</v>
       </c>
-      <c r="H1" s="127"/>
-      <c r="I1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="129"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -33896,10 +33898,10 @@
         <v>122.72425068954949</v>
       </c>
       <c r="E4" s="112"/>
-      <c r="G4" s="126" t="s">
+      <c r="G4" s="127" t="s">
         <v>115</v>
       </c>
-      <c r="H4" s="127"/>
+      <c r="H4" s="128"/>
       <c r="I4" s="122">
         <f>SUM(I3)</f>
         <v>16500.517352669427</v>
@@ -34612,12 +34614,12 @@
       <c r="E53" s="113"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="126" t="s">
+      <c r="A54" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="127"/>
-      <c r="C54" s="127"/>
-      <c r="D54" s="127"/>
+      <c r="B54" s="128"/>
+      <c r="C54" s="128"/>
+      <c r="D54" s="128"/>
       <c r="E54" s="114">
         <f>SUM(E3:E53)</f>
         <v>16500.517352669427</v>
@@ -34640,4 +34642,3663 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C034FB62-BD60-4D19-91EB-FF898F716C5A}">
+  <dimension ref="A1:R82"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.5546875" customWidth="1"/>
+    <col min="5" max="5" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="130" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="125" t="s">
+        <v>213</v>
+      </c>
+      <c r="N1" s="127" t="s">
+        <v>203</v>
+      </c>
+      <c r="O1" s="128"/>
+      <c r="P1" s="129"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="118"/>
+      <c r="N2" s="119" t="s">
+        <v>205</v>
+      </c>
+      <c r="O2" s="118" t="s">
+        <v>204</v>
+      </c>
+      <c r="P2" s="120" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="111" t="str">
+        <f t="shared" ref="H3:H66" si="0">_xlfn.XLOOKUP(E3,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <v/>
+      </c>
+      <c r="I3" s="111" t="str">
+        <f>IFERROR(H3*F3,"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="115">
+        <f>SUM(J4:J19)</f>
+        <v>1194.7710082745937</v>
+      </c>
+      <c r="L3" s="110" t="str">
+        <f>IFERROR(I3+($P$10*F3),"")</f>
+        <v/>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P3" s="121">
+        <f>K74</f>
+        <v>13383.612572529586</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I4" s="111">
+        <f t="shared" ref="I4:I67" si="1">IFERROR(H4*F4,"")</f>
+        <v>99.564250689549496</v>
+      </c>
+      <c r="J4" s="111">
+        <f>I4</f>
+        <v>99.564250689549496</v>
+      </c>
+      <c r="K4" s="112"/>
+      <c r="L4" s="110">
+        <f t="shared" ref="L4:L67" si="2">IFERROR(I4+($P$10*F4),"")</f>
+        <v>122.5442506895495</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" t="s">
+        <v>207</v>
+      </c>
+      <c r="P4" s="121">
+        <f>K81</f>
+        <v>172.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I5" s="111">
+        <f t="shared" si="1"/>
+        <v>99.564250689549496</v>
+      </c>
+      <c r="J5" s="111">
+        <f>I5</f>
+        <v>99.564250689549496</v>
+      </c>
+      <c r="K5" s="112"/>
+      <c r="L5" s="110">
+        <f t="shared" si="2"/>
+        <v>122.5442506895495</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" t="s">
+        <v>208</v>
+      </c>
+      <c r="P5" s="112">
+        <f>0.25*(P3+P4)</f>
+        <v>3389.0281431323965</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="111" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I6" s="111" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J6" s="111">
+        <f>SUM(I7:I19)</f>
+        <v>995.64250689549476</v>
+      </c>
+      <c r="K6" s="112"/>
+      <c r="L6" s="110"/>
+      <c r="N6" s="127" t="s">
+        <v>115</v>
+      </c>
+      <c r="O6" s="128"/>
+      <c r="P6" s="122">
+        <f>SUM(P3:P5)</f>
+        <v>16945.140715661983</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I7" s="111">
+        <f t="shared" si="1"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="J7" s="111"/>
+      <c r="K7" s="112"/>
+      <c r="L7" s="110">
+        <f t="shared" si="2"/>
+        <v>61.27212534477475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I8" s="111">
+        <f t="shared" si="1"/>
+        <v>99.564250689549496</v>
+      </c>
+      <c r="J8" s="111"/>
+      <c r="K8" s="112"/>
+      <c r="L8" s="110">
+        <f t="shared" si="2"/>
+        <v>122.5442506895495</v>
+      </c>
+      <c r="O8" t="s">
+        <v>211</v>
+      </c>
+      <c r="P8" s="111">
+        <f>P6-P3</f>
+        <v>3561.5281431323965</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I9" s="111">
+        <f t="shared" si="1"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="J9" s="111"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="110">
+        <f t="shared" si="2"/>
+        <v>61.27212534477475</v>
+      </c>
+      <c r="O9" t="s">
+        <v>214</v>
+      </c>
+      <c r="P9" s="126">
+        <f>SUM(F4:F73)</f>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I10" s="111">
+        <f t="shared" si="1"/>
+        <v>99.564250689549496</v>
+      </c>
+      <c r="J10" s="111"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="110">
+        <f t="shared" si="2"/>
+        <v>122.5442506895495</v>
+      </c>
+      <c r="O10" t="s">
+        <v>215</v>
+      </c>
+      <c r="P10" s="123">
+        <f>ROUNDUP(P8/P9,2)</f>
+        <v>11.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I11" s="111">
+        <f t="shared" si="1"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="J11" s="111"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="110">
+        <f t="shared" si="2"/>
+        <v>61.27212534477475</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I12" s="111">
+        <f t="shared" si="1"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="J12" s="111"/>
+      <c r="K12" s="112"/>
+      <c r="L12" s="110">
+        <f t="shared" si="2"/>
+        <v>61.27212534477475</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I13" s="111">
+        <f t="shared" si="1"/>
+        <v>99.564250689549496</v>
+      </c>
+      <c r="J13" s="111"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="110">
+        <f t="shared" si="2"/>
+        <v>122.5442506895495</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H14" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I14" s="111">
+        <f t="shared" si="1"/>
+        <v>99.564250689549496</v>
+      </c>
+      <c r="J14" s="111"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="110">
+        <f t="shared" si="2"/>
+        <v>122.5442506895495</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I15" s="111">
+        <f t="shared" si="1"/>
+        <v>99.564250689549496</v>
+      </c>
+      <c r="J15" s="111"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="110">
+        <f t="shared" si="2"/>
+        <v>122.5442506895495</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I16" s="111">
+        <f t="shared" si="1"/>
+        <v>99.564250689549496</v>
+      </c>
+      <c r="J16" s="111"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="110">
+        <f t="shared" si="2"/>
+        <v>122.5442506895495</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I17" s="111">
+        <f t="shared" si="1"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="J17" s="111"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="110">
+        <f t="shared" si="2"/>
+        <v>61.27212534477475</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I18" s="111">
+        <f t="shared" si="1"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="J18" s="111"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="110">
+        <f t="shared" si="2"/>
+        <v>61.27212534477475</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I19" s="111">
+        <f t="shared" si="1"/>
+        <v>99.564250689549496</v>
+      </c>
+      <c r="J19" s="111"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="110">
+        <f t="shared" si="2"/>
+        <v>122.5442506895495</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="R19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="111" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I20" s="111" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J20" s="111"/>
+      <c r="K20" s="112">
+        <f>SUM(J21:J30)</f>
+        <v>2433.690244536559</v>
+      </c>
+      <c r="L20" s="110" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R20" s="110">
+        <f>'Company definition'!F82</f>
+        <v>49.782125344774748</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" s="111">
+        <f t="shared" si="0"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="I21" s="111">
+        <f t="shared" si="1"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="J21" s="111">
+        <f t="shared" ref="J21:J30" si="3">I21</f>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="K21" s="112"/>
+      <c r="L21" s="110">
+        <f t="shared" si="2"/>
+        <v>53.64926917330677</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>107</v>
+      </c>
+      <c r="R21" s="110">
+        <f>'Company definition'!F85</f>
+        <v>45.220459339114129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H22" s="111">
+        <f t="shared" si="0"/>
+        <v>45.220459339114129</v>
+      </c>
+      <c r="I22" s="111">
+        <f t="shared" si="1"/>
+        <v>180.88183735645651</v>
+      </c>
+      <c r="J22" s="111">
+        <f t="shared" si="3"/>
+        <v>180.88183735645651</v>
+      </c>
+      <c r="K22" s="112"/>
+      <c r="L22" s="110">
+        <f t="shared" si="2"/>
+        <v>226.84183735645652</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>106</v>
+      </c>
+      <c r="R22" s="110">
+        <f>'Company definition'!F84</f>
+        <v>42.159269173306768</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" s="111">
+        <f t="shared" si="0"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="I23" s="111">
+        <f t="shared" si="1"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="J23" s="111">
+        <f t="shared" si="3"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="K23" s="112"/>
+      <c r="L23" s="110">
+        <f t="shared" si="2"/>
+        <v>53.64926917330677</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>108</v>
+      </c>
+      <c r="R23" s="110">
+        <f>'Company definition'!F86</f>
+        <v>49.154057104913683</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>103</v>
+      </c>
+      <c r="H24" s="111">
+        <f t="shared" si="0"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="I24" s="111">
+        <f t="shared" si="1"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="J24" s="111">
+        <f t="shared" si="3"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="K24" s="112"/>
+      <c r="L24" s="110">
+        <f t="shared" si="2"/>
+        <v>53.64926917330677</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>109</v>
+      </c>
+      <c r="R24" s="110">
+        <f>'Company definition'!F87</f>
+        <v>43.846666276072185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25" t="s">
+        <v>103</v>
+      </c>
+      <c r="H25" s="111">
+        <f t="shared" si="0"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="I25" s="111">
+        <f t="shared" si="1"/>
+        <v>84.318538346613536</v>
+      </c>
+      <c r="J25" s="111">
+        <f t="shared" si="3"/>
+        <v>84.318538346613536</v>
+      </c>
+      <c r="K25" s="112"/>
+      <c r="L25" s="110">
+        <f t="shared" si="2"/>
+        <v>107.29853834661354</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>110</v>
+      </c>
+      <c r="R25" s="110">
+        <f>'Company definition'!F88</f>
+        <v>38.551814171883898</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26">
+        <v>6</v>
+      </c>
+      <c r="G26" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="111">
+        <f t="shared" si="0"/>
+        <v>45.220459339114129</v>
+      </c>
+      <c r="I26" s="111">
+        <f t="shared" si="1"/>
+        <v>271.32275603468474</v>
+      </c>
+      <c r="J26" s="111">
+        <f t="shared" si="3"/>
+        <v>271.32275603468474</v>
+      </c>
+      <c r="K26" s="112"/>
+      <c r="L26" s="110">
+        <f t="shared" si="2"/>
+        <v>340.26275603468474</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27">
+        <v>22</v>
+      </c>
+      <c r="G27" t="s">
+        <v>103</v>
+      </c>
+      <c r="H27" s="111">
+        <f t="shared" si="0"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="I27" s="111">
+        <f t="shared" si="1"/>
+        <v>927.5039218127489</v>
+      </c>
+      <c r="J27" s="111">
+        <f t="shared" si="3"/>
+        <v>927.5039218127489</v>
+      </c>
+      <c r="K27" s="112"/>
+      <c r="L27" s="110">
+        <f t="shared" si="2"/>
+        <v>1180.283921812749</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="D28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28">
+        <v>8</v>
+      </c>
+      <c r="G28" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28" s="111">
+        <f t="shared" si="0"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="I28" s="111">
+        <f t="shared" si="1"/>
+        <v>337.27415338645415</v>
+      </c>
+      <c r="J28" s="111">
+        <f t="shared" si="3"/>
+        <v>337.27415338645415</v>
+      </c>
+      <c r="K28" s="112"/>
+      <c r="L28" s="110">
+        <f t="shared" si="2"/>
+        <v>429.19415338645416</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29" t="s">
+        <v>103</v>
+      </c>
+      <c r="H29" s="111">
+        <f t="shared" si="0"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="I29" s="111">
+        <f t="shared" si="1"/>
+        <v>168.63707669322707</v>
+      </c>
+      <c r="J29" s="111">
+        <f t="shared" si="3"/>
+        <v>168.63707669322707</v>
+      </c>
+      <c r="K29" s="112"/>
+      <c r="L29" s="110">
+        <f t="shared" si="2"/>
+        <v>214.59707669322708</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+      <c r="B30" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
+      </c>
+      <c r="G30" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" s="111">
+        <f t="shared" si="0"/>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="I30" s="111">
+        <f t="shared" si="1"/>
+        <v>337.27415338645415</v>
+      </c>
+      <c r="J30" s="111">
+        <f t="shared" si="3"/>
+        <v>337.27415338645415</v>
+      </c>
+      <c r="K30" s="112"/>
+      <c r="L30" s="110">
+        <f t="shared" si="2"/>
+        <v>429.19415338645416</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H31" s="111" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I31" s="111" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J31" s="111"/>
+      <c r="K31" s="112">
+        <f>SUM(J32:J38)</f>
+        <v>2361.0626646076757</v>
+      </c>
+      <c r="L31" s="110" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" t="s">
+        <v>108</v>
+      </c>
+      <c r="F32">
+        <v>10</v>
+      </c>
+      <c r="G32" t="s">
+        <v>103</v>
+      </c>
+      <c r="H32" s="111">
+        <f t="shared" si="0"/>
+        <v>49.154057104913683</v>
+      </c>
+      <c r="I32" s="111">
+        <f t="shared" si="1"/>
+        <v>491.54057104913682</v>
+      </c>
+      <c r="J32" s="111">
+        <f t="shared" ref="J32:J38" si="4">I32</f>
+        <v>491.54057104913682</v>
+      </c>
+      <c r="K32" s="112"/>
+      <c r="L32" s="110">
+        <f t="shared" si="2"/>
+        <v>606.44057104913679</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" t="s">
+        <v>110</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33" t="s">
+        <v>103</v>
+      </c>
+      <c r="H33" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I33" s="111">
+        <f t="shared" si="1"/>
+        <v>115.65544251565169</v>
+      </c>
+      <c r="J33" s="111">
+        <f t="shared" si="4"/>
+        <v>115.65544251565169</v>
+      </c>
+      <c r="K33" s="112"/>
+      <c r="L33" s="110">
+        <f t="shared" si="2"/>
+        <v>150.12544251565168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+      <c r="B34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" t="s">
+        <v>109</v>
+      </c>
+      <c r="F34">
+        <v>8</v>
+      </c>
+      <c r="G34" t="s">
+        <v>103</v>
+      </c>
+      <c r="H34" s="111">
+        <f t="shared" si="0"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I34" s="111">
+        <f t="shared" si="1"/>
+        <v>350.77333020857748</v>
+      </c>
+      <c r="J34" s="111">
+        <f t="shared" si="4"/>
+        <v>350.77333020857748</v>
+      </c>
+      <c r="K34" s="112"/>
+      <c r="L34" s="110">
+        <f t="shared" si="2"/>
+        <v>442.69333020857749</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+      <c r="B35" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" t="s">
+        <v>109</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" s="111">
+        <f t="shared" si="0"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I35" s="111">
+        <f t="shared" si="1"/>
+        <v>175.38666510428874</v>
+      </c>
+      <c r="J35" s="111">
+        <f t="shared" si="4"/>
+        <v>175.38666510428874</v>
+      </c>
+      <c r="K35" s="112"/>
+      <c r="L35" s="110">
+        <f t="shared" si="2"/>
+        <v>221.34666510428875</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" t="s">
+        <v>109</v>
+      </c>
+      <c r="F36">
+        <v>6</v>
+      </c>
+      <c r="G36" t="s">
+        <v>103</v>
+      </c>
+      <c r="H36" s="111">
+        <f t="shared" si="0"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I36" s="111">
+        <f t="shared" si="1"/>
+        <v>263.07999765643308</v>
+      </c>
+      <c r="J36" s="111">
+        <f t="shared" si="4"/>
+        <v>263.07999765643308</v>
+      </c>
+      <c r="K36" s="112"/>
+      <c r="L36" s="110">
+        <f t="shared" si="2"/>
+        <v>332.01999765643308</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="5"/>
+      <c r="B37" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" t="s">
+        <v>109</v>
+      </c>
+      <c r="F37">
+        <v>12</v>
+      </c>
+      <c r="G37" t="s">
+        <v>103</v>
+      </c>
+      <c r="H37" s="111">
+        <f t="shared" si="0"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I37" s="111">
+        <f t="shared" si="1"/>
+        <v>526.15999531286616</v>
+      </c>
+      <c r="J37" s="111">
+        <f t="shared" si="4"/>
+        <v>526.15999531286616</v>
+      </c>
+      <c r="K37" s="112"/>
+      <c r="L37" s="110">
+        <f t="shared" si="2"/>
+        <v>664.03999531286615</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F38">
+        <v>10</v>
+      </c>
+      <c r="G38" t="s">
+        <v>103</v>
+      </c>
+      <c r="H38" s="111">
+        <f t="shared" si="0"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I38" s="111">
+        <f t="shared" si="1"/>
+        <v>438.46666276072187</v>
+      </c>
+      <c r="J38" s="111">
+        <f t="shared" si="4"/>
+        <v>438.46666276072187</v>
+      </c>
+      <c r="K38" s="112"/>
+      <c r="L38" s="110">
+        <f t="shared" si="2"/>
+        <v>553.36666276072185</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F39">
+        <v>6</v>
+      </c>
+      <c r="G39" t="s">
+        <v>103</v>
+      </c>
+      <c r="H39" s="111">
+        <f t="shared" si="0"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I39" s="111">
+        <f t="shared" si="1"/>
+        <v>263.07999765643308</v>
+      </c>
+      <c r="J39" s="111">
+        <f>SUM(I39)</f>
+        <v>263.07999765643308</v>
+      </c>
+      <c r="K39" s="111">
+        <f>SUM(J39)</f>
+        <v>263.07999765643308</v>
+      </c>
+      <c r="L39" s="110">
+        <f t="shared" si="2"/>
+        <v>332.01999765643308</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H40" s="111" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I40" s="111" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J40" s="111"/>
+      <c r="K40" s="112">
+        <f>SUM(J41:J50)</f>
+        <v>4485.1818305489533</v>
+      </c>
+      <c r="L40" s="110" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="6"/>
+      <c r="D41" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" t="s">
+        <v>108</v>
+      </c>
+      <c r="F41">
+        <v>6</v>
+      </c>
+      <c r="G41" t="s">
+        <v>103</v>
+      </c>
+      <c r="H41" s="111">
+        <f t="shared" si="0"/>
+        <v>49.154057104913683</v>
+      </c>
+      <c r="I41" s="111">
+        <f t="shared" si="1"/>
+        <v>294.92434262948211</v>
+      </c>
+      <c r="J41" s="111">
+        <f>I41</f>
+        <v>294.92434262948211</v>
+      </c>
+      <c r="K41" s="112"/>
+      <c r="L41" s="110">
+        <f t="shared" si="2"/>
+        <v>363.86434262948211</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="6"/>
+      <c r="D42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>103</v>
+      </c>
+      <c r="H42" s="111">
+        <f t="shared" si="0"/>
+        <v>49.154057104913683</v>
+      </c>
+      <c r="I42" s="111">
+        <f t="shared" si="1"/>
+        <v>49.154057104913683</v>
+      </c>
+      <c r="J42" s="111">
+        <f>I42</f>
+        <v>49.154057104913683</v>
+      </c>
+      <c r="K42" s="112"/>
+      <c r="L42" s="110">
+        <f t="shared" si="2"/>
+        <v>60.644057104913685</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="6"/>
+      <c r="D43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H43" s="111" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I43" s="111" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J43" s="111">
+        <f>SUM(I44:I50)</f>
+        <v>4141.1034308145572</v>
+      </c>
+      <c r="K43" s="112"/>
+      <c r="L43" s="110" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="5"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" t="s">
+        <v>110</v>
+      </c>
+      <c r="F44">
+        <v>22</v>
+      </c>
+      <c r="G44" t="s">
+        <v>103</v>
+      </c>
+      <c r="H44" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I44" s="111">
+        <f t="shared" si="1"/>
+        <v>848.13991178144579</v>
+      </c>
+      <c r="J44" s="111"/>
+      <c r="K44" s="112"/>
+      <c r="L44" s="110">
+        <f t="shared" si="2"/>
+        <v>1100.9199117814458</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="5"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" t="s">
+        <v>110</v>
+      </c>
+      <c r="F45">
+        <v>6</v>
+      </c>
+      <c r="G45" t="s">
+        <v>103</v>
+      </c>
+      <c r="H45" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I45" s="111">
+        <f t="shared" si="1"/>
+        <v>231.31088503130337</v>
+      </c>
+      <c r="J45" s="111"/>
+      <c r="K45" s="112"/>
+      <c r="L45" s="110">
+        <f t="shared" si="2"/>
+        <v>300.25088503130337</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="5"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" t="s">
+        <v>109</v>
+      </c>
+      <c r="F46">
+        <v>24</v>
+      </c>
+      <c r="G46" t="s">
+        <v>103</v>
+      </c>
+      <c r="H46" s="111">
+        <f t="shared" si="0"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I46" s="111">
+        <f t="shared" si="1"/>
+        <v>1052.3199906257323</v>
+      </c>
+      <c r="J46" s="111"/>
+      <c r="K46" s="112"/>
+      <c r="L46" s="110">
+        <f t="shared" si="2"/>
+        <v>1328.0799906257323</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="5"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" t="s">
+        <v>110</v>
+      </c>
+      <c r="F47">
+        <v>12</v>
+      </c>
+      <c r="G47" t="s">
+        <v>103</v>
+      </c>
+      <c r="H47" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I47" s="111">
+        <f t="shared" si="1"/>
+        <v>462.62177006260674</v>
+      </c>
+      <c r="J47" s="111"/>
+      <c r="K47" s="112"/>
+      <c r="L47" s="110">
+        <f t="shared" si="2"/>
+        <v>600.50177006260674</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="5"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F48">
+        <v>20</v>
+      </c>
+      <c r="G48" t="s">
+        <v>103</v>
+      </c>
+      <c r="H48" s="111">
+        <f t="shared" si="0"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I48" s="111">
+        <f t="shared" si="1"/>
+        <v>876.93332552144375</v>
+      </c>
+      <c r="J48" s="111"/>
+      <c r="K48" s="112"/>
+      <c r="L48" s="110">
+        <f t="shared" si="2"/>
+        <v>1106.7333255214437</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" t="s">
+        <v>109</v>
+      </c>
+      <c r="F49">
+        <v>10</v>
+      </c>
+      <c r="G49" t="s">
+        <v>103</v>
+      </c>
+      <c r="H49" s="111">
+        <f t="shared" si="0"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I49" s="111">
+        <f t="shared" si="1"/>
+        <v>438.46666276072187</v>
+      </c>
+      <c r="J49" s="111"/>
+      <c r="K49" s="112"/>
+      <c r="L49" s="110">
+        <f t="shared" si="2"/>
+        <v>553.36666276072185</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="5"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" t="s">
+        <v>110</v>
+      </c>
+      <c r="F50">
+        <v>6</v>
+      </c>
+      <c r="G50" t="s">
+        <v>103</v>
+      </c>
+      <c r="H50" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I50" s="111">
+        <f t="shared" si="1"/>
+        <v>231.31088503130337</v>
+      </c>
+      <c r="J50" s="111"/>
+      <c r="K50" s="112"/>
+      <c r="L50" s="110">
+        <f t="shared" si="2"/>
+        <v>300.25088503130337</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H51" s="111" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I51" s="111" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J51" s="111"/>
+      <c r="K51" s="112">
+        <f>SUM(J52:J60)</f>
+        <v>1359.9032002243127</v>
+      </c>
+      <c r="L51" s="110" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="5"/>
+      <c r="B52" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="6"/>
+      <c r="D52" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E52" t="s">
+        <v>110</v>
+      </c>
+      <c r="F52">
+        <v>6</v>
+      </c>
+      <c r="G52" t="s">
+        <v>103</v>
+      </c>
+      <c r="H52" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I52" s="111">
+        <f t="shared" si="1"/>
+        <v>231.31088503130337</v>
+      </c>
+      <c r="J52" s="111">
+        <f t="shared" ref="J52:J60" si="5">I52</f>
+        <v>231.31088503130337</v>
+      </c>
+      <c r="K52" s="112"/>
+      <c r="L52" s="110">
+        <f t="shared" si="2"/>
+        <v>300.25088503130337</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="5"/>
+      <c r="B53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="6"/>
+      <c r="D53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" t="s">
+        <v>110</v>
+      </c>
+      <c r="F53">
+        <v>4</v>
+      </c>
+      <c r="G53" t="s">
+        <v>103</v>
+      </c>
+      <c r="H53" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I53" s="111">
+        <f t="shared" si="1"/>
+        <v>154.20725668753559</v>
+      </c>
+      <c r="J53" s="111">
+        <f t="shared" si="5"/>
+        <v>154.20725668753559</v>
+      </c>
+      <c r="K53" s="112"/>
+      <c r="L53" s="110">
+        <f t="shared" si="2"/>
+        <v>200.1672566875356</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="5"/>
+      <c r="B54" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="6"/>
+      <c r="D54" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" t="s">
+        <v>110</v>
+      </c>
+      <c r="F54">
+        <v>5</v>
+      </c>
+      <c r="G54" t="s">
+        <v>103</v>
+      </c>
+      <c r="H54" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I54" s="111">
+        <f t="shared" si="1"/>
+        <v>192.7590708594195</v>
+      </c>
+      <c r="J54" s="111">
+        <f t="shared" si="5"/>
+        <v>192.7590708594195</v>
+      </c>
+      <c r="K54" s="112"/>
+      <c r="L54" s="110">
+        <f t="shared" si="2"/>
+        <v>250.20907085941951</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="5"/>
+      <c r="B55" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C55" s="6"/>
+      <c r="D55" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" t="s">
+        <v>110</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="G55" t="s">
+        <v>103</v>
+      </c>
+      <c r="H55" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I55" s="111">
+        <f t="shared" si="1"/>
+        <v>115.65544251565169</v>
+      </c>
+      <c r="J55" s="111">
+        <f t="shared" si="5"/>
+        <v>115.65544251565169</v>
+      </c>
+      <c r="K55" s="112"/>
+      <c r="L55" s="110">
+        <f t="shared" si="2"/>
+        <v>150.12544251565168</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="5"/>
+      <c r="B56" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" s="6"/>
+      <c r="D56" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E56" t="s">
+        <v>110</v>
+      </c>
+      <c r="F56">
+        <v>4</v>
+      </c>
+      <c r="G56" t="s">
+        <v>103</v>
+      </c>
+      <c r="H56" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I56" s="111">
+        <f t="shared" si="1"/>
+        <v>154.20725668753559</v>
+      </c>
+      <c r="J56" s="111">
+        <f t="shared" si="5"/>
+        <v>154.20725668753559</v>
+      </c>
+      <c r="K56" s="112"/>
+      <c r="L56" s="110">
+        <f t="shared" si="2"/>
+        <v>200.1672566875356</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="5"/>
+      <c r="B57" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" s="6"/>
+      <c r="D57" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E57" t="s">
+        <v>110</v>
+      </c>
+      <c r="F57">
+        <v>5</v>
+      </c>
+      <c r="G57" t="s">
+        <v>103</v>
+      </c>
+      <c r="H57" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I57" s="111">
+        <f t="shared" si="1"/>
+        <v>192.7590708594195</v>
+      </c>
+      <c r="J57" s="111">
+        <f t="shared" si="5"/>
+        <v>192.7590708594195</v>
+      </c>
+      <c r="K57" s="112"/>
+      <c r="L57" s="110">
+        <f t="shared" si="2"/>
+        <v>250.20907085941951</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="5"/>
+      <c r="B58" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" s="6"/>
+      <c r="D58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" t="s">
+        <v>110</v>
+      </c>
+      <c r="F58">
+        <v>3</v>
+      </c>
+      <c r="G58" t="s">
+        <v>103</v>
+      </c>
+      <c r="H58" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I58" s="111">
+        <f t="shared" si="1"/>
+        <v>115.65544251565169</v>
+      </c>
+      <c r="J58" s="111">
+        <f t="shared" si="5"/>
+        <v>115.65544251565169</v>
+      </c>
+      <c r="K58" s="112"/>
+      <c r="L58" s="110">
+        <f t="shared" si="2"/>
+        <v>150.12544251565168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="5"/>
+      <c r="B59" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="6"/>
+      <c r="D59" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E59" t="s">
+        <v>110</v>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59" t="s">
+        <v>103</v>
+      </c>
+      <c r="H59" s="111">
+        <f t="shared" si="0"/>
+        <v>38.551814171883898</v>
+      </c>
+      <c r="I59" s="111">
+        <f t="shared" si="1"/>
+        <v>115.65544251565169</v>
+      </c>
+      <c r="J59" s="111">
+        <f t="shared" si="5"/>
+        <v>115.65544251565169</v>
+      </c>
+      <c r="K59" s="112"/>
+      <c r="L59" s="110">
+        <f t="shared" si="2"/>
+        <v>150.12544251565168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="5"/>
+      <c r="B60" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" s="6"/>
+      <c r="D60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" t="s">
+        <v>109</v>
+      </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+      <c r="G60" t="s">
+        <v>103</v>
+      </c>
+      <c r="H60" s="111">
+        <f t="shared" si="0"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I60" s="111">
+        <f t="shared" si="1"/>
+        <v>87.693332552144369</v>
+      </c>
+      <c r="J60" s="111">
+        <f t="shared" si="5"/>
+        <v>87.693332552144369</v>
+      </c>
+      <c r="K60" s="112"/>
+      <c r="L60" s="110">
+        <f t="shared" si="2"/>
+        <v>110.67333255214437</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H61" s="111" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I61" s="111" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J61" s="111"/>
+      <c r="K61" s="112">
+        <f>SUM(J62:J73)</f>
+        <v>1285.9236266810587</v>
+      </c>
+      <c r="L61" s="110" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="5"/>
+      <c r="B62" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="6"/>
+      <c r="D62" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E62" t="s">
+        <v>104</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" t="s">
+        <v>103</v>
+      </c>
+      <c r="H62" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I62" s="111">
+        <f t="shared" si="1"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="J62" s="111">
+        <f t="shared" ref="J62:J73" si="6">I62</f>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="K62" s="112"/>
+      <c r="L62" s="110">
+        <f t="shared" si="2"/>
+        <v>61.27212534477475</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="5"/>
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6"/>
+      <c r="D63" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E63" t="s">
+        <v>104</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63" t="s">
+        <v>103</v>
+      </c>
+      <c r="H63" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I63" s="111">
+        <f t="shared" si="1"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="J63" s="111">
+        <f t="shared" si="6"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="K63" s="112"/>
+      <c r="L63" s="110">
+        <f t="shared" si="2"/>
+        <v>61.27212534477475</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="5"/>
+      <c r="B64" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="6"/>
+      <c r="D64" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E64" t="s">
+        <v>107</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>103</v>
+      </c>
+      <c r="H64" s="111">
+        <f t="shared" si="0"/>
+        <v>45.220459339114129</v>
+      </c>
+      <c r="I64" s="111">
+        <f t="shared" si="1"/>
+        <v>45.220459339114129</v>
+      </c>
+      <c r="J64" s="111">
+        <f t="shared" si="6"/>
+        <v>45.220459339114129</v>
+      </c>
+      <c r="K64" s="112"/>
+      <c r="L64" s="110">
+        <f t="shared" si="2"/>
+        <v>56.710459339114131</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="5"/>
+      <c r="B65" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C65" s="6"/>
+      <c r="D65" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E65" t="s">
+        <v>107</v>
+      </c>
+      <c r="F65">
+        <v>2</v>
+      </c>
+      <c r="G65" t="s">
+        <v>103</v>
+      </c>
+      <c r="H65" s="111">
+        <f t="shared" si="0"/>
+        <v>45.220459339114129</v>
+      </c>
+      <c r="I65" s="111">
+        <f t="shared" si="1"/>
+        <v>90.440918678228257</v>
+      </c>
+      <c r="J65" s="111">
+        <f t="shared" si="6"/>
+        <v>90.440918678228257</v>
+      </c>
+      <c r="K65" s="112"/>
+      <c r="L65" s="110">
+        <f t="shared" si="2"/>
+        <v>113.42091867822826</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="5"/>
+      <c r="B66" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C66" s="6"/>
+      <c r="D66" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E66" t="s">
+        <v>104</v>
+      </c>
+      <c r="F66">
+        <v>3</v>
+      </c>
+      <c r="G66" t="s">
+        <v>103</v>
+      </c>
+      <c r="H66" s="111">
+        <f t="shared" si="0"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I66" s="111">
+        <f t="shared" si="1"/>
+        <v>149.34637603432424</v>
+      </c>
+      <c r="J66" s="111">
+        <f t="shared" si="6"/>
+        <v>149.34637603432424</v>
+      </c>
+      <c r="K66" s="112"/>
+      <c r="L66" s="110">
+        <f t="shared" si="2"/>
+        <v>183.81637603432424</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="5"/>
+      <c r="B67" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C67" s="6"/>
+      <c r="D67" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E67" t="s">
+        <v>106</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67" t="s">
+        <v>103</v>
+      </c>
+      <c r="H67" s="111">
+        <f t="shared" ref="H67:H73" si="7">_xlfn.XLOOKUP(E67,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <v>42.159269173306768</v>
+      </c>
+      <c r="I67" s="111">
+        <f t="shared" si="1"/>
+        <v>84.318538346613536</v>
+      </c>
+      <c r="J67" s="111">
+        <f t="shared" si="6"/>
+        <v>84.318538346613536</v>
+      </c>
+      <c r="K67" s="112"/>
+      <c r="L67" s="110">
+        <f t="shared" si="2"/>
+        <v>107.29853834661354</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="5"/>
+      <c r="B68" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C68" s="6"/>
+      <c r="D68" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E68" t="s">
+        <v>108</v>
+      </c>
+      <c r="F68">
+        <v>3</v>
+      </c>
+      <c r="G68" t="s">
+        <v>103</v>
+      </c>
+      <c r="H68" s="111">
+        <f t="shared" si="7"/>
+        <v>49.154057104913683</v>
+      </c>
+      <c r="I68" s="111">
+        <f t="shared" ref="I68:I73" si="8">IFERROR(H68*F68,"")</f>
+        <v>147.46217131474106</v>
+      </c>
+      <c r="J68" s="111">
+        <f t="shared" si="6"/>
+        <v>147.46217131474106</v>
+      </c>
+      <c r="K68" s="112"/>
+      <c r="L68" s="110">
+        <f t="shared" ref="L68:L73" si="9">IFERROR(I68+($P$10*F68),"")</f>
+        <v>181.93217131474105</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="5"/>
+      <c r="B69" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C69" s="6"/>
+      <c r="D69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E69" t="s">
+        <v>109</v>
+      </c>
+      <c r="F69">
+        <v>6</v>
+      </c>
+      <c r="G69" t="s">
+        <v>103</v>
+      </c>
+      <c r="H69" s="111">
+        <f t="shared" si="7"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I69" s="111">
+        <f t="shared" si="8"/>
+        <v>263.07999765643308</v>
+      </c>
+      <c r="J69" s="111">
+        <f t="shared" si="6"/>
+        <v>263.07999765643308</v>
+      </c>
+      <c r="K69" s="112"/>
+      <c r="L69" s="110">
+        <f t="shared" si="9"/>
+        <v>332.01999765643308</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="5"/>
+      <c r="B70" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C70" s="6"/>
+      <c r="D70" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E70" t="s">
+        <v>109</v>
+      </c>
+      <c r="F70">
+        <v>2</v>
+      </c>
+      <c r="G70" t="s">
+        <v>103</v>
+      </c>
+      <c r="H70" s="111">
+        <f t="shared" si="7"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I70" s="111">
+        <f t="shared" si="8"/>
+        <v>87.693332552144369</v>
+      </c>
+      <c r="J70" s="111">
+        <f t="shared" si="6"/>
+        <v>87.693332552144369</v>
+      </c>
+      <c r="K70" s="112"/>
+      <c r="L70" s="110">
+        <f t="shared" si="9"/>
+        <v>110.67333255214437</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="5"/>
+      <c r="B71" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C71" s="6"/>
+      <c r="D71" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E71" t="s">
+        <v>109</v>
+      </c>
+      <c r="F71">
+        <v>5</v>
+      </c>
+      <c r="G71" t="s">
+        <v>103</v>
+      </c>
+      <c r="H71" s="111">
+        <f t="shared" si="7"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I71" s="111">
+        <f t="shared" si="8"/>
+        <v>219.23333138036094</v>
+      </c>
+      <c r="J71" s="111">
+        <f t="shared" si="6"/>
+        <v>219.23333138036094</v>
+      </c>
+      <c r="K71" s="112"/>
+      <c r="L71" s="110">
+        <f t="shared" si="9"/>
+        <v>276.68333138036093</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="5"/>
+      <c r="B72" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C72" s="6"/>
+      <c r="D72" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E72" t="s">
+        <v>104</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72" t="s">
+        <v>103</v>
+      </c>
+      <c r="H72" s="111">
+        <f t="shared" si="7"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I72" s="111">
+        <f t="shared" si="8"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="J72" s="111">
+        <f t="shared" si="6"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="K72" s="112"/>
+      <c r="L72" s="110">
+        <f t="shared" si="9"/>
+        <v>61.27212534477475</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="8"/>
+      <c r="B73" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C73" s="9"/>
+      <c r="D73" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F73" s="11">
+        <v>1</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H73" s="111">
+        <f t="shared" si="7"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I73" s="111">
+        <f t="shared" si="8"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="J73" s="111">
+        <f t="shared" si="6"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="K73" s="113"/>
+      <c r="L73" s="110">
+        <f t="shared" si="9"/>
+        <v>61.27212534477475</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="127" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" s="128"/>
+      <c r="C74" s="128"/>
+      <c r="D74" s="128"/>
+      <c r="E74" s="128"/>
+      <c r="F74" s="128"/>
+      <c r="G74" s="128"/>
+      <c r="H74" s="128"/>
+      <c r="I74" s="128"/>
+      <c r="J74" s="128"/>
+      <c r="K74" s="114">
+        <f>SUM(K3:K73)</f>
+        <v>13383.612572529586</v>
+      </c>
+      <c r="L74" s="111">
+        <f>SUM(L3:L73)</f>
+        <v>16945.512572529584</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+    </row>
+    <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="133" t="s">
+        <v>192</v>
+      </c>
+      <c r="B76" s="134"/>
+      <c r="C76" s="134"/>
+      <c r="D76" s="134"/>
+      <c r="E76" s="134"/>
+      <c r="F76" s="134"/>
+      <c r="G76" s="134"/>
+      <c r="H76" s="134"/>
+      <c r="I76" s="134"/>
+      <c r="J76" s="134"/>
+      <c r="K76" s="135"/>
+      <c r="L76" s="124"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J77" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="K77" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="L77" s="118"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" t="s">
+        <v>197</v>
+      </c>
+      <c r="H78" s="116"/>
+      <c r="I78" s="116"/>
+      <c r="J78" s="116">
+        <f>SUM(I79:I80)</f>
+        <v>172.5</v>
+      </c>
+      <c r="K78" s="117">
+        <f>J78</f>
+        <v>172.5</v>
+      </c>
+      <c r="L78" s="116"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="5"/>
+      <c r="B79" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="6"/>
+      <c r="D79" t="s">
+        <v>198</v>
+      </c>
+      <c r="E79" t="s">
+        <v>200</v>
+      </c>
+      <c r="F79">
+        <v>150</v>
+      </c>
+      <c r="G79" t="s">
+        <v>201</v>
+      </c>
+      <c r="H79" s="116">
+        <v>0.35</v>
+      </c>
+      <c r="I79" s="116">
+        <f>H79*F79</f>
+        <v>52.5</v>
+      </c>
+      <c r="J79" s="116"/>
+      <c r="K79" s="117"/>
+      <c r="L79" s="116"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="5"/>
+      <c r="B80" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" s="6"/>
+      <c r="D80" t="s">
+        <v>199</v>
+      </c>
+      <c r="E80" t="s">
+        <v>200</v>
+      </c>
+      <c r="F80">
+        <v>6</v>
+      </c>
+      <c r="G80" t="s">
+        <v>202</v>
+      </c>
+      <c r="H80" s="116">
+        <v>20</v>
+      </c>
+      <c r="I80" s="116">
+        <f>H80*F80</f>
+        <v>120</v>
+      </c>
+      <c r="J80" s="116"/>
+      <c r="K80" s="117"/>
+      <c r="L80" s="116"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="127" t="s">
+        <v>4</v>
+      </c>
+      <c r="B81" s="128"/>
+      <c r="C81" s="128"/>
+      <c r="D81" s="128"/>
+      <c r="E81" s="128"/>
+      <c r="F81" s="128"/>
+      <c r="G81" s="128"/>
+      <c r="H81" s="128"/>
+      <c r="I81" s="128"/>
+      <c r="J81" s="128"/>
+      <c r="K81" s="114">
+        <f>SUM(K78:K80)</f>
+        <v>172.5</v>
+      </c>
+      <c r="L81" s="111"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A76:K76"/>
+    <mergeCell ref="A81:J81"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E73" xr:uid="{C5BB27AF-9B30-4FCF-8E44-DCCBC0FC7FF5}">
+      <formula1>$Q$20:$Q$25</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84438618-631B-43FB-9820-9583257CBFE8}">
+  <dimension ref="A1:K56"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="130" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="132"/>
+      <c r="G1" s="127" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="128"/>
+      <c r="I1" s="129"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="119" t="s">
+        <v>205</v>
+      </c>
+      <c r="H2" s="118" t="s">
+        <v>204</v>
+      </c>
+      <c r="I2" s="120" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="123"/>
+      <c r="E3" s="115">
+        <f>SUM(D4:D6)</f>
+        <v>1470.5310082745939</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I3" s="121">
+        <f>E54</f>
+        <v>16945.512572529587</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="123">
+        <f>Costs_final!L4</f>
+        <v>122.5442506895495</v>
+      </c>
+      <c r="E4" s="112"/>
+      <c r="G4" s="127" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="128"/>
+      <c r="I4" s="122">
+        <f>SUM(I3)</f>
+        <v>16945.512572529587</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="123">
+        <f>Costs_final!L5</f>
+        <v>122.5442506895495</v>
+      </c>
+      <c r="E5" s="112"/>
+      <c r="G5" s="6"/>
+      <c r="I5" s="111"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="123">
+        <f>SUM(Costs_final!L7:L19)</f>
+        <v>1225.4425068954949</v>
+      </c>
+      <c r="E6" s="112"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="123"/>
+      <c r="E7" s="112">
+        <f>SUM(D8:D17)</f>
+        <v>3088.6202445365593</v>
+      </c>
+      <c r="K7" s="110"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="123">
+        <f>Costs_final!L21</f>
+        <v>53.64926917330677</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="K8" s="110"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="123">
+        <f>Costs_final!L22</f>
+        <v>226.84183735645652</v>
+      </c>
+      <c r="E9" s="112"/>
+      <c r="K9" s="110"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="123">
+        <f>Costs_final!L23</f>
+        <v>53.64926917330677</v>
+      </c>
+      <c r="E10" s="112"/>
+      <c r="K10" s="110"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="123">
+        <f>Costs_final!L24</f>
+        <v>53.64926917330677</v>
+      </c>
+      <c r="E11" s="112"/>
+      <c r="K11" s="110"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="123">
+        <f>Costs_final!L25</f>
+        <v>107.29853834661354</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="K12" s="110"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="123">
+        <f>Costs_final!L26</f>
+        <v>340.26275603468474</v>
+      </c>
+      <c r="E13" s="112"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="123">
+        <f>Costs_final!L27</f>
+        <v>1180.283921812749</v>
+      </c>
+      <c r="E14" s="112"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="123">
+        <f>Costs_final!L28</f>
+        <v>429.19415338645416</v>
+      </c>
+      <c r="E15" s="112"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="123">
+        <f>Costs_final!L29</f>
+        <v>214.59707669322708</v>
+      </c>
+      <c r="E16" s="112"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="123">
+        <f>Costs_final!L30</f>
+        <v>429.19415338645416</v>
+      </c>
+      <c r="E17" s="112"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="123" t="str">
+        <f>Costs_final!L31</f>
+        <v/>
+      </c>
+      <c r="E18" s="112">
+        <f>SUM(D19:D25)</f>
+        <v>2970.032664607676</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="123">
+        <f>Costs_final!L32</f>
+        <v>606.44057104913679</v>
+      </c>
+      <c r="E19" s="112"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="123">
+        <f>Costs_final!L33</f>
+        <v>150.12544251565168</v>
+      </c>
+      <c r="E20" s="112"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="123">
+        <f>Costs_final!L34</f>
+        <v>442.69333020857749</v>
+      </c>
+      <c r="E21" s="112"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="123">
+        <f>Costs_final!L35</f>
+        <v>221.34666510428875</v>
+      </c>
+      <c r="E22" s="112"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="123">
+        <f>Costs_final!L36</f>
+        <v>332.01999765643308</v>
+      </c>
+      <c r="E23" s="112"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="123">
+        <f>Costs_final!L37</f>
+        <v>664.03999531286615</v>
+      </c>
+      <c r="E24" s="112"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" s="123">
+        <f>Costs_final!L38</f>
+        <v>553.36666276072185</v>
+      </c>
+      <c r="E25" s="112"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="123">
+        <f>Costs_final!L39</f>
+        <v>332.01999765643308</v>
+      </c>
+      <c r="E26" s="111">
+        <f>D26</f>
+        <v>332.01999765643308</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="123" t="str">
+        <f>Costs_final!L40</f>
+        <v/>
+      </c>
+      <c r="E27" s="112">
+        <f>SUM(D28:D30)</f>
+        <v>5714.6118305489526</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="123">
+        <f>Costs_final!L41</f>
+        <v>363.86434262948211</v>
+      </c>
+      <c r="E28" s="112"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="123">
+        <f>Costs_final!L42</f>
+        <v>60.644057104913685</v>
+      </c>
+      <c r="E29" s="112"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+      <c r="B30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="123">
+        <f>SUM(Costs_final!L44:L50)</f>
+        <v>5290.1034308145572</v>
+      </c>
+      <c r="E30" s="112"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="123"/>
+      <c r="E31" s="112">
+        <f>SUM(D32:D40)</f>
+        <v>1762.0532002243128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="123">
+        <f>Costs_final!L52</f>
+        <v>300.25088503130337</v>
+      </c>
+      <c r="E32" s="112"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="123">
+        <f>Costs_final!L53</f>
+        <v>200.1672566875356</v>
+      </c>
+      <c r="E33" s="112"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+      <c r="B34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="123">
+        <f>Costs_final!L54</f>
+        <v>250.20907085941951</v>
+      </c>
+      <c r="E34" s="112"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+      <c r="B35" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="123">
+        <f>Costs_final!L55</f>
+        <v>150.12544251565168</v>
+      </c>
+      <c r="E35" s="112"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" s="123">
+        <f>Costs_final!L56</f>
+        <v>200.1672566875356</v>
+      </c>
+      <c r="E36" s="112"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="5"/>
+      <c r="B37" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="123">
+        <f>Costs_final!L57</f>
+        <v>250.20907085941951</v>
+      </c>
+      <c r="E37" s="112"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" s="123">
+        <f>Costs_final!L58</f>
+        <v>150.12544251565168</v>
+      </c>
+      <c r="E38" s="112"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" s="123">
+        <f>Costs_final!L59</f>
+        <v>150.12544251565168</v>
+      </c>
+      <c r="E39" s="112"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" s="123">
+        <f>Costs_final!L60</f>
+        <v>110.67333255214437</v>
+      </c>
+      <c r="E40" s="112"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="123" t="str">
+        <f>Costs_final!L61</f>
+        <v/>
+      </c>
+      <c r="E41" s="112">
+        <f>SUM(D42:D53)</f>
+        <v>1607.6436266810585</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" s="123">
+        <f>Costs_final!L62</f>
+        <v>61.27212534477475</v>
+      </c>
+      <c r="E42" s="112"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" s="123">
+        <f>Costs_final!L63</f>
+        <v>61.27212534477475</v>
+      </c>
+      <c r="E43" s="112"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="5"/>
+      <c r="B44" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" s="123">
+        <f>Costs_final!L64</f>
+        <v>56.710459339114131</v>
+      </c>
+      <c r="E44" s="112"/>
+    </row>
+    <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="5"/>
+      <c r="B45" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="123">
+        <f>Costs_final!L65</f>
+        <v>113.42091867822826</v>
+      </c>
+      <c r="E45" s="112"/>
+    </row>
+    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="5"/>
+      <c r="B46" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="123">
+        <f>Costs_final!L66</f>
+        <v>183.81637603432424</v>
+      </c>
+      <c r="E46" s="112"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="5"/>
+      <c r="B47" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="123">
+        <f>Costs_final!L67</f>
+        <v>107.29853834661354</v>
+      </c>
+      <c r="E47" s="112"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="5"/>
+      <c r="B48" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="123">
+        <f>Costs_final!L68</f>
+        <v>181.93217131474105</v>
+      </c>
+      <c r="E48" s="112"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
+      <c r="B49" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" s="123">
+        <f>Costs_final!L69</f>
+        <v>332.01999765643308</v>
+      </c>
+      <c r="E49" s="112"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="5"/>
+      <c r="B50" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="123">
+        <f>Costs_final!L70</f>
+        <v>110.67333255214437</v>
+      </c>
+      <c r="E50" s="112"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="5"/>
+      <c r="B51" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D51" s="123">
+        <f>Costs_final!L71</f>
+        <v>276.68333138036093</v>
+      </c>
+      <c r="E51" s="112"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="5"/>
+      <c r="B52" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="123">
+        <f>Costs_final!L72</f>
+        <v>61.27212534477475</v>
+      </c>
+      <c r="E52" s="112"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="8"/>
+      <c r="B53" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" s="123">
+        <f>Costs_final!L73</f>
+        <v>61.27212534477475</v>
+      </c>
+      <c r="E53" s="113"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="127" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="128"/>
+      <c r="C54" s="128"/>
+      <c r="D54" s="128"/>
+      <c r="E54" s="114">
+        <f>SUM(E3:E53)</f>
+        <v>16945.512572529587</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A54:D54"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/budget.xlsx
+++ b/docs/budget.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Desktop\proyectos\IRBoard\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE692509-35D9-4BFA-B51B-C27FC9234824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF91FD6-6829-470F-87AD-E183670224AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Company definition" sheetId="2" r:id="rId1"/>
     <sheet name="Costs_init" sheetId="1" r:id="rId2"/>
     <sheet name="Client_init" sheetId="5" r:id="rId3"/>
     <sheet name="Costs_final" sheetId="6" r:id="rId4"/>
-    <sheet name="Client_final" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="217">
   <si>
     <t>I1</t>
   </si>
@@ -689,6 +688,9 @@
   <si>
     <t>Dilution increase per billable hour</t>
   </si>
+  <si>
+    <t>deviation from original</t>
+  </si>
 </sst>
 </file>
 
@@ -1124,7 +1126,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1338,15 +1340,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1354,6 +1347,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1365,6 +1364,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -31006,27 +31010,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="127" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="132"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="129"/>
       <c r="L1" s="125" t="s">
         <v>213</v>
       </c>
-      <c r="N1" s="127" t="s">
+      <c r="N1" s="130" t="s">
         <v>203</v>
       </c>
-      <c r="O1" s="128"/>
-      <c r="P1" s="129"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="135"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -31190,15 +31194,13 @@
         <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
-      <c r="N5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="O5" t="s">
-        <v>208</v>
-      </c>
-      <c r="P5" s="112">
-        <f>0.25*(P3+P4)</f>
-        <v>3299.7543381673559</v>
+      <c r="N5" s="130" t="s">
+        <v>115</v>
+      </c>
+      <c r="O5" s="131"/>
+      <c r="P5" s="122">
+        <f>SUM(P3:P4)</f>
+        <v>13199.017352669423</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -31224,14 +31226,6 @@
       </c>
       <c r="K6" s="112"/>
       <c r="L6" s="110"/>
-      <c r="N6" s="127" t="s">
-        <v>115</v>
-      </c>
-      <c r="O6" s="128"/>
-      <c r="P6" s="122">
-        <f>SUM(P3:P5)</f>
-        <v>16498.77169083678</v>
-      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
@@ -31265,6 +31259,13 @@
         <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
+      <c r="O7" t="s">
+        <v>208</v>
+      </c>
+      <c r="P7" s="111">
+        <f>0.25*(P3+P4)</f>
+        <v>3299.7543381673559</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
@@ -31302,7 +31303,7 @@
         <v>211</v>
       </c>
       <c r="P8" s="111">
-        <f>P6-P3</f>
+        <f>P5+P7-P3</f>
         <v>3472.2543381673568</v>
       </c>
     </row>
@@ -33604,18 +33605,18 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="127" t="s">
+      <c r="A74" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="B74" s="128"/>
-      <c r="C74" s="128"/>
-      <c r="D74" s="128"/>
-      <c r="E74" s="128"/>
-      <c r="F74" s="128"/>
-      <c r="G74" s="128"/>
-      <c r="H74" s="128"/>
-      <c r="I74" s="128"/>
-      <c r="J74" s="128"/>
+      <c r="B74" s="131"/>
+      <c r="C74" s="131"/>
+      <c r="D74" s="131"/>
+      <c r="E74" s="131"/>
+      <c r="F74" s="131"/>
+      <c r="G74" s="131"/>
+      <c r="H74" s="131"/>
+      <c r="I74" s="131"/>
+      <c r="J74" s="131"/>
       <c r="K74" s="114">
         <f>SUM(K3:K73)</f>
         <v>13026.517352669423</v>
@@ -33630,19 +33631,19 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="133" t="s">
+      <c r="A76" s="132" t="s">
         <v>192</v>
       </c>
-      <c r="B76" s="134"/>
-      <c r="C76" s="134"/>
-      <c r="D76" s="134"/>
-      <c r="E76" s="134"/>
-      <c r="F76" s="134"/>
-      <c r="G76" s="134"/>
-      <c r="H76" s="134"/>
-      <c r="I76" s="134"/>
-      <c r="J76" s="134"/>
-      <c r="K76" s="135"/>
+      <c r="B76" s="133"/>
+      <c r="C76" s="133"/>
+      <c r="D76" s="133"/>
+      <c r="E76" s="133"/>
+      <c r="F76" s="133"/>
+      <c r="G76" s="133"/>
+      <c r="H76" s="133"/>
+      <c r="I76" s="133"/>
+      <c r="J76" s="133"/>
+      <c r="K76" s="134"/>
       <c r="L76" s="124"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
@@ -33761,18 +33762,18 @@
       <c r="L80" s="116"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="127" t="s">
+      <c r="A81" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="B81" s="128"/>
-      <c r="C81" s="128"/>
-      <c r="D81" s="128"/>
-      <c r="E81" s="128"/>
-      <c r="F81" s="128"/>
-      <c r="G81" s="128"/>
-      <c r="H81" s="128"/>
-      <c r="I81" s="128"/>
-      <c r="J81" s="128"/>
+      <c r="B81" s="131"/>
+      <c r="C81" s="131"/>
+      <c r="D81" s="131"/>
+      <c r="E81" s="131"/>
+      <c r="F81" s="131"/>
+      <c r="G81" s="131"/>
+      <c r="H81" s="131"/>
+      <c r="I81" s="131"/>
+      <c r="J81" s="131"/>
       <c r="K81" s="114">
         <f>SUM(K78:K80)</f>
         <v>172.5</v>
@@ -33791,7 +33792,7 @@
     <mergeCell ref="A76:K76"/>
     <mergeCell ref="A81:J81"/>
     <mergeCell ref="N1:P1"/>
-    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N5:O5"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
@@ -33822,18 +33823,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="127" t="s">
         <v>210</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="132"/>
-      <c r="G1" s="127" t="s">
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="129"/>
+      <c r="G1" s="130" t="s">
         <v>209</v>
       </c>
-      <c r="H1" s="128"/>
-      <c r="I1" s="129"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="135"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -33898,10 +33899,10 @@
         <v>122.72425068954949</v>
       </c>
       <c r="E4" s="112"/>
-      <c r="G4" s="127" t="s">
+      <c r="G4" s="130" t="s">
         <v>115</v>
       </c>
-      <c r="H4" s="128"/>
+      <c r="H4" s="131"/>
       <c r="I4" s="122">
         <f>SUM(I3)</f>
         <v>16500.517352669427</v>
@@ -34614,12 +34615,12 @@
       <c r="E53" s="113"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="127" t="s">
+      <c r="A54" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="128"/>
-      <c r="C54" s="128"/>
-      <c r="D54" s="128"/>
+      <c r="B54" s="131"/>
+      <c r="C54" s="131"/>
+      <c r="D54" s="131"/>
       <c r="E54" s="114">
         <f>SUM(E3:E53)</f>
         <v>16500.517352669427</v>
@@ -34665,30 +34666,30 @@
     <col min="18" max="18" width="23.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="130" t="s">
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="127" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="132"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="129"/>
       <c r="L1" s="125" t="s">
         <v>213</v>
       </c>
-      <c r="N1" s="127" t="s">
+      <c r="N1" s="130" t="s">
         <v>203</v>
       </c>
-      <c r="O1" s="128"/>
-      <c r="P1" s="129"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="135"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -34732,8 +34733,11 @@
       <c r="P2" s="120" t="s">
         <v>4</v>
       </c>
+      <c r="Q2" s="136" t="s">
+        <v>216</v>
+      </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -34768,8 +34772,12 @@
         <f>K74</f>
         <v>13383.612572529586</v>
       </c>
+      <c r="Q3" s="137">
+        <f>((P3-Costs_init!P3)/Costs_init!P3)</f>
+        <v>2.7412946238235029E-2</v>
+      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
         <v>7</v>
@@ -34802,7 +34810,7 @@
       <c r="K4" s="112"/>
       <c r="L4" s="110">
         <f t="shared" ref="L4:L67" si="2">IFERROR(I4+($P$10*F4),"")</f>
-        <v>122.5442506895495</v>
+        <v>121.9842506895495</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>8</v>
@@ -34814,8 +34822,12 @@
         <f>K81</f>
         <v>172.5</v>
       </c>
+      <c r="Q4" s="137">
+        <f>((P4-Costs_init!P4)/Costs_init!P4)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
         <v>13</v>
@@ -34848,20 +34860,22 @@
       <c r="K5" s="112"/>
       <c r="L5" s="110">
         <f t="shared" si="2"/>
-        <v>122.5442506895495</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="O5" t="s">
-        <v>208</v>
-      </c>
-      <c r="P5" s="112">
-        <f>0.25*(P3+P4)</f>
-        <v>3389.0281431323965</v>
+        <v>121.9842506895495</v>
+      </c>
+      <c r="N5" s="130" t="s">
+        <v>115</v>
+      </c>
+      <c r="O5" s="131"/>
+      <c r="P5" s="122">
+        <f>SUM(P3:P4)</f>
+        <v>13556.112572529586</v>
+      </c>
+      <c r="Q5" s="137">
+        <f>((P5-Costs_init!P5)/Costs_init!P5)</f>
+        <v>2.7054682202379422E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
         <v>14</v>
@@ -34884,16 +34898,9 @@
       </c>
       <c r="K6" s="112"/>
       <c r="L6" s="110"/>
-      <c r="N6" s="127" t="s">
-        <v>115</v>
-      </c>
-      <c r="O6" s="128"/>
-      <c r="P6" s="122">
-        <f>SUM(P3:P5)</f>
-        <v>16945.140715661983</v>
-      </c>
+      <c r="Q6" s="137"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
@@ -34923,10 +34930,18 @@
       <c r="K7" s="112"/>
       <c r="L7" s="110">
         <f t="shared" si="2"/>
-        <v>61.27212534477475</v>
-      </c>
+        <v>60.992125344774749</v>
+      </c>
+      <c r="O7" t="s">
+        <v>208</v>
+      </c>
+      <c r="P7">
+        <f>Costs_init!P7</f>
+        <v>3299.7543381673559</v>
+      </c>
+      <c r="Q7" s="137"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
@@ -34956,17 +34971,17 @@
       <c r="K8" s="112"/>
       <c r="L8" s="110">
         <f t="shared" si="2"/>
-        <v>122.5442506895495</v>
+        <v>121.9842506895495</v>
       </c>
       <c r="O8" t="s">
         <v>211</v>
       </c>
       <c r="P8" s="111">
-        <f>P6-P3</f>
-        <v>3561.5281431323965</v>
+        <f>P5+P7-P3</f>
+        <v>3472.2543381673568</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
@@ -34996,7 +35011,7 @@
       <c r="K9" s="112"/>
       <c r="L9" s="110">
         <f t="shared" si="2"/>
-        <v>61.27212534477475</v>
+        <v>60.992125344774749</v>
       </c>
       <c r="O9" t="s">
         <v>214</v>
@@ -35006,7 +35021,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
@@ -35036,17 +35051,17 @@
       <c r="K10" s="112"/>
       <c r="L10" s="110">
         <f t="shared" si="2"/>
-        <v>122.5442506895495</v>
+        <v>121.9842506895495</v>
       </c>
       <c r="O10" t="s">
         <v>215</v>
       </c>
       <c r="P10" s="123">
         <f>ROUNDUP(P8/P9,2)</f>
-        <v>11.49</v>
+        <v>11.209999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
@@ -35076,10 +35091,10 @@
       <c r="K11" s="112"/>
       <c r="L11" s="110">
         <f t="shared" si="2"/>
-        <v>61.27212534477475</v>
+        <v>60.992125344774749</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
@@ -35109,10 +35124,10 @@
       <c r="K12" s="112"/>
       <c r="L12" s="110">
         <f t="shared" si="2"/>
-        <v>61.27212534477475</v>
+        <v>60.992125344774749</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
@@ -35142,10 +35157,10 @@
       <c r="K13" s="112"/>
       <c r="L13" s="110">
         <f t="shared" si="2"/>
-        <v>122.5442506895495</v>
+        <v>121.9842506895495</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
@@ -35175,10 +35190,10 @@
       <c r="K14" s="112"/>
       <c r="L14" s="110">
         <f t="shared" si="2"/>
-        <v>122.5442506895495</v>
+        <v>121.9842506895495</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
@@ -35208,10 +35223,10 @@
       <c r="K15" s="112"/>
       <c r="L15" s="110">
         <f t="shared" si="2"/>
-        <v>122.5442506895495</v>
+        <v>121.9842506895495</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
@@ -35241,7 +35256,7 @@
       <c r="K16" s="112"/>
       <c r="L16" s="110">
         <f t="shared" si="2"/>
-        <v>122.5442506895495</v>
+        <v>121.9842506895495</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -35274,7 +35289,7 @@
       <c r="K17" s="112"/>
       <c r="L17" s="110">
         <f t="shared" si="2"/>
-        <v>61.27212534477475</v>
+        <v>60.992125344774749</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -35307,7 +35322,7 @@
       <c r="K18" s="112"/>
       <c r="L18" s="110">
         <f t="shared" si="2"/>
-        <v>61.27212534477475</v>
+        <v>60.992125344774749</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -35340,7 +35355,7 @@
       <c r="K19" s="112"/>
       <c r="L19" s="110">
         <f t="shared" si="2"/>
-        <v>122.5442506895495</v>
+        <v>121.9842506895495</v>
       </c>
       <c r="Q19" s="7" t="s">
         <v>105</v>
@@ -35416,7 +35431,7 @@
       <c r="K21" s="112"/>
       <c r="L21" s="110">
         <f t="shared" si="2"/>
-        <v>53.64926917330677</v>
+        <v>53.369269173306769</v>
       </c>
       <c r="Q21" t="s">
         <v>107</v>
@@ -35459,7 +35474,7 @@
       <c r="K22" s="112"/>
       <c r="L22" s="110">
         <f t="shared" si="2"/>
-        <v>226.84183735645652</v>
+        <v>225.72183735645652</v>
       </c>
       <c r="Q22" t="s">
         <v>106</v>
@@ -35502,7 +35517,7 @@
       <c r="K23" s="112"/>
       <c r="L23" s="110">
         <f t="shared" si="2"/>
-        <v>53.64926917330677</v>
+        <v>53.369269173306769</v>
       </c>
       <c r="Q23" t="s">
         <v>108</v>
@@ -35545,7 +35560,7 @@
       <c r="K24" s="112"/>
       <c r="L24" s="110">
         <f t="shared" si="2"/>
-        <v>53.64926917330677</v>
+        <v>53.369269173306769</v>
       </c>
       <c r="Q24" t="s">
         <v>109</v>
@@ -35588,7 +35603,7 @@
       <c r="K25" s="112"/>
       <c r="L25" s="110">
         <f t="shared" si="2"/>
-        <v>107.29853834661354</v>
+        <v>106.73853834661354</v>
       </c>
       <c r="Q25" t="s">
         <v>110</v>
@@ -35631,7 +35646,7 @@
       <c r="K26" s="112"/>
       <c r="L26" s="110">
         <f t="shared" si="2"/>
-        <v>340.26275603468474</v>
+        <v>338.58275603468473</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -35667,7 +35682,7 @@
       <c r="K27" s="112"/>
       <c r="L27" s="110">
         <f t="shared" si="2"/>
-        <v>1180.283921812749</v>
+        <v>1174.1239218127489</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -35703,7 +35718,7 @@
       <c r="K28" s="112"/>
       <c r="L28" s="110">
         <f t="shared" si="2"/>
-        <v>429.19415338645416</v>
+        <v>426.95415338645415</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -35739,7 +35754,7 @@
       <c r="K29" s="112"/>
       <c r="L29" s="110">
         <f t="shared" si="2"/>
-        <v>214.59707669322708</v>
+        <v>213.47707669322708</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -35775,7 +35790,7 @@
       <c r="K30" s="112"/>
       <c r="L30" s="110">
         <f t="shared" si="2"/>
-        <v>429.19415338645416</v>
+        <v>426.95415338645415</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
@@ -35838,7 +35853,7 @@
       <c r="K32" s="112"/>
       <c r="L32" s="110">
         <f t="shared" si="2"/>
-        <v>606.44057104913679</v>
+        <v>603.64057104913684</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -35874,7 +35889,7 @@
       <c r="K33" s="112"/>
       <c r="L33" s="110">
         <f t="shared" si="2"/>
-        <v>150.12544251565168</v>
+        <v>149.28544251565168</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -35910,7 +35925,7 @@
       <c r="K34" s="112"/>
       <c r="L34" s="110">
         <f t="shared" si="2"/>
-        <v>442.69333020857749</v>
+        <v>440.45333020857748</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -35946,7 +35961,7 @@
       <c r="K35" s="112"/>
       <c r="L35" s="110">
         <f t="shared" si="2"/>
-        <v>221.34666510428875</v>
+        <v>220.22666510428874</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -35982,7 +35997,7 @@
       <c r="K36" s="112"/>
       <c r="L36" s="110">
         <f t="shared" si="2"/>
-        <v>332.01999765643308</v>
+        <v>330.33999765643307</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -36018,7 +36033,7 @@
       <c r="K37" s="112"/>
       <c r="L37" s="110">
         <f t="shared" si="2"/>
-        <v>664.03999531286615</v>
+        <v>660.67999531286614</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -36054,7 +36069,7 @@
       <c r="K38" s="112"/>
       <c r="L38" s="110">
         <f t="shared" si="2"/>
-        <v>553.36666276072185</v>
+        <v>550.5666627607219</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -36093,7 +36108,7 @@
       </c>
       <c r="L39" s="110">
         <f t="shared" si="2"/>
-        <v>332.01999765643308</v>
+        <v>330.33999765643307</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -36156,7 +36171,7 @@
       <c r="K41" s="112"/>
       <c r="L41" s="110">
         <f t="shared" si="2"/>
-        <v>363.86434262948211</v>
+        <v>362.1843426294821</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -36192,7 +36207,7 @@
       <c r="K42" s="112"/>
       <c r="L42" s="110">
         <f t="shared" si="2"/>
-        <v>60.644057104913685</v>
+        <v>60.364057104913684</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -36252,7 +36267,7 @@
       <c r="K44" s="112"/>
       <c r="L44" s="110">
         <f t="shared" si="2"/>
-        <v>1100.9199117814458</v>
+        <v>1094.7599117814457</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -36285,7 +36300,7 @@
       <c r="K45" s="112"/>
       <c r="L45" s="110">
         <f t="shared" si="2"/>
-        <v>300.25088503130337</v>
+        <v>298.57088503130336</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -36318,7 +36333,7 @@
       <c r="K46" s="112"/>
       <c r="L46" s="110">
         <f t="shared" si="2"/>
-        <v>1328.0799906257323</v>
+        <v>1321.3599906257323</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -36351,7 +36366,7 @@
       <c r="K47" s="112"/>
       <c r="L47" s="110">
         <f t="shared" si="2"/>
-        <v>600.50177006260674</v>
+        <v>597.14177006260672</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -36384,7 +36399,7 @@
       <c r="K48" s="112"/>
       <c r="L48" s="110">
         <f t="shared" si="2"/>
-        <v>1106.7333255214437</v>
+        <v>1101.1333255214438</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -36417,7 +36432,7 @@
       <c r="K49" s="112"/>
       <c r="L49" s="110">
         <f t="shared" si="2"/>
-        <v>553.36666276072185</v>
+        <v>550.5666627607219</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -36450,7 +36465,7 @@
       <c r="K50" s="112"/>
       <c r="L50" s="110">
         <f t="shared" si="2"/>
-        <v>300.25088503130337</v>
+        <v>298.57088503130336</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -36513,7 +36528,7 @@
       <c r="K52" s="112"/>
       <c r="L52" s="110">
         <f t="shared" si="2"/>
-        <v>300.25088503130337</v>
+        <v>298.57088503130336</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -36549,7 +36564,7 @@
       <c r="K53" s="112"/>
       <c r="L53" s="110">
         <f t="shared" si="2"/>
-        <v>200.1672566875356</v>
+        <v>199.04725668753559</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -36585,7 +36600,7 @@
       <c r="K54" s="112"/>
       <c r="L54" s="110">
         <f t="shared" si="2"/>
-        <v>250.20907085941951</v>
+        <v>248.80907085941948</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -36621,7 +36636,7 @@
       <c r="K55" s="112"/>
       <c r="L55" s="110">
         <f t="shared" si="2"/>
-        <v>150.12544251565168</v>
+        <v>149.28544251565168</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -36657,7 +36672,7 @@
       <c r="K56" s="112"/>
       <c r="L56" s="110">
         <f t="shared" si="2"/>
-        <v>200.1672566875356</v>
+        <v>199.04725668753559</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -36693,7 +36708,7 @@
       <c r="K57" s="112"/>
       <c r="L57" s="110">
         <f t="shared" si="2"/>
-        <v>250.20907085941951</v>
+        <v>248.80907085941948</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -36729,7 +36744,7 @@
       <c r="K58" s="112"/>
       <c r="L58" s="110">
         <f t="shared" si="2"/>
-        <v>150.12544251565168</v>
+        <v>149.28544251565168</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -36765,7 +36780,7 @@
       <c r="K59" s="112"/>
       <c r="L59" s="110">
         <f t="shared" si="2"/>
-        <v>150.12544251565168</v>
+        <v>149.28544251565168</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
@@ -36801,7 +36816,7 @@
       <c r="K60" s="112"/>
       <c r="L60" s="110">
         <f t="shared" si="2"/>
-        <v>110.67333255214437</v>
+        <v>110.11333255214437</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -36864,7 +36879,7 @@
       <c r="K62" s="112"/>
       <c r="L62" s="110">
         <f t="shared" si="2"/>
-        <v>61.27212534477475</v>
+        <v>60.992125344774749</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -36900,7 +36915,7 @@
       <c r="K63" s="112"/>
       <c r="L63" s="110">
         <f t="shared" si="2"/>
-        <v>61.27212534477475</v>
+        <v>60.992125344774749</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
@@ -36936,7 +36951,7 @@
       <c r="K64" s="112"/>
       <c r="L64" s="110">
         <f t="shared" si="2"/>
-        <v>56.710459339114131</v>
+        <v>56.43045933911413</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -36972,7 +36987,7 @@
       <c r="K65" s="112"/>
       <c r="L65" s="110">
         <f t="shared" si="2"/>
-        <v>113.42091867822826</v>
+        <v>112.86091867822826</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -37008,7 +37023,7 @@
       <c r="K66" s="112"/>
       <c r="L66" s="110">
         <f t="shared" si="2"/>
-        <v>183.81637603432424</v>
+        <v>182.97637603432423</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
@@ -37044,7 +37059,7 @@
       <c r="K67" s="112"/>
       <c r="L67" s="110">
         <f t="shared" si="2"/>
-        <v>107.29853834661354</v>
+        <v>106.73853834661354</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
@@ -37080,7 +37095,7 @@
       <c r="K68" s="112"/>
       <c r="L68" s="110">
         <f t="shared" ref="L68:L73" si="9">IFERROR(I68+($P$10*F68),"")</f>
-        <v>181.93217131474105</v>
+        <v>181.09217131474105</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
@@ -37116,7 +37131,7 @@
       <c r="K69" s="112"/>
       <c r="L69" s="110">
         <f t="shared" si="9"/>
-        <v>332.01999765643308</v>
+        <v>330.33999765643307</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
@@ -37152,7 +37167,7 @@
       <c r="K70" s="112"/>
       <c r="L70" s="110">
         <f t="shared" si="9"/>
-        <v>110.67333255214437</v>
+        <v>110.11333255214437</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
@@ -37188,7 +37203,7 @@
       <c r="K71" s="112"/>
       <c r="L71" s="110">
         <f t="shared" si="9"/>
-        <v>276.68333138036093</v>
+        <v>275.28333138036095</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -37224,7 +37239,7 @@
       <c r="K72" s="112"/>
       <c r="L72" s="110">
         <f t="shared" si="9"/>
-        <v>61.27212534477475</v>
+        <v>60.992125344774749</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -37260,29 +37275,29 @@
       <c r="K73" s="113"/>
       <c r="L73" s="110">
         <f t="shared" si="9"/>
-        <v>61.27212534477475</v>
+        <v>60.992125344774749</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="127" t="s">
+      <c r="A74" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="B74" s="128"/>
-      <c r="C74" s="128"/>
-      <c r="D74" s="128"/>
-      <c r="E74" s="128"/>
-      <c r="F74" s="128"/>
-      <c r="G74" s="128"/>
-      <c r="H74" s="128"/>
-      <c r="I74" s="128"/>
-      <c r="J74" s="128"/>
+      <c r="B74" s="131"/>
+      <c r="C74" s="131"/>
+      <c r="D74" s="131"/>
+      <c r="E74" s="131"/>
+      <c r="F74" s="131"/>
+      <c r="G74" s="131"/>
+      <c r="H74" s="131"/>
+      <c r="I74" s="131"/>
+      <c r="J74" s="131"/>
       <c r="K74" s="114">
         <f>SUM(K3:K73)</f>
         <v>13383.612572529586</v>
       </c>
       <c r="L74" s="111">
         <f>SUM(L3:L73)</f>
-        <v>16945.512572529584</v>
+        <v>16858.712572529592</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
@@ -37290,19 +37305,19 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="133" t="s">
+      <c r="A76" s="132" t="s">
         <v>192</v>
       </c>
-      <c r="B76" s="134"/>
-      <c r="C76" s="134"/>
-      <c r="D76" s="134"/>
-      <c r="E76" s="134"/>
-      <c r="F76" s="134"/>
-      <c r="G76" s="134"/>
-      <c r="H76" s="134"/>
-      <c r="I76" s="134"/>
-      <c r="J76" s="134"/>
-      <c r="K76" s="135"/>
+      <c r="B76" s="133"/>
+      <c r="C76" s="133"/>
+      <c r="D76" s="133"/>
+      <c r="E76" s="133"/>
+      <c r="F76" s="133"/>
+      <c r="G76" s="133"/>
+      <c r="H76" s="133"/>
+      <c r="I76" s="133"/>
+      <c r="J76" s="133"/>
+      <c r="K76" s="134"/>
       <c r="L76" s="124"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
@@ -37421,18 +37436,18 @@
       <c r="L80" s="116"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="127" t="s">
+      <c r="A81" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="B81" s="128"/>
-      <c r="C81" s="128"/>
-      <c r="D81" s="128"/>
-      <c r="E81" s="128"/>
-      <c r="F81" s="128"/>
-      <c r="G81" s="128"/>
-      <c r="H81" s="128"/>
-      <c r="I81" s="128"/>
-      <c r="J81" s="128"/>
+      <c r="B81" s="131"/>
+      <c r="C81" s="131"/>
+      <c r="D81" s="131"/>
+      <c r="E81" s="131"/>
+      <c r="F81" s="131"/>
+      <c r="G81" s="131"/>
+      <c r="H81" s="131"/>
+      <c r="I81" s="131"/>
+      <c r="J81" s="131"/>
       <c r="K81" s="114">
         <f>SUM(K78:K80)</f>
         <v>172.5</v>
@@ -37446,12 +37461,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A81:J81"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="N1:P1"/>
-    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N5:O5"/>
     <mergeCell ref="A74:J74"/>
     <mergeCell ref="A76:K76"/>
-    <mergeCell ref="A81:J81"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E73" xr:uid="{C5BB27AF-9B30-4FCF-8E44-DCCBC0FC7FF5}">
@@ -37461,844 +37476,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84438618-631B-43FB-9820-9583257CBFE8}">
-  <dimension ref="A1:K56"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="130" t="s">
-        <v>210</v>
-      </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="132"/>
-      <c r="G1" s="127" t="s">
-        <v>209</v>
-      </c>
-      <c r="H1" s="128"/>
-      <c r="I1" s="129"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="119" t="s">
-        <v>205</v>
-      </c>
-      <c r="H2" s="118" t="s">
-        <v>204</v>
-      </c>
-      <c r="I2" s="120" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="123"/>
-      <c r="E3" s="115">
-        <f>SUM(D4:D6)</f>
-        <v>1470.5310082745939</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" t="s">
-        <v>206</v>
-      </c>
-      <c r="I3" s="121">
-        <f>E54</f>
-        <v>16945.512572529587</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="123">
-        <f>Costs_final!L4</f>
-        <v>122.5442506895495</v>
-      </c>
-      <c r="E4" s="112"/>
-      <c r="G4" s="127" t="s">
-        <v>115</v>
-      </c>
-      <c r="H4" s="128"/>
-      <c r="I4" s="122">
-        <f>SUM(I3)</f>
-        <v>16945.512572529587</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="123">
-        <f>Costs_final!L5</f>
-        <v>122.5442506895495</v>
-      </c>
-      <c r="E5" s="112"/>
-      <c r="G5" s="6"/>
-      <c r="I5" s="111"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="123">
-        <f>SUM(Costs_final!L7:L19)</f>
-        <v>1225.4425068954949</v>
-      </c>
-      <c r="E6" s="112"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="123"/>
-      <c r="E7" s="112">
-        <f>SUM(D8:D17)</f>
-        <v>3088.6202445365593</v>
-      </c>
-      <c r="K7" s="110"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="123">
-        <f>Costs_final!L21</f>
-        <v>53.64926917330677</v>
-      </c>
-      <c r="E8" s="112"/>
-      <c r="K8" s="110"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="123">
-        <f>Costs_final!L22</f>
-        <v>226.84183735645652</v>
-      </c>
-      <c r="E9" s="112"/>
-      <c r="K9" s="110"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="123">
-        <f>Costs_final!L23</f>
-        <v>53.64926917330677</v>
-      </c>
-      <c r="E10" s="112"/>
-      <c r="K10" s="110"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="123">
-        <f>Costs_final!L24</f>
-        <v>53.64926917330677</v>
-      </c>
-      <c r="E11" s="112"/>
-      <c r="K11" s="110"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="123">
-        <f>Costs_final!L25</f>
-        <v>107.29853834661354</v>
-      </c>
-      <c r="E12" s="112"/>
-      <c r="K12" s="110"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="123">
-        <f>Costs_final!L26</f>
-        <v>340.26275603468474</v>
-      </c>
-      <c r="E13" s="112"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="123">
-        <f>Costs_final!L27</f>
-        <v>1180.283921812749</v>
-      </c>
-      <c r="E14" s="112"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="123">
-        <f>Costs_final!L28</f>
-        <v>429.19415338645416</v>
-      </c>
-      <c r="E15" s="112"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="123">
-        <f>Costs_final!L29</f>
-        <v>214.59707669322708</v>
-      </c>
-      <c r="E16" s="112"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="123">
-        <f>Costs_final!L30</f>
-        <v>429.19415338645416</v>
-      </c>
-      <c r="E17" s="112"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="123" t="str">
-        <f>Costs_final!L31</f>
-        <v/>
-      </c>
-      <c r="E18" s="112">
-        <f>SUM(D19:D25)</f>
-        <v>2970.032664607676</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="123">
-        <f>Costs_final!L32</f>
-        <v>606.44057104913679</v>
-      </c>
-      <c r="E19" s="112"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="123">
-        <f>Costs_final!L33</f>
-        <v>150.12544251565168</v>
-      </c>
-      <c r="E20" s="112"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="123">
-        <f>Costs_final!L34</f>
-        <v>442.69333020857749</v>
-      </c>
-      <c r="E21" s="112"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="123">
-        <f>Costs_final!L35</f>
-        <v>221.34666510428875</v>
-      </c>
-      <c r="E22" s="112"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="123">
-        <f>Costs_final!L36</f>
-        <v>332.01999765643308</v>
-      </c>
-      <c r="E23" s="112"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="123">
-        <f>Costs_final!L37</f>
-        <v>664.03999531286615</v>
-      </c>
-      <c r="E24" s="112"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D25" s="123">
-        <f>Costs_final!L38</f>
-        <v>553.36666276072185</v>
-      </c>
-      <c r="E25" s="112"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="123">
-        <f>Costs_final!L39</f>
-        <v>332.01999765643308</v>
-      </c>
-      <c r="E26" s="111">
-        <f>D26</f>
-        <v>332.01999765643308</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="123" t="str">
-        <f>Costs_final!L40</f>
-        <v/>
-      </c>
-      <c r="E27" s="112">
-        <f>SUM(D28:D30)</f>
-        <v>5714.6118305489526</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="123">
-        <f>Costs_final!L41</f>
-        <v>363.86434262948211</v>
-      </c>
-      <c r="E28" s="112"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" s="123">
-        <f>Costs_final!L42</f>
-        <v>60.644057104913685</v>
-      </c>
-      <c r="E29" s="112"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="123">
-        <f>SUM(Costs_final!L44:L50)</f>
-        <v>5290.1034308145572</v>
-      </c>
-      <c r="E30" s="112"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="123"/>
-      <c r="E31" s="112">
-        <f>SUM(D32:D40)</f>
-        <v>1762.0532002243128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="123">
-        <f>Costs_final!L52</f>
-        <v>300.25088503130337</v>
-      </c>
-      <c r="E32" s="112"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="123">
-        <f>Costs_final!L53</f>
-        <v>200.1672566875356</v>
-      </c>
-      <c r="E33" s="112"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
-      <c r="B34" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D34" s="123">
-        <f>Costs_final!L54</f>
-        <v>250.20907085941951</v>
-      </c>
-      <c r="E34" s="112"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="123">
-        <f>Costs_final!L55</f>
-        <v>150.12544251565168</v>
-      </c>
-      <c r="E35" s="112"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D36" s="123">
-        <f>Costs_final!L56</f>
-        <v>200.1672566875356</v>
-      </c>
-      <c r="E36" s="112"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D37" s="123">
-        <f>Costs_final!L57</f>
-        <v>250.20907085941951</v>
-      </c>
-      <c r="E37" s="112"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D38" s="123">
-        <f>Costs_final!L58</f>
-        <v>150.12544251565168</v>
-      </c>
-      <c r="E38" s="112"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D39" s="123">
-        <f>Costs_final!L59</f>
-        <v>150.12544251565168</v>
-      </c>
-      <c r="E39" s="112"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D40" s="123">
-        <f>Costs_final!L60</f>
-        <v>110.67333255214437</v>
-      </c>
-      <c r="E40" s="112"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D41" s="123" t="str">
-        <f>Costs_final!L61</f>
-        <v/>
-      </c>
-      <c r="E41" s="112">
-        <f>SUM(D42:D53)</f>
-        <v>1607.6436266810585</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D42" s="123">
-        <f>Costs_final!L62</f>
-        <v>61.27212534477475</v>
-      </c>
-      <c r="E42" s="112"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43" s="123">
-        <f>Costs_final!L63</f>
-        <v>61.27212534477475</v>
-      </c>
-      <c r="E43" s="112"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="5"/>
-      <c r="B44" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D44" s="123">
-        <f>Costs_final!L64</f>
-        <v>56.710459339114131</v>
-      </c>
-      <c r="E44" s="112"/>
-    </row>
-    <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D45" s="123">
-        <f>Costs_final!L65</f>
-        <v>113.42091867822826</v>
-      </c>
-      <c r="E45" s="112"/>
-    </row>
-    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="5"/>
-      <c r="B46" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D46" s="123">
-        <f>Costs_final!L66</f>
-        <v>183.81637603432424</v>
-      </c>
-      <c r="E46" s="112"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="5"/>
-      <c r="B47" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D47" s="123">
-        <f>Costs_final!L67</f>
-        <v>107.29853834661354</v>
-      </c>
-      <c r="E47" s="112"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="5"/>
-      <c r="B48" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D48" s="123">
-        <f>Costs_final!L68</f>
-        <v>181.93217131474105</v>
-      </c>
-      <c r="E48" s="112"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="5"/>
-      <c r="B49" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D49" s="123">
-        <f>Costs_final!L69</f>
-        <v>332.01999765643308</v>
-      </c>
-      <c r="E49" s="112"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="5"/>
-      <c r="B50" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D50" s="123">
-        <f>Costs_final!L70</f>
-        <v>110.67333255214437</v>
-      </c>
-      <c r="E50" s="112"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="5"/>
-      <c r="B51" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D51" s="123">
-        <f>Costs_final!L71</f>
-        <v>276.68333138036093</v>
-      </c>
-      <c r="E51" s="112"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="5"/>
-      <c r="B52" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D52" s="123">
-        <f>Costs_final!L72</f>
-        <v>61.27212534477475</v>
-      </c>
-      <c r="E52" s="112"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D53" s="123">
-        <f>Costs_final!L73</f>
-        <v>61.27212534477475</v>
-      </c>
-      <c r="E53" s="113"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="127" t="s">
-        <v>4</v>
-      </c>
-      <c r="B54" s="128"/>
-      <c r="C54" s="128"/>
-      <c r="D54" s="128"/>
-      <c r="E54" s="114">
-        <f>SUM(E3:E53)</f>
-        <v>16945.512572529587</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E55" s="2"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A54:D54"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/docs/budget.xlsx
+++ b/docs/budget.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Desktop\proyectos\IRBoard\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF91FD6-6829-470F-87AD-E183670224AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0BE4025-46F3-4B5F-AD18-B937C6BD7178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Company definition" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="221">
   <si>
     <t>I1</t>
   </si>
@@ -691,6 +691,18 @@
   <si>
     <t>deviation from original</t>
   </si>
+  <si>
+    <t>deviation</t>
+  </si>
+  <si>
+    <t>Actual profit</t>
+  </si>
+  <si>
+    <t>Profit deviation</t>
+  </si>
+  <si>
+    <t>estimated client cost:</t>
+  </si>
 </sst>
 </file>
 
@@ -1340,6 +1352,13 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1349,10 +1368,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1364,11 +1380,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -31010,27 +31022,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="130" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="129"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="132"/>
       <c r="L1" s="125" t="s">
         <v>213</v>
       </c>
-      <c r="N1" s="130" t="s">
+      <c r="N1" s="128" t="s">
         <v>203</v>
       </c>
-      <c r="O1" s="131"/>
-      <c r="P1" s="135"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="133"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -31145,7 +31157,7 @@
       </c>
       <c r="K4" s="112"/>
       <c r="L4" s="110">
-        <f t="shared" ref="L4:L67" si="2">IFERROR(I4+($P$10*F4),"")</f>
+        <f>IFERROR(I4+($P$10*F4),"")</f>
         <v>122.72425068954949</v>
       </c>
       <c r="N4" s="5" t="s">
@@ -31191,13 +31203,13 @@
       </c>
       <c r="K5" s="112"/>
       <c r="L5" s="110">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="L4:L67" si="2">IFERROR(I5+($P$10*F5),"")</f>
         <v>122.72425068954949</v>
       </c>
-      <c r="N5" s="130" t="s">
+      <c r="N5" s="128" t="s">
         <v>115</v>
       </c>
-      <c r="O5" s="131"/>
+      <c r="O5" s="129"/>
       <c r="P5" s="122">
         <f>SUM(P3:P4)</f>
         <v>13199.017352669423</v>
@@ -31419,6 +31431,13 @@
         <f t="shared" si="2"/>
         <v>122.72425068954949</v>
       </c>
+      <c r="O11" t="s">
+        <v>220</v>
+      </c>
+      <c r="P11" s="111">
+        <f>P5+P7</f>
+        <v>16498.77169083678</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
@@ -33605,18 +33624,18 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="130" t="s">
+      <c r="A74" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B74" s="131"/>
-      <c r="C74" s="131"/>
-      <c r="D74" s="131"/>
-      <c r="E74" s="131"/>
-      <c r="F74" s="131"/>
-      <c r="G74" s="131"/>
-      <c r="H74" s="131"/>
-      <c r="I74" s="131"/>
-      <c r="J74" s="131"/>
+      <c r="B74" s="129"/>
+      <c r="C74" s="129"/>
+      <c r="D74" s="129"/>
+      <c r="E74" s="129"/>
+      <c r="F74" s="129"/>
+      <c r="G74" s="129"/>
+      <c r="H74" s="129"/>
+      <c r="I74" s="129"/>
+      <c r="J74" s="129"/>
       <c r="K74" s="114">
         <f>SUM(K3:K73)</f>
         <v>13026.517352669423</v>
@@ -33631,19 +33650,19 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="132" t="s">
+      <c r="A76" s="134" t="s">
         <v>192</v>
       </c>
-      <c r="B76" s="133"/>
-      <c r="C76" s="133"/>
-      <c r="D76" s="133"/>
-      <c r="E76" s="133"/>
-      <c r="F76" s="133"/>
-      <c r="G76" s="133"/>
-      <c r="H76" s="133"/>
-      <c r="I76" s="133"/>
-      <c r="J76" s="133"/>
-      <c r="K76" s="134"/>
+      <c r="B76" s="135"/>
+      <c r="C76" s="135"/>
+      <c r="D76" s="135"/>
+      <c r="E76" s="135"/>
+      <c r="F76" s="135"/>
+      <c r="G76" s="135"/>
+      <c r="H76" s="135"/>
+      <c r="I76" s="135"/>
+      <c r="J76" s="135"/>
+      <c r="K76" s="136"/>
       <c r="L76" s="124"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
@@ -33762,18 +33781,18 @@
       <c r="L80" s="116"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="130" t="s">
+      <c r="A81" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B81" s="131"/>
-      <c r="C81" s="131"/>
-      <c r="D81" s="131"/>
-      <c r="E81" s="131"/>
-      <c r="F81" s="131"/>
-      <c r="G81" s="131"/>
-      <c r="H81" s="131"/>
-      <c r="I81" s="131"/>
-      <c r="J81" s="131"/>
+      <c r="B81" s="129"/>
+      <c r="C81" s="129"/>
+      <c r="D81" s="129"/>
+      <c r="E81" s="129"/>
+      <c r="F81" s="129"/>
+      <c r="G81" s="129"/>
+      <c r="H81" s="129"/>
+      <c r="I81" s="129"/>
+      <c r="J81" s="129"/>
       <c r="K81" s="114">
         <f>SUM(K78:K80)</f>
         <v>172.5</v>
@@ -33795,7 +33814,7 @@
     <mergeCell ref="N5:O5"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E73" xr:uid="{2FF9A132-8776-4FE0-B050-ADA1CD0962E0}">
       <formula1>$Q$20:$Q$25</formula1>
     </dataValidation>
@@ -33823,18 +33842,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="130" t="s">
         <v>210</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="129"/>
-      <c r="G1" s="130" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="132"/>
+      <c r="G1" s="128" t="s">
         <v>209</v>
       </c>
-      <c r="H1" s="131"/>
-      <c r="I1" s="135"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="133"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -33899,10 +33918,10 @@
         <v>122.72425068954949</v>
       </c>
       <c r="E4" s="112"/>
-      <c r="G4" s="130" t="s">
+      <c r="G4" s="128" t="s">
         <v>115</v>
       </c>
-      <c r="H4" s="131"/>
+      <c r="H4" s="129"/>
       <c r="I4" s="122">
         <f>SUM(I3)</f>
         <v>16500.517352669427</v>
@@ -34615,12 +34634,12 @@
       <c r="E53" s="113"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="130" t="s">
+      <c r="A54" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="131"/>
-      <c r="C54" s="131"/>
-      <c r="D54" s="131"/>
+      <c r="B54" s="129"/>
+      <c r="C54" s="129"/>
+      <c r="D54" s="129"/>
       <c r="E54" s="114">
         <f>SUM(E3:E53)</f>
         <v>16500.517352669427</v>
@@ -34667,27 +34686,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="130" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="125" t="s">
-        <v>213</v>
-      </c>
-      <c r="N1" s="130" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="125"/>
+      <c r="N1" s="128" t="s">
         <v>203</v>
       </c>
-      <c r="O1" s="131"/>
-      <c r="P1" s="135"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="133"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -34723,7 +34740,9 @@
       <c r="K2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="118"/>
+      <c r="L2" s="118" t="s">
+        <v>217</v>
+      </c>
       <c r="N2" s="119" t="s">
         <v>205</v>
       </c>
@@ -34733,7 +34752,7 @@
       <c r="P2" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="136" t="s">
+      <c r="Q2" s="118" t="s">
         <v>216</v>
       </c>
     </row>
@@ -34758,9 +34777,9 @@
         <f>SUM(J4:J19)</f>
         <v>1194.7710082745937</v>
       </c>
-      <c r="L3" s="110" t="str">
-        <f>IFERROR(I3+($P$10*F3),"")</f>
-        <v/>
+      <c r="L3" s="127">
+        <f>((K3-Costs_init!K3)/Costs_init!K3)</f>
+        <v>-0.19999999999999998</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>6</v>
@@ -34772,7 +34791,7 @@
         <f>K74</f>
         <v>13383.612572529586</v>
       </c>
-      <c r="Q3" s="137">
+      <c r="Q3" s="127">
         <f>((P3-Costs_init!P3)/Costs_init!P3)</f>
         <v>2.7412946238235029E-2</v>
       </c>
@@ -34808,9 +34827,9 @@
         <v>99.564250689549496</v>
       </c>
       <c r="K4" s="112"/>
-      <c r="L4" s="110">
-        <f t="shared" ref="L4:L67" si="2">IFERROR(I4+($P$10*F4),"")</f>
-        <v>121.9842506895495</v>
+      <c r="L4" s="127">
+        <f>((J4-Costs_init!J4)/Costs_init!J4)</f>
+        <v>0</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>8</v>
@@ -34822,7 +34841,7 @@
         <f>K81</f>
         <v>172.5</v>
       </c>
-      <c r="Q4" s="137">
+      <c r="Q4" s="127">
         <f>((P4-Costs_init!P4)/Costs_init!P4)</f>
         <v>0</v>
       </c>
@@ -34858,19 +34877,19 @@
         <v>99.564250689549496</v>
       </c>
       <c r="K5" s="112"/>
-      <c r="L5" s="110">
-        <f t="shared" si="2"/>
-        <v>121.9842506895495</v>
-      </c>
-      <c r="N5" s="130" t="s">
+      <c r="L5" s="127">
+        <f>((J5-Costs_init!J5)/Costs_init!J5)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="128" t="s">
         <v>115</v>
       </c>
-      <c r="O5" s="131"/>
+      <c r="O5" s="129"/>
       <c r="P5" s="122">
         <f>SUM(P3:P4)</f>
         <v>13556.112572529586</v>
       </c>
-      <c r="Q5" s="137">
+      <c r="Q5" s="127">
         <f>((P5-Costs_init!P5)/Costs_init!P5)</f>
         <v>2.7054682202379422E-2</v>
       </c>
@@ -34897,8 +34916,11 @@
         <v>995.64250689549476</v>
       </c>
       <c r="K6" s="112"/>
-      <c r="L6" s="110"/>
-      <c r="Q6" s="137"/>
+      <c r="L6" s="127">
+        <f>((J6-Costs_init!J6)/Costs_init!J6)</f>
+        <v>-0.23076923076923073</v>
+      </c>
+      <c r="Q6" s="127"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
@@ -34928,18 +34950,18 @@
       </c>
       <c r="J7" s="111"/>
       <c r="K7" s="112"/>
-      <c r="L7" s="110">
-        <f t="shared" si="2"/>
-        <v>60.992125344774749</v>
+      <c r="L7" s="127">
+        <f>((I7-Costs_init!I7)/Costs_init!I7)</f>
+        <v>-0.5</v>
       </c>
       <c r="O7" t="s">
-        <v>208</v>
-      </c>
-      <c r="P7">
-        <f>Costs_init!P7</f>
-        <v>3299.7543381673559</v>
-      </c>
-      <c r="Q7" s="137"/>
+        <v>218</v>
+      </c>
+      <c r="P7" s="111">
+        <f>Client_init!I4-Costs_final!P5</f>
+        <v>2944.404780139841</v>
+      </c>
+      <c r="Q7" s="127"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
@@ -34969,16 +34991,16 @@
       </c>
       <c r="J8" s="111"/>
       <c r="K8" s="112"/>
-      <c r="L8" s="110">
-        <f t="shared" si="2"/>
-        <v>121.9842506895495</v>
+      <c r="L8" s="127">
+        <f>((I8-Costs_init!I8)/Costs_init!I8)</f>
+        <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>211</v>
-      </c>
-      <c r="P8" s="111">
-        <f>P5+P7-P3</f>
-        <v>3472.2543381673568</v>
+        <v>219</v>
+      </c>
+      <c r="P8" s="127">
+        <f>((P7-Costs_init!P7)/Costs_init!P7)</f>
+        <v>-0.10768970099297505</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -35009,16 +35031,13 @@
       </c>
       <c r="J9" s="111"/>
       <c r="K9" s="112"/>
-      <c r="L9" s="110">
-        <f t="shared" si="2"/>
-        <v>60.992125344774749</v>
-      </c>
-      <c r="O9" t="s">
-        <v>214</v>
-      </c>
-      <c r="P9" s="126">
-        <f>SUM(F4:F73)</f>
-        <v>310</v>
+      <c r="L9" s="127">
+        <f>((I9-Costs_init!I9)/Costs_init!I9)</f>
+        <v>-0.5</v>
+      </c>
+      <c r="P9" s="123">
+        <f>(0.21)*(P3+P4)</f>
+        <v>2846.7836402312128</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -35049,16 +35068,13 @@
       </c>
       <c r="J10" s="111"/>
       <c r="K10" s="112"/>
-      <c r="L10" s="110">
-        <f t="shared" si="2"/>
-        <v>121.9842506895495</v>
-      </c>
-      <c r="O10" t="s">
-        <v>215</v>
-      </c>
-      <c r="P10" s="123">
-        <f>ROUNDUP(P8/P9,2)</f>
-        <v>11.209999999999999</v>
+      <c r="L10" s="127">
+        <f>((I10-Costs_init!I10)/Costs_init!I10)</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="137">
+        <f>P5+P9</f>
+        <v>16402.896212760799</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -35089,9 +35105,9 @@
       </c>
       <c r="J11" s="111"/>
       <c r="K11" s="112"/>
-      <c r="L11" s="110">
-        <f t="shared" si="2"/>
-        <v>60.992125344774749</v>
+      <c r="L11" s="127">
+        <f>((I11-Costs_init!I11)/Costs_init!I11)</f>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -35122,9 +35138,9 @@
       </c>
       <c r="J12" s="111"/>
       <c r="K12" s="112"/>
-      <c r="L12" s="110">
-        <f t="shared" si="2"/>
-        <v>60.992125344774749</v>
+      <c r="L12" s="127">
+        <f>((I12-Costs_init!I12)/Costs_init!I12)</f>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
@@ -35155,9 +35171,9 @@
       </c>
       <c r="J13" s="111"/>
       <c r="K13" s="112"/>
-      <c r="L13" s="110">
-        <f t="shared" si="2"/>
-        <v>121.9842506895495</v>
+      <c r="L13" s="127">
+        <f>((I13-Costs_init!I13)/Costs_init!I13)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
@@ -35188,9 +35204,9 @@
       </c>
       <c r="J14" s="111"/>
       <c r="K14" s="112"/>
-      <c r="L14" s="110">
-        <f t="shared" si="2"/>
-        <v>121.9842506895495</v>
+      <c r="L14" s="127">
+        <f>((I14-Costs_init!I14)/Costs_init!I14)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -35221,9 +35237,9 @@
       </c>
       <c r="J15" s="111"/>
       <c r="K15" s="112"/>
-      <c r="L15" s="110">
-        <f t="shared" si="2"/>
-        <v>121.9842506895495</v>
+      <c r="L15" s="127">
+        <f>((I15-Costs_init!I15)/Costs_init!I15)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -35254,9 +35270,9 @@
       </c>
       <c r="J16" s="111"/>
       <c r="K16" s="112"/>
-      <c r="L16" s="110">
-        <f t="shared" si="2"/>
-        <v>121.9842506895495</v>
+      <c r="L16" s="127">
+        <f>((I16-Costs_init!I16)/Costs_init!I16)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -35287,9 +35303,9 @@
       </c>
       <c r="J17" s="111"/>
       <c r="K17" s="112"/>
-      <c r="L17" s="110">
-        <f t="shared" si="2"/>
-        <v>60.992125344774749</v>
+      <c r="L17" s="127">
+        <f>((I17-Costs_init!I17)/Costs_init!I17)</f>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -35320,9 +35336,9 @@
       </c>
       <c r="J18" s="111"/>
       <c r="K18" s="112"/>
-      <c r="L18" s="110">
-        <f t="shared" si="2"/>
-        <v>60.992125344774749</v>
+      <c r="L18" s="127">
+        <f>((I18-Costs_init!I18)/Costs_init!I18)</f>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -35353,9 +35369,9 @@
       </c>
       <c r="J19" s="111"/>
       <c r="K19" s="112"/>
-      <c r="L19" s="110">
-        <f t="shared" si="2"/>
-        <v>121.9842506895495</v>
+      <c r="L19" s="127">
+        <f>((I19-Costs_init!I19)/Costs_init!I19)</f>
+        <v>0</v>
       </c>
       <c r="Q19" s="7" t="s">
         <v>105</v>
@@ -35386,9 +35402,9 @@
         <f>SUM(J21:J30)</f>
         <v>2433.690244536559</v>
       </c>
-      <c r="L20" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="L20" s="127">
+        <f>((K20-Costs_init!K20)/Costs_init!K20)</f>
+        <v>5.4818449090653899E-2</v>
       </c>
       <c r="Q20" t="s">
         <v>104</v>
@@ -35425,13 +35441,13 @@
         <v>42.159269173306768</v>
       </c>
       <c r="J21" s="111">
-        <f t="shared" ref="J21:J30" si="3">I21</f>
+        <f t="shared" ref="J21:J30" si="2">I21</f>
         <v>42.159269173306768</v>
       </c>
       <c r="K21" s="112"/>
-      <c r="L21" s="110">
-        <f t="shared" si="2"/>
-        <v>53.369269173306769</v>
+      <c r="L21" s="127">
+        <f>((J21-Costs_init!J21)/Costs_init!J21)</f>
+        <v>0</v>
       </c>
       <c r="Q21" t="s">
         <v>107</v>
@@ -35468,13 +35484,13 @@
         <v>180.88183735645651</v>
       </c>
       <c r="J22" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>180.88183735645651</v>
       </c>
       <c r="K22" s="112"/>
-      <c r="L22" s="110">
-        <f t="shared" si="2"/>
-        <v>225.72183735645652</v>
+      <c r="L22" s="127">
+        <f>((J22-Costs_init!J22)/Costs_init!J22)</f>
+        <v>0</v>
       </c>
       <c r="Q22" t="s">
         <v>106</v>
@@ -35511,13 +35527,13 @@
         <v>42.159269173306768</v>
       </c>
       <c r="J23" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>42.159269173306768</v>
       </c>
       <c r="K23" s="112"/>
-      <c r="L23" s="110">
-        <f t="shared" si="2"/>
-        <v>53.369269173306769</v>
+      <c r="L23" s="127">
+        <f>((J23-Costs_init!J23)/Costs_init!J23)</f>
+        <v>-0.5</v>
       </c>
       <c r="Q23" t="s">
         <v>108</v>
@@ -35554,13 +35570,13 @@
         <v>42.159269173306768</v>
       </c>
       <c r="J24" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>42.159269173306768</v>
       </c>
       <c r="K24" s="112"/>
-      <c r="L24" s="110">
-        <f t="shared" si="2"/>
-        <v>53.369269173306769</v>
+      <c r="L24" s="127">
+        <f>((J24-Costs_init!J24)/Costs_init!J24)</f>
+        <v>0</v>
       </c>
       <c r="Q24" t="s">
         <v>109</v>
@@ -35597,13 +35613,13 @@
         <v>84.318538346613536</v>
       </c>
       <c r="J25" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>84.318538346613536</v>
       </c>
       <c r="K25" s="112"/>
-      <c r="L25" s="110">
-        <f t="shared" si="2"/>
-        <v>106.73853834661354</v>
+      <c r="L25" s="127">
+        <f>((J25-Costs_init!J25)/Costs_init!J25)</f>
+        <v>0</v>
       </c>
       <c r="Q25" t="s">
         <v>110</v>
@@ -35640,13 +35656,13 @@
         <v>271.32275603468474</v>
       </c>
       <c r="J26" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>271.32275603468474</v>
       </c>
       <c r="K26" s="112"/>
-      <c r="L26" s="110">
-        <f t="shared" si="2"/>
-        <v>338.58275603468473</v>
+      <c r="L26" s="127">
+        <f>((J26-Costs_init!J26)/Costs_init!J26)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -35676,13 +35692,13 @@
         <v>927.5039218127489</v>
       </c>
       <c r="J27" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>927.5039218127489</v>
       </c>
       <c r="K27" s="112"/>
-      <c r="L27" s="110">
-        <f t="shared" si="2"/>
-        <v>1174.1239218127489</v>
+      <c r="L27" s="127">
+        <f>((J27-Costs_init!J27)/Costs_init!J27)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -35712,13 +35728,13 @@
         <v>337.27415338645415</v>
       </c>
       <c r="J28" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>337.27415338645415</v>
       </c>
       <c r="K28" s="112"/>
-      <c r="L28" s="110">
-        <f t="shared" si="2"/>
-        <v>426.95415338645415</v>
+      <c r="L28" s="127">
+        <f>((J28-Costs_init!J28)/Costs_init!J28)</f>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -35748,13 +35764,13 @@
         <v>168.63707669322707</v>
       </c>
       <c r="J29" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>168.63707669322707</v>
       </c>
       <c r="K29" s="112"/>
-      <c r="L29" s="110">
-        <f t="shared" si="2"/>
-        <v>213.47707669322708</v>
+      <c r="L29" s="127">
+        <f>((J29-Costs_init!J29)/Costs_init!J29)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -35784,13 +35800,13 @@
         <v>337.27415338645415</v>
       </c>
       <c r="J30" s="111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>337.27415338645415</v>
       </c>
       <c r="K30" s="112"/>
-      <c r="L30" s="110">
-        <f t="shared" si="2"/>
-        <v>426.95415338645415</v>
+      <c r="L30" s="127">
+        <f>((J30-Costs_init!J30)/Costs_init!J30)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
@@ -35815,9 +35831,9 @@
         <f>SUM(J32:J38)</f>
         <v>2361.0626646076757</v>
       </c>
-      <c r="L31" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="L31" s="127">
+        <f>((K31-Costs_init!K31)/Costs_init!K31)</f>
+        <v>3.8574168884760181E-2</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
@@ -35847,13 +35863,13 @@
         <v>491.54057104913682</v>
       </c>
       <c r="J32" s="111">
-        <f t="shared" ref="J32:J38" si="4">I32</f>
+        <f t="shared" ref="J32:J38" si="3">I32</f>
         <v>491.54057104913682</v>
       </c>
       <c r="K32" s="112"/>
-      <c r="L32" s="110">
-        <f t="shared" si="2"/>
-        <v>603.64057104913684</v>
+      <c r="L32" s="127">
+        <f>((J32-Costs_init!J32)/Costs_init!J32)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -35883,13 +35899,13 @@
         <v>115.65544251565169</v>
       </c>
       <c r="J33" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>115.65544251565169</v>
       </c>
       <c r="K33" s="112"/>
-      <c r="L33" s="110">
-        <f t="shared" si="2"/>
-        <v>149.28544251565168</v>
+      <c r="L33" s="127">
+        <f>((J33-Costs_init!J33)/Costs_init!J33)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -35919,13 +35935,13 @@
         <v>350.77333020857748</v>
       </c>
       <c r="J34" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>350.77333020857748</v>
       </c>
       <c r="K34" s="112"/>
-      <c r="L34" s="110">
-        <f t="shared" si="2"/>
-        <v>440.45333020857748</v>
+      <c r="L34" s="127">
+        <f>((J34-Costs_init!J34)/Costs_init!J34)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -35955,13 +35971,13 @@
         <v>175.38666510428874</v>
       </c>
       <c r="J35" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>175.38666510428874</v>
       </c>
       <c r="K35" s="112"/>
-      <c r="L35" s="110">
-        <f t="shared" si="2"/>
-        <v>220.22666510428874</v>
+      <c r="L35" s="127">
+        <f>((J35-Costs_init!J35)/Costs_init!J35)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -35991,13 +36007,13 @@
         <v>263.07999765643308</v>
       </c>
       <c r="J36" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>263.07999765643308</v>
       </c>
       <c r="K36" s="112"/>
-      <c r="L36" s="110">
-        <f t="shared" si="2"/>
-        <v>330.33999765643307</v>
+      <c r="L36" s="127">
+        <f>((J36-Costs_init!J36)/Costs_init!J36)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -36027,13 +36043,13 @@
         <v>526.15999531286616</v>
       </c>
       <c r="J37" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>526.15999531286616</v>
       </c>
       <c r="K37" s="112"/>
-      <c r="L37" s="110">
-        <f t="shared" si="2"/>
-        <v>660.67999531286614</v>
+      <c r="L37" s="127">
+        <f>((J37-Costs_init!J37)/Costs_init!J37)</f>
+        <v>0.19999999999999979</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -36063,13 +36079,13 @@
         <v>438.46666276072187</v>
       </c>
       <c r="J38" s="111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>438.46666276072187</v>
       </c>
       <c r="K38" s="112"/>
-      <c r="L38" s="110">
-        <f t="shared" si="2"/>
-        <v>550.5666627607219</v>
+      <c r="L38" s="127">
+        <f>((J38-Costs_init!J38)/Costs_init!J38)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -36106,9 +36122,9 @@
         <f>SUM(J39)</f>
         <v>263.07999765643308</v>
       </c>
-      <c r="L39" s="110">
-        <f t="shared" si="2"/>
-        <v>330.33999765643307</v>
+      <c r="L39" s="127">
+        <f>((K39-Costs_init!K39)/Costs_init!K39)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -36133,9 +36149,9 @@
         <f>SUM(J41:J50)</f>
         <v>4485.1818305489533</v>
       </c>
-      <c r="L40" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="L40" s="127">
+        <f>((K40-Costs_init!K40)/Costs_init!K40)</f>
+        <v>2.240376206072581E-2</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -36169,9 +36185,9 @@
         <v>294.92434262948211</v>
       </c>
       <c r="K41" s="112"/>
-      <c r="L41" s="110">
-        <f t="shared" si="2"/>
-        <v>362.1843426294821</v>
+      <c r="L41" s="127">
+        <f>((J41-Costs_init!J41)/Costs_init!J41)</f>
+        <v>0.50000000000000011</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -36205,9 +36221,9 @@
         <v>49.154057104913683</v>
       </c>
       <c r="K42" s="112"/>
-      <c r="L42" s="110">
-        <f t="shared" si="2"/>
-        <v>60.364057104913684</v>
+      <c r="L42" s="127">
+        <f>((J42-Costs_init!J42)/Costs_init!J42)</f>
+        <v>-0.66666666666666674</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -36232,9 +36248,9 @@
         <v>4141.1034308145572</v>
       </c>
       <c r="K43" s="112"/>
-      <c r="L43" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="L43" s="127">
+        <f>((J43-Costs_init!J43)/Costs_init!J43)</f>
+        <v>2.4310512756161532E-2</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
@@ -36265,9 +36281,9 @@
       </c>
       <c r="J44" s="111"/>
       <c r="K44" s="112"/>
-      <c r="L44" s="110">
-        <f t="shared" si="2"/>
-        <v>1094.7599117814457</v>
+      <c r="L44" s="127">
+        <f>((I44-Costs_init!I44)/Costs_init!I44)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -36298,9 +36314,9 @@
       </c>
       <c r="J45" s="111"/>
       <c r="K45" s="112"/>
-      <c r="L45" s="110">
-        <f t="shared" si="2"/>
-        <v>298.57088503130336</v>
+      <c r="L45" s="127">
+        <f>((I45-Costs_init!I45)/Costs_init!I45)</f>
+        <v>-0.40000000000000008</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -36331,9 +36347,9 @@
       </c>
       <c r="J46" s="111"/>
       <c r="K46" s="112"/>
-      <c r="L46" s="110">
-        <f t="shared" si="2"/>
-        <v>1321.3599906257323</v>
+      <c r="L46" s="127">
+        <f>((I46-Costs_init!I46)/Costs_init!I46)</f>
+        <v>-4.0000000000000063E-2</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -36364,9 +36380,9 @@
       </c>
       <c r="J47" s="111"/>
       <c r="K47" s="112"/>
-      <c r="L47" s="110">
-        <f t="shared" si="2"/>
-        <v>597.14177006260672</v>
+      <c r="L47" s="127">
+        <f>((I47-Costs_init!I47)/Costs_init!I47)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -36397,9 +36413,9 @@
       </c>
       <c r="J48" s="111"/>
       <c r="K48" s="112"/>
-      <c r="L48" s="110">
-        <f t="shared" si="2"/>
-        <v>1101.1333255214438</v>
+      <c r="L48" s="127">
+        <f>((I48-Costs_init!I48)/Costs_init!I48)</f>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -36430,9 +36446,9 @@
       </c>
       <c r="J49" s="111"/>
       <c r="K49" s="112"/>
-      <c r="L49" s="110">
-        <f t="shared" si="2"/>
-        <v>550.5666627607219</v>
+      <c r="L49" s="127">
+        <f>((I49-Costs_init!I49)/Costs_init!I49)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -36463,9 +36479,9 @@
       </c>
       <c r="J50" s="111"/>
       <c r="K50" s="112"/>
-      <c r="L50" s="110">
-        <f t="shared" si="2"/>
-        <v>298.57088503130336</v>
+      <c r="L50" s="127">
+        <f>((I50-Costs_init!I50)/Costs_init!I50)</f>
+        <v>-0.40000000000000008</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -36490,9 +36506,9 @@
         <f>SUM(J52:J60)</f>
         <v>1359.9032002243127</v>
       </c>
-      <c r="L51" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="L51" s="127">
+        <f>((K51-Costs_init!K51)/Costs_init!K51)</f>
+        <v>0.29331225074729717</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -36522,13 +36538,13 @@
         <v>231.31088503130337</v>
       </c>
       <c r="J52" s="111">
-        <f t="shared" ref="J52:J60" si="5">I52</f>
+        <f t="shared" ref="J52:J60" si="4">I52</f>
         <v>231.31088503130337</v>
       </c>
       <c r="K52" s="112"/>
-      <c r="L52" s="110">
-        <f t="shared" si="2"/>
-        <v>298.57088503130336</v>
+      <c r="L52" s="127">
+        <f>((J52-Costs_init!J52)/Costs_init!J52)</f>
+        <v>0.49999999999999989</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -36558,13 +36574,13 @@
         <v>154.20725668753559</v>
       </c>
       <c r="J53" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>154.20725668753559</v>
       </c>
       <c r="K53" s="112"/>
-      <c r="L53" s="110">
-        <f t="shared" si="2"/>
-        <v>199.04725668753559</v>
+      <c r="L53" s="127">
+        <f>((J53-Costs_init!J53)/Costs_init!J53)</f>
+        <v>0.33333333333333343</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -36594,13 +36610,13 @@
         <v>192.7590708594195</v>
       </c>
       <c r="J54" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>192.7590708594195</v>
       </c>
       <c r="K54" s="112"/>
-      <c r="L54" s="110">
-        <f t="shared" si="2"/>
-        <v>248.80907085941948</v>
+      <c r="L54" s="127">
+        <f>((J54-Costs_init!J54)/Costs_init!J54)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -36630,13 +36646,13 @@
         <v>115.65544251565169</v>
       </c>
       <c r="J55" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>115.65544251565169</v>
       </c>
       <c r="K55" s="112"/>
-      <c r="L55" s="110">
-        <f t="shared" si="2"/>
-        <v>149.28544251565168</v>
+      <c r="L55" s="127">
+        <f>((J55-Costs_init!J55)/Costs_init!J55)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -36666,13 +36682,13 @@
         <v>154.20725668753559</v>
       </c>
       <c r="J56" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>154.20725668753559</v>
       </c>
       <c r="K56" s="112"/>
-      <c r="L56" s="110">
-        <f t="shared" si="2"/>
-        <v>199.04725668753559</v>
+      <c r="L56" s="127">
+        <f>((J56-Costs_init!J56)/Costs_init!J56)</f>
+        <v>0.33333333333333343</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -36702,13 +36718,13 @@
         <v>192.7590708594195</v>
       </c>
       <c r="J57" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>192.7590708594195</v>
       </c>
       <c r="K57" s="112"/>
-      <c r="L57" s="110">
-        <f t="shared" si="2"/>
-        <v>248.80907085941948</v>
+      <c r="L57" s="127">
+        <f>((J57-Costs_init!J57)/Costs_init!J57)</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -36738,13 +36754,13 @@
         <v>115.65544251565169</v>
       </c>
       <c r="J58" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>115.65544251565169</v>
       </c>
       <c r="K58" s="112"/>
-      <c r="L58" s="110">
-        <f t="shared" si="2"/>
-        <v>149.28544251565168</v>
+      <c r="L58" s="127">
+        <f>((J58-Costs_init!J58)/Costs_init!J58)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -36774,13 +36790,13 @@
         <v>115.65544251565169</v>
       </c>
       <c r="J59" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>115.65544251565169</v>
       </c>
       <c r="K59" s="112"/>
-      <c r="L59" s="110">
-        <f t="shared" si="2"/>
-        <v>149.28544251565168</v>
+      <c r="L59" s="127">
+        <f>((J59-Costs_init!J59)/Costs_init!J59)</f>
+        <v>0.49999999999999989</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
@@ -36810,13 +36826,13 @@
         <v>87.693332552144369</v>
       </c>
       <c r="J60" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>87.693332552144369</v>
       </c>
       <c r="K60" s="112"/>
-      <c r="L60" s="110">
-        <f t="shared" si="2"/>
-        <v>110.11333255214437</v>
+      <c r="L60" s="127">
+        <f>((J60-Costs_init!J60)/Costs_init!J60)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -36841,9 +36857,9 @@
         <f>SUM(J62:J73)</f>
         <v>1285.9236266810587</v>
       </c>
-      <c r="L61" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="L61" s="127">
+        <f>((K61-Costs_init!K61)/Costs_init!K61)</f>
+        <v>-6.9886161367037875E-2</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -36873,13 +36889,13 @@
         <v>49.782125344774748</v>
       </c>
       <c r="J62" s="111">
-        <f t="shared" ref="J62:J73" si="6">I62</f>
+        <f t="shared" ref="J62:J73" si="5">I62</f>
         <v>49.782125344774748</v>
       </c>
       <c r="K62" s="112"/>
-      <c r="L62" s="110">
-        <f t="shared" si="2"/>
-        <v>60.992125344774749</v>
+      <c r="L62" s="127">
+        <f>((J62-Costs_init!J62)/Costs_init!J62)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -36909,13 +36925,13 @@
         <v>49.782125344774748</v>
       </c>
       <c r="J63" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>49.782125344774748</v>
       </c>
       <c r="K63" s="112"/>
-      <c r="L63" s="110">
-        <f t="shared" si="2"/>
-        <v>60.992125344774749</v>
+      <c r="L63" s="127">
+        <f>((J63-Costs_init!J63)/Costs_init!J63)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
@@ -36945,13 +36961,13 @@
         <v>45.220459339114129</v>
       </c>
       <c r="J64" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45.220459339114129</v>
       </c>
       <c r="K64" s="112"/>
-      <c r="L64" s="110">
-        <f t="shared" si="2"/>
-        <v>56.43045933911413</v>
+      <c r="L64" s="127">
+        <f>((J64-Costs_init!J64)/Costs_init!J64)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -36981,13 +36997,13 @@
         <v>90.440918678228257</v>
       </c>
       <c r="J65" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>90.440918678228257</v>
       </c>
       <c r="K65" s="112"/>
-      <c r="L65" s="110">
-        <f t="shared" si="2"/>
-        <v>112.86091867822826</v>
+      <c r="L65" s="127">
+        <f>((J65-Costs_init!J65)/Costs_init!J65)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -37017,13 +37033,13 @@
         <v>149.34637603432424</v>
       </c>
       <c r="J66" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>149.34637603432424</v>
       </c>
       <c r="K66" s="112"/>
-      <c r="L66" s="110">
-        <f t="shared" si="2"/>
-        <v>182.97637603432423</v>
+      <c r="L66" s="127">
+        <f>((J66-Costs_init!J66)/Costs_init!J66)</f>
+        <v>0.49999999999999994</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
@@ -37045,7 +37061,7 @@
         <v>103</v>
       </c>
       <c r="H67" s="111">
-        <f t="shared" ref="H67:H73" si="7">_xlfn.XLOOKUP(E67,$Q$20:$Q$25,$R$20:$R$25,"")</f>
+        <f t="shared" ref="H67:H73" si="6">_xlfn.XLOOKUP(E67,$Q$20:$Q$25,$R$20:$R$25,"")</f>
         <v>42.159269173306768</v>
       </c>
       <c r="I67" s="111">
@@ -37053,13 +37069,13 @@
         <v>84.318538346613536</v>
       </c>
       <c r="J67" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>84.318538346613536</v>
       </c>
       <c r="K67" s="112"/>
-      <c r="L67" s="110">
-        <f t="shared" si="2"/>
-        <v>106.73853834661354</v>
+      <c r="L67" s="127">
+        <f>((J67-Costs_init!J67)/Costs_init!J67)</f>
+        <v>-0.33333333333333331</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
@@ -37081,21 +37097,21 @@
         <v>103</v>
       </c>
       <c r="H68" s="111">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>49.154057104913683</v>
       </c>
       <c r="I68" s="111">
-        <f t="shared" ref="I68:I73" si="8">IFERROR(H68*F68,"")</f>
+        <f t="shared" ref="I68:I73" si="7">IFERROR(H68*F68,"")</f>
         <v>147.46217131474106</v>
       </c>
       <c r="J68" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>147.46217131474106</v>
       </c>
       <c r="K68" s="112"/>
-      <c r="L68" s="110">
-        <f t="shared" ref="L68:L73" si="9">IFERROR(I68+($P$10*F68),"")</f>
-        <v>181.09217131474105</v>
+      <c r="L68" s="127">
+        <f>((J68-Costs_init!J68)/Costs_init!J68)</f>
+        <v>-0.39999999999999997</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
@@ -37117,21 +37133,21 @@
         <v>103</v>
       </c>
       <c r="H69" s="111">
+        <f t="shared" si="6"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I69" s="111">
         <f t="shared" si="7"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I69" s="111">
-        <f t="shared" si="8"/>
         <v>263.07999765643308</v>
       </c>
       <c r="J69" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>263.07999765643308</v>
       </c>
       <c r="K69" s="112"/>
-      <c r="L69" s="110">
-        <f t="shared" si="9"/>
-        <v>330.33999765643307</v>
+      <c r="L69" s="127">
+        <f>((J69-Costs_init!J69)/Costs_init!J69)</f>
+        <v>0.19999999999999979</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
@@ -37153,21 +37169,21 @@
         <v>103</v>
       </c>
       <c r="H70" s="111">
+        <f t="shared" si="6"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I70" s="111">
         <f t="shared" si="7"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I70" s="111">
-        <f t="shared" si="8"/>
         <v>87.693332552144369</v>
       </c>
       <c r="J70" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>87.693332552144369</v>
       </c>
       <c r="K70" s="112"/>
-      <c r="L70" s="110">
-        <f t="shared" si="9"/>
-        <v>110.11333255214437</v>
+      <c r="L70" s="127">
+        <f>((J70-Costs_init!J70)/Costs_init!J70)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
@@ -37189,21 +37205,21 @@
         <v>103</v>
       </c>
       <c r="H71" s="111">
+        <f t="shared" si="6"/>
+        <v>43.846666276072185</v>
+      </c>
+      <c r="I71" s="111">
         <f t="shared" si="7"/>
-        <v>43.846666276072185</v>
-      </c>
-      <c r="I71" s="111">
-        <f t="shared" si="8"/>
         <v>219.23333138036094</v>
       </c>
       <c r="J71" s="111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>219.23333138036094</v>
       </c>
       <c r="K71" s="112"/>
-      <c r="L71" s="110">
-        <f t="shared" si="9"/>
-        <v>275.28333138036095</v>
+      <c r="L71" s="127">
+        <f>((J71-Costs_init!J71)/Costs_init!J71)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -37225,21 +37241,21 @@
         <v>103</v>
       </c>
       <c r="H72" s="111">
+        <f t="shared" si="6"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I72" s="111">
         <f t="shared" si="7"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I72" s="111">
-        <f t="shared" si="8"/>
+      <c r="J72" s="111">
+        <f t="shared" si="5"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J72" s="111">
-        <f t="shared" si="6"/>
-        <v>49.782125344774748</v>
-      </c>
       <c r="K72" s="112"/>
-      <c r="L72" s="110">
-        <f t="shared" si="9"/>
-        <v>60.992125344774749</v>
+      <c r="L72" s="127">
+        <f>((J72-Costs_init!J72)/Costs_init!J72)</f>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -37261,43 +37277,43 @@
         <v>103</v>
       </c>
       <c r="H73" s="111">
+        <f t="shared" si="6"/>
+        <v>49.782125344774748</v>
+      </c>
+      <c r="I73" s="111">
         <f t="shared" si="7"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="I73" s="111">
-        <f t="shared" si="8"/>
+      <c r="J73" s="111">
+        <f t="shared" si="5"/>
         <v>49.782125344774748</v>
       </c>
-      <c r="J73" s="111">
-        <f t="shared" si="6"/>
-        <v>49.782125344774748</v>
-      </c>
       <c r="K73" s="113"/>
-      <c r="L73" s="110">
-        <f t="shared" si="9"/>
-        <v>60.992125344774749</v>
+      <c r="L73" s="127">
+        <f>((J73-Costs_init!J73)/Costs_init!J73)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="130" t="s">
+      <c r="A74" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B74" s="131"/>
-      <c r="C74" s="131"/>
-      <c r="D74" s="131"/>
-      <c r="E74" s="131"/>
-      <c r="F74" s="131"/>
-      <c r="G74" s="131"/>
-      <c r="H74" s="131"/>
-      <c r="I74" s="131"/>
-      <c r="J74" s="131"/>
+      <c r="B74" s="129"/>
+      <c r="C74" s="129"/>
+      <c r="D74" s="129"/>
+      <c r="E74" s="129"/>
+      <c r="F74" s="129"/>
+      <c r="G74" s="129"/>
+      <c r="H74" s="129"/>
+      <c r="I74" s="129"/>
+      <c r="J74" s="129"/>
       <c r="K74" s="114">
         <f>SUM(K3:K73)</f>
         <v>13383.612572529586</v>
       </c>
-      <c r="L74" s="111">
-        <f>SUM(L3:L73)</f>
-        <v>16858.712572529592</v>
+      <c r="L74" s="127">
+        <f>((K74-Costs_init!K74)/Costs_init!K74)</f>
+        <v>2.7412946238235029E-2</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
@@ -37305,19 +37321,19 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="132" t="s">
+      <c r="A76" s="134" t="s">
         <v>192</v>
       </c>
-      <c r="B76" s="133"/>
-      <c r="C76" s="133"/>
-      <c r="D76" s="133"/>
-      <c r="E76" s="133"/>
-      <c r="F76" s="133"/>
-      <c r="G76" s="133"/>
-      <c r="H76" s="133"/>
-      <c r="I76" s="133"/>
-      <c r="J76" s="133"/>
-      <c r="K76" s="134"/>
+      <c r="B76" s="135"/>
+      <c r="C76" s="135"/>
+      <c r="D76" s="135"/>
+      <c r="E76" s="135"/>
+      <c r="F76" s="135"/>
+      <c r="G76" s="135"/>
+      <c r="H76" s="135"/>
+      <c r="I76" s="135"/>
+      <c r="J76" s="135"/>
+      <c r="K76" s="136"/>
       <c r="L76" s="124"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
@@ -37436,18 +37452,18 @@
       <c r="L80" s="116"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="130" t="s">
+      <c r="A81" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B81" s="131"/>
-      <c r="C81" s="131"/>
-      <c r="D81" s="131"/>
-      <c r="E81" s="131"/>
-      <c r="F81" s="131"/>
-      <c r="G81" s="131"/>
-      <c r="H81" s="131"/>
-      <c r="I81" s="131"/>
-      <c r="J81" s="131"/>
+      <c r="B81" s="129"/>
+      <c r="C81" s="129"/>
+      <c r="D81" s="129"/>
+      <c r="E81" s="129"/>
+      <c r="F81" s="129"/>
+      <c r="G81" s="129"/>
+      <c r="H81" s="129"/>
+      <c r="I81" s="129"/>
+      <c r="J81" s="129"/>
       <c r="K81" s="114">
         <f>SUM(K78:K80)</f>
         <v>172.5</v>
